--- a/Aug_2026/daily Reports/LMT Orders.xlsx
+++ b/Aug_2026/daily Reports/LMT Orders.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8527503B-1FEB-42A9-AF7D-250E82ADD9CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C66538C2-9476-468F-8271-0798325F0CE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1183,7 +1183,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="184">
+  <cellXfs count="175">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1546,6 +1546,45 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1576,48 +1615,15 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1644,33 +1650,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2207,14 +2186,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="152">
+      <c r="B1" s="141">
         <f ca="1">TODAY()</f>
         <v>46235</v>
       </c>
-      <c r="C1" s="152"/>
-      <c r="D1" s="152"/>
-      <c r="E1" s="152"/>
-      <c r="F1" s="152"/>
+      <c r="C1" s="141"/>
+      <c r="D1" s="141"/>
+      <c r="E1" s="141"/>
+      <c r="F1" s="141"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
       <c r="I1" s="10"/>
@@ -2236,10 +2215,10 @@
       <c r="Y1" s="10"/>
     </row>
     <row r="2" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="173" t="s">
+      <c r="A2" s="163" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="153" t="s">
+      <c r="B2" s="142" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2272,13 +2251,13 @@
       <c r="L2" s="15">
         <v>120</v>
       </c>
-      <c r="M2" s="142"/>
-      <c r="N2" s="143"/>
-      <c r="O2" s="144"/>
-      <c r="P2" s="145" t="s">
+      <c r="M2" s="155"/>
+      <c r="N2" s="156"/>
+      <c r="O2" s="157"/>
+      <c r="P2" s="158" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="146"/>
+      <c r="Q2" s="159"/>
       <c r="R2" s="18">
         <v>0.05</v>
       </c>
@@ -2297,8 +2276,8 @@
       <c r="Y2" s="20"/>
     </row>
     <row r="3" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="173"/>
-      <c r="B3" s="154"/>
+      <c r="A3" s="163"/>
+      <c r="B3" s="143"/>
       <c r="C3" s="23" t="s">
         <v>15</v>
       </c>
@@ -2329,29 +2308,29 @@
       <c r="L3" s="29">
         <v>72.64</v>
       </c>
-      <c r="M3" s="147" t="s">
+      <c r="M3" s="160" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="148"/>
-      <c r="O3" s="149"/>
+      <c r="N3" s="161"/>
+      <c r="O3" s="162"/>
       <c r="P3" s="71"/>
       <c r="Q3" s="72"/>
-      <c r="R3" s="156" t="s">
+      <c r="R3" s="145" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="157"/>
-      <c r="T3" s="157"/>
-      <c r="U3" s="158"/>
-      <c r="V3" s="159" t="s">
+      <c r="S3" s="146"/>
+      <c r="T3" s="146"/>
+      <c r="U3" s="147"/>
+      <c r="V3" s="148" t="s">
         <v>17</v>
       </c>
-      <c r="W3" s="160"/>
-      <c r="X3" s="160"/>
-      <c r="Y3" s="161"/>
+      <c r="W3" s="149"/>
+      <c r="X3" s="149"/>
+      <c r="Y3" s="150"/>
     </row>
     <row r="4" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="173"/>
-      <c r="B4" s="155"/>
+      <c r="A4" s="163"/>
+      <c r="B4" s="144"/>
       <c r="C4" s="30" t="s">
         <v>18</v>
       </c>
@@ -5911,21 +5890,21 @@
       <c r="Y59" s="56"/>
     </row>
     <row r="60" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A60" s="174"/>
-      <c r="B60" s="175">
+      <c r="A60" s="78"/>
+      <c r="B60" s="47">
         <v>56</v>
       </c>
-      <c r="C60" s="176"/>
-      <c r="D60" s="177"/>
-      <c r="E60" s="177"/>
-      <c r="F60" s="177"/>
-      <c r="G60" s="177"/>
-      <c r="H60" s="177"/>
-      <c r="I60" s="178"/>
-      <c r="J60" s="177"/>
-      <c r="K60" s="177"/>
-      <c r="L60" s="177"/>
-      <c r="M60" s="179">
+      <c r="C60" s="57"/>
+      <c r="D60" s="75"/>
+      <c r="E60" s="75"/>
+      <c r="F60" s="75"/>
+      <c r="G60" s="75"/>
+      <c r="H60" s="75"/>
+      <c r="I60" s="128"/>
+      <c r="J60" s="75"/>
+      <c r="K60" s="75"/>
+      <c r="L60" s="75"/>
+      <c r="M60" s="130">
         <f t="shared" si="52"/>
         <v>0</v>
       </c>
@@ -5979,21 +5958,21 @@
       </c>
     </row>
     <row r="61" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A61" s="174"/>
-      <c r="B61" s="175">
+      <c r="A61" s="78"/>
+      <c r="B61" s="47">
         <v>57</v>
       </c>
-      <c r="C61" s="180"/>
-      <c r="D61" s="177"/>
-      <c r="E61" s="177"/>
-      <c r="F61" s="177"/>
-      <c r="G61" s="177"/>
-      <c r="H61" s="177"/>
-      <c r="I61" s="178"/>
-      <c r="J61" s="177"/>
-      <c r="K61" s="177"/>
-      <c r="L61" s="177"/>
-      <c r="M61" s="179">
+      <c r="C61" s="129"/>
+      <c r="D61" s="75"/>
+      <c r="E61" s="75"/>
+      <c r="F61" s="75"/>
+      <c r="G61" s="75"/>
+      <c r="H61" s="75"/>
+      <c r="I61" s="128"/>
+      <c r="J61" s="75"/>
+      <c r="K61" s="75"/>
+      <c r="L61" s="75"/>
+      <c r="M61" s="130">
         <f t="shared" ref="M61:M83" si="81">SUM(D61:L61)/40</f>
         <v>0</v>
       </c>
@@ -6047,21 +6026,21 @@
       </c>
     </row>
     <row r="62" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A62" s="174"/>
-      <c r="B62" s="175">
+      <c r="A62" s="78"/>
+      <c r="B62" s="47">
         <v>58</v>
       </c>
-      <c r="C62" s="180"/>
-      <c r="D62" s="177"/>
-      <c r="E62" s="177"/>
-      <c r="F62" s="177"/>
-      <c r="G62" s="177"/>
-      <c r="H62" s="177"/>
-      <c r="I62" s="178"/>
-      <c r="J62" s="177"/>
-      <c r="K62" s="177"/>
-      <c r="L62" s="177"/>
-      <c r="M62" s="179">
+      <c r="C62" s="129"/>
+      <c r="D62" s="75"/>
+      <c r="E62" s="75"/>
+      <c r="F62" s="75"/>
+      <c r="G62" s="75"/>
+      <c r="H62" s="75"/>
+      <c r="I62" s="128"/>
+      <c r="J62" s="75"/>
+      <c r="K62" s="75"/>
+      <c r="L62" s="75"/>
+      <c r="M62" s="130">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
@@ -6115,21 +6094,21 @@
       </c>
     </row>
     <row r="63" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A63" s="174"/>
-      <c r="B63" s="175">
+      <c r="A63" s="78"/>
+      <c r="B63" s="47">
         <v>59</v>
       </c>
-      <c r="C63" s="180"/>
-      <c r="D63" s="177"/>
-      <c r="E63" s="177"/>
-      <c r="F63" s="177"/>
-      <c r="G63" s="177"/>
-      <c r="H63" s="177"/>
-      <c r="I63" s="178"/>
-      <c r="J63" s="177"/>
-      <c r="K63" s="177"/>
-      <c r="L63" s="177"/>
-      <c r="M63" s="179">
+      <c r="C63" s="129"/>
+      <c r="D63" s="75"/>
+      <c r="E63" s="75"/>
+      <c r="F63" s="75"/>
+      <c r="G63" s="75"/>
+      <c r="H63" s="75"/>
+      <c r="I63" s="128"/>
+      <c r="J63" s="75"/>
+      <c r="K63" s="75"/>
+      <c r="L63" s="75"/>
+      <c r="M63" s="130">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
@@ -6183,21 +6162,21 @@
       </c>
     </row>
     <row r="64" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A64" s="174"/>
-      <c r="B64" s="175">
+      <c r="A64" s="78"/>
+      <c r="B64" s="47">
         <v>60</v>
       </c>
-      <c r="C64" s="180"/>
-      <c r="D64" s="177"/>
-      <c r="E64" s="177"/>
-      <c r="F64" s="177"/>
-      <c r="G64" s="177"/>
-      <c r="H64" s="177"/>
-      <c r="I64" s="178"/>
-      <c r="J64" s="177"/>
-      <c r="K64" s="177"/>
-      <c r="L64" s="177"/>
-      <c r="M64" s="179">
+      <c r="C64" s="129"/>
+      <c r="D64" s="75"/>
+      <c r="E64" s="75"/>
+      <c r="F64" s="75"/>
+      <c r="G64" s="75"/>
+      <c r="H64" s="75"/>
+      <c r="I64" s="128"/>
+      <c r="J64" s="75"/>
+      <c r="K64" s="75"/>
+      <c r="L64" s="75"/>
+      <c r="M64" s="130">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
@@ -6251,21 +6230,21 @@
       </c>
     </row>
     <row r="65" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A65" s="174"/>
-      <c r="B65" s="175">
+      <c r="A65" s="78"/>
+      <c r="B65" s="47">
         <v>61</v>
       </c>
-      <c r="C65" s="180"/>
-      <c r="D65" s="177"/>
-      <c r="E65" s="177"/>
-      <c r="F65" s="177"/>
-      <c r="G65" s="177"/>
-      <c r="H65" s="177"/>
-      <c r="I65" s="178"/>
-      <c r="J65" s="177"/>
-      <c r="K65" s="177"/>
-      <c r="L65" s="177"/>
-      <c r="M65" s="179">
+      <c r="C65" s="129"/>
+      <c r="D65" s="75"/>
+      <c r="E65" s="75"/>
+      <c r="F65" s="75"/>
+      <c r="G65" s="75"/>
+      <c r="H65" s="75"/>
+      <c r="I65" s="128"/>
+      <c r="J65" s="75"/>
+      <c r="K65" s="75"/>
+      <c r="L65" s="75"/>
+      <c r="M65" s="130">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
@@ -6319,21 +6298,21 @@
       </c>
     </row>
     <row r="66" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A66" s="174"/>
-      <c r="B66" s="175">
+      <c r="A66" s="78"/>
+      <c r="B66" s="47">
         <v>62</v>
       </c>
-      <c r="C66" s="180"/>
-      <c r="D66" s="177"/>
-      <c r="E66" s="177"/>
-      <c r="F66" s="177"/>
-      <c r="G66" s="177"/>
-      <c r="H66" s="177"/>
-      <c r="I66" s="178"/>
-      <c r="J66" s="177"/>
-      <c r="K66" s="177"/>
-      <c r="L66" s="177"/>
-      <c r="M66" s="179">
+      <c r="C66" s="129"/>
+      <c r="D66" s="75"/>
+      <c r="E66" s="75"/>
+      <c r="F66" s="75"/>
+      <c r="G66" s="75"/>
+      <c r="H66" s="75"/>
+      <c r="I66" s="128"/>
+      <c r="J66" s="75"/>
+      <c r="K66" s="75"/>
+      <c r="L66" s="75"/>
+      <c r="M66" s="130">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
@@ -6387,21 +6366,21 @@
       </c>
     </row>
     <row r="67" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A67" s="174"/>
-      <c r="B67" s="175">
+      <c r="A67" s="78"/>
+      <c r="B67" s="47">
         <v>63</v>
       </c>
-      <c r="C67" s="180"/>
-      <c r="D67" s="177"/>
-      <c r="E67" s="177"/>
-      <c r="F67" s="177"/>
-      <c r="G67" s="177"/>
-      <c r="H67" s="177"/>
-      <c r="I67" s="178"/>
-      <c r="J67" s="177"/>
-      <c r="K67" s="177"/>
-      <c r="L67" s="177"/>
-      <c r="M67" s="179">
+      <c r="C67" s="129"/>
+      <c r="D67" s="75"/>
+      <c r="E67" s="75"/>
+      <c r="F67" s="75"/>
+      <c r="G67" s="75"/>
+      <c r="H67" s="75"/>
+      <c r="I67" s="128"/>
+      <c r="J67" s="75"/>
+      <c r="K67" s="75"/>
+      <c r="L67" s="75"/>
+      <c r="M67" s="130">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
@@ -6455,21 +6434,21 @@
       </c>
     </row>
     <row r="68" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A68" s="174"/>
-      <c r="B68" s="175">
+      <c r="A68" s="78"/>
+      <c r="B68" s="47">
         <v>64</v>
       </c>
-      <c r="C68" s="180"/>
-      <c r="D68" s="177"/>
-      <c r="E68" s="177"/>
-      <c r="F68" s="177"/>
-      <c r="G68" s="177"/>
-      <c r="H68" s="177"/>
-      <c r="I68" s="178"/>
-      <c r="J68" s="177"/>
-      <c r="K68" s="177"/>
-      <c r="L68" s="177"/>
-      <c r="M68" s="179">
+      <c r="C68" s="129"/>
+      <c r="D68" s="75"/>
+      <c r="E68" s="75"/>
+      <c r="F68" s="75"/>
+      <c r="G68" s="75"/>
+      <c r="H68" s="75"/>
+      <c r="I68" s="128"/>
+      <c r="J68" s="75"/>
+      <c r="K68" s="75"/>
+      <c r="L68" s="75"/>
+      <c r="M68" s="130">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
@@ -6523,21 +6502,21 @@
       </c>
     </row>
     <row r="69" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A69" s="174"/>
-      <c r="B69" s="175">
+      <c r="A69" s="78"/>
+      <c r="B69" s="47">
         <v>65</v>
       </c>
-      <c r="C69" s="180"/>
-      <c r="D69" s="177"/>
-      <c r="E69" s="177"/>
-      <c r="F69" s="177"/>
-      <c r="G69" s="177"/>
-      <c r="H69" s="177"/>
-      <c r="I69" s="178"/>
-      <c r="J69" s="177"/>
-      <c r="K69" s="177"/>
-      <c r="L69" s="177"/>
-      <c r="M69" s="179">
+      <c r="C69" s="129"/>
+      <c r="D69" s="75"/>
+      <c r="E69" s="75"/>
+      <c r="F69" s="75"/>
+      <c r="G69" s="75"/>
+      <c r="H69" s="75"/>
+      <c r="I69" s="128"/>
+      <c r="J69" s="75"/>
+      <c r="K69" s="75"/>
+      <c r="L69" s="75"/>
+      <c r="M69" s="130">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
@@ -6591,21 +6570,21 @@
       </c>
     </row>
     <row r="70" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A70" s="174"/>
-      <c r="B70" s="175">
+      <c r="A70" s="78"/>
+      <c r="B70" s="47">
         <v>66</v>
       </c>
-      <c r="C70" s="180"/>
-      <c r="D70" s="177"/>
-      <c r="E70" s="177"/>
-      <c r="F70" s="177"/>
-      <c r="G70" s="177"/>
-      <c r="H70" s="177"/>
-      <c r="I70" s="178"/>
-      <c r="J70" s="177"/>
-      <c r="K70" s="177"/>
-      <c r="L70" s="177"/>
-      <c r="M70" s="179">
+      <c r="C70" s="129"/>
+      <c r="D70" s="75"/>
+      <c r="E70" s="75"/>
+      <c r="F70" s="75"/>
+      <c r="G70" s="75"/>
+      <c r="H70" s="75"/>
+      <c r="I70" s="128"/>
+      <c r="J70" s="75"/>
+      <c r="K70" s="75"/>
+      <c r="L70" s="75"/>
+      <c r="M70" s="130">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
@@ -6659,21 +6638,21 @@
       </c>
     </row>
     <row r="71" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A71" s="174"/>
-      <c r="B71" s="175">
+      <c r="A71" s="78"/>
+      <c r="B71" s="47">
         <v>67</v>
       </c>
-      <c r="C71" s="180"/>
-      <c r="D71" s="177"/>
-      <c r="E71" s="177"/>
-      <c r="F71" s="177"/>
-      <c r="G71" s="177"/>
-      <c r="H71" s="177"/>
-      <c r="I71" s="178"/>
-      <c r="J71" s="177"/>
-      <c r="K71" s="177"/>
-      <c r="L71" s="177"/>
-      <c r="M71" s="179">
+      <c r="C71" s="129"/>
+      <c r="D71" s="75"/>
+      <c r="E71" s="75"/>
+      <c r="F71" s="75"/>
+      <c r="G71" s="75"/>
+      <c r="H71" s="75"/>
+      <c r="I71" s="128"/>
+      <c r="J71" s="75"/>
+      <c r="K71" s="75"/>
+      <c r="L71" s="75"/>
+      <c r="M71" s="130">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
@@ -6727,21 +6706,21 @@
       </c>
     </row>
     <row r="72" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A72" s="174"/>
-      <c r="B72" s="175">
+      <c r="A72" s="78"/>
+      <c r="B72" s="47">
         <v>68</v>
       </c>
-      <c r="C72" s="180"/>
-      <c r="D72" s="177"/>
-      <c r="E72" s="177"/>
-      <c r="F72" s="177"/>
-      <c r="G72" s="177"/>
-      <c r="H72" s="177"/>
-      <c r="I72" s="178"/>
-      <c r="J72" s="177"/>
-      <c r="K72" s="177"/>
-      <c r="L72" s="177"/>
-      <c r="M72" s="179">
+      <c r="C72" s="129"/>
+      <c r="D72" s="75"/>
+      <c r="E72" s="75"/>
+      <c r="F72" s="75"/>
+      <c r="G72" s="75"/>
+      <c r="H72" s="75"/>
+      <c r="I72" s="128"/>
+      <c r="J72" s="75"/>
+      <c r="K72" s="75"/>
+      <c r="L72" s="75"/>
+      <c r="M72" s="130">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
@@ -6795,21 +6774,21 @@
       </c>
     </row>
     <row r="73" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A73" s="174"/>
-      <c r="B73" s="175">
+      <c r="A73" s="78"/>
+      <c r="B73" s="47">
         <v>69</v>
       </c>
-      <c r="C73" s="180"/>
-      <c r="D73" s="177"/>
-      <c r="E73" s="177"/>
-      <c r="F73" s="177"/>
-      <c r="G73" s="177"/>
-      <c r="H73" s="177"/>
-      <c r="I73" s="178"/>
-      <c r="J73" s="177"/>
-      <c r="K73" s="177"/>
-      <c r="L73" s="177"/>
-      <c r="M73" s="179">
+      <c r="C73" s="129"/>
+      <c r="D73" s="75"/>
+      <c r="E73" s="75"/>
+      <c r="F73" s="75"/>
+      <c r="G73" s="75"/>
+      <c r="H73" s="75"/>
+      <c r="I73" s="128"/>
+      <c r="J73" s="75"/>
+      <c r="K73" s="75"/>
+      <c r="L73" s="75"/>
+      <c r="M73" s="130">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
@@ -6863,21 +6842,21 @@
       </c>
     </row>
     <row r="74" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A74" s="174"/>
-      <c r="B74" s="175">
+      <c r="A74" s="78"/>
+      <c r="B74" s="47">
         <v>70</v>
       </c>
-      <c r="C74" s="181"/>
-      <c r="D74" s="177"/>
-      <c r="E74" s="177"/>
-      <c r="F74" s="182"/>
-      <c r="G74" s="177"/>
-      <c r="H74" s="177"/>
-      <c r="I74" s="178"/>
-      <c r="J74" s="177"/>
-      <c r="K74" s="177"/>
-      <c r="L74" s="177"/>
-      <c r="M74" s="179">
+      <c r="C74" s="140"/>
+      <c r="D74" s="75"/>
+      <c r="E74" s="75"/>
+      <c r="F74" s="50"/>
+      <c r="G74" s="75"/>
+      <c r="H74" s="75"/>
+      <c r="I74" s="128"/>
+      <c r="J74" s="75"/>
+      <c r="K74" s="75"/>
+      <c r="L74" s="75"/>
+      <c r="M74" s="130">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
@@ -6931,21 +6910,21 @@
       </c>
     </row>
     <row r="75" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A75" s="174"/>
-      <c r="B75" s="175">
+      <c r="A75" s="78"/>
+      <c r="B75" s="47">
         <v>71</v>
       </c>
-      <c r="C75" s="181"/>
-      <c r="D75" s="177"/>
-      <c r="E75" s="182"/>
-      <c r="F75" s="182"/>
-      <c r="G75" s="177"/>
-      <c r="H75" s="177"/>
-      <c r="I75" s="178"/>
-      <c r="J75" s="177"/>
-      <c r="K75" s="177"/>
-      <c r="L75" s="177"/>
-      <c r="M75" s="179">
+      <c r="C75" s="140"/>
+      <c r="D75" s="75"/>
+      <c r="E75" s="50"/>
+      <c r="F75" s="50"/>
+      <c r="G75" s="75"/>
+      <c r="H75" s="75"/>
+      <c r="I75" s="128"/>
+      <c r="J75" s="75"/>
+      <c r="K75" s="75"/>
+      <c r="L75" s="75"/>
+      <c r="M75" s="130">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
@@ -6999,21 +6978,21 @@
       </c>
     </row>
     <row r="76" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A76" s="174"/>
-      <c r="B76" s="175">
+      <c r="A76" s="78"/>
+      <c r="B76" s="47">
         <v>72</v>
       </c>
-      <c r="C76" s="181"/>
-      <c r="D76" s="177"/>
-      <c r="E76" s="182"/>
-      <c r="F76" s="182"/>
-      <c r="G76" s="177"/>
-      <c r="H76" s="177"/>
-      <c r="I76" s="178"/>
-      <c r="J76" s="177"/>
-      <c r="K76" s="177"/>
-      <c r="L76" s="177"/>
-      <c r="M76" s="179">
+      <c r="C76" s="140"/>
+      <c r="D76" s="75"/>
+      <c r="E76" s="50"/>
+      <c r="F76" s="50"/>
+      <c r="G76" s="75"/>
+      <c r="H76" s="75"/>
+      <c r="I76" s="128"/>
+      <c r="J76" s="75"/>
+      <c r="K76" s="75"/>
+      <c r="L76" s="75"/>
+      <c r="M76" s="130">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
@@ -7067,21 +7046,21 @@
       </c>
     </row>
     <row r="77" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A77" s="174"/>
-      <c r="B77" s="175">
+      <c r="A77" s="78"/>
+      <c r="B77" s="47">
         <v>73</v>
       </c>
-      <c r="C77" s="181"/>
-      <c r="D77" s="177"/>
-      <c r="E77" s="182"/>
-      <c r="F77" s="182"/>
-      <c r="G77" s="182"/>
-      <c r="H77" s="182"/>
-      <c r="I77" s="179"/>
-      <c r="J77" s="182"/>
-      <c r="K77" s="182"/>
-      <c r="L77" s="182"/>
-      <c r="M77" s="179">
+      <c r="C77" s="140"/>
+      <c r="D77" s="75"/>
+      <c r="E77" s="50"/>
+      <c r="F77" s="50"/>
+      <c r="G77" s="50"/>
+      <c r="H77" s="50"/>
+      <c r="I77" s="130"/>
+      <c r="J77" s="50"/>
+      <c r="K77" s="50"/>
+      <c r="L77" s="50"/>
+      <c r="M77" s="130">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
@@ -7135,21 +7114,21 @@
       </c>
     </row>
     <row r="78" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A78" s="174"/>
-      <c r="B78" s="175">
+      <c r="A78" s="78"/>
+      <c r="B78" s="47">
         <v>74</v>
       </c>
-      <c r="C78" s="181"/>
-      <c r="D78" s="177"/>
-      <c r="E78" s="182"/>
-      <c r="F78" s="182"/>
-      <c r="G78" s="182"/>
-      <c r="H78" s="182"/>
-      <c r="I78" s="179"/>
-      <c r="J78" s="182"/>
-      <c r="K78" s="182"/>
-      <c r="L78" s="182"/>
-      <c r="M78" s="179">
+      <c r="C78" s="140"/>
+      <c r="D78" s="75"/>
+      <c r="E78" s="50"/>
+      <c r="F78" s="50"/>
+      <c r="G78" s="50"/>
+      <c r="H78" s="50"/>
+      <c r="I78" s="130"/>
+      <c r="J78" s="50"/>
+      <c r="K78" s="50"/>
+      <c r="L78" s="50"/>
+      <c r="M78" s="130">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
@@ -7203,21 +7182,21 @@
       </c>
     </row>
     <row r="79" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A79" s="174"/>
-      <c r="B79" s="175">
+      <c r="A79" s="78"/>
+      <c r="B79" s="47">
         <v>75</v>
       </c>
-      <c r="C79" s="180"/>
-      <c r="D79" s="182"/>
-      <c r="E79" s="182"/>
-      <c r="F79" s="182"/>
-      <c r="G79" s="182"/>
-      <c r="H79" s="182"/>
-      <c r="I79" s="179"/>
-      <c r="J79" s="182"/>
-      <c r="K79" s="182"/>
-      <c r="L79" s="182"/>
-      <c r="M79" s="179">
+      <c r="C79" s="129"/>
+      <c r="D79" s="50"/>
+      <c r="E79" s="50"/>
+      <c r="F79" s="50"/>
+      <c r="G79" s="50"/>
+      <c r="H79" s="50"/>
+      <c r="I79" s="130"/>
+      <c r="J79" s="50"/>
+      <c r="K79" s="50"/>
+      <c r="L79" s="50"/>
+      <c r="M79" s="130">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
@@ -7271,21 +7250,21 @@
       </c>
     </row>
     <row r="80" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A80" s="174"/>
-      <c r="B80" s="175">
+      <c r="A80" s="78"/>
+      <c r="B80" s="47">
         <v>76</v>
       </c>
-      <c r="C80" s="180"/>
-      <c r="D80" s="182"/>
-      <c r="E80" s="182"/>
-      <c r="F80" s="182"/>
-      <c r="G80" s="182"/>
-      <c r="H80" s="182"/>
-      <c r="I80" s="179"/>
-      <c r="J80" s="182"/>
-      <c r="K80" s="182"/>
-      <c r="L80" s="182"/>
-      <c r="M80" s="179">
+      <c r="C80" s="129"/>
+      <c r="D80" s="50"/>
+      <c r="E80" s="50"/>
+      <c r="F80" s="50"/>
+      <c r="G80" s="50"/>
+      <c r="H80" s="50"/>
+      <c r="I80" s="130"/>
+      <c r="J80" s="50"/>
+      <c r="K80" s="50"/>
+      <c r="L80" s="50"/>
+      <c r="M80" s="130">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
@@ -7339,21 +7318,21 @@
       </c>
     </row>
     <row r="81" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A81" s="174"/>
-      <c r="B81" s="175">
+      <c r="A81" s="78"/>
+      <c r="B81" s="47">
         <v>77</v>
       </c>
-      <c r="C81" s="180"/>
-      <c r="D81" s="182"/>
-      <c r="E81" s="182"/>
-      <c r="F81" s="182"/>
-      <c r="G81" s="182"/>
-      <c r="H81" s="182"/>
-      <c r="I81" s="179"/>
-      <c r="J81" s="182"/>
-      <c r="K81" s="182"/>
-      <c r="L81" s="182"/>
-      <c r="M81" s="179">
+      <c r="C81" s="129"/>
+      <c r="D81" s="50"/>
+      <c r="E81" s="50"/>
+      <c r="F81" s="50"/>
+      <c r="G81" s="50"/>
+      <c r="H81" s="50"/>
+      <c r="I81" s="130"/>
+      <c r="J81" s="50"/>
+      <c r="K81" s="50"/>
+      <c r="L81" s="50"/>
+      <c r="M81" s="130">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
@@ -7407,21 +7386,21 @@
       </c>
     </row>
     <row r="82" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A82" s="174"/>
-      <c r="B82" s="175">
+      <c r="A82" s="78"/>
+      <c r="B82" s="47">
         <v>78</v>
       </c>
-      <c r="C82" s="180"/>
-      <c r="D82" s="182"/>
-      <c r="E82" s="182"/>
-      <c r="F82" s="182"/>
-      <c r="G82" s="182"/>
-      <c r="H82" s="182"/>
-      <c r="I82" s="179"/>
-      <c r="J82" s="182"/>
-      <c r="K82" s="182"/>
-      <c r="L82" s="182"/>
-      <c r="M82" s="179">
+      <c r="C82" s="129"/>
+      <c r="D82" s="50"/>
+      <c r="E82" s="50"/>
+      <c r="F82" s="50"/>
+      <c r="G82" s="50"/>
+      <c r="H82" s="50"/>
+      <c r="I82" s="130"/>
+      <c r="J82" s="50"/>
+      <c r="K82" s="50"/>
+      <c r="L82" s="50"/>
+      <c r="M82" s="130">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
@@ -7475,21 +7454,21 @@
       </c>
     </row>
     <row r="83" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A83" s="174"/>
-      <c r="B83" s="175">
+      <c r="A83" s="78"/>
+      <c r="B83" s="47">
         <v>79</v>
       </c>
-      <c r="C83" s="180"/>
-      <c r="D83" s="182"/>
-      <c r="E83" s="182"/>
-      <c r="F83" s="182"/>
-      <c r="G83" s="182"/>
-      <c r="H83" s="182"/>
-      <c r="I83" s="179"/>
-      <c r="J83" s="182"/>
-      <c r="K83" s="182"/>
-      <c r="L83" s="182"/>
-      <c r="M83" s="179">
+      <c r="C83" s="129"/>
+      <c r="D83" s="50"/>
+      <c r="E83" s="50"/>
+      <c r="F83" s="50"/>
+      <c r="G83" s="50"/>
+      <c r="H83" s="50"/>
+      <c r="I83" s="130"/>
+      <c r="J83" s="50"/>
+      <c r="K83" s="50"/>
+      <c r="L83" s="50"/>
+      <c r="M83" s="130">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
@@ -7543,21 +7522,21 @@
       </c>
     </row>
     <row r="84" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A84" s="174"/>
-      <c r="B84" s="175">
+      <c r="A84" s="78"/>
+      <c r="B84" s="47">
         <v>80</v>
       </c>
-      <c r="C84" s="180"/>
-      <c r="D84" s="182"/>
-      <c r="E84" s="182"/>
-      <c r="F84" s="182"/>
-      <c r="G84" s="182"/>
-      <c r="H84" s="182"/>
-      <c r="I84" s="179"/>
-      <c r="J84" s="182"/>
-      <c r="K84" s="182"/>
-      <c r="L84" s="182"/>
-      <c r="M84" s="179">
+      <c r="C84" s="129"/>
+      <c r="D84" s="50"/>
+      <c r="E84" s="50"/>
+      <c r="F84" s="50"/>
+      <c r="G84" s="50"/>
+      <c r="H84" s="50"/>
+      <c r="I84" s="130"/>
+      <c r="J84" s="50"/>
+      <c r="K84" s="50"/>
+      <c r="L84" s="50"/>
+      <c r="M84" s="130">
         <f t="shared" ref="M84:M131" si="96">SUM(D84:L84)/40</f>
         <v>0</v>
       </c>
@@ -7611,21 +7590,21 @@
       </c>
     </row>
     <row r="85" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A85" s="174"/>
-      <c r="B85" s="175">
+      <c r="A85" s="78"/>
+      <c r="B85" s="47">
         <v>81</v>
       </c>
-      <c r="C85" s="180"/>
-      <c r="D85" s="182"/>
-      <c r="E85" s="182"/>
-      <c r="F85" s="182"/>
-      <c r="G85" s="182"/>
-      <c r="H85" s="182"/>
-      <c r="I85" s="179"/>
-      <c r="J85" s="182"/>
-      <c r="K85" s="182"/>
-      <c r="L85" s="182"/>
-      <c r="M85" s="179">
+      <c r="C85" s="129"/>
+      <c r="D85" s="50"/>
+      <c r="E85" s="50"/>
+      <c r="F85" s="50"/>
+      <c r="G85" s="50"/>
+      <c r="H85" s="50"/>
+      <c r="I85" s="130"/>
+      <c r="J85" s="50"/>
+      <c r="K85" s="50"/>
+      <c r="L85" s="50"/>
+      <c r="M85" s="130">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -7679,21 +7658,21 @@
       </c>
     </row>
     <row r="86" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A86" s="174"/>
-      <c r="B86" s="175">
+      <c r="A86" s="78"/>
+      <c r="B86" s="47">
         <v>82</v>
       </c>
-      <c r="C86" s="180"/>
-      <c r="D86" s="182"/>
-      <c r="E86" s="182"/>
-      <c r="F86" s="182"/>
-      <c r="G86" s="182"/>
-      <c r="H86" s="182"/>
-      <c r="I86" s="179"/>
-      <c r="J86" s="182"/>
-      <c r="K86" s="182"/>
-      <c r="L86" s="182"/>
-      <c r="M86" s="179">
+      <c r="C86" s="129"/>
+      <c r="D86" s="50"/>
+      <c r="E86" s="50"/>
+      <c r="F86" s="50"/>
+      <c r="G86" s="50"/>
+      <c r="H86" s="50"/>
+      <c r="I86" s="130"/>
+      <c r="J86" s="50"/>
+      <c r="K86" s="50"/>
+      <c r="L86" s="50"/>
+      <c r="M86" s="130">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -7747,21 +7726,21 @@
       </c>
     </row>
     <row r="87" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A87" s="174"/>
-      <c r="B87" s="175">
+      <c r="A87" s="78"/>
+      <c r="B87" s="47">
         <v>83</v>
       </c>
-      <c r="C87" s="180"/>
-      <c r="D87" s="182"/>
-      <c r="E87" s="182"/>
-      <c r="F87" s="182"/>
-      <c r="G87" s="182"/>
-      <c r="H87" s="182"/>
-      <c r="I87" s="179"/>
-      <c r="J87" s="182"/>
-      <c r="K87" s="182"/>
-      <c r="L87" s="182"/>
-      <c r="M87" s="179">
+      <c r="C87" s="129"/>
+      <c r="D87" s="50"/>
+      <c r="E87" s="50"/>
+      <c r="F87" s="50"/>
+      <c r="G87" s="50"/>
+      <c r="H87" s="50"/>
+      <c r="I87" s="130"/>
+      <c r="J87" s="50"/>
+      <c r="K87" s="50"/>
+      <c r="L87" s="50"/>
+      <c r="M87" s="130">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -7815,21 +7794,21 @@
       </c>
     </row>
     <row r="88" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A88" s="174"/>
-      <c r="B88" s="175">
+      <c r="A88" s="78"/>
+      <c r="B88" s="47">
         <v>84</v>
       </c>
-      <c r="C88" s="180"/>
-      <c r="D88" s="182"/>
-      <c r="E88" s="182"/>
-      <c r="F88" s="182"/>
-      <c r="G88" s="182"/>
-      <c r="H88" s="182"/>
-      <c r="I88" s="179"/>
-      <c r="J88" s="182"/>
-      <c r="K88" s="182"/>
-      <c r="L88" s="182"/>
-      <c r="M88" s="179">
+      <c r="C88" s="129"/>
+      <c r="D88" s="50"/>
+      <c r="E88" s="50"/>
+      <c r="F88" s="50"/>
+      <c r="G88" s="50"/>
+      <c r="H88" s="50"/>
+      <c r="I88" s="130"/>
+      <c r="J88" s="50"/>
+      <c r="K88" s="50"/>
+      <c r="L88" s="50"/>
+      <c r="M88" s="130">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -7883,21 +7862,21 @@
       </c>
     </row>
     <row r="89" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A89" s="174"/>
-      <c r="B89" s="175">
+      <c r="A89" s="78"/>
+      <c r="B89" s="47">
         <v>85</v>
       </c>
-      <c r="C89" s="180"/>
-      <c r="D89" s="182"/>
-      <c r="E89" s="182"/>
-      <c r="F89" s="182"/>
-      <c r="G89" s="182"/>
-      <c r="H89" s="182"/>
-      <c r="I89" s="179"/>
-      <c r="J89" s="182"/>
-      <c r="K89" s="182"/>
-      <c r="L89" s="182"/>
-      <c r="M89" s="179">
+      <c r="C89" s="129"/>
+      <c r="D89" s="50"/>
+      <c r="E89" s="50"/>
+      <c r="F89" s="50"/>
+      <c r="G89" s="50"/>
+      <c r="H89" s="50"/>
+      <c r="I89" s="130"/>
+      <c r="J89" s="50"/>
+      <c r="K89" s="50"/>
+      <c r="L89" s="50"/>
+      <c r="M89" s="130">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -7951,21 +7930,21 @@
       </c>
     </row>
     <row r="90" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A90" s="174"/>
-      <c r="B90" s="175">
+      <c r="A90" s="78"/>
+      <c r="B90" s="47">
         <v>86</v>
       </c>
-      <c r="C90" s="180"/>
-      <c r="D90" s="182"/>
-      <c r="E90" s="182"/>
-      <c r="F90" s="182"/>
-      <c r="G90" s="182"/>
-      <c r="H90" s="182"/>
-      <c r="I90" s="179"/>
-      <c r="J90" s="182"/>
-      <c r="K90" s="182"/>
-      <c r="L90" s="182"/>
-      <c r="M90" s="179">
+      <c r="C90" s="129"/>
+      <c r="D90" s="50"/>
+      <c r="E90" s="50"/>
+      <c r="F90" s="50"/>
+      <c r="G90" s="50"/>
+      <c r="H90" s="50"/>
+      <c r="I90" s="130"/>
+      <c r="J90" s="50"/>
+      <c r="K90" s="50"/>
+      <c r="L90" s="50"/>
+      <c r="M90" s="130">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -8019,21 +7998,21 @@
       </c>
     </row>
     <row r="91" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A91" s="174"/>
-      <c r="B91" s="175">
+      <c r="A91" s="78"/>
+      <c r="B91" s="47">
         <v>87</v>
       </c>
-      <c r="C91" s="180"/>
-      <c r="D91" s="182"/>
-      <c r="E91" s="182"/>
-      <c r="F91" s="182"/>
-      <c r="G91" s="182"/>
-      <c r="H91" s="182"/>
-      <c r="I91" s="179"/>
-      <c r="J91" s="182"/>
-      <c r="K91" s="182"/>
-      <c r="L91" s="182"/>
-      <c r="M91" s="179">
+      <c r="C91" s="129"/>
+      <c r="D91" s="50"/>
+      <c r="E91" s="50"/>
+      <c r="F91" s="50"/>
+      <c r="G91" s="50"/>
+      <c r="H91" s="50"/>
+      <c r="I91" s="130"/>
+      <c r="J91" s="50"/>
+      <c r="K91" s="50"/>
+      <c r="L91" s="50"/>
+      <c r="M91" s="130">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -8087,21 +8066,21 @@
       </c>
     </row>
     <row r="92" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A92" s="174"/>
-      <c r="B92" s="175">
+      <c r="A92" s="78"/>
+      <c r="B92" s="47">
         <v>88</v>
       </c>
-      <c r="C92" s="180"/>
-      <c r="D92" s="182"/>
-      <c r="E92" s="182"/>
-      <c r="F92" s="182"/>
-      <c r="G92" s="182"/>
-      <c r="H92" s="182"/>
-      <c r="I92" s="179"/>
-      <c r="J92" s="182"/>
-      <c r="K92" s="182"/>
-      <c r="L92" s="182"/>
-      <c r="M92" s="179">
+      <c r="C92" s="129"/>
+      <c r="D92" s="50"/>
+      <c r="E92" s="50"/>
+      <c r="F92" s="50"/>
+      <c r="G92" s="50"/>
+      <c r="H92" s="50"/>
+      <c r="I92" s="130"/>
+      <c r="J92" s="50"/>
+      <c r="K92" s="50"/>
+      <c r="L92" s="50"/>
+      <c r="M92" s="130">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -8155,21 +8134,21 @@
       </c>
     </row>
     <row r="93" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A93" s="174"/>
-      <c r="B93" s="175">
+      <c r="A93" s="78"/>
+      <c r="B93" s="47">
         <v>89</v>
       </c>
-      <c r="C93" s="180"/>
-      <c r="D93" s="182"/>
-      <c r="E93" s="182"/>
-      <c r="F93" s="182"/>
-      <c r="G93" s="182"/>
-      <c r="H93" s="182"/>
-      <c r="I93" s="179"/>
-      <c r="J93" s="182"/>
-      <c r="K93" s="182"/>
-      <c r="L93" s="182"/>
-      <c r="M93" s="179">
+      <c r="C93" s="129"/>
+      <c r="D93" s="50"/>
+      <c r="E93" s="50"/>
+      <c r="F93" s="50"/>
+      <c r="G93" s="50"/>
+      <c r="H93" s="50"/>
+      <c r="I93" s="130"/>
+      <c r="J93" s="50"/>
+      <c r="K93" s="50"/>
+      <c r="L93" s="50"/>
+      <c r="M93" s="130">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -8223,21 +8202,21 @@
       </c>
     </row>
     <row r="94" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A94" s="174"/>
-      <c r="B94" s="175">
+      <c r="A94" s="78"/>
+      <c r="B94" s="47">
         <v>90</v>
       </c>
-      <c r="C94" s="180"/>
-      <c r="D94" s="182"/>
-      <c r="E94" s="182"/>
-      <c r="F94" s="182"/>
-      <c r="G94" s="182"/>
-      <c r="H94" s="182"/>
-      <c r="I94" s="179"/>
-      <c r="J94" s="182"/>
-      <c r="K94" s="182"/>
-      <c r="L94" s="182"/>
-      <c r="M94" s="179">
+      <c r="C94" s="129"/>
+      <c r="D94" s="50"/>
+      <c r="E94" s="50"/>
+      <c r="F94" s="50"/>
+      <c r="G94" s="50"/>
+      <c r="H94" s="50"/>
+      <c r="I94" s="130"/>
+      <c r="J94" s="50"/>
+      <c r="K94" s="50"/>
+      <c r="L94" s="50"/>
+      <c r="M94" s="130">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -8291,21 +8270,21 @@
       </c>
     </row>
     <row r="95" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A95" s="174"/>
-      <c r="B95" s="175">
+      <c r="A95" s="78"/>
+      <c r="B95" s="47">
         <v>91</v>
       </c>
-      <c r="C95" s="180"/>
-      <c r="D95" s="182"/>
-      <c r="E95" s="182"/>
-      <c r="F95" s="182"/>
-      <c r="G95" s="182"/>
-      <c r="H95" s="182"/>
-      <c r="I95" s="179"/>
-      <c r="J95" s="182"/>
-      <c r="K95" s="182"/>
-      <c r="L95" s="182"/>
-      <c r="M95" s="179">
+      <c r="C95" s="129"/>
+      <c r="D95" s="50"/>
+      <c r="E95" s="50"/>
+      <c r="F95" s="50"/>
+      <c r="G95" s="50"/>
+      <c r="H95" s="50"/>
+      <c r="I95" s="130"/>
+      <c r="J95" s="50"/>
+      <c r="K95" s="50"/>
+      <c r="L95" s="50"/>
+      <c r="M95" s="130">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -8359,21 +8338,21 @@
       </c>
     </row>
     <row r="96" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A96" s="174"/>
-      <c r="B96" s="175">
+      <c r="A96" s="78"/>
+      <c r="B96" s="47">
         <v>92</v>
       </c>
-      <c r="C96" s="180"/>
-      <c r="D96" s="182"/>
-      <c r="E96" s="182"/>
-      <c r="F96" s="182"/>
-      <c r="G96" s="182"/>
-      <c r="H96" s="182"/>
-      <c r="I96" s="179"/>
-      <c r="J96" s="182"/>
-      <c r="K96" s="182"/>
-      <c r="L96" s="182"/>
-      <c r="M96" s="179">
+      <c r="C96" s="129"/>
+      <c r="D96" s="50"/>
+      <c r="E96" s="50"/>
+      <c r="F96" s="50"/>
+      <c r="G96" s="50"/>
+      <c r="H96" s="50"/>
+      <c r="I96" s="130"/>
+      <c r="J96" s="50"/>
+      <c r="K96" s="50"/>
+      <c r="L96" s="50"/>
+      <c r="M96" s="130">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -8427,21 +8406,21 @@
       </c>
     </row>
     <row r="97" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A97" s="174"/>
-      <c r="B97" s="175">
+      <c r="A97" s="78"/>
+      <c r="B97" s="47">
         <v>93</v>
       </c>
-      <c r="C97" s="180"/>
-      <c r="D97" s="182"/>
-      <c r="E97" s="182"/>
-      <c r="F97" s="182"/>
-      <c r="G97" s="182"/>
-      <c r="H97" s="182"/>
-      <c r="I97" s="179"/>
-      <c r="J97" s="182"/>
-      <c r="K97" s="182"/>
-      <c r="L97" s="182"/>
-      <c r="M97" s="179">
+      <c r="C97" s="129"/>
+      <c r="D97" s="50"/>
+      <c r="E97" s="50"/>
+      <c r="F97" s="50"/>
+      <c r="G97" s="50"/>
+      <c r="H97" s="50"/>
+      <c r="I97" s="130"/>
+      <c r="J97" s="50"/>
+      <c r="K97" s="50"/>
+      <c r="L97" s="50"/>
+      <c r="M97" s="130">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -8495,21 +8474,21 @@
       </c>
     </row>
     <row r="98" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A98" s="174"/>
-      <c r="B98" s="175">
+      <c r="A98" s="78"/>
+      <c r="B98" s="47">
         <v>94</v>
       </c>
-      <c r="C98" s="180"/>
-      <c r="D98" s="182"/>
-      <c r="E98" s="182"/>
-      <c r="F98" s="182"/>
-      <c r="G98" s="182"/>
-      <c r="H98" s="182"/>
-      <c r="I98" s="179"/>
-      <c r="J98" s="182"/>
-      <c r="K98" s="182"/>
-      <c r="L98" s="182"/>
-      <c r="M98" s="179">
+      <c r="C98" s="129"/>
+      <c r="D98" s="50"/>
+      <c r="E98" s="50"/>
+      <c r="F98" s="50"/>
+      <c r="G98" s="50"/>
+      <c r="H98" s="50"/>
+      <c r="I98" s="130"/>
+      <c r="J98" s="50"/>
+      <c r="K98" s="50"/>
+      <c r="L98" s="50"/>
+      <c r="M98" s="130">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -8563,21 +8542,21 @@
       </c>
     </row>
     <row r="99" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A99" s="174"/>
-      <c r="B99" s="175">
+      <c r="A99" s="78"/>
+      <c r="B99" s="47">
         <v>95</v>
       </c>
-      <c r="C99" s="180"/>
-      <c r="D99" s="182"/>
-      <c r="E99" s="182"/>
-      <c r="F99" s="182"/>
-      <c r="G99" s="182"/>
-      <c r="H99" s="182"/>
-      <c r="I99" s="179"/>
-      <c r="J99" s="182"/>
-      <c r="K99" s="182"/>
-      <c r="L99" s="182"/>
-      <c r="M99" s="179">
+      <c r="C99" s="129"/>
+      <c r="D99" s="50"/>
+      <c r="E99" s="50"/>
+      <c r="F99" s="50"/>
+      <c r="G99" s="50"/>
+      <c r="H99" s="50"/>
+      <c r="I99" s="130"/>
+      <c r="J99" s="50"/>
+      <c r="K99" s="50"/>
+      <c r="L99" s="50"/>
+      <c r="M99" s="130">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -8631,21 +8610,21 @@
       </c>
     </row>
     <row r="100" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A100" s="174"/>
-      <c r="B100" s="175">
+      <c r="A100" s="78"/>
+      <c r="B100" s="47">
         <v>96</v>
       </c>
-      <c r="C100" s="180"/>
-      <c r="D100" s="182"/>
-      <c r="E100" s="182"/>
-      <c r="F100" s="182"/>
-      <c r="G100" s="182"/>
-      <c r="H100" s="182"/>
-      <c r="I100" s="179"/>
-      <c r="J100" s="182"/>
-      <c r="K100" s="182"/>
-      <c r="L100" s="182"/>
-      <c r="M100" s="179">
+      <c r="C100" s="129"/>
+      <c r="D100" s="50"/>
+      <c r="E100" s="50"/>
+      <c r="F100" s="50"/>
+      <c r="G100" s="50"/>
+      <c r="H100" s="50"/>
+      <c r="I100" s="130"/>
+      <c r="J100" s="50"/>
+      <c r="K100" s="50"/>
+      <c r="L100" s="50"/>
+      <c r="M100" s="130">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -8699,21 +8678,21 @@
       </c>
     </row>
     <row r="101" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A101" s="174"/>
-      <c r="B101" s="175">
+      <c r="A101" s="78"/>
+      <c r="B101" s="47">
         <v>97</v>
       </c>
-      <c r="C101" s="180"/>
-      <c r="D101" s="182"/>
-      <c r="E101" s="182"/>
-      <c r="F101" s="182"/>
-      <c r="G101" s="182"/>
-      <c r="H101" s="182"/>
-      <c r="I101" s="179"/>
-      <c r="J101" s="182"/>
-      <c r="K101" s="182"/>
-      <c r="L101" s="182"/>
-      <c r="M101" s="179">
+      <c r="C101" s="129"/>
+      <c r="D101" s="50"/>
+      <c r="E101" s="50"/>
+      <c r="F101" s="50"/>
+      <c r="G101" s="50"/>
+      <c r="H101" s="50"/>
+      <c r="I101" s="130"/>
+      <c r="J101" s="50"/>
+      <c r="K101" s="50"/>
+      <c r="L101" s="50"/>
+      <c r="M101" s="130">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -8767,21 +8746,21 @@
       </c>
     </row>
     <row r="102" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A102" s="174"/>
-      <c r="B102" s="175">
+      <c r="A102" s="78"/>
+      <c r="B102" s="47">
         <v>98</v>
       </c>
-      <c r="C102" s="180"/>
-      <c r="D102" s="182"/>
-      <c r="E102" s="182"/>
-      <c r="F102" s="182"/>
-      <c r="G102" s="182"/>
-      <c r="H102" s="182"/>
-      <c r="I102" s="179"/>
-      <c r="J102" s="182"/>
-      <c r="K102" s="182"/>
-      <c r="L102" s="182"/>
-      <c r="M102" s="179">
+      <c r="C102" s="129"/>
+      <c r="D102" s="50"/>
+      <c r="E102" s="50"/>
+      <c r="F102" s="50"/>
+      <c r="G102" s="50"/>
+      <c r="H102" s="50"/>
+      <c r="I102" s="130"/>
+      <c r="J102" s="50"/>
+      <c r="K102" s="50"/>
+      <c r="L102" s="50"/>
+      <c r="M102" s="130">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -8835,21 +8814,21 @@
       </c>
     </row>
     <row r="103" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A103" s="174"/>
-      <c r="B103" s="175">
+      <c r="A103" s="78"/>
+      <c r="B103" s="47">
         <v>99</v>
       </c>
-      <c r="C103" s="180"/>
-      <c r="D103" s="182"/>
-      <c r="E103" s="182"/>
-      <c r="F103" s="182"/>
-      <c r="G103" s="182"/>
-      <c r="H103" s="182"/>
-      <c r="I103" s="179"/>
-      <c r="J103" s="182"/>
-      <c r="K103" s="182"/>
-      <c r="L103" s="182"/>
-      <c r="M103" s="179">
+      <c r="C103" s="129"/>
+      <c r="D103" s="50"/>
+      <c r="E103" s="50"/>
+      <c r="F103" s="50"/>
+      <c r="G103" s="50"/>
+      <c r="H103" s="50"/>
+      <c r="I103" s="130"/>
+      <c r="J103" s="50"/>
+      <c r="K103" s="50"/>
+      <c r="L103" s="50"/>
+      <c r="M103" s="130">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -8903,21 +8882,21 @@
       </c>
     </row>
     <row r="104" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A104" s="174"/>
-      <c r="B104" s="175">
+      <c r="A104" s="78"/>
+      <c r="B104" s="47">
         <v>100</v>
       </c>
-      <c r="C104" s="180"/>
-      <c r="D104" s="182"/>
-      <c r="E104" s="182"/>
-      <c r="F104" s="182"/>
-      <c r="G104" s="182"/>
-      <c r="H104" s="182"/>
-      <c r="I104" s="179"/>
-      <c r="J104" s="182"/>
-      <c r="K104" s="182"/>
-      <c r="L104" s="182"/>
-      <c r="M104" s="179">
+      <c r="C104" s="129"/>
+      <c r="D104" s="50"/>
+      <c r="E104" s="50"/>
+      <c r="F104" s="50"/>
+      <c r="G104" s="50"/>
+      <c r="H104" s="50"/>
+      <c r="I104" s="130"/>
+      <c r="J104" s="50"/>
+      <c r="K104" s="50"/>
+      <c r="L104" s="50"/>
+      <c r="M104" s="130">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -8971,21 +8950,21 @@
       </c>
     </row>
     <row r="105" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A105" s="174"/>
-      <c r="B105" s="175">
+      <c r="A105" s="78"/>
+      <c r="B105" s="47">
         <v>101</v>
       </c>
-      <c r="C105" s="180"/>
-      <c r="D105" s="182"/>
-      <c r="E105" s="182"/>
-      <c r="F105" s="182"/>
-      <c r="G105" s="182"/>
-      <c r="H105" s="182"/>
-      <c r="I105" s="179"/>
-      <c r="J105" s="182"/>
-      <c r="K105" s="182"/>
-      <c r="L105" s="182"/>
-      <c r="M105" s="179">
+      <c r="C105" s="129"/>
+      <c r="D105" s="50"/>
+      <c r="E105" s="50"/>
+      <c r="F105" s="50"/>
+      <c r="G105" s="50"/>
+      <c r="H105" s="50"/>
+      <c r="I105" s="130"/>
+      <c r="J105" s="50"/>
+      <c r="K105" s="50"/>
+      <c r="L105" s="50"/>
+      <c r="M105" s="130">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -9039,21 +9018,21 @@
       </c>
     </row>
     <row r="106" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A106" s="174"/>
-      <c r="B106" s="175">
+      <c r="A106" s="78"/>
+      <c r="B106" s="47">
         <v>102</v>
       </c>
-      <c r="C106" s="180"/>
-      <c r="D106" s="182"/>
-      <c r="E106" s="182"/>
-      <c r="F106" s="182"/>
-      <c r="G106" s="182"/>
-      <c r="H106" s="182"/>
-      <c r="I106" s="179"/>
-      <c r="J106" s="182"/>
-      <c r="K106" s="182"/>
-      <c r="L106" s="182"/>
-      <c r="M106" s="179">
+      <c r="C106" s="129"/>
+      <c r="D106" s="50"/>
+      <c r="E106" s="50"/>
+      <c r="F106" s="50"/>
+      <c r="G106" s="50"/>
+      <c r="H106" s="50"/>
+      <c r="I106" s="130"/>
+      <c r="J106" s="50"/>
+      <c r="K106" s="50"/>
+      <c r="L106" s="50"/>
+      <c r="M106" s="130">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -9107,21 +9086,21 @@
       </c>
     </row>
     <row r="107" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A107" s="174"/>
-      <c r="B107" s="175">
+      <c r="A107" s="78"/>
+      <c r="B107" s="47">
         <v>103</v>
       </c>
-      <c r="C107" s="180"/>
-      <c r="D107" s="182"/>
-      <c r="E107" s="182"/>
-      <c r="F107" s="182"/>
-      <c r="G107" s="182"/>
-      <c r="H107" s="182"/>
-      <c r="I107" s="179"/>
-      <c r="J107" s="182"/>
-      <c r="K107" s="182"/>
-      <c r="L107" s="182"/>
-      <c r="M107" s="179">
+      <c r="C107" s="129"/>
+      <c r="D107" s="50"/>
+      <c r="E107" s="50"/>
+      <c r="F107" s="50"/>
+      <c r="G107" s="50"/>
+      <c r="H107" s="50"/>
+      <c r="I107" s="130"/>
+      <c r="J107" s="50"/>
+      <c r="K107" s="50"/>
+      <c r="L107" s="50"/>
+      <c r="M107" s="130">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -9175,21 +9154,21 @@
       </c>
     </row>
     <row r="108" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A108" s="174"/>
-      <c r="B108" s="175">
+      <c r="A108" s="78"/>
+      <c r="B108" s="47">
         <v>104</v>
       </c>
-      <c r="C108" s="180"/>
-      <c r="D108" s="182"/>
-      <c r="E108" s="182"/>
-      <c r="F108" s="182"/>
-      <c r="G108" s="182"/>
-      <c r="H108" s="182"/>
-      <c r="I108" s="179"/>
-      <c r="J108" s="182"/>
-      <c r="K108" s="182"/>
-      <c r="L108" s="182"/>
-      <c r="M108" s="179">
+      <c r="C108" s="129"/>
+      <c r="D108" s="50"/>
+      <c r="E108" s="50"/>
+      <c r="F108" s="50"/>
+      <c r="G108" s="50"/>
+      <c r="H108" s="50"/>
+      <c r="I108" s="130"/>
+      <c r="J108" s="50"/>
+      <c r="K108" s="50"/>
+      <c r="L108" s="50"/>
+      <c r="M108" s="130">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -9243,21 +9222,21 @@
       </c>
     </row>
     <row r="109" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A109" s="174"/>
-      <c r="B109" s="175">
+      <c r="A109" s="78"/>
+      <c r="B109" s="47">
         <v>105</v>
       </c>
-      <c r="C109" s="180"/>
-      <c r="D109" s="182"/>
-      <c r="E109" s="182"/>
-      <c r="F109" s="182"/>
-      <c r="G109" s="182"/>
-      <c r="H109" s="182"/>
-      <c r="I109" s="179"/>
-      <c r="J109" s="182"/>
-      <c r="K109" s="182"/>
-      <c r="L109" s="182"/>
-      <c r="M109" s="179">
+      <c r="C109" s="129"/>
+      <c r="D109" s="50"/>
+      <c r="E109" s="50"/>
+      <c r="F109" s="50"/>
+      <c r="G109" s="50"/>
+      <c r="H109" s="50"/>
+      <c r="I109" s="130"/>
+      <c r="J109" s="50"/>
+      <c r="K109" s="50"/>
+      <c r="L109" s="50"/>
+      <c r="M109" s="130">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -9311,21 +9290,21 @@
       </c>
     </row>
     <row r="110" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A110" s="174"/>
-      <c r="B110" s="175">
+      <c r="A110" s="78"/>
+      <c r="B110" s="47">
         <v>106</v>
       </c>
-      <c r="C110" s="180"/>
-      <c r="D110" s="182"/>
-      <c r="E110" s="182"/>
-      <c r="F110" s="182"/>
-      <c r="G110" s="182"/>
-      <c r="H110" s="182"/>
-      <c r="I110" s="179"/>
-      <c r="J110" s="182"/>
-      <c r="K110" s="182"/>
-      <c r="L110" s="182"/>
-      <c r="M110" s="179">
+      <c r="C110" s="129"/>
+      <c r="D110" s="50"/>
+      <c r="E110" s="50"/>
+      <c r="F110" s="50"/>
+      <c r="G110" s="50"/>
+      <c r="H110" s="50"/>
+      <c r="I110" s="130"/>
+      <c r="J110" s="50"/>
+      <c r="K110" s="50"/>
+      <c r="L110" s="50"/>
+      <c r="M110" s="130">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -9379,21 +9358,21 @@
       </c>
     </row>
     <row r="111" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A111" s="174"/>
-      <c r="B111" s="175">
+      <c r="A111" s="78"/>
+      <c r="B111" s="47">
         <v>107</v>
       </c>
-      <c r="C111" s="180"/>
-      <c r="D111" s="182"/>
-      <c r="E111" s="182"/>
-      <c r="F111" s="182"/>
-      <c r="G111" s="182"/>
-      <c r="H111" s="182"/>
-      <c r="I111" s="179"/>
-      <c r="J111" s="182"/>
-      <c r="K111" s="182"/>
-      <c r="L111" s="182"/>
-      <c r="M111" s="179">
+      <c r="C111" s="129"/>
+      <c r="D111" s="50"/>
+      <c r="E111" s="50"/>
+      <c r="F111" s="50"/>
+      <c r="G111" s="50"/>
+      <c r="H111" s="50"/>
+      <c r="I111" s="130"/>
+      <c r="J111" s="50"/>
+      <c r="K111" s="50"/>
+      <c r="L111" s="50"/>
+      <c r="M111" s="130">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -9447,21 +9426,21 @@
       </c>
     </row>
     <row r="112" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A112" s="174"/>
-      <c r="B112" s="175">
+      <c r="A112" s="78"/>
+      <c r="B112" s="47">
         <v>108</v>
       </c>
-      <c r="C112" s="180"/>
-      <c r="D112" s="182"/>
-      <c r="E112" s="182"/>
-      <c r="F112" s="182"/>
-      <c r="G112" s="182"/>
-      <c r="H112" s="182"/>
-      <c r="I112" s="179"/>
-      <c r="J112" s="182"/>
-      <c r="K112" s="182"/>
-      <c r="L112" s="182"/>
-      <c r="M112" s="179">
+      <c r="C112" s="129"/>
+      <c r="D112" s="50"/>
+      <c r="E112" s="50"/>
+      <c r="F112" s="50"/>
+      <c r="G112" s="50"/>
+      <c r="H112" s="50"/>
+      <c r="I112" s="130"/>
+      <c r="J112" s="50"/>
+      <c r="K112" s="50"/>
+      <c r="L112" s="50"/>
+      <c r="M112" s="130">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -9515,21 +9494,21 @@
       </c>
     </row>
     <row r="113" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A113" s="174"/>
-      <c r="B113" s="175">
+      <c r="A113" s="78"/>
+      <c r="B113" s="47">
         <v>109</v>
       </c>
-      <c r="C113" s="180"/>
-      <c r="D113" s="182"/>
-      <c r="E113" s="182"/>
-      <c r="F113" s="182"/>
-      <c r="G113" s="182"/>
-      <c r="H113" s="182"/>
-      <c r="I113" s="179"/>
-      <c r="J113" s="182"/>
-      <c r="K113" s="182"/>
-      <c r="L113" s="182"/>
-      <c r="M113" s="179">
+      <c r="C113" s="129"/>
+      <c r="D113" s="50"/>
+      <c r="E113" s="50"/>
+      <c r="F113" s="50"/>
+      <c r="G113" s="50"/>
+      <c r="H113" s="50"/>
+      <c r="I113" s="130"/>
+      <c r="J113" s="50"/>
+      <c r="K113" s="50"/>
+      <c r="L113" s="50"/>
+      <c r="M113" s="130">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -9583,21 +9562,21 @@
       </c>
     </row>
     <row r="114" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A114" s="174"/>
-      <c r="B114" s="175">
+      <c r="A114" s="78"/>
+      <c r="B114" s="47">
         <v>110</v>
       </c>
-      <c r="C114" s="180"/>
-      <c r="D114" s="182"/>
-      <c r="E114" s="182"/>
-      <c r="F114" s="182"/>
-      <c r="G114" s="182"/>
-      <c r="H114" s="182"/>
-      <c r="I114" s="179"/>
-      <c r="J114" s="182"/>
-      <c r="K114" s="182"/>
-      <c r="L114" s="182"/>
-      <c r="M114" s="179">
+      <c r="C114" s="129"/>
+      <c r="D114" s="50"/>
+      <c r="E114" s="50"/>
+      <c r="F114" s="50"/>
+      <c r="G114" s="50"/>
+      <c r="H114" s="50"/>
+      <c r="I114" s="130"/>
+      <c r="J114" s="50"/>
+      <c r="K114" s="50"/>
+      <c r="L114" s="50"/>
+      <c r="M114" s="130">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -9651,21 +9630,21 @@
       </c>
     </row>
     <row r="115" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A115" s="174"/>
-      <c r="B115" s="175">
+      <c r="A115" s="78"/>
+      <c r="B115" s="47">
         <v>111</v>
       </c>
-      <c r="C115" s="180"/>
-      <c r="D115" s="182"/>
-      <c r="E115" s="182"/>
-      <c r="F115" s="182"/>
-      <c r="G115" s="182"/>
-      <c r="H115" s="182"/>
-      <c r="I115" s="179"/>
-      <c r="J115" s="182"/>
-      <c r="K115" s="182"/>
-      <c r="L115" s="182"/>
-      <c r="M115" s="179">
+      <c r="C115" s="129"/>
+      <c r="D115" s="50"/>
+      <c r="E115" s="50"/>
+      <c r="F115" s="50"/>
+      <c r="G115" s="50"/>
+      <c r="H115" s="50"/>
+      <c r="I115" s="130"/>
+      <c r="J115" s="50"/>
+      <c r="K115" s="50"/>
+      <c r="L115" s="50"/>
+      <c r="M115" s="130">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -9719,21 +9698,21 @@
       </c>
     </row>
     <row r="116" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A116" s="174"/>
-      <c r="B116" s="175">
+      <c r="A116" s="78"/>
+      <c r="B116" s="47">
         <v>112</v>
       </c>
-      <c r="C116" s="180"/>
-      <c r="D116" s="182"/>
-      <c r="E116" s="182"/>
-      <c r="F116" s="182"/>
-      <c r="G116" s="182"/>
-      <c r="H116" s="182"/>
-      <c r="I116" s="179"/>
-      <c r="J116" s="182"/>
-      <c r="K116" s="182"/>
-      <c r="L116" s="182"/>
-      <c r="M116" s="179">
+      <c r="C116" s="129"/>
+      <c r="D116" s="50"/>
+      <c r="E116" s="50"/>
+      <c r="F116" s="50"/>
+      <c r="G116" s="50"/>
+      <c r="H116" s="50"/>
+      <c r="I116" s="130"/>
+      <c r="J116" s="50"/>
+      <c r="K116" s="50"/>
+      <c r="L116" s="50"/>
+      <c r="M116" s="130">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -9787,21 +9766,21 @@
       </c>
     </row>
     <row r="117" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A117" s="174"/>
-      <c r="B117" s="175">
+      <c r="A117" s="78"/>
+      <c r="B117" s="47">
         <v>113</v>
       </c>
-      <c r="C117" s="180"/>
-      <c r="D117" s="182"/>
-      <c r="E117" s="182"/>
-      <c r="F117" s="182"/>
-      <c r="G117" s="182"/>
-      <c r="H117" s="182"/>
-      <c r="I117" s="179"/>
-      <c r="J117" s="182"/>
-      <c r="K117" s="182"/>
-      <c r="L117" s="182"/>
-      <c r="M117" s="179">
+      <c r="C117" s="129"/>
+      <c r="D117" s="50"/>
+      <c r="E117" s="50"/>
+      <c r="F117" s="50"/>
+      <c r="G117" s="50"/>
+      <c r="H117" s="50"/>
+      <c r="I117" s="130"/>
+      <c r="J117" s="50"/>
+      <c r="K117" s="50"/>
+      <c r="L117" s="50"/>
+      <c r="M117" s="130">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -9855,21 +9834,21 @@
       </c>
     </row>
     <row r="118" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A118" s="174"/>
-      <c r="B118" s="175">
+      <c r="A118" s="78"/>
+      <c r="B118" s="47">
         <v>114</v>
       </c>
-      <c r="C118" s="180"/>
-      <c r="D118" s="182"/>
-      <c r="E118" s="182"/>
-      <c r="F118" s="182"/>
-      <c r="G118" s="182"/>
-      <c r="H118" s="182"/>
-      <c r="I118" s="179"/>
-      <c r="J118" s="182"/>
-      <c r="K118" s="182"/>
-      <c r="L118" s="182"/>
-      <c r="M118" s="179">
+      <c r="C118" s="129"/>
+      <c r="D118" s="50"/>
+      <c r="E118" s="50"/>
+      <c r="F118" s="50"/>
+      <c r="G118" s="50"/>
+      <c r="H118" s="50"/>
+      <c r="I118" s="130"/>
+      <c r="J118" s="50"/>
+      <c r="K118" s="50"/>
+      <c r="L118" s="50"/>
+      <c r="M118" s="130">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -9923,21 +9902,21 @@
       </c>
     </row>
     <row r="119" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A119" s="174"/>
-      <c r="B119" s="175">
+      <c r="A119" s="78"/>
+      <c r="B119" s="47">
         <v>115</v>
       </c>
-      <c r="C119" s="180"/>
-      <c r="D119" s="182"/>
-      <c r="E119" s="182"/>
-      <c r="F119" s="182"/>
-      <c r="G119" s="182"/>
-      <c r="H119" s="182"/>
-      <c r="I119" s="179"/>
-      <c r="J119" s="182"/>
-      <c r="K119" s="182"/>
-      <c r="L119" s="182"/>
-      <c r="M119" s="179">
+      <c r="C119" s="129"/>
+      <c r="D119" s="50"/>
+      <c r="E119" s="50"/>
+      <c r="F119" s="50"/>
+      <c r="G119" s="50"/>
+      <c r="H119" s="50"/>
+      <c r="I119" s="130"/>
+      <c r="J119" s="50"/>
+      <c r="K119" s="50"/>
+      <c r="L119" s="50"/>
+      <c r="M119" s="130">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -9991,21 +9970,21 @@
       </c>
     </row>
     <row r="120" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A120" s="174"/>
-      <c r="B120" s="175">
+      <c r="A120" s="78"/>
+      <c r="B120" s="47">
         <v>116</v>
       </c>
-      <c r="C120" s="180"/>
-      <c r="D120" s="182"/>
-      <c r="E120" s="182"/>
-      <c r="F120" s="182"/>
-      <c r="G120" s="182"/>
-      <c r="H120" s="182"/>
-      <c r="I120" s="179"/>
-      <c r="J120" s="182"/>
-      <c r="K120" s="182"/>
-      <c r="L120" s="182"/>
-      <c r="M120" s="179">
+      <c r="C120" s="129"/>
+      <c r="D120" s="50"/>
+      <c r="E120" s="50"/>
+      <c r="F120" s="50"/>
+      <c r="G120" s="50"/>
+      <c r="H120" s="50"/>
+      <c r="I120" s="130"/>
+      <c r="J120" s="50"/>
+      <c r="K120" s="50"/>
+      <c r="L120" s="50"/>
+      <c r="M120" s="130">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -10059,21 +10038,21 @@
       </c>
     </row>
     <row r="121" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A121" s="174"/>
-      <c r="B121" s="175">
+      <c r="A121" s="78"/>
+      <c r="B121" s="47">
         <v>117</v>
       </c>
-      <c r="C121" s="180"/>
-      <c r="D121" s="182"/>
-      <c r="E121" s="182"/>
-      <c r="F121" s="182"/>
-      <c r="G121" s="182"/>
-      <c r="H121" s="182"/>
-      <c r="I121" s="179"/>
-      <c r="J121" s="182"/>
-      <c r="K121" s="182"/>
-      <c r="L121" s="182"/>
-      <c r="M121" s="179">
+      <c r="C121" s="129"/>
+      <c r="D121" s="50"/>
+      <c r="E121" s="50"/>
+      <c r="F121" s="50"/>
+      <c r="G121" s="50"/>
+      <c r="H121" s="50"/>
+      <c r="I121" s="130"/>
+      <c r="J121" s="50"/>
+      <c r="K121" s="50"/>
+      <c r="L121" s="50"/>
+      <c r="M121" s="130">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -10127,21 +10106,21 @@
       </c>
     </row>
     <row r="122" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A122" s="174"/>
-      <c r="B122" s="175">
+      <c r="A122" s="78"/>
+      <c r="B122" s="47">
         <v>118</v>
       </c>
-      <c r="C122" s="180"/>
-      <c r="D122" s="182"/>
-      <c r="E122" s="182"/>
-      <c r="F122" s="182"/>
-      <c r="G122" s="182"/>
-      <c r="H122" s="182"/>
-      <c r="I122" s="179"/>
-      <c r="J122" s="182"/>
-      <c r="K122" s="182"/>
-      <c r="L122" s="182"/>
-      <c r="M122" s="179">
+      <c r="C122" s="129"/>
+      <c r="D122" s="50"/>
+      <c r="E122" s="50"/>
+      <c r="F122" s="50"/>
+      <c r="G122" s="50"/>
+      <c r="H122" s="50"/>
+      <c r="I122" s="130"/>
+      <c r="J122" s="50"/>
+      <c r="K122" s="50"/>
+      <c r="L122" s="50"/>
+      <c r="M122" s="130">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -10195,21 +10174,21 @@
       </c>
     </row>
     <row r="123" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A123" s="174"/>
-      <c r="B123" s="175">
+      <c r="A123" s="78"/>
+      <c r="B123" s="47">
         <v>119</v>
       </c>
-      <c r="C123" s="180"/>
-      <c r="D123" s="182"/>
-      <c r="E123" s="182"/>
-      <c r="F123" s="182"/>
-      <c r="G123" s="182"/>
-      <c r="H123" s="182"/>
-      <c r="I123" s="179"/>
-      <c r="J123" s="182"/>
-      <c r="K123" s="182"/>
-      <c r="L123" s="182"/>
-      <c r="M123" s="179">
+      <c r="C123" s="129"/>
+      <c r="D123" s="50"/>
+      <c r="E123" s="50"/>
+      <c r="F123" s="50"/>
+      <c r="G123" s="50"/>
+      <c r="H123" s="50"/>
+      <c r="I123" s="130"/>
+      <c r="J123" s="50"/>
+      <c r="K123" s="50"/>
+      <c r="L123" s="50"/>
+      <c r="M123" s="130">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -10263,19 +10242,19 @@
       </c>
     </row>
     <row r="124" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A124" s="174"/>
-      <c r="B124" s="183"/>
-      <c r="C124" s="180"/>
-      <c r="D124" s="182"/>
-      <c r="E124" s="182"/>
-      <c r="F124" s="182"/>
-      <c r="G124" s="182"/>
-      <c r="H124" s="182"/>
-      <c r="I124" s="179"/>
-      <c r="J124" s="182"/>
-      <c r="K124" s="182"/>
-      <c r="L124" s="182"/>
-      <c r="M124" s="179">
+      <c r="A124" s="78"/>
+      <c r="B124" s="108"/>
+      <c r="C124" s="129"/>
+      <c r="D124" s="50"/>
+      <c r="E124" s="50"/>
+      <c r="F124" s="50"/>
+      <c r="G124" s="50"/>
+      <c r="H124" s="50"/>
+      <c r="I124" s="130"/>
+      <c r="J124" s="50"/>
+      <c r="K124" s="50"/>
+      <c r="L124" s="50"/>
+      <c r="M124" s="130">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -10329,19 +10308,19 @@
       </c>
     </row>
     <row r="125" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A125" s="174"/>
-      <c r="B125" s="183"/>
-      <c r="C125" s="180"/>
-      <c r="D125" s="182"/>
-      <c r="E125" s="182"/>
-      <c r="F125" s="182"/>
-      <c r="G125" s="182"/>
-      <c r="H125" s="182"/>
-      <c r="I125" s="179"/>
-      <c r="J125" s="182"/>
-      <c r="K125" s="182"/>
-      <c r="L125" s="182"/>
-      <c r="M125" s="179">
+      <c r="A125" s="78"/>
+      <c r="B125" s="108"/>
+      <c r="C125" s="129"/>
+      <c r="D125" s="50"/>
+      <c r="E125" s="50"/>
+      <c r="F125" s="50"/>
+      <c r="G125" s="50"/>
+      <c r="H125" s="50"/>
+      <c r="I125" s="130"/>
+      <c r="J125" s="50"/>
+      <c r="K125" s="50"/>
+      <c r="L125" s="50"/>
+      <c r="M125" s="130">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -10395,19 +10374,19 @@
       </c>
     </row>
     <row r="126" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A126" s="174"/>
-      <c r="B126" s="183"/>
-      <c r="C126" s="180"/>
-      <c r="D126" s="182"/>
-      <c r="E126" s="182"/>
-      <c r="F126" s="182"/>
-      <c r="G126" s="182"/>
-      <c r="H126" s="182"/>
-      <c r="I126" s="179"/>
-      <c r="J126" s="182"/>
-      <c r="K126" s="182"/>
-      <c r="L126" s="182"/>
-      <c r="M126" s="179">
+      <c r="A126" s="78"/>
+      <c r="B126" s="108"/>
+      <c r="C126" s="129"/>
+      <c r="D126" s="50"/>
+      <c r="E126" s="50"/>
+      <c r="F126" s="50"/>
+      <c r="G126" s="50"/>
+      <c r="H126" s="50"/>
+      <c r="I126" s="130"/>
+      <c r="J126" s="50"/>
+      <c r="K126" s="50"/>
+      <c r="L126" s="50"/>
+      <c r="M126" s="130">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -10461,19 +10440,19 @@
       </c>
     </row>
     <row r="127" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A127" s="174"/>
-      <c r="B127" s="183"/>
-      <c r="C127" s="180"/>
-      <c r="D127" s="182"/>
-      <c r="E127" s="182"/>
-      <c r="F127" s="182"/>
-      <c r="G127" s="182"/>
-      <c r="H127" s="182"/>
-      <c r="I127" s="179"/>
-      <c r="J127" s="182"/>
-      <c r="K127" s="182"/>
-      <c r="L127" s="182"/>
-      <c r="M127" s="179">
+      <c r="A127" s="78"/>
+      <c r="B127" s="108"/>
+      <c r="C127" s="129"/>
+      <c r="D127" s="50"/>
+      <c r="E127" s="50"/>
+      <c r="F127" s="50"/>
+      <c r="G127" s="50"/>
+      <c r="H127" s="50"/>
+      <c r="I127" s="130"/>
+      <c r="J127" s="50"/>
+      <c r="K127" s="50"/>
+      <c r="L127" s="50"/>
+      <c r="M127" s="130">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -10792,10 +10771,10 @@
     </row>
     <row r="132" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A132" s="78"/>
-      <c r="B132" s="162" t="s">
+      <c r="B132" s="151" t="s">
         <v>11</v>
       </c>
-      <c r="C132" s="163"/>
+      <c r="C132" s="152"/>
       <c r="D132" s="84">
         <f t="shared" ref="D132:L132" si="104">SUM(D6:D60)</f>
         <v>0</v>
@@ -11059,10 +11038,10 @@
       </c>
     </row>
     <row r="136" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B136" s="150" t="s">
+      <c r="B136" s="164" t="s">
         <v>71</v>
       </c>
-      <c r="C136" s="151"/>
+      <c r="C136" s="165"/>
       <c r="D136" s="83">
         <f>SUM(D134:D135)</f>
         <v>0</v>
@@ -11153,10 +11132,10 @@
       </c>
     </row>
     <row r="137" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B137" s="140" t="s">
+      <c r="B137" s="153" t="s">
         <v>11</v>
       </c>
-      <c r="C137" s="141"/>
+      <c r="C137" s="154"/>
       <c r="D137" s="85">
         <f>SUM(D132,D136)</f>
         <v>0</v>
@@ -11248,17 +11227,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="R3:U3"/>
-    <mergeCell ref="V3:Y3"/>
-    <mergeCell ref="B132:C132"/>
     <mergeCell ref="B137:C137"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="P2:Q2"/>
     <mergeCell ref="M3:O3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B136:C136"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="R3:U3"/>
+    <mergeCell ref="V3:Y3"/>
+    <mergeCell ref="B132:C132"/>
   </mergeCells>
   <conditionalFormatting sqref="C45:C59">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
@@ -11270,7 +11249,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="C2:Z31"/>
+  <dimension ref="C2:Z29"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="4.453125" customWidth="1"/>
@@ -11294,25 +11273,25 @@
   <sheetData>
     <row r="2" spans="3:26" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="3:26" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C3" s="166" t="s">
+      <c r="C3" s="168" t="s">
         <v>49</v>
       </c>
-      <c r="D3" s="167"/>
-      <c r="E3" s="167"/>
-      <c r="F3" s="167"/>
-      <c r="G3" s="168"/>
-      <c r="H3" s="170" t="s">
+      <c r="D3" s="169"/>
+      <c r="E3" s="169"/>
+      <c r="F3" s="169"/>
+      <c r="G3" s="170"/>
+      <c r="H3" s="172" t="s">
         <v>63</v>
       </c>
-      <c r="I3" s="171"/>
-      <c r="K3" s="172" t="s">
+      <c r="I3" s="173"/>
+      <c r="K3" s="174" t="s">
         <v>67</v>
       </c>
-      <c r="L3" s="172"/>
-      <c r="M3" s="172"/>
-      <c r="N3" s="172"/>
-      <c r="O3" s="172"/>
-      <c r="P3" s="172"/>
+      <c r="L3" s="174"/>
+      <c r="M3" s="174"/>
+      <c r="N3" s="174"/>
+      <c r="O3" s="174"/>
+      <c r="P3" s="174"/>
     </row>
     <row r="4" spans="3:26" ht="29.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C4" s="99"/>
@@ -11598,14 +11577,14 @@
       </c>
     </row>
     <row r="11" spans="3:26" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C11" s="169" t="s">
+      <c r="C11" s="171" t="s">
         <v>60</v>
       </c>
-      <c r="D11" s="169"/>
-      <c r="F11" s="169" t="s">
+      <c r="D11" s="171"/>
+      <c r="F11" s="171" t="s">
         <v>69</v>
       </c>
-      <c r="G11" s="169"/>
+      <c r="G11" s="171"/>
       <c r="K11" s="1" t="s">
         <v>7</v>
       </c>
@@ -11703,10 +11682,10 @@
         <f>G12*40</f>
         <v>168000</v>
       </c>
-      <c r="S13" s="164" t="s">
+      <c r="S13" s="166" t="s">
         <v>86</v>
       </c>
-      <c r="T13" s="164"/>
+      <c r="T13" s="166"/>
       <c r="U13" s="136">
         <f>SUM(U8:U12)</f>
         <v>100</v>
@@ -11795,13 +11774,13 @@
       </c>
     </row>
     <row r="20" spans="4:15" ht="24" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="D20" s="165" t="s">
+      <c r="D20" s="167" t="s">
         <v>67</v>
       </c>
-      <c r="E20" s="165"/>
-      <c r="F20" s="165"/>
-      <c r="G20" s="165"/>
-      <c r="H20" s="165"/>
+      <c r="E20" s="167"/>
+      <c r="F20" s="167"/>
+      <c r="G20" s="167"/>
+      <c r="H20" s="167"/>
       <c r="K20" s="1" t="s">
         <v>4</v>
       </c>
@@ -12014,23 +11993,6 @@
       <c r="H29" s="9">
         <f>SUM(H22:H28)</f>
         <v>0</v>
-      </c>
-      <c r="K29">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="30" spans="4:15" x14ac:dyDescent="0.35">
-      <c r="J30">
-        <f>K30+K29</f>
-        <v>1067</v>
-      </c>
-      <c r="K30">
-        <v>767</v>
-      </c>
-    </row>
-    <row r="31" spans="4:15" x14ac:dyDescent="0.35">
-      <c r="K31">
-        <v>1060</v>
       </c>
     </row>
   </sheetData>

--- a/Aug_2026/daily Reports/LMT Orders.xlsx
+++ b/Aug_2026/daily Reports/LMT Orders.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C66538C2-9476-468F-8271-0798325F0CE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0054EE2A-8D7E-4ACA-ABC8-CDCE69547342}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="98">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -296,6 +296,27 @@
   <si>
     <t>Opening Aug 2026</t>
   </si>
+  <si>
+    <t xml:space="preserve">Zohra Mart </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Risen Gajumata </t>
+  </si>
+  <si>
+    <t>Raheem Store</t>
+  </si>
+  <si>
+    <t>SS DEPARTMENTAL STORE (Cario Mart)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aslam Mart </t>
+  </si>
+  <si>
+    <t xml:space="preserve">HA Mega Mart </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lutaf Mart </t>
+  </si>
 </sst>
 </file>
 
@@ -1549,6 +1570,45 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1583,45 +1643,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2181,19 +2202,19 @@
   <dimension ref="A1:Y137"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="3" width="28.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.90625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="141">
+      <c r="B1" s="154">
         <f ca="1">TODAY()</f>
-        <v>46235</v>
-      </c>
-      <c r="C1" s="141"/>
-      <c r="D1" s="141"/>
-      <c r="E1" s="141"/>
-      <c r="F1" s="141"/>
+        <v>46240</v>
+      </c>
+      <c r="C1" s="154"/>
+      <c r="D1" s="154"/>
+      <c r="E1" s="154"/>
+      <c r="F1" s="154"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
       <c r="I1" s="10"/>
@@ -2215,10 +2236,10 @@
       <c r="Y1" s="10"/>
     </row>
     <row r="2" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="163" t="s">
+      <c r="A2" s="151" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="142" t="s">
+      <c r="B2" s="155" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2251,13 +2272,13 @@
       <c r="L2" s="15">
         <v>120</v>
       </c>
-      <c r="M2" s="155"/>
-      <c r="N2" s="156"/>
-      <c r="O2" s="157"/>
-      <c r="P2" s="158" t="s">
+      <c r="M2" s="143"/>
+      <c r="N2" s="144"/>
+      <c r="O2" s="145"/>
+      <c r="P2" s="146" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="159"/>
+      <c r="Q2" s="147"/>
       <c r="R2" s="18">
         <v>0.05</v>
       </c>
@@ -2276,8 +2297,8 @@
       <c r="Y2" s="20"/>
     </row>
     <row r="3" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="163"/>
-      <c r="B3" s="143"/>
+      <c r="A3" s="151"/>
+      <c r="B3" s="156"/>
       <c r="C3" s="23" t="s">
         <v>15</v>
       </c>
@@ -2308,29 +2329,29 @@
       <c r="L3" s="29">
         <v>72.64</v>
       </c>
-      <c r="M3" s="160" t="s">
+      <c r="M3" s="148" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="161"/>
-      <c r="O3" s="162"/>
+      <c r="N3" s="149"/>
+      <c r="O3" s="150"/>
       <c r="P3" s="71"/>
       <c r="Q3" s="72"/>
-      <c r="R3" s="145" t="s">
+      <c r="R3" s="158" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="146"/>
-      <c r="T3" s="146"/>
-      <c r="U3" s="147"/>
-      <c r="V3" s="148" t="s">
+      <c r="S3" s="159"/>
+      <c r="T3" s="159"/>
+      <c r="U3" s="160"/>
+      <c r="V3" s="161" t="s">
         <v>17</v>
       </c>
-      <c r="W3" s="149"/>
-      <c r="X3" s="149"/>
-      <c r="Y3" s="150"/>
+      <c r="W3" s="162"/>
+      <c r="X3" s="162"/>
+      <c r="Y3" s="163"/>
     </row>
     <row r="4" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="163"/>
-      <c r="B4" s="144"/>
+      <c r="A4" s="151"/>
+      <c r="B4" s="157"/>
       <c r="C4" s="30" t="s">
         <v>18</v>
       </c>
@@ -2402,23 +2423,33 @@
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A5" s="78"/>
+      <c r="A5" s="78">
+        <v>46239</v>
+      </c>
       <c r="B5" s="36">
         <v>1</v>
       </c>
-      <c r="C5" s="131"/>
+      <c r="C5" s="131" t="s">
+        <v>96</v>
+      </c>
       <c r="D5" s="132"/>
       <c r="E5" s="133"/>
       <c r="F5" s="38"/>
       <c r="G5" s="134"/>
       <c r="H5" s="133"/>
-      <c r="I5" s="38"/>
+      <c r="I5" s="38">
+        <v>120</v>
+      </c>
       <c r="J5" s="134"/>
-      <c r="K5" s="133"/>
-      <c r="L5" s="135"/>
+      <c r="K5" s="133">
+        <v>40</v>
+      </c>
+      <c r="L5" s="135">
+        <v>40</v>
+      </c>
       <c r="M5" s="37">
         <f>SUM(D5:L5)/40</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N5" s="39">
         <f>SUMPRODUCT($D$4:$L$4,$D$6:$L$6)</f>
@@ -2426,15 +2457,15 @@
       </c>
       <c r="O5" s="38">
         <f>SUMPRODUCT($D$3:$L$3,$D$6:$L$6)/1000</f>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P5" s="73">
         <f>SUM(G5:I5)/20</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q5" s="40">
         <f>SUM(J5:L5)/20</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R5" s="41" t="e">
         <f>SUMPRODUCT($D$4:$F$4,$D$6:$F$6)*$R$3</f>
@@ -2470,23 +2501,39 @@
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A6" s="78"/>
+      <c r="A6" s="78">
+        <v>46239</v>
+      </c>
       <c r="B6" s="47">
         <v>2</v>
       </c>
-      <c r="C6" s="57"/>
+      <c r="C6" s="57" t="s">
+        <v>97</v>
+      </c>
       <c r="D6" s="74"/>
       <c r="E6" s="75"/>
       <c r="F6" s="76"/>
-      <c r="G6" s="50"/>
-      <c r="H6" s="75"/>
-      <c r="I6" s="49"/>
-      <c r="J6" s="50"/>
-      <c r="K6" s="75"/>
-      <c r="L6" s="76"/>
+      <c r="G6" s="50">
+        <v>120</v>
+      </c>
+      <c r="H6" s="75">
+        <v>120</v>
+      </c>
+      <c r="I6" s="49">
+        <v>120</v>
+      </c>
+      <c r="J6" s="50">
+        <v>200</v>
+      </c>
+      <c r="K6" s="75">
+        <v>200</v>
+      </c>
+      <c r="L6" s="76">
+        <v>200</v>
+      </c>
       <c r="M6" s="48">
         <f t="shared" ref="M6:M137" si="0">SUM(D6:L6)/40</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N6" s="39">
         <f>SUMPRODUCT($D$4:$L$4,$D$6:$L$6)</f>
@@ -2494,15 +2541,15 @@
       </c>
       <c r="O6" s="49">
         <f t="shared" ref="O6:O136" si="1">SUMPRODUCT($D$3:$L$3,$D$6:$L$6)/1000</f>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P6" s="73">
         <f t="shared" ref="P6" si="2">SUM(G6:I6)/20</f>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Q6" s="40">
         <f t="shared" ref="Q6" si="3">SUM(J6:L6)/20</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="R6" s="51" t="e">
         <f t="shared" ref="R6:R136" si="4">SUMPRODUCT($D$4:$F$4,$D$6:$F$6)*$R$3</f>
@@ -2538,23 +2585,33 @@
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A7" s="78"/>
+      <c r="A7" s="78">
+        <v>46240</v>
+      </c>
       <c r="B7" s="47">
         <v>3</v>
       </c>
-      <c r="C7" s="57"/>
+      <c r="C7" s="57" t="s">
+        <v>91</v>
+      </c>
       <c r="D7" s="74"/>
       <c r="E7" s="75"/>
       <c r="F7" s="76"/>
       <c r="G7" s="50"/>
       <c r="H7" s="75"/>
       <c r="I7" s="49"/>
-      <c r="J7" s="50"/>
-      <c r="K7" s="75"/>
-      <c r="L7" s="76"/>
+      <c r="J7" s="50">
+        <v>120</v>
+      </c>
+      <c r="K7" s="75">
+        <v>120</v>
+      </c>
+      <c r="L7" s="76">
+        <v>120</v>
+      </c>
       <c r="M7" s="48">
         <f t="shared" ref="M7:M15" si="12">SUM(D7:L7)/40</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N7" s="39">
         <f>SUMPRODUCT($D$4:$L$4,$D$6:$L$6)</f>
@@ -2562,7 +2619,7 @@
       </c>
       <c r="O7" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P7" s="73">
         <f t="shared" ref="P7:P15" si="13">SUM(G7:I7)/20</f>
@@ -2570,7 +2627,7 @@
       </c>
       <c r="Q7" s="40">
         <f t="shared" ref="Q7:Q15" si="14">SUM(J7:L7)/20</f>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="R7" s="51" t="e">
         <f t="shared" si="4"/>
@@ -2606,23 +2663,35 @@
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A8" s="78"/>
+      <c r="A8" s="78">
+        <v>46240</v>
+      </c>
       <c r="B8" s="47">
         <v>4</v>
       </c>
-      <c r="C8" s="57"/>
+      <c r="C8" s="57" t="s">
+        <v>92</v>
+      </c>
       <c r="D8" s="74"/>
       <c r="E8" s="75"/>
       <c r="F8" s="76"/>
-      <c r="G8" s="50"/>
+      <c r="G8" s="50">
+        <v>198</v>
+      </c>
       <c r="H8" s="75"/>
-      <c r="I8" s="49"/>
-      <c r="J8" s="50"/>
+      <c r="I8" s="49">
+        <v>160</v>
+      </c>
+      <c r="J8" s="50">
+        <v>120</v>
+      </c>
       <c r="K8" s="75"/>
-      <c r="L8" s="76"/>
+      <c r="L8" s="76">
+        <v>158</v>
+      </c>
       <c r="M8" s="48">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>15.9</v>
       </c>
       <c r="N8" s="39">
         <f t="shared" ref="N8:N136" si="18">SUMPRODUCT($D$4:$L$4,$D$6:$L$6)</f>
@@ -2630,15 +2699,15 @@
       </c>
       <c r="O8" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P8" s="73">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>17.899999999999999</v>
       </c>
       <c r="Q8" s="40">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>13.9</v>
       </c>
       <c r="R8" s="51" t="e">
         <f t="shared" si="4"/>
@@ -2674,23 +2743,39 @@
       </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A9" s="78"/>
+      <c r="A9" s="78">
+        <v>46240</v>
+      </c>
       <c r="B9" s="47">
         <v>5</v>
       </c>
-      <c r="C9" s="57"/>
+      <c r="C9" s="57" t="s">
+        <v>93</v>
+      </c>
       <c r="D9" s="74"/>
       <c r="E9" s="75"/>
       <c r="F9" s="76"/>
-      <c r="G9" s="50"/>
-      <c r="H9" s="75"/>
-      <c r="I9" s="49"/>
-      <c r="J9" s="50"/>
-      <c r="K9" s="75"/>
-      <c r="L9" s="76"/>
+      <c r="G9" s="50">
+        <v>200</v>
+      </c>
+      <c r="H9" s="75">
+        <v>240</v>
+      </c>
+      <c r="I9" s="49">
+        <v>239</v>
+      </c>
+      <c r="J9" s="50">
+        <v>320</v>
+      </c>
+      <c r="K9" s="75">
+        <v>320</v>
+      </c>
+      <c r="L9" s="76">
+        <v>600</v>
+      </c>
       <c r="M9" s="48">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>47.975000000000001</v>
       </c>
       <c r="N9" s="39">
         <f t="shared" si="18"/>
@@ -2698,15 +2783,15 @@
       </c>
       <c r="O9" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P9" s="73">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>33.950000000000003</v>
       </c>
       <c r="Q9" s="40">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="R9" s="51" t="e">
         <f t="shared" si="4"/>
@@ -2742,23 +2827,35 @@
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A10" s="78"/>
+      <c r="A10" s="78">
+        <v>46240</v>
+      </c>
       <c r="B10" s="47">
         <v>6</v>
       </c>
-      <c r="C10" s="57"/>
-      <c r="D10" s="74"/>
+      <c r="C10" s="57" t="s">
+        <v>94</v>
+      </c>
+      <c r="D10" s="74">
+        <v>80</v>
+      </c>
       <c r="E10" s="75"/>
       <c r="F10" s="76"/>
-      <c r="G10" s="50"/>
-      <c r="H10" s="75"/>
-      <c r="I10" s="49"/>
+      <c r="G10" s="50">
+        <v>40</v>
+      </c>
+      <c r="H10" s="75">
+        <v>40</v>
+      </c>
+      <c r="I10" s="49">
+        <v>80</v>
+      </c>
       <c r="J10" s="50"/>
       <c r="K10" s="75"/>
       <c r="L10" s="76"/>
       <c r="M10" s="48">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N10" s="39">
         <f t="shared" si="18"/>
@@ -2766,11 +2863,11 @@
       </c>
       <c r="O10" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P10" s="73">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q10" s="40">
         <f t="shared" si="14"/>
@@ -2810,23 +2907,41 @@
       </c>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A11" s="78"/>
+      <c r="A11" s="78">
+        <v>46240</v>
+      </c>
       <c r="B11" s="47">
         <v>7</v>
       </c>
-      <c r="C11" s="57"/>
-      <c r="D11" s="74"/>
+      <c r="C11" s="57" t="s">
+        <v>95</v>
+      </c>
+      <c r="D11" s="74">
+        <v>200</v>
+      </c>
       <c r="E11" s="75"/>
       <c r="F11" s="76"/>
-      <c r="G11" s="50"/>
-      <c r="H11" s="75"/>
-      <c r="I11" s="49"/>
-      <c r="J11" s="50"/>
-      <c r="K11" s="75"/>
-      <c r="L11" s="76"/>
+      <c r="G11" s="50">
+        <v>200</v>
+      </c>
+      <c r="H11" s="75">
+        <v>200</v>
+      </c>
+      <c r="I11" s="49">
+        <v>200</v>
+      </c>
+      <c r="J11" s="50">
+        <v>200</v>
+      </c>
+      <c r="K11" s="75">
+        <v>200</v>
+      </c>
+      <c r="L11" s="76">
+        <v>200</v>
+      </c>
       <c r="M11" s="48">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="N11" s="39">
         <f t="shared" si="18"/>
@@ -2834,15 +2949,15 @@
       </c>
       <c r="O11" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P11" s="73">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="Q11" s="40">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="R11" s="51" t="e">
         <f t="shared" si="4"/>
@@ -2902,7 +3017,7 @@
       </c>
       <c r="O12" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P12" s="73">
         <f t="shared" si="13"/>
@@ -2970,7 +3085,7 @@
       </c>
       <c r="O13" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P13" s="73">
         <f t="shared" si="13"/>
@@ -3038,7 +3153,7 @@
       </c>
       <c r="O14" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P14" s="73">
         <f t="shared" si="13"/>
@@ -3106,7 +3221,7 @@
       </c>
       <c r="O15" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P15" s="73">
         <f t="shared" si="13"/>
@@ -3174,7 +3289,7 @@
       </c>
       <c r="O16" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P16" s="73">
         <f t="shared" ref="P16:P17" si="22">SUM(G16:I16)/20</f>
@@ -3242,7 +3357,7 @@
       </c>
       <c r="O17" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P17" s="73">
         <f t="shared" si="22"/>
@@ -3310,7 +3425,7 @@
       </c>
       <c r="O18" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P18" s="73">
         <f t="shared" ref="P18:P20" si="30">SUM(G18:I18)/20</f>
@@ -3378,7 +3493,7 @@
       </c>
       <c r="O19" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P19" s="73">
         <f t="shared" si="30"/>
@@ -3446,7 +3561,7 @@
       </c>
       <c r="O20" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P20" s="73">
         <f t="shared" si="30"/>
@@ -3514,7 +3629,7 @@
       </c>
       <c r="O21" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P21" s="73">
         <f t="shared" ref="P21:P23" si="38">SUM(G21:I21)/20</f>
@@ -3582,7 +3697,7 @@
       </c>
       <c r="O22" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P22" s="73">
         <f t="shared" si="38"/>
@@ -3650,7 +3765,7 @@
       </c>
       <c r="O23" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P23" s="73">
         <f t="shared" si="38"/>
@@ -3718,7 +3833,7 @@
       </c>
       <c r="O24" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P24" s="73">
         <f t="shared" ref="P24:P27" si="48">SUM(G24:I24)/20</f>
@@ -3786,7 +3901,7 @@
       </c>
       <c r="O25" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P25" s="73">
         <f t="shared" si="48"/>
@@ -3854,7 +3969,7 @@
       </c>
       <c r="O26" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P26" s="73">
         <f t="shared" si="48"/>
@@ -3922,7 +4037,7 @@
       </c>
       <c r="O27" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P27" s="73">
         <f t="shared" si="48"/>
@@ -3990,7 +4105,7 @@
       </c>
       <c r="O28" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P28" s="73">
         <f t="shared" ref="P28:P60" si="53">SUM(G28:I28)/20</f>
@@ -4058,7 +4173,7 @@
       </c>
       <c r="O29" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P29" s="73">
         <f t="shared" ref="P29" si="61">SUM(G29:I29)/20</f>
@@ -4126,7 +4241,7 @@
       </c>
       <c r="O30" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P30" s="73">
         <f t="shared" si="53"/>
@@ -4194,7 +4309,7 @@
       </c>
       <c r="O31" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P31" s="73">
         <f t="shared" si="53"/>
@@ -4262,7 +4377,7 @@
       </c>
       <c r="O32" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P32" s="73">
         <f t="shared" si="53"/>
@@ -4330,7 +4445,7 @@
       </c>
       <c r="O33" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P33" s="73">
         <f t="shared" si="53"/>
@@ -4398,7 +4513,7 @@
       </c>
       <c r="O34" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P34" s="73">
         <f t="shared" ref="P34:P46" si="69">SUM(G34:I34)/20</f>
@@ -4466,7 +4581,7 @@
       </c>
       <c r="O35" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P35" s="73">
         <f t="shared" si="69"/>
@@ -4534,7 +4649,7 @@
       </c>
       <c r="O36" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P36" s="73">
         <f t="shared" si="69"/>
@@ -4602,7 +4717,7 @@
       </c>
       <c r="O37" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P37" s="73">
         <f t="shared" si="69"/>
@@ -4670,7 +4785,7 @@
       </c>
       <c r="O38" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P38" s="73">
         <f t="shared" si="69"/>
@@ -4738,7 +4853,7 @@
       </c>
       <c r="O39" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P39" s="73">
         <f t="shared" si="69"/>
@@ -4806,7 +4921,7 @@
       </c>
       <c r="O40" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P40" s="73">
         <f t="shared" si="69"/>
@@ -4874,7 +4989,7 @@
       </c>
       <c r="O41" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P41" s="73">
         <f t="shared" si="69"/>
@@ -4942,7 +5057,7 @@
       </c>
       <c r="O42" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P42" s="73">
         <f t="shared" si="69"/>
@@ -5010,7 +5125,7 @@
       </c>
       <c r="O43" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P43" s="73">
         <f t="shared" si="69"/>
@@ -5078,7 +5193,7 @@
       </c>
       <c r="O44" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P44" s="73">
         <f t="shared" si="69"/>
@@ -5146,7 +5261,7 @@
       </c>
       <c r="O45" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P45" s="73">
         <f t="shared" si="69"/>
@@ -5214,7 +5329,7 @@
       </c>
       <c r="O46" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P46" s="73">
         <f t="shared" si="69"/>
@@ -5264,7 +5379,7 @@
       </c>
       <c r="O47" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P47" s="73">
         <f t="shared" ref="P47:P59" si="77">SUM(G47:I47)/20</f>
@@ -5314,7 +5429,7 @@
       </c>
       <c r="O48" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P48" s="73">
         <f t="shared" si="77"/>
@@ -5364,7 +5479,7 @@
       </c>
       <c r="O49" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P49" s="73">
         <f t="shared" si="77"/>
@@ -5414,7 +5529,7 @@
       </c>
       <c r="O50" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P50" s="73">
         <f t="shared" si="77"/>
@@ -5464,7 +5579,7 @@
       </c>
       <c r="O51" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P51" s="73">
         <f t="shared" si="77"/>
@@ -5514,7 +5629,7 @@
       </c>
       <c r="O52" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P52" s="73">
         <f t="shared" si="77"/>
@@ -5564,7 +5679,7 @@
       </c>
       <c r="O53" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P53" s="73">
         <f t="shared" si="77"/>
@@ -5614,7 +5729,7 @@
       </c>
       <c r="O54" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P54" s="73">
         <f t="shared" si="77"/>
@@ -5664,7 +5779,7 @@
       </c>
       <c r="O55" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P55" s="73">
         <f t="shared" si="77"/>
@@ -5714,7 +5829,7 @@
       </c>
       <c r="O56" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P56" s="73">
         <f t="shared" si="77"/>
@@ -5764,7 +5879,7 @@
       </c>
       <c r="O57" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P57" s="73">
         <f t="shared" si="77"/>
@@ -5814,7 +5929,7 @@
       </c>
       <c r="O58" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P58" s="73">
         <f t="shared" si="77"/>
@@ -5864,7 +5979,7 @@
       </c>
       <c r="O59" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P59" s="73">
         <f t="shared" si="77"/>
@@ -5914,7 +6029,7 @@
       </c>
       <c r="O60" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P60" s="73">
         <f t="shared" si="53"/>
@@ -5982,7 +6097,7 @@
       </c>
       <c r="O61" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P61" s="73">
         <f t="shared" ref="P61:P78" si="82">SUM(G61:I61)/20</f>
@@ -6050,7 +6165,7 @@
       </c>
       <c r="O62" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P62" s="73">
         <f t="shared" si="82"/>
@@ -6118,7 +6233,7 @@
       </c>
       <c r="O63" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P63" s="73">
         <f t="shared" si="82"/>
@@ -6186,7 +6301,7 @@
       </c>
       <c r="O64" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P64" s="73">
         <f t="shared" si="82"/>
@@ -6254,7 +6369,7 @@
       </c>
       <c r="O65" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P65" s="73">
         <f t="shared" si="82"/>
@@ -6322,7 +6437,7 @@
       </c>
       <c r="O66" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P66" s="73">
         <f t="shared" si="82"/>
@@ -6390,7 +6505,7 @@
       </c>
       <c r="O67" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P67" s="73">
         <f t="shared" si="82"/>
@@ -6458,7 +6573,7 @@
       </c>
       <c r="O68" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P68" s="73">
         <f t="shared" si="82"/>
@@ -6526,7 +6641,7 @@
       </c>
       <c r="O69" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P69" s="73">
         <f t="shared" si="82"/>
@@ -6594,7 +6709,7 @@
       </c>
       <c r="O70" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P70" s="73">
         <f t="shared" si="82"/>
@@ -6662,7 +6777,7 @@
       </c>
       <c r="O71" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P71" s="73">
         <f t="shared" si="82"/>
@@ -6730,7 +6845,7 @@
       </c>
       <c r="O72" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P72" s="73">
         <f t="shared" si="82"/>
@@ -6798,7 +6913,7 @@
       </c>
       <c r="O73" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P73" s="73">
         <f t="shared" si="82"/>
@@ -6866,7 +6981,7 @@
       </c>
       <c r="O74" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P74" s="73">
         <f t="shared" si="82"/>
@@ -6934,7 +7049,7 @@
       </c>
       <c r="O75" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P75" s="73">
         <f t="shared" si="82"/>
@@ -7002,7 +7117,7 @@
       </c>
       <c r="O76" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P76" s="73">
         <f t="shared" si="82"/>
@@ -7070,7 +7185,7 @@
       </c>
       <c r="O77" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P77" s="73">
         <f t="shared" si="82"/>
@@ -7138,7 +7253,7 @@
       </c>
       <c r="O78" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P78" s="73">
         <f t="shared" si="82"/>
@@ -7206,7 +7321,7 @@
       </c>
       <c r="O79" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P79" s="73">
         <f t="shared" ref="P79:P83" si="89">SUM(G79:I79)/20</f>
@@ -7274,7 +7389,7 @@
       </c>
       <c r="O80" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P80" s="73">
         <f t="shared" si="89"/>
@@ -7342,7 +7457,7 @@
       </c>
       <c r="O81" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P81" s="73">
         <f t="shared" si="89"/>
@@ -7410,7 +7525,7 @@
       </c>
       <c r="O82" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P82" s="73">
         <f t="shared" si="89"/>
@@ -7478,7 +7593,7 @@
       </c>
       <c r="O83" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P83" s="73">
         <f t="shared" si="89"/>
@@ -7546,7 +7661,7 @@
       </c>
       <c r="O84" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P84" s="73">
         <f t="shared" ref="P84:P131" si="97">SUM(G84:I84)/20</f>
@@ -7614,7 +7729,7 @@
       </c>
       <c r="O85" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P85" s="73">
         <f t="shared" si="97"/>
@@ -7682,7 +7797,7 @@
       </c>
       <c r="O86" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P86" s="73">
         <f t="shared" si="97"/>
@@ -7750,7 +7865,7 @@
       </c>
       <c r="O87" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P87" s="73">
         <f t="shared" si="97"/>
@@ -7818,7 +7933,7 @@
       </c>
       <c r="O88" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P88" s="73">
         <f t="shared" si="97"/>
@@ -7886,7 +8001,7 @@
       </c>
       <c r="O89" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P89" s="73">
         <f t="shared" si="97"/>
@@ -7954,7 +8069,7 @@
       </c>
       <c r="O90" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P90" s="73">
         <f t="shared" si="97"/>
@@ -8022,7 +8137,7 @@
       </c>
       <c r="O91" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P91" s="73">
         <f t="shared" si="97"/>
@@ -8090,7 +8205,7 @@
       </c>
       <c r="O92" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P92" s="73">
         <f t="shared" si="97"/>
@@ -8158,7 +8273,7 @@
       </c>
       <c r="O93" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P93" s="73">
         <f t="shared" si="97"/>
@@ -8226,7 +8341,7 @@
       </c>
       <c r="O94" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P94" s="73">
         <f t="shared" si="97"/>
@@ -8294,7 +8409,7 @@
       </c>
       <c r="O95" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P95" s="73">
         <f t="shared" si="97"/>
@@ -8362,7 +8477,7 @@
       </c>
       <c r="O96" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P96" s="73">
         <f t="shared" si="97"/>
@@ -8430,7 +8545,7 @@
       </c>
       <c r="O97" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P97" s="73">
         <f t="shared" si="97"/>
@@ -8498,7 +8613,7 @@
       </c>
       <c r="O98" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P98" s="73">
         <f t="shared" si="97"/>
@@ -8566,7 +8681,7 @@
       </c>
       <c r="O99" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P99" s="73">
         <f t="shared" si="97"/>
@@ -8634,7 +8749,7 @@
       </c>
       <c r="O100" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P100" s="73">
         <f t="shared" si="97"/>
@@ -8702,7 +8817,7 @@
       </c>
       <c r="O101" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P101" s="73">
         <f t="shared" si="97"/>
@@ -8770,7 +8885,7 @@
       </c>
       <c r="O102" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P102" s="73">
         <f t="shared" si="97"/>
@@ -8838,7 +8953,7 @@
       </c>
       <c r="O103" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P103" s="73">
         <f t="shared" si="97"/>
@@ -8906,7 +9021,7 @@
       </c>
       <c r="O104" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P104" s="73">
         <f t="shared" si="97"/>
@@ -8974,7 +9089,7 @@
       </c>
       <c r="O105" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P105" s="73">
         <f t="shared" si="97"/>
@@ -9042,7 +9157,7 @@
       </c>
       <c r="O106" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P106" s="73">
         <f t="shared" si="97"/>
@@ -9110,7 +9225,7 @@
       </c>
       <c r="O107" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P107" s="73">
         <f t="shared" si="97"/>
@@ -9178,7 +9293,7 @@
       </c>
       <c r="O108" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P108" s="73">
         <f t="shared" si="97"/>
@@ -9246,7 +9361,7 @@
       </c>
       <c r="O109" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P109" s="73">
         <f t="shared" si="97"/>
@@ -9314,7 +9429,7 @@
       </c>
       <c r="O110" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P110" s="73">
         <f t="shared" si="97"/>
@@ -9382,7 +9497,7 @@
       </c>
       <c r="O111" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P111" s="73">
         <f t="shared" si="97"/>
@@ -9450,7 +9565,7 @@
       </c>
       <c r="O112" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P112" s="73">
         <f t="shared" si="97"/>
@@ -9518,7 +9633,7 @@
       </c>
       <c r="O113" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P113" s="73">
         <f t="shared" si="97"/>
@@ -9586,7 +9701,7 @@
       </c>
       <c r="O114" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P114" s="73">
         <f t="shared" si="97"/>
@@ -9654,7 +9769,7 @@
       </c>
       <c r="O115" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P115" s="73">
         <f t="shared" si="97"/>
@@ -9722,7 +9837,7 @@
       </c>
       <c r="O116" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P116" s="73">
         <f t="shared" si="97"/>
@@ -9790,7 +9905,7 @@
       </c>
       <c r="O117" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P117" s="73">
         <f t="shared" si="97"/>
@@ -9858,7 +9973,7 @@
       </c>
       <c r="O118" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P118" s="73">
         <f t="shared" si="97"/>
@@ -9926,7 +10041,7 @@
       </c>
       <c r="O119" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P119" s="73">
         <f t="shared" si="97"/>
@@ -9994,7 +10109,7 @@
       </c>
       <c r="O120" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P120" s="73">
         <f t="shared" si="97"/>
@@ -10062,7 +10177,7 @@
       </c>
       <c r="O121" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P121" s="73">
         <f t="shared" si="97"/>
@@ -10130,7 +10245,7 @@
       </c>
       <c r="O122" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P122" s="73">
         <f t="shared" si="97"/>
@@ -10198,7 +10313,7 @@
       </c>
       <c r="O123" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P123" s="73">
         <f t="shared" si="97"/>
@@ -10264,7 +10379,7 @@
       </c>
       <c r="O124" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P124" s="73">
         <f t="shared" si="97"/>
@@ -10330,7 +10445,7 @@
       </c>
       <c r="O125" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P125" s="73">
         <f t="shared" si="97"/>
@@ -10396,7 +10511,7 @@
       </c>
       <c r="O126" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P126" s="73">
         <f t="shared" si="97"/>
@@ -10462,7 +10577,7 @@
       </c>
       <c r="O127" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P127" s="73">
         <f t="shared" si="97"/>
@@ -10528,7 +10643,7 @@
       </c>
       <c r="O128" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P128" s="73">
         <f t="shared" si="97"/>
@@ -10594,7 +10709,7 @@
       </c>
       <c r="O129" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P129" s="73">
         <f t="shared" si="97"/>
@@ -10660,7 +10775,7 @@
       </c>
       <c r="O130" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P130" s="73">
         <f t="shared" si="97"/>
@@ -10726,7 +10841,7 @@
       </c>
       <c r="O131" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P131" s="73">
         <f t="shared" si="97"/>
@@ -10771,13 +10886,13 @@
     </row>
     <row r="132" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A132" s="78"/>
-      <c r="B132" s="151" t="s">
+      <c r="B132" s="164" t="s">
         <v>11</v>
       </c>
-      <c r="C132" s="152"/>
+      <c r="C132" s="165"/>
       <c r="D132" s="84">
         <f t="shared" ref="D132:L132" si="104">SUM(D6:D60)</f>
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="E132" s="84">
         <f t="shared" si="104"/>
@@ -10789,31 +10904,31 @@
       </c>
       <c r="G132" s="84">
         <f t="shared" si="104"/>
-        <v>0</v>
+        <v>758</v>
       </c>
       <c r="H132" s="84">
         <f t="shared" si="104"/>
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="I132" s="84">
         <f t="shared" si="104"/>
-        <v>0</v>
+        <v>799</v>
       </c>
       <c r="J132" s="84">
         <f t="shared" si="104"/>
-        <v>0</v>
+        <v>960</v>
       </c>
       <c r="K132" s="84">
         <f t="shared" si="104"/>
-        <v>0</v>
+        <v>840</v>
       </c>
       <c r="L132" s="84">
         <f t="shared" si="104"/>
-        <v>0</v>
+        <v>1278</v>
       </c>
       <c r="M132" s="48">
         <f t="shared" ref="M132:M135" si="105">SUM(D132:L132)/40</f>
-        <v>0</v>
+        <v>137.875</v>
       </c>
       <c r="N132" s="39">
         <f t="shared" si="18"/>
@@ -10821,15 +10936,15 @@
       </c>
       <c r="O132" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P132" s="73">
         <f t="shared" ref="P132:P136" si="106">SUM(G132:I132)/20</f>
-        <v>0</v>
+        <v>107.85</v>
       </c>
       <c r="Q132" s="40">
         <f t="shared" ref="Q132:Q136" si="107">SUM(J132:L132)/20</f>
-        <v>0</v>
+        <v>153.9</v>
       </c>
       <c r="R132" s="51" t="e">
         <f t="shared" si="4"/>
@@ -10925,7 +11040,7 @@
       </c>
       <c r="O134" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P134" s="73">
         <f t="shared" si="106"/>
@@ -10994,7 +11109,7 @@
       </c>
       <c r="O135" s="49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P135" s="73">
         <f t="shared" si="106"/>
@@ -11038,10 +11153,10 @@
       </c>
     </row>
     <row r="136" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B136" s="164" t="s">
+      <c r="B136" s="152" t="s">
         <v>71</v>
       </c>
-      <c r="C136" s="165"/>
+      <c r="C136" s="153"/>
       <c r="D136" s="83">
         <f>SUM(D134:D135)</f>
         <v>0</v>
@@ -11088,7 +11203,7 @@
       </c>
       <c r="O136" s="58">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62.470500000000001</v>
       </c>
       <c r="P136" s="73">
         <f t="shared" si="106"/>
@@ -11132,13 +11247,13 @@
       </c>
     </row>
     <row r="137" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B137" s="153" t="s">
+      <c r="B137" s="141" t="s">
         <v>11</v>
       </c>
-      <c r="C137" s="154"/>
+      <c r="C137" s="142"/>
       <c r="D137" s="85">
         <f>SUM(D132,D136)</f>
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="E137" s="85">
         <f t="shared" ref="E137:L137" si="112">SUM(E132,E136)</f>
@@ -11150,31 +11265,31 @@
       </c>
       <c r="G137" s="85">
         <f t="shared" si="112"/>
-        <v>0</v>
+        <v>758</v>
       </c>
       <c r="H137" s="85">
         <f t="shared" si="112"/>
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="I137" s="85">
         <f t="shared" si="112"/>
-        <v>0</v>
+        <v>799</v>
       </c>
       <c r="J137" s="85">
         <f t="shared" si="112"/>
-        <v>0</v>
+        <v>960</v>
       </c>
       <c r="K137" s="85">
         <f t="shared" si="112"/>
-        <v>0</v>
+        <v>840</v>
       </c>
       <c r="L137" s="85">
         <f t="shared" si="112"/>
-        <v>0</v>
+        <v>1278</v>
       </c>
       <c r="M137" s="60">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>137.875</v>
       </c>
       <c r="N137" s="63">
         <f>SUM(N5:N136)</f>
@@ -11182,15 +11297,15 @@
       </c>
       <c r="O137" s="61">
         <f t="shared" ref="O137:Y137" si="113">SUM(O5:O136)</f>
-        <v>0</v>
+        <v>8183.6355000000185</v>
       </c>
       <c r="P137" s="62">
         <f t="shared" si="113"/>
-        <v>0</v>
+        <v>221.7</v>
       </c>
       <c r="Q137" s="64">
         <f t="shared" si="113"/>
-        <v>0</v>
+        <v>311.8</v>
       </c>
       <c r="R137" s="65" t="e">
         <f t="shared" si="113"/>
@@ -11227,17 +11342,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="R3:U3"/>
+    <mergeCell ref="V3:Y3"/>
+    <mergeCell ref="B132:C132"/>
     <mergeCell ref="B137:C137"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="P2:Q2"/>
     <mergeCell ref="M3:O3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B136:C136"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="R3:U3"/>
-    <mergeCell ref="V3:Y3"/>
-    <mergeCell ref="B132:C132"/>
   </mergeCells>
   <conditionalFormatting sqref="C45:C59">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>

--- a/Aug_2026/daily Reports/LMT Orders.xlsx
+++ b/Aug_2026/daily Reports/LMT Orders.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0054EE2A-8D7E-4ACA-ABC8-CDCE69547342}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95D145A1-2F42-44A1-961C-E82EC9A71606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="98">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -1204,7 +1204,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="175">
+  <cellXfs count="174">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1484,9 +1484,6 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="1" fontId="7" fillId="2" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1570,6 +1567,42 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1607,42 +1640,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2021,7 +2018,7 @@
       <c r="D9" s="77" t="s">
         <v>35</v>
       </c>
-      <c r="E9" s="124" t="s">
+      <c r="E9" s="123" t="s">
         <v>14</v>
       </c>
       <c r="F9" s="92" t="s">
@@ -2038,7 +2035,7 @@
       <c r="D10" s="88">
         <v>3520247902365</v>
       </c>
-      <c r="E10" s="125"/>
+      <c r="E10" s="124"/>
       <c r="F10">
         <v>10000</v>
       </c>
@@ -2049,7 +2046,7 @@
       </c>
       <c r="C11" s="79"/>
       <c r="D11" s="79"/>
-      <c r="E11" s="125"/>
+      <c r="E11" s="124"/>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B12" s="79" t="s">
@@ -2061,7 +2058,7 @@
       <c r="D12" s="88">
         <v>300426949714</v>
       </c>
-      <c r="E12" s="125"/>
+      <c r="E12" s="124"/>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B13" s="79" t="s">
@@ -2073,7 +2070,7 @@
       <c r="D13" s="88">
         <v>3277876126916</v>
       </c>
-      <c r="E13" s="125"/>
+      <c r="E13" s="124"/>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B14" s="79" t="s">
@@ -2085,7 +2082,7 @@
       <c r="D14" s="88">
         <v>3520255124113</v>
       </c>
-      <c r="E14" s="125"/>
+      <c r="E14" s="124"/>
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B15" s="79" t="s">
@@ -2097,7 +2094,7 @@
       <c r="D15" s="88">
         <v>3520255124113</v>
       </c>
-      <c r="E15" s="125"/>
+      <c r="E15" s="124"/>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B16" s="79" t="s">
@@ -2109,7 +2106,7 @@
       <c r="D16" s="88">
         <v>3520268948847</v>
       </c>
-      <c r="E16" s="125"/>
+      <c r="E16" s="124"/>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B17" s="79" t="s">
@@ -2119,7 +2116,7 @@
         <v>44</v>
       </c>
       <c r="D17" s="79"/>
-      <c r="E17" s="125"/>
+      <c r="E17" s="124"/>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B18" s="79" t="s">
@@ -2131,63 +2128,63 @@
       <c r="D18" s="79" t="s">
         <v>45</v>
       </c>
-      <c r="E18" s="125"/>
+      <c r="E18" s="124"/>
     </row>
     <row r="19" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="126" t="s">
+      <c r="B19" s="125" t="s">
         <v>54</v>
       </c>
-      <c r="C19" s="125" t="s">
+      <c r="C19" s="124" t="s">
         <v>55</v>
       </c>
-      <c r="D19" s="125"/>
-      <c r="E19" s="125"/>
+      <c r="D19" s="124"/>
+      <c r="E19" s="124"/>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B20" s="126" t="s">
+      <c r="B20" s="125" t="s">
         <v>56</v>
       </c>
-      <c r="C20" s="125"/>
-      <c r="D20" s="125"/>
-      <c r="E20" s="125"/>
+      <c r="C20" s="124"/>
+      <c r="D20" s="124"/>
+      <c r="E20" s="124"/>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B21" s="126" t="s">
+      <c r="B21" s="125" t="s">
         <v>57</v>
       </c>
-      <c r="C21" s="125"/>
-      <c r="D21" s="125"/>
-      <c r="E21" s="125"/>
+      <c r="C21" s="124"/>
+      <c r="D21" s="124"/>
+      <c r="E21" s="124"/>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B22" s="126" t="s">
+      <c r="B22" s="125" t="s">
         <v>58</v>
       </c>
-      <c r="C22" s="125"/>
-      <c r="D22" s="125"/>
-      <c r="E22" s="125"/>
+      <c r="C22" s="124"/>
+      <c r="D22" s="124"/>
+      <c r="E22" s="124"/>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B23" s="126" t="s">
+      <c r="B23" s="125" t="s">
         <v>65</v>
       </c>
-      <c r="C23" s="125" t="s">
+      <c r="C23" s="124" t="s">
         <v>66</v>
       </c>
-      <c r="D23" s="127">
+      <c r="D23" s="126">
         <v>3277876231301</v>
       </c>
-      <c r="E23" s="125"/>
+      <c r="E23" s="124"/>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B24" s="126" t="s">
+      <c r="B24" s="125" t="s">
         <v>77</v>
       </c>
-      <c r="C24" s="125" t="s">
+      <c r="C24" s="124" t="s">
         <v>78</v>
       </c>
-      <c r="D24" s="125"/>
-      <c r="E24" s="125" t="s">
+      <c r="D24" s="124"/>
+      <c r="E24" s="124" t="s">
         <v>79</v>
       </c>
     </row>
@@ -2207,14 +2204,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="154">
+      <c r="B1" s="140">
         <f ca="1">TODAY()</f>
-        <v>46240</v>
-      </c>
-      <c r="C1" s="154"/>
-      <c r="D1" s="154"/>
-      <c r="E1" s="154"/>
-      <c r="F1" s="154"/>
+        <v>46241</v>
+      </c>
+      <c r="C1" s="140"/>
+      <c r="D1" s="140"/>
+      <c r="E1" s="140"/>
+      <c r="F1" s="140"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
       <c r="I1" s="10"/>
@@ -2236,10 +2233,10 @@
       <c r="Y1" s="10"/>
     </row>
     <row r="2" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="151" t="s">
+      <c r="A2" s="162" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="155" t="s">
+      <c r="B2" s="141" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2272,13 +2269,13 @@
       <c r="L2" s="15">
         <v>120</v>
       </c>
-      <c r="M2" s="143"/>
-      <c r="N2" s="144"/>
-      <c r="O2" s="145"/>
-      <c r="P2" s="146" t="s">
+      <c r="M2" s="154"/>
+      <c r="N2" s="155"/>
+      <c r="O2" s="156"/>
+      <c r="P2" s="157" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="147"/>
+      <c r="Q2" s="158"/>
       <c r="R2" s="18">
         <v>0.05</v>
       </c>
@@ -2297,8 +2294,8 @@
       <c r="Y2" s="20"/>
     </row>
     <row r="3" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="151"/>
-      <c r="B3" s="156"/>
+      <c r="A3" s="162"/>
+      <c r="B3" s="142"/>
       <c r="C3" s="23" t="s">
         <v>15</v>
       </c>
@@ -2329,29 +2326,29 @@
       <c r="L3" s="29">
         <v>72.64</v>
       </c>
-      <c r="M3" s="148" t="s">
+      <c r="M3" s="159" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="149"/>
-      <c r="O3" s="150"/>
+      <c r="N3" s="160"/>
+      <c r="O3" s="161"/>
       <c r="P3" s="71"/>
       <c r="Q3" s="72"/>
-      <c r="R3" s="158" t="s">
+      <c r="R3" s="144" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="159"/>
-      <c r="T3" s="159"/>
-      <c r="U3" s="160"/>
-      <c r="V3" s="161" t="s">
+      <c r="S3" s="145"/>
+      <c r="T3" s="145"/>
+      <c r="U3" s="146"/>
+      <c r="V3" s="147" t="s">
         <v>17</v>
       </c>
-      <c r="W3" s="162"/>
-      <c r="X3" s="162"/>
-      <c r="Y3" s="163"/>
+      <c r="W3" s="148"/>
+      <c r="X3" s="148"/>
+      <c r="Y3" s="149"/>
     </row>
     <row r="4" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="151"/>
-      <c r="B4" s="157"/>
+      <c r="A4" s="162"/>
+      <c r="B4" s="143"/>
       <c r="C4" s="30" t="s">
         <v>18</v>
       </c>
@@ -2429,22 +2426,22 @@
       <c r="B5" s="36">
         <v>1</v>
       </c>
-      <c r="C5" s="131" t="s">
+      <c r="C5" s="130" t="s">
         <v>96</v>
       </c>
-      <c r="D5" s="132"/>
-      <c r="E5" s="133"/>
+      <c r="D5" s="131"/>
+      <c r="E5" s="132"/>
       <c r="F5" s="38"/>
-      <c r="G5" s="134"/>
-      <c r="H5" s="133"/>
+      <c r="G5" s="133"/>
+      <c r="H5" s="132"/>
       <c r="I5" s="38">
         <v>120</v>
       </c>
-      <c r="J5" s="134"/>
-      <c r="K5" s="133">
+      <c r="J5" s="133"/>
+      <c r="K5" s="132">
         <v>40</v>
       </c>
-      <c r="L5" s="135">
+      <c r="L5" s="134">
         <v>40</v>
       </c>
       <c r="M5" s="37">
@@ -2993,23 +2990,35 @@
       </c>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A12" s="78"/>
+      <c r="A12" s="78">
+        <v>46240</v>
+      </c>
       <c r="B12" s="47">
         <v>8</v>
       </c>
-      <c r="C12" s="57"/>
-      <c r="D12" s="74"/>
+      <c r="C12" s="57" t="s">
+        <v>70</v>
+      </c>
+      <c r="D12" s="74">
+        <v>1600</v>
+      </c>
       <c r="E12" s="75"/>
       <c r="F12" s="76"/>
       <c r="G12" s="50"/>
       <c r="H12" s="75"/>
       <c r="I12" s="49"/>
-      <c r="J12" s="50"/>
-      <c r="K12" s="75"/>
-      <c r="L12" s="76"/>
+      <c r="J12" s="50">
+        <v>600</v>
+      </c>
+      <c r="K12" s="75">
+        <v>800</v>
+      </c>
+      <c r="L12" s="76">
+        <v>1000</v>
+      </c>
       <c r="M12" s="48">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N12" s="39">
         <f t="shared" si="18"/>
@@ -3025,7 +3034,7 @@
       </c>
       <c r="Q12" s="40">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="R12" s="51" t="e">
         <f t="shared" si="4"/>
@@ -5865,11 +5874,11 @@
       <c r="F57" s="75"/>
       <c r="G57" s="75"/>
       <c r="H57" s="75"/>
-      <c r="I57" s="128"/>
+      <c r="I57" s="127"/>
       <c r="J57" s="75"/>
       <c r="K57" s="75"/>
       <c r="L57" s="75"/>
-      <c r="M57" s="130">
+      <c r="M57" s="129">
         <f t="shared" si="76"/>
         <v>0</v>
       </c>
@@ -5915,11 +5924,11 @@
       <c r="F58" s="75"/>
       <c r="G58" s="75"/>
       <c r="H58" s="75"/>
-      <c r="I58" s="128"/>
+      <c r="I58" s="127"/>
       <c r="J58" s="75"/>
       <c r="K58" s="75"/>
       <c r="L58" s="75"/>
-      <c r="M58" s="130">
+      <c r="M58" s="129">
         <f t="shared" si="76"/>
         <v>0</v>
       </c>
@@ -5965,11 +5974,11 @@
       <c r="F59" s="75"/>
       <c r="G59" s="75"/>
       <c r="H59" s="75"/>
-      <c r="I59" s="128"/>
+      <c r="I59" s="127"/>
       <c r="J59" s="75"/>
       <c r="K59" s="75"/>
       <c r="L59" s="75"/>
-      <c r="M59" s="130">
+      <c r="M59" s="129">
         <f t="shared" si="76"/>
         <v>0</v>
       </c>
@@ -6015,11 +6024,11 @@
       <c r="F60" s="75"/>
       <c r="G60" s="75"/>
       <c r="H60" s="75"/>
-      <c r="I60" s="128"/>
+      <c r="I60" s="127"/>
       <c r="J60" s="75"/>
       <c r="K60" s="75"/>
       <c r="L60" s="75"/>
-      <c r="M60" s="130">
+      <c r="M60" s="129">
         <f t="shared" si="52"/>
         <v>0</v>
       </c>
@@ -6077,17 +6086,17 @@
       <c r="B61" s="47">
         <v>57</v>
       </c>
-      <c r="C61" s="129"/>
+      <c r="C61" s="128"/>
       <c r="D61" s="75"/>
       <c r="E61" s="75"/>
       <c r="F61" s="75"/>
       <c r="G61" s="75"/>
       <c r="H61" s="75"/>
-      <c r="I61" s="128"/>
+      <c r="I61" s="127"/>
       <c r="J61" s="75"/>
       <c r="K61" s="75"/>
       <c r="L61" s="75"/>
-      <c r="M61" s="130">
+      <c r="M61" s="129">
         <f t="shared" ref="M61:M83" si="81">SUM(D61:L61)/40</f>
         <v>0</v>
       </c>
@@ -6145,17 +6154,17 @@
       <c r="B62" s="47">
         <v>58</v>
       </c>
-      <c r="C62" s="129"/>
+      <c r="C62" s="128"/>
       <c r="D62" s="75"/>
       <c r="E62" s="75"/>
       <c r="F62" s="75"/>
       <c r="G62" s="75"/>
       <c r="H62" s="75"/>
-      <c r="I62" s="128"/>
+      <c r="I62" s="127"/>
       <c r="J62" s="75"/>
       <c r="K62" s="75"/>
       <c r="L62" s="75"/>
-      <c r="M62" s="130">
+      <c r="M62" s="129">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
@@ -6213,17 +6222,17 @@
       <c r="B63" s="47">
         <v>59</v>
       </c>
-      <c r="C63" s="129"/>
+      <c r="C63" s="128"/>
       <c r="D63" s="75"/>
       <c r="E63" s="75"/>
       <c r="F63" s="75"/>
       <c r="G63" s="75"/>
       <c r="H63" s="75"/>
-      <c r="I63" s="128"/>
+      <c r="I63" s="127"/>
       <c r="J63" s="75"/>
       <c r="K63" s="75"/>
       <c r="L63" s="75"/>
-      <c r="M63" s="130">
+      <c r="M63" s="129">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
@@ -6281,17 +6290,17 @@
       <c r="B64" s="47">
         <v>60</v>
       </c>
-      <c r="C64" s="129"/>
+      <c r="C64" s="128"/>
       <c r="D64" s="75"/>
       <c r="E64" s="75"/>
       <c r="F64" s="75"/>
       <c r="G64" s="75"/>
       <c r="H64" s="75"/>
-      <c r="I64" s="128"/>
+      <c r="I64" s="127"/>
       <c r="J64" s="75"/>
       <c r="K64" s="75"/>
       <c r="L64" s="75"/>
-      <c r="M64" s="130">
+      <c r="M64" s="129">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
@@ -6349,17 +6358,17 @@
       <c r="B65" s="47">
         <v>61</v>
       </c>
-      <c r="C65" s="129"/>
+      <c r="C65" s="128"/>
       <c r="D65" s="75"/>
       <c r="E65" s="75"/>
       <c r="F65" s="75"/>
       <c r="G65" s="75"/>
       <c r="H65" s="75"/>
-      <c r="I65" s="128"/>
+      <c r="I65" s="127"/>
       <c r="J65" s="75"/>
       <c r="K65" s="75"/>
       <c r="L65" s="75"/>
-      <c r="M65" s="130">
+      <c r="M65" s="129">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
@@ -6417,17 +6426,17 @@
       <c r="B66" s="47">
         <v>62</v>
       </c>
-      <c r="C66" s="129"/>
+      <c r="C66" s="128"/>
       <c r="D66" s="75"/>
       <c r="E66" s="75"/>
       <c r="F66" s="75"/>
       <c r="G66" s="75"/>
       <c r="H66" s="75"/>
-      <c r="I66" s="128"/>
+      <c r="I66" s="127"/>
       <c r="J66" s="75"/>
       <c r="K66" s="75"/>
       <c r="L66" s="75"/>
-      <c r="M66" s="130">
+      <c r="M66" s="129">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
@@ -6485,17 +6494,17 @@
       <c r="B67" s="47">
         <v>63</v>
       </c>
-      <c r="C67" s="129"/>
+      <c r="C67" s="128"/>
       <c r="D67" s="75"/>
       <c r="E67" s="75"/>
       <c r="F67" s="75"/>
       <c r="G67" s="75"/>
       <c r="H67" s="75"/>
-      <c r="I67" s="128"/>
+      <c r="I67" s="127"/>
       <c r="J67" s="75"/>
       <c r="K67" s="75"/>
       <c r="L67" s="75"/>
-      <c r="M67" s="130">
+      <c r="M67" s="129">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
@@ -6553,17 +6562,17 @@
       <c r="B68" s="47">
         <v>64</v>
       </c>
-      <c r="C68" s="129"/>
+      <c r="C68" s="128"/>
       <c r="D68" s="75"/>
       <c r="E68" s="75"/>
       <c r="F68" s="75"/>
       <c r="G68" s="75"/>
       <c r="H68" s="75"/>
-      <c r="I68" s="128"/>
+      <c r="I68" s="127"/>
       <c r="J68" s="75"/>
       <c r="K68" s="75"/>
       <c r="L68" s="75"/>
-      <c r="M68" s="130">
+      <c r="M68" s="129">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
@@ -6621,17 +6630,17 @@
       <c r="B69" s="47">
         <v>65</v>
       </c>
-      <c r="C69" s="129"/>
+      <c r="C69" s="128"/>
       <c r="D69" s="75"/>
       <c r="E69" s="75"/>
       <c r="F69" s="75"/>
       <c r="G69" s="75"/>
       <c r="H69" s="75"/>
-      <c r="I69" s="128"/>
+      <c r="I69" s="127"/>
       <c r="J69" s="75"/>
       <c r="K69" s="75"/>
       <c r="L69" s="75"/>
-      <c r="M69" s="130">
+      <c r="M69" s="129">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
@@ -6689,17 +6698,17 @@
       <c r="B70" s="47">
         <v>66</v>
       </c>
-      <c r="C70" s="129"/>
+      <c r="C70" s="128"/>
       <c r="D70" s="75"/>
       <c r="E70" s="75"/>
       <c r="F70" s="75"/>
       <c r="G70" s="75"/>
       <c r="H70" s="75"/>
-      <c r="I70" s="128"/>
+      <c r="I70" s="127"/>
       <c r="J70" s="75"/>
       <c r="K70" s="75"/>
       <c r="L70" s="75"/>
-      <c r="M70" s="130">
+      <c r="M70" s="129">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
@@ -6757,17 +6766,17 @@
       <c r="B71" s="47">
         <v>67</v>
       </c>
-      <c r="C71" s="129"/>
+      <c r="C71" s="128"/>
       <c r="D71" s="75"/>
       <c r="E71" s="75"/>
       <c r="F71" s="75"/>
       <c r="G71" s="75"/>
       <c r="H71" s="75"/>
-      <c r="I71" s="128"/>
+      <c r="I71" s="127"/>
       <c r="J71" s="75"/>
       <c r="K71" s="75"/>
       <c r="L71" s="75"/>
-      <c r="M71" s="130">
+      <c r="M71" s="129">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
@@ -6825,17 +6834,17 @@
       <c r="B72" s="47">
         <v>68</v>
       </c>
-      <c r="C72" s="129"/>
+      <c r="C72" s="128"/>
       <c r="D72" s="75"/>
       <c r="E72" s="75"/>
       <c r="F72" s="75"/>
       <c r="G72" s="75"/>
       <c r="H72" s="75"/>
-      <c r="I72" s="128"/>
+      <c r="I72" s="127"/>
       <c r="J72" s="75"/>
       <c r="K72" s="75"/>
       <c r="L72" s="75"/>
-      <c r="M72" s="130">
+      <c r="M72" s="129">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
@@ -6893,17 +6902,17 @@
       <c r="B73" s="47">
         <v>69</v>
       </c>
-      <c r="C73" s="129"/>
+      <c r="C73" s="128"/>
       <c r="D73" s="75"/>
       <c r="E73" s="75"/>
       <c r="F73" s="75"/>
       <c r="G73" s="75"/>
       <c r="H73" s="75"/>
-      <c r="I73" s="128"/>
+      <c r="I73" s="127"/>
       <c r="J73" s="75"/>
       <c r="K73" s="75"/>
       <c r="L73" s="75"/>
-      <c r="M73" s="130">
+      <c r="M73" s="129">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
@@ -6961,17 +6970,17 @@
       <c r="B74" s="47">
         <v>70</v>
       </c>
-      <c r="C74" s="140"/>
+      <c r="C74" s="139"/>
       <c r="D74" s="75"/>
       <c r="E74" s="75"/>
       <c r="F74" s="50"/>
       <c r="G74" s="75"/>
       <c r="H74" s="75"/>
-      <c r="I74" s="128"/>
+      <c r="I74" s="127"/>
       <c r="J74" s="75"/>
       <c r="K74" s="75"/>
       <c r="L74" s="75"/>
-      <c r="M74" s="130">
+      <c r="M74" s="129">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
@@ -7029,17 +7038,17 @@
       <c r="B75" s="47">
         <v>71</v>
       </c>
-      <c r="C75" s="140"/>
+      <c r="C75" s="139"/>
       <c r="D75" s="75"/>
       <c r="E75" s="50"/>
       <c r="F75" s="50"/>
       <c r="G75" s="75"/>
       <c r="H75" s="75"/>
-      <c r="I75" s="128"/>
+      <c r="I75" s="127"/>
       <c r="J75" s="75"/>
       <c r="K75" s="75"/>
       <c r="L75" s="75"/>
-      <c r="M75" s="130">
+      <c r="M75" s="129">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
@@ -7097,17 +7106,17 @@
       <c r="B76" s="47">
         <v>72</v>
       </c>
-      <c r="C76" s="140"/>
+      <c r="C76" s="139"/>
       <c r="D76" s="75"/>
       <c r="E76" s="50"/>
       <c r="F76" s="50"/>
       <c r="G76" s="75"/>
       <c r="H76" s="75"/>
-      <c r="I76" s="128"/>
+      <c r="I76" s="127"/>
       <c r="J76" s="75"/>
       <c r="K76" s="75"/>
       <c r="L76" s="75"/>
-      <c r="M76" s="130">
+      <c r="M76" s="129">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
@@ -7165,17 +7174,17 @@
       <c r="B77" s="47">
         <v>73</v>
       </c>
-      <c r="C77" s="140"/>
+      <c r="C77" s="139"/>
       <c r="D77" s="75"/>
       <c r="E77" s="50"/>
       <c r="F77" s="50"/>
       <c r="G77" s="50"/>
       <c r="H77" s="50"/>
-      <c r="I77" s="130"/>
+      <c r="I77" s="129"/>
       <c r="J77" s="50"/>
       <c r="K77" s="50"/>
       <c r="L77" s="50"/>
-      <c r="M77" s="130">
+      <c r="M77" s="129">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
@@ -7233,17 +7242,17 @@
       <c r="B78" s="47">
         <v>74</v>
       </c>
-      <c r="C78" s="140"/>
+      <c r="C78" s="139"/>
       <c r="D78" s="75"/>
       <c r="E78" s="50"/>
       <c r="F78" s="50"/>
       <c r="G78" s="50"/>
       <c r="H78" s="50"/>
-      <c r="I78" s="130"/>
+      <c r="I78" s="129"/>
       <c r="J78" s="50"/>
       <c r="K78" s="50"/>
       <c r="L78" s="50"/>
-      <c r="M78" s="130">
+      <c r="M78" s="129">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
@@ -7301,17 +7310,17 @@
       <c r="B79" s="47">
         <v>75</v>
       </c>
-      <c r="C79" s="129"/>
+      <c r="C79" s="128"/>
       <c r="D79" s="50"/>
       <c r="E79" s="50"/>
       <c r="F79" s="50"/>
       <c r="G79" s="50"/>
       <c r="H79" s="50"/>
-      <c r="I79" s="130"/>
+      <c r="I79" s="129"/>
       <c r="J79" s="50"/>
       <c r="K79" s="50"/>
       <c r="L79" s="50"/>
-      <c r="M79" s="130">
+      <c r="M79" s="129">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
@@ -7369,17 +7378,17 @@
       <c r="B80" s="47">
         <v>76</v>
       </c>
-      <c r="C80" s="129"/>
+      <c r="C80" s="128"/>
       <c r="D80" s="50"/>
       <c r="E80" s="50"/>
       <c r="F80" s="50"/>
       <c r="G80" s="50"/>
       <c r="H80" s="50"/>
-      <c r="I80" s="130"/>
+      <c r="I80" s="129"/>
       <c r="J80" s="50"/>
       <c r="K80" s="50"/>
       <c r="L80" s="50"/>
-      <c r="M80" s="130">
+      <c r="M80" s="129">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
@@ -7437,17 +7446,17 @@
       <c r="B81" s="47">
         <v>77</v>
       </c>
-      <c r="C81" s="129"/>
+      <c r="C81" s="128"/>
       <c r="D81" s="50"/>
       <c r="E81" s="50"/>
       <c r="F81" s="50"/>
       <c r="G81" s="50"/>
       <c r="H81" s="50"/>
-      <c r="I81" s="130"/>
+      <c r="I81" s="129"/>
       <c r="J81" s="50"/>
       <c r="K81" s="50"/>
       <c r="L81" s="50"/>
-      <c r="M81" s="130">
+      <c r="M81" s="129">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
@@ -7505,17 +7514,17 @@
       <c r="B82" s="47">
         <v>78</v>
       </c>
-      <c r="C82" s="129"/>
+      <c r="C82" s="128"/>
       <c r="D82" s="50"/>
       <c r="E82" s="50"/>
       <c r="F82" s="50"/>
       <c r="G82" s="50"/>
       <c r="H82" s="50"/>
-      <c r="I82" s="130"/>
+      <c r="I82" s="129"/>
       <c r="J82" s="50"/>
       <c r="K82" s="50"/>
       <c r="L82" s="50"/>
-      <c r="M82" s="130">
+      <c r="M82" s="129">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
@@ -7573,17 +7582,17 @@
       <c r="B83" s="47">
         <v>79</v>
       </c>
-      <c r="C83" s="129"/>
+      <c r="C83" s="128"/>
       <c r="D83" s="50"/>
       <c r="E83" s="50"/>
       <c r="F83" s="50"/>
       <c r="G83" s="50"/>
       <c r="H83" s="50"/>
-      <c r="I83" s="130"/>
+      <c r="I83" s="129"/>
       <c r="J83" s="50"/>
       <c r="K83" s="50"/>
       <c r="L83" s="50"/>
-      <c r="M83" s="130">
+      <c r="M83" s="129">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
@@ -7641,17 +7650,17 @@
       <c r="B84" s="47">
         <v>80</v>
       </c>
-      <c r="C84" s="129"/>
+      <c r="C84" s="128"/>
       <c r="D84" s="50"/>
       <c r="E84" s="50"/>
       <c r="F84" s="50"/>
       <c r="G84" s="50"/>
       <c r="H84" s="50"/>
-      <c r="I84" s="130"/>
+      <c r="I84" s="129"/>
       <c r="J84" s="50"/>
       <c r="K84" s="50"/>
       <c r="L84" s="50"/>
-      <c r="M84" s="130">
+      <c r="M84" s="129">
         <f t="shared" ref="M84:M131" si="96">SUM(D84:L84)/40</f>
         <v>0</v>
       </c>
@@ -7709,17 +7718,17 @@
       <c r="B85" s="47">
         <v>81</v>
       </c>
-      <c r="C85" s="129"/>
+      <c r="C85" s="128"/>
       <c r="D85" s="50"/>
       <c r="E85" s="50"/>
       <c r="F85" s="50"/>
       <c r="G85" s="50"/>
       <c r="H85" s="50"/>
-      <c r="I85" s="130"/>
+      <c r="I85" s="129"/>
       <c r="J85" s="50"/>
       <c r="K85" s="50"/>
       <c r="L85" s="50"/>
-      <c r="M85" s="130">
+      <c r="M85" s="129">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -7777,17 +7786,17 @@
       <c r="B86" s="47">
         <v>82</v>
       </c>
-      <c r="C86" s="129"/>
+      <c r="C86" s="128"/>
       <c r="D86" s="50"/>
       <c r="E86" s="50"/>
       <c r="F86" s="50"/>
       <c r="G86" s="50"/>
       <c r="H86" s="50"/>
-      <c r="I86" s="130"/>
+      <c r="I86" s="129"/>
       <c r="J86" s="50"/>
       <c r="K86" s="50"/>
       <c r="L86" s="50"/>
-      <c r="M86" s="130">
+      <c r="M86" s="129">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -7845,17 +7854,17 @@
       <c r="B87" s="47">
         <v>83</v>
       </c>
-      <c r="C87" s="129"/>
+      <c r="C87" s="128"/>
       <c r="D87" s="50"/>
       <c r="E87" s="50"/>
       <c r="F87" s="50"/>
       <c r="G87" s="50"/>
       <c r="H87" s="50"/>
-      <c r="I87" s="130"/>
+      <c r="I87" s="129"/>
       <c r="J87" s="50"/>
       <c r="K87" s="50"/>
       <c r="L87" s="50"/>
-      <c r="M87" s="130">
+      <c r="M87" s="129">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -7913,17 +7922,17 @@
       <c r="B88" s="47">
         <v>84</v>
       </c>
-      <c r="C88" s="129"/>
+      <c r="C88" s="128"/>
       <c r="D88" s="50"/>
       <c r="E88" s="50"/>
       <c r="F88" s="50"/>
       <c r="G88" s="50"/>
       <c r="H88" s="50"/>
-      <c r="I88" s="130"/>
+      <c r="I88" s="129"/>
       <c r="J88" s="50"/>
       <c r="K88" s="50"/>
       <c r="L88" s="50"/>
-      <c r="M88" s="130">
+      <c r="M88" s="129">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -7981,17 +7990,17 @@
       <c r="B89" s="47">
         <v>85</v>
       </c>
-      <c r="C89" s="129"/>
+      <c r="C89" s="128"/>
       <c r="D89" s="50"/>
       <c r="E89" s="50"/>
       <c r="F89" s="50"/>
       <c r="G89" s="50"/>
       <c r="H89" s="50"/>
-      <c r="I89" s="130"/>
+      <c r="I89" s="129"/>
       <c r="J89" s="50"/>
       <c r="K89" s="50"/>
       <c r="L89" s="50"/>
-      <c r="M89" s="130">
+      <c r="M89" s="129">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -8049,17 +8058,17 @@
       <c r="B90" s="47">
         <v>86</v>
       </c>
-      <c r="C90" s="129"/>
+      <c r="C90" s="128"/>
       <c r="D90" s="50"/>
       <c r="E90" s="50"/>
       <c r="F90" s="50"/>
       <c r="G90" s="50"/>
       <c r="H90" s="50"/>
-      <c r="I90" s="130"/>
+      <c r="I90" s="129"/>
       <c r="J90" s="50"/>
       <c r="K90" s="50"/>
       <c r="L90" s="50"/>
-      <c r="M90" s="130">
+      <c r="M90" s="129">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -8117,17 +8126,17 @@
       <c r="B91" s="47">
         <v>87</v>
       </c>
-      <c r="C91" s="129"/>
+      <c r="C91" s="128"/>
       <c r="D91" s="50"/>
       <c r="E91" s="50"/>
       <c r="F91" s="50"/>
       <c r="G91" s="50"/>
       <c r="H91" s="50"/>
-      <c r="I91" s="130"/>
+      <c r="I91" s="129"/>
       <c r="J91" s="50"/>
       <c r="K91" s="50"/>
       <c r="L91" s="50"/>
-      <c r="M91" s="130">
+      <c r="M91" s="129">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -8185,17 +8194,17 @@
       <c r="B92" s="47">
         <v>88</v>
       </c>
-      <c r="C92" s="129"/>
+      <c r="C92" s="128"/>
       <c r="D92" s="50"/>
       <c r="E92" s="50"/>
       <c r="F92" s="50"/>
       <c r="G92" s="50"/>
       <c r="H92" s="50"/>
-      <c r="I92" s="130"/>
+      <c r="I92" s="129"/>
       <c r="J92" s="50"/>
       <c r="K92" s="50"/>
       <c r="L92" s="50"/>
-      <c r="M92" s="130">
+      <c r="M92" s="129">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -8253,17 +8262,17 @@
       <c r="B93" s="47">
         <v>89</v>
       </c>
-      <c r="C93" s="129"/>
+      <c r="C93" s="128"/>
       <c r="D93" s="50"/>
       <c r="E93" s="50"/>
       <c r="F93" s="50"/>
       <c r="G93" s="50"/>
       <c r="H93" s="50"/>
-      <c r="I93" s="130"/>
+      <c r="I93" s="129"/>
       <c r="J93" s="50"/>
       <c r="K93" s="50"/>
       <c r="L93" s="50"/>
-      <c r="M93" s="130">
+      <c r="M93" s="129">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -8321,17 +8330,17 @@
       <c r="B94" s="47">
         <v>90</v>
       </c>
-      <c r="C94" s="129"/>
+      <c r="C94" s="128"/>
       <c r="D94" s="50"/>
       <c r="E94" s="50"/>
       <c r="F94" s="50"/>
       <c r="G94" s="50"/>
       <c r="H94" s="50"/>
-      <c r="I94" s="130"/>
+      <c r="I94" s="129"/>
       <c r="J94" s="50"/>
       <c r="K94" s="50"/>
       <c r="L94" s="50"/>
-      <c r="M94" s="130">
+      <c r="M94" s="129">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -8389,17 +8398,17 @@
       <c r="B95" s="47">
         <v>91</v>
       </c>
-      <c r="C95" s="129"/>
+      <c r="C95" s="128"/>
       <c r="D95" s="50"/>
       <c r="E95" s="50"/>
       <c r="F95" s="50"/>
       <c r="G95" s="50"/>
       <c r="H95" s="50"/>
-      <c r="I95" s="130"/>
+      <c r="I95" s="129"/>
       <c r="J95" s="50"/>
       <c r="K95" s="50"/>
       <c r="L95" s="50"/>
-      <c r="M95" s="130">
+      <c r="M95" s="129">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -8457,17 +8466,17 @@
       <c r="B96" s="47">
         <v>92</v>
       </c>
-      <c r="C96" s="129"/>
+      <c r="C96" s="128"/>
       <c r="D96" s="50"/>
       <c r="E96" s="50"/>
       <c r="F96" s="50"/>
       <c r="G96" s="50"/>
       <c r="H96" s="50"/>
-      <c r="I96" s="130"/>
+      <c r="I96" s="129"/>
       <c r="J96" s="50"/>
       <c r="K96" s="50"/>
       <c r="L96" s="50"/>
-      <c r="M96" s="130">
+      <c r="M96" s="129">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -8525,17 +8534,17 @@
       <c r="B97" s="47">
         <v>93</v>
       </c>
-      <c r="C97" s="129"/>
+      <c r="C97" s="128"/>
       <c r="D97" s="50"/>
       <c r="E97" s="50"/>
       <c r="F97" s="50"/>
       <c r="G97" s="50"/>
       <c r="H97" s="50"/>
-      <c r="I97" s="130"/>
+      <c r="I97" s="129"/>
       <c r="J97" s="50"/>
       <c r="K97" s="50"/>
       <c r="L97" s="50"/>
-      <c r="M97" s="130">
+      <c r="M97" s="129">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -8593,17 +8602,17 @@
       <c r="B98" s="47">
         <v>94</v>
       </c>
-      <c r="C98" s="129"/>
+      <c r="C98" s="128"/>
       <c r="D98" s="50"/>
       <c r="E98" s="50"/>
       <c r="F98" s="50"/>
       <c r="G98" s="50"/>
       <c r="H98" s="50"/>
-      <c r="I98" s="130"/>
+      <c r="I98" s="129"/>
       <c r="J98" s="50"/>
       <c r="K98" s="50"/>
       <c r="L98" s="50"/>
-      <c r="M98" s="130">
+      <c r="M98" s="129">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -8661,17 +8670,17 @@
       <c r="B99" s="47">
         <v>95</v>
       </c>
-      <c r="C99" s="129"/>
+      <c r="C99" s="128"/>
       <c r="D99" s="50"/>
       <c r="E99" s="50"/>
       <c r="F99" s="50"/>
       <c r="G99" s="50"/>
       <c r="H99" s="50"/>
-      <c r="I99" s="130"/>
+      <c r="I99" s="129"/>
       <c r="J99" s="50"/>
       <c r="K99" s="50"/>
       <c r="L99" s="50"/>
-      <c r="M99" s="130">
+      <c r="M99" s="129">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -8729,17 +8738,17 @@
       <c r="B100" s="47">
         <v>96</v>
       </c>
-      <c r="C100" s="129"/>
+      <c r="C100" s="128"/>
       <c r="D100" s="50"/>
       <c r="E100" s="50"/>
       <c r="F100" s="50"/>
       <c r="G100" s="50"/>
       <c r="H100" s="50"/>
-      <c r="I100" s="130"/>
+      <c r="I100" s="129"/>
       <c r="J100" s="50"/>
       <c r="K100" s="50"/>
       <c r="L100" s="50"/>
-      <c r="M100" s="130">
+      <c r="M100" s="129">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -8797,17 +8806,17 @@
       <c r="B101" s="47">
         <v>97</v>
       </c>
-      <c r="C101" s="129"/>
+      <c r="C101" s="128"/>
       <c r="D101" s="50"/>
       <c r="E101" s="50"/>
       <c r="F101" s="50"/>
       <c r="G101" s="50"/>
       <c r="H101" s="50"/>
-      <c r="I101" s="130"/>
+      <c r="I101" s="129"/>
       <c r="J101" s="50"/>
       <c r="K101" s="50"/>
       <c r="L101" s="50"/>
-      <c r="M101" s="130">
+      <c r="M101" s="129">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -8865,17 +8874,17 @@
       <c r="B102" s="47">
         <v>98</v>
       </c>
-      <c r="C102" s="129"/>
+      <c r="C102" s="128"/>
       <c r="D102" s="50"/>
       <c r="E102" s="50"/>
       <c r="F102" s="50"/>
       <c r="G102" s="50"/>
       <c r="H102" s="50"/>
-      <c r="I102" s="130"/>
+      <c r="I102" s="129"/>
       <c r="J102" s="50"/>
       <c r="K102" s="50"/>
       <c r="L102" s="50"/>
-      <c r="M102" s="130">
+      <c r="M102" s="129">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -8933,17 +8942,17 @@
       <c r="B103" s="47">
         <v>99</v>
       </c>
-      <c r="C103" s="129"/>
+      <c r="C103" s="128"/>
       <c r="D103" s="50"/>
       <c r="E103" s="50"/>
       <c r="F103" s="50"/>
       <c r="G103" s="50"/>
       <c r="H103" s="50"/>
-      <c r="I103" s="130"/>
+      <c r="I103" s="129"/>
       <c r="J103" s="50"/>
       <c r="K103" s="50"/>
       <c r="L103" s="50"/>
-      <c r="M103" s="130">
+      <c r="M103" s="129">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -9001,17 +9010,17 @@
       <c r="B104" s="47">
         <v>100</v>
       </c>
-      <c r="C104" s="129"/>
+      <c r="C104" s="128"/>
       <c r="D104" s="50"/>
       <c r="E104" s="50"/>
       <c r="F104" s="50"/>
       <c r="G104" s="50"/>
       <c r="H104" s="50"/>
-      <c r="I104" s="130"/>
+      <c r="I104" s="129"/>
       <c r="J104" s="50"/>
       <c r="K104" s="50"/>
       <c r="L104" s="50"/>
-      <c r="M104" s="130">
+      <c r="M104" s="129">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -9069,17 +9078,17 @@
       <c r="B105" s="47">
         <v>101</v>
       </c>
-      <c r="C105" s="129"/>
+      <c r="C105" s="128"/>
       <c r="D105" s="50"/>
       <c r="E105" s="50"/>
       <c r="F105" s="50"/>
       <c r="G105" s="50"/>
       <c r="H105" s="50"/>
-      <c r="I105" s="130"/>
+      <c r="I105" s="129"/>
       <c r="J105" s="50"/>
       <c r="K105" s="50"/>
       <c r="L105" s="50"/>
-      <c r="M105" s="130">
+      <c r="M105" s="129">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -9137,17 +9146,17 @@
       <c r="B106" s="47">
         <v>102</v>
       </c>
-      <c r="C106" s="129"/>
+      <c r="C106" s="128"/>
       <c r="D106" s="50"/>
       <c r="E106" s="50"/>
       <c r="F106" s="50"/>
       <c r="G106" s="50"/>
       <c r="H106" s="50"/>
-      <c r="I106" s="130"/>
+      <c r="I106" s="129"/>
       <c r="J106" s="50"/>
       <c r="K106" s="50"/>
       <c r="L106" s="50"/>
-      <c r="M106" s="130">
+      <c r="M106" s="129">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -9205,17 +9214,17 @@
       <c r="B107" s="47">
         <v>103</v>
       </c>
-      <c r="C107" s="129"/>
+      <c r="C107" s="128"/>
       <c r="D107" s="50"/>
       <c r="E107" s="50"/>
       <c r="F107" s="50"/>
       <c r="G107" s="50"/>
       <c r="H107" s="50"/>
-      <c r="I107" s="130"/>
+      <c r="I107" s="129"/>
       <c r="J107" s="50"/>
       <c r="K107" s="50"/>
       <c r="L107" s="50"/>
-      <c r="M107" s="130">
+      <c r="M107" s="129">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -9273,17 +9282,17 @@
       <c r="B108" s="47">
         <v>104</v>
       </c>
-      <c r="C108" s="129"/>
+      <c r="C108" s="128"/>
       <c r="D108" s="50"/>
       <c r="E108" s="50"/>
       <c r="F108" s="50"/>
       <c r="G108" s="50"/>
       <c r="H108" s="50"/>
-      <c r="I108" s="130"/>
+      <c r="I108" s="129"/>
       <c r="J108" s="50"/>
       <c r="K108" s="50"/>
       <c r="L108" s="50"/>
-      <c r="M108" s="130">
+      <c r="M108" s="129">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -9341,17 +9350,17 @@
       <c r="B109" s="47">
         <v>105</v>
       </c>
-      <c r="C109" s="129"/>
+      <c r="C109" s="128"/>
       <c r="D109" s="50"/>
       <c r="E109" s="50"/>
       <c r="F109" s="50"/>
       <c r="G109" s="50"/>
       <c r="H109" s="50"/>
-      <c r="I109" s="130"/>
+      <c r="I109" s="129"/>
       <c r="J109" s="50"/>
       <c r="K109" s="50"/>
       <c r="L109" s="50"/>
-      <c r="M109" s="130">
+      <c r="M109" s="129">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -9409,17 +9418,17 @@
       <c r="B110" s="47">
         <v>106</v>
       </c>
-      <c r="C110" s="129"/>
+      <c r="C110" s="128"/>
       <c r="D110" s="50"/>
       <c r="E110" s="50"/>
       <c r="F110" s="50"/>
       <c r="G110" s="50"/>
       <c r="H110" s="50"/>
-      <c r="I110" s="130"/>
+      <c r="I110" s="129"/>
       <c r="J110" s="50"/>
       <c r="K110" s="50"/>
       <c r="L110" s="50"/>
-      <c r="M110" s="130">
+      <c r="M110" s="129">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -9477,17 +9486,17 @@
       <c r="B111" s="47">
         <v>107</v>
       </c>
-      <c r="C111" s="129"/>
+      <c r="C111" s="128"/>
       <c r="D111" s="50"/>
       <c r="E111" s="50"/>
       <c r="F111" s="50"/>
       <c r="G111" s="50"/>
       <c r="H111" s="50"/>
-      <c r="I111" s="130"/>
+      <c r="I111" s="129"/>
       <c r="J111" s="50"/>
       <c r="K111" s="50"/>
       <c r="L111" s="50"/>
-      <c r="M111" s="130">
+      <c r="M111" s="129">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -9545,17 +9554,17 @@
       <c r="B112" s="47">
         <v>108</v>
       </c>
-      <c r="C112" s="129"/>
+      <c r="C112" s="128"/>
       <c r="D112" s="50"/>
       <c r="E112" s="50"/>
       <c r="F112" s="50"/>
       <c r="G112" s="50"/>
       <c r="H112" s="50"/>
-      <c r="I112" s="130"/>
+      <c r="I112" s="129"/>
       <c r="J112" s="50"/>
       <c r="K112" s="50"/>
       <c r="L112" s="50"/>
-      <c r="M112" s="130">
+      <c r="M112" s="129">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -9613,17 +9622,17 @@
       <c r="B113" s="47">
         <v>109</v>
       </c>
-      <c r="C113" s="129"/>
+      <c r="C113" s="128"/>
       <c r="D113" s="50"/>
       <c r="E113" s="50"/>
       <c r="F113" s="50"/>
       <c r="G113" s="50"/>
       <c r="H113" s="50"/>
-      <c r="I113" s="130"/>
+      <c r="I113" s="129"/>
       <c r="J113" s="50"/>
       <c r="K113" s="50"/>
       <c r="L113" s="50"/>
-      <c r="M113" s="130">
+      <c r="M113" s="129">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -9681,17 +9690,17 @@
       <c r="B114" s="47">
         <v>110</v>
       </c>
-      <c r="C114" s="129"/>
+      <c r="C114" s="128"/>
       <c r="D114" s="50"/>
       <c r="E114" s="50"/>
       <c r="F114" s="50"/>
       <c r="G114" s="50"/>
       <c r="H114" s="50"/>
-      <c r="I114" s="130"/>
+      <c r="I114" s="129"/>
       <c r="J114" s="50"/>
       <c r="K114" s="50"/>
       <c r="L114" s="50"/>
-      <c r="M114" s="130">
+      <c r="M114" s="129">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -9749,17 +9758,17 @@
       <c r="B115" s="47">
         <v>111</v>
       </c>
-      <c r="C115" s="129"/>
+      <c r="C115" s="128"/>
       <c r="D115" s="50"/>
       <c r="E115" s="50"/>
       <c r="F115" s="50"/>
       <c r="G115" s="50"/>
       <c r="H115" s="50"/>
-      <c r="I115" s="130"/>
+      <c r="I115" s="129"/>
       <c r="J115" s="50"/>
       <c r="K115" s="50"/>
       <c r="L115" s="50"/>
-      <c r="M115" s="130">
+      <c r="M115" s="129">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -9817,17 +9826,17 @@
       <c r="B116" s="47">
         <v>112</v>
       </c>
-      <c r="C116" s="129"/>
+      <c r="C116" s="128"/>
       <c r="D116" s="50"/>
       <c r="E116" s="50"/>
       <c r="F116" s="50"/>
       <c r="G116" s="50"/>
       <c r="H116" s="50"/>
-      <c r="I116" s="130"/>
+      <c r="I116" s="129"/>
       <c r="J116" s="50"/>
       <c r="K116" s="50"/>
       <c r="L116" s="50"/>
-      <c r="M116" s="130">
+      <c r="M116" s="129">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -9885,17 +9894,17 @@
       <c r="B117" s="47">
         <v>113</v>
       </c>
-      <c r="C117" s="129"/>
+      <c r="C117" s="128"/>
       <c r="D117" s="50"/>
       <c r="E117" s="50"/>
       <c r="F117" s="50"/>
       <c r="G117" s="50"/>
       <c r="H117" s="50"/>
-      <c r="I117" s="130"/>
+      <c r="I117" s="129"/>
       <c r="J117" s="50"/>
       <c r="K117" s="50"/>
       <c r="L117" s="50"/>
-      <c r="M117" s="130">
+      <c r="M117" s="129">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -9953,17 +9962,17 @@
       <c r="B118" s="47">
         <v>114</v>
       </c>
-      <c r="C118" s="129"/>
+      <c r="C118" s="128"/>
       <c r="D118" s="50"/>
       <c r="E118" s="50"/>
       <c r="F118" s="50"/>
       <c r="G118" s="50"/>
       <c r="H118" s="50"/>
-      <c r="I118" s="130"/>
+      <c r="I118" s="129"/>
       <c r="J118" s="50"/>
       <c r="K118" s="50"/>
       <c r="L118" s="50"/>
-      <c r="M118" s="130">
+      <c r="M118" s="129">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -10021,17 +10030,17 @@
       <c r="B119" s="47">
         <v>115</v>
       </c>
-      <c r="C119" s="129"/>
+      <c r="C119" s="128"/>
       <c r="D119" s="50"/>
       <c r="E119" s="50"/>
       <c r="F119" s="50"/>
       <c r="G119" s="50"/>
       <c r="H119" s="50"/>
-      <c r="I119" s="130"/>
+      <c r="I119" s="129"/>
       <c r="J119" s="50"/>
       <c r="K119" s="50"/>
       <c r="L119" s="50"/>
-      <c r="M119" s="130">
+      <c r="M119" s="129">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -10089,17 +10098,17 @@
       <c r="B120" s="47">
         <v>116</v>
       </c>
-      <c r="C120" s="129"/>
+      <c r="C120" s="128"/>
       <c r="D120" s="50"/>
       <c r="E120" s="50"/>
       <c r="F120" s="50"/>
       <c r="G120" s="50"/>
       <c r="H120" s="50"/>
-      <c r="I120" s="130"/>
+      <c r="I120" s="129"/>
       <c r="J120" s="50"/>
       <c r="K120" s="50"/>
       <c r="L120" s="50"/>
-      <c r="M120" s="130">
+      <c r="M120" s="129">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -10157,17 +10166,17 @@
       <c r="B121" s="47">
         <v>117</v>
       </c>
-      <c r="C121" s="129"/>
+      <c r="C121" s="128"/>
       <c r="D121" s="50"/>
       <c r="E121" s="50"/>
       <c r="F121" s="50"/>
       <c r="G121" s="50"/>
       <c r="H121" s="50"/>
-      <c r="I121" s="130"/>
+      <c r="I121" s="129"/>
       <c r="J121" s="50"/>
       <c r="K121" s="50"/>
       <c r="L121" s="50"/>
-      <c r="M121" s="130">
+      <c r="M121" s="129">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -10225,17 +10234,17 @@
       <c r="B122" s="47">
         <v>118</v>
       </c>
-      <c r="C122" s="129"/>
+      <c r="C122" s="128"/>
       <c r="D122" s="50"/>
       <c r="E122" s="50"/>
       <c r="F122" s="50"/>
       <c r="G122" s="50"/>
       <c r="H122" s="50"/>
-      <c r="I122" s="130"/>
+      <c r="I122" s="129"/>
       <c r="J122" s="50"/>
       <c r="K122" s="50"/>
       <c r="L122" s="50"/>
-      <c r="M122" s="130">
+      <c r="M122" s="129">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -10293,17 +10302,17 @@
       <c r="B123" s="47">
         <v>119</v>
       </c>
-      <c r="C123" s="129"/>
+      <c r="C123" s="128"/>
       <c r="D123" s="50"/>
       <c r="E123" s="50"/>
       <c r="F123" s="50"/>
       <c r="G123" s="50"/>
       <c r="H123" s="50"/>
-      <c r="I123" s="130"/>
+      <c r="I123" s="129"/>
       <c r="J123" s="50"/>
       <c r="K123" s="50"/>
       <c r="L123" s="50"/>
-      <c r="M123" s="130">
+      <c r="M123" s="129">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -10358,18 +10367,18 @@
     </row>
     <row r="124" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A124" s="78"/>
-      <c r="B124" s="108"/>
-      <c r="C124" s="129"/>
+      <c r="B124" s="107"/>
+      <c r="C124" s="128"/>
       <c r="D124" s="50"/>
       <c r="E124" s="50"/>
       <c r="F124" s="50"/>
       <c r="G124" s="50"/>
       <c r="H124" s="50"/>
-      <c r="I124" s="130"/>
+      <c r="I124" s="129"/>
       <c r="J124" s="50"/>
       <c r="K124" s="50"/>
       <c r="L124" s="50"/>
-      <c r="M124" s="130">
+      <c r="M124" s="129">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -10424,18 +10433,18 @@
     </row>
     <row r="125" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A125" s="78"/>
-      <c r="B125" s="108"/>
-      <c r="C125" s="129"/>
+      <c r="B125" s="107"/>
+      <c r="C125" s="128"/>
       <c r="D125" s="50"/>
       <c r="E125" s="50"/>
       <c r="F125" s="50"/>
       <c r="G125" s="50"/>
       <c r="H125" s="50"/>
-      <c r="I125" s="130"/>
+      <c r="I125" s="129"/>
       <c r="J125" s="50"/>
       <c r="K125" s="50"/>
       <c r="L125" s="50"/>
-      <c r="M125" s="130">
+      <c r="M125" s="129">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -10490,18 +10499,18 @@
     </row>
     <row r="126" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A126" s="78"/>
-      <c r="B126" s="108"/>
-      <c r="C126" s="129"/>
+      <c r="B126" s="107"/>
+      <c r="C126" s="128"/>
       <c r="D126" s="50"/>
       <c r="E126" s="50"/>
       <c r="F126" s="50"/>
       <c r="G126" s="50"/>
       <c r="H126" s="50"/>
-      <c r="I126" s="130"/>
+      <c r="I126" s="129"/>
       <c r="J126" s="50"/>
       <c r="K126" s="50"/>
       <c r="L126" s="50"/>
-      <c r="M126" s="130">
+      <c r="M126" s="129">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -10556,18 +10565,18 @@
     </row>
     <row r="127" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A127" s="78"/>
-      <c r="B127" s="108"/>
-      <c r="C127" s="129"/>
+      <c r="B127" s="107"/>
+      <c r="C127" s="128"/>
       <c r="D127" s="50"/>
       <c r="E127" s="50"/>
       <c r="F127" s="50"/>
       <c r="G127" s="50"/>
       <c r="H127" s="50"/>
-      <c r="I127" s="130"/>
+      <c r="I127" s="129"/>
       <c r="J127" s="50"/>
       <c r="K127" s="50"/>
       <c r="L127" s="50"/>
-      <c r="M127" s="130">
+      <c r="M127" s="129">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -10622,18 +10631,18 @@
     </row>
     <row r="128" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A128" s="78"/>
-      <c r="B128" s="108"/>
-      <c r="C128" s="129"/>
+      <c r="B128" s="107"/>
+      <c r="C128" s="128"/>
       <c r="D128" s="50"/>
       <c r="E128" s="50"/>
       <c r="F128" s="50"/>
       <c r="G128" s="50"/>
       <c r="H128" s="50"/>
-      <c r="I128" s="130"/>
+      <c r="I128" s="129"/>
       <c r="J128" s="50"/>
       <c r="K128" s="50"/>
       <c r="L128" s="50"/>
-      <c r="M128" s="130">
+      <c r="M128" s="129">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -10688,18 +10697,18 @@
     </row>
     <row r="129" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A129" s="78"/>
-      <c r="B129" s="108"/>
-      <c r="C129" s="129"/>
+      <c r="B129" s="107"/>
+      <c r="C129" s="128"/>
       <c r="D129" s="50"/>
       <c r="E129" s="50"/>
       <c r="F129" s="50"/>
       <c r="G129" s="50"/>
       <c r="H129" s="50"/>
-      <c r="I129" s="130"/>
+      <c r="I129" s="129"/>
       <c r="J129" s="50"/>
       <c r="K129" s="50"/>
       <c r="L129" s="50"/>
-      <c r="M129" s="130">
+      <c r="M129" s="129">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -10754,18 +10763,18 @@
     </row>
     <row r="130" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A130" s="78"/>
-      <c r="B130" s="108"/>
-      <c r="C130" s="129"/>
+      <c r="B130" s="107"/>
+      <c r="C130" s="128"/>
       <c r="D130" s="50"/>
       <c r="E130" s="50"/>
       <c r="F130" s="50"/>
       <c r="G130" s="50"/>
       <c r="H130" s="50"/>
-      <c r="I130" s="130"/>
+      <c r="I130" s="129"/>
       <c r="J130" s="50"/>
       <c r="K130" s="50"/>
       <c r="L130" s="50"/>
-      <c r="M130" s="130">
+      <c r="M130" s="129">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -10820,18 +10829,18 @@
     </row>
     <row r="131" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A131" s="78"/>
-      <c r="B131" s="108"/>
-      <c r="C131" s="129"/>
+      <c r="B131" s="107"/>
+      <c r="C131" s="128"/>
       <c r="D131" s="50"/>
       <c r="E131" s="50"/>
       <c r="F131" s="50"/>
       <c r="G131" s="50"/>
       <c r="H131" s="50"/>
-      <c r="I131" s="130"/>
+      <c r="I131" s="129"/>
       <c r="J131" s="50"/>
       <c r="K131" s="50"/>
       <c r="L131" s="50"/>
-      <c r="M131" s="130">
+      <c r="M131" s="129">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -10886,13 +10895,13 @@
     </row>
     <row r="132" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A132" s="78"/>
-      <c r="B132" s="164" t="s">
+      <c r="B132" s="150" t="s">
         <v>11</v>
       </c>
-      <c r="C132" s="165"/>
+      <c r="C132" s="151"/>
       <c r="D132" s="84">
         <f t="shared" ref="D132:L132" si="104">SUM(D6:D60)</f>
-        <v>280</v>
+        <v>1880</v>
       </c>
       <c r="E132" s="84">
         <f t="shared" si="104"/>
@@ -10916,19 +10925,19 @@
       </c>
       <c r="J132" s="84">
         <f t="shared" si="104"/>
-        <v>960</v>
+        <v>1560</v>
       </c>
       <c r="K132" s="84">
         <f t="shared" si="104"/>
-        <v>840</v>
+        <v>1640</v>
       </c>
       <c r="L132" s="84">
         <f t="shared" si="104"/>
-        <v>1278</v>
+        <v>2278</v>
       </c>
       <c r="M132" s="48">
         <f t="shared" ref="M132:M135" si="105">SUM(D132:L132)/40</f>
-        <v>137.875</v>
+        <v>237.875</v>
       </c>
       <c r="N132" s="39">
         <f t="shared" si="18"/>
@@ -10944,7 +10953,7 @@
       </c>
       <c r="Q132" s="40">
         <f t="shared" ref="Q132:Q136" si="107">SUM(J132:L132)/20</f>
-        <v>153.9</v>
+        <v>273.89999999999998</v>
       </c>
       <c r="R132" s="51" t="e">
         <f t="shared" si="4"/>
@@ -10981,22 +10990,22 @@
     </row>
     <row r="133" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A133" s="78"/>
-      <c r="B133" s="108">
+      <c r="B133" s="107">
         <v>0</v>
       </c>
       <c r="C133" s="57" t="s">
         <v>70</v>
       </c>
-      <c r="D133" s="109"/>
-      <c r="E133" s="110"/>
-      <c r="F133" s="111"/>
-      <c r="G133" s="110"/>
-      <c r="H133" s="110"/>
-      <c r="I133" s="111"/>
-      <c r="J133" s="110"/>
-      <c r="K133" s="110"/>
-      <c r="L133" s="111"/>
-      <c r="M133" s="112">
+      <c r="D133" s="108"/>
+      <c r="E133" s="109"/>
+      <c r="F133" s="110"/>
+      <c r="G133" s="109"/>
+      <c r="H133" s="109"/>
+      <c r="I133" s="110"/>
+      <c r="J133" s="109"/>
+      <c r="K133" s="109"/>
+      <c r="L133" s="110"/>
+      <c r="M133" s="111">
         <f>SUM(D133:L133)</f>
         <v>0</v>
       </c>
@@ -11153,10 +11162,10 @@
       </c>
     </row>
     <row r="136" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B136" s="152" t="s">
+      <c r="B136" s="163" t="s">
         <v>71</v>
       </c>
-      <c r="C136" s="153"/>
+      <c r="C136" s="164"/>
       <c r="D136" s="83">
         <f>SUM(D134:D135)</f>
         <v>0</v>
@@ -11193,7 +11202,7 @@
         <f t="shared" si="111"/>
         <v>0</v>
       </c>
-      <c r="M136" s="113">
+      <c r="M136" s="112">
         <f>SUM(M133:M135)</f>
         <v>0</v>
       </c>
@@ -11247,13 +11256,13 @@
       </c>
     </row>
     <row r="137" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B137" s="141" t="s">
+      <c r="B137" s="152" t="s">
         <v>11</v>
       </c>
-      <c r="C137" s="142"/>
+      <c r="C137" s="153"/>
       <c r="D137" s="85">
         <f>SUM(D132,D136)</f>
-        <v>280</v>
+        <v>1880</v>
       </c>
       <c r="E137" s="85">
         <f t="shared" ref="E137:L137" si="112">SUM(E132,E136)</f>
@@ -11277,19 +11286,19 @@
       </c>
       <c r="J137" s="85">
         <f t="shared" si="112"/>
-        <v>960</v>
+        <v>1560</v>
       </c>
       <c r="K137" s="85">
         <f t="shared" si="112"/>
-        <v>840</v>
+        <v>1640</v>
       </c>
       <c r="L137" s="85">
         <f t="shared" si="112"/>
-        <v>1278</v>
+        <v>2278</v>
       </c>
       <c r="M137" s="60">
         <f t="shared" si="0"/>
-        <v>137.875</v>
+        <v>237.875</v>
       </c>
       <c r="N137" s="63">
         <f>SUM(N5:N136)</f>
@@ -11305,7 +11314,7 @@
       </c>
       <c r="Q137" s="64">
         <f t="shared" si="113"/>
-        <v>311.8</v>
+        <v>551.79999999999995</v>
       </c>
       <c r="R137" s="65" t="e">
         <f t="shared" si="113"/>
@@ -11342,17 +11351,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="R3:U3"/>
-    <mergeCell ref="V3:Y3"/>
-    <mergeCell ref="B132:C132"/>
     <mergeCell ref="B137:C137"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="P2:Q2"/>
     <mergeCell ref="M3:O3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B136:C136"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="R3:U3"/>
+    <mergeCell ref="V3:Y3"/>
+    <mergeCell ref="B132:C132"/>
   </mergeCells>
   <conditionalFormatting sqref="C45:C59">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
@@ -11388,25 +11397,25 @@
   <sheetData>
     <row r="2" spans="3:26" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="3:26" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C3" s="168" t="s">
+      <c r="C3" s="167" t="s">
         <v>49</v>
       </c>
-      <c r="D3" s="169"/>
-      <c r="E3" s="169"/>
-      <c r="F3" s="169"/>
-      <c r="G3" s="170"/>
-      <c r="H3" s="172" t="s">
+      <c r="D3" s="168"/>
+      <c r="E3" s="168"/>
+      <c r="F3" s="168"/>
+      <c r="G3" s="169"/>
+      <c r="H3" s="171" t="s">
         <v>63</v>
       </c>
-      <c r="I3" s="173"/>
-      <c r="K3" s="174" t="s">
+      <c r="I3" s="172"/>
+      <c r="K3" s="173" t="s">
         <v>67</v>
       </c>
-      <c r="L3" s="174"/>
-      <c r="M3" s="174"/>
-      <c r="N3" s="174"/>
-      <c r="O3" s="174"/>
-      <c r="P3" s="174"/>
+      <c r="L3" s="173"/>
+      <c r="M3" s="173"/>
+      <c r="N3" s="173"/>
+      <c r="O3" s="173"/>
+      <c r="P3" s="173"/>
     </row>
     <row r="4" spans="3:26" ht="29.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C4" s="99"/>
@@ -11443,7 +11452,7 @@
       <c r="O4" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="P4" s="139" t="s">
+      <c r="P4" s="138" t="s">
         <v>89</v>
       </c>
     </row>
@@ -11451,19 +11460,25 @@
       <c r="C5" s="101" t="s">
         <v>50</v>
       </c>
-      <c r="D5" s="88"/>
-      <c r="E5" s="79"/>
-      <c r="F5" s="79"/>
+      <c r="D5" s="88">
+        <v>165</v>
+      </c>
+      <c r="E5" s="79">
+        <v>143</v>
+      </c>
+      <c r="F5" s="79">
+        <v>100</v>
+      </c>
       <c r="G5" s="102">
         <f>SUM(D5:F5)</f>
-        <v>0</v>
+        <v>408</v>
       </c>
       <c r="H5" s="95">
         <v>10000</v>
       </c>
       <c r="I5" s="96">
         <f>G5-H5</f>
-        <v>-10000</v>
+        <v>-9592</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>1</v>
@@ -11482,12 +11497,21 @@
       <c r="C6" s="103" t="s">
         <v>51</v>
       </c>
-      <c r="D6" s="104"/>
-      <c r="E6" s="105"/>
-      <c r="F6" s="105"/>
-      <c r="G6" s="106">
+      <c r="D6" s="104">
+        <f>D5*40</f>
+        <v>6600</v>
+      </c>
+      <c r="E6" s="104">
+        <f t="shared" ref="E6:F6" si="1">E5*40</f>
+        <v>5720</v>
+      </c>
+      <c r="F6" s="104">
+        <f t="shared" si="1"/>
+        <v>4000</v>
+      </c>
+      <c r="G6" s="105">
         <f>SUM(D6:F6)</f>
-        <v>0</v>
+        <v>16320</v>
       </c>
       <c r="H6" s="97">
         <f>H5*40</f>
@@ -11495,7 +11519,7 @@
       </c>
       <c r="I6" s="98">
         <f>G6-H6</f>
-        <v>-400000</v>
+        <v>-383680</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>2</v>
@@ -11509,21 +11533,21 @@
         <v>0</v>
       </c>
       <c r="O6" s="81"/>
-      <c r="S6" s="125"/>
-      <c r="T6" s="125"/>
-      <c r="U6" s="138">
+      <c r="S6" s="124"/>
+      <c r="T6" s="124"/>
+      <c r="U6" s="137">
         <v>46180</v>
       </c>
-      <c r="V6" s="138">
+      <c r="V6" s="137">
         <v>46180</v>
       </c>
-      <c r="W6" s="138">
+      <c r="W6" s="137">
         <v>46333</v>
       </c>
-      <c r="X6" s="138">
+      <c r="X6" s="137">
         <v>46210</v>
       </c>
-      <c r="Y6" s="138">
+      <c r="Y6" s="137">
         <v>46210</v>
       </c>
     </row>
@@ -11541,28 +11565,28 @@
         <v>0</v>
       </c>
       <c r="O7" s="81"/>
-      <c r="S7" s="137" t="s">
+      <c r="S7" s="136" t="s">
         <v>88</v>
       </c>
-      <c r="T7" s="137" t="s">
+      <c r="T7" s="136" t="s">
         <v>87</v>
       </c>
       <c r="U7" s="77" t="s">
         <v>81</v>
       </c>
-      <c r="V7" s="137" t="s">
+      <c r="V7" s="136" t="s">
         <v>85</v>
       </c>
-      <c r="W7" s="137" t="s">
+      <c r="W7" s="136" t="s">
         <v>84</v>
       </c>
-      <c r="X7" s="137" t="s">
+      <c r="X7" s="136" t="s">
         <v>84</v>
       </c>
-      <c r="Y7" s="137" t="s">
+      <c r="Y7" s="136" t="s">
         <v>84</v>
       </c>
-      <c r="Z7" s="137" t="s">
+      <c r="Z7" s="136" t="s">
         <v>86</v>
       </c>
     </row>
@@ -11588,7 +11612,7 @@
       <c r="T8" s="79" t="s">
         <v>80</v>
       </c>
-      <c r="U8" s="136">
+      <c r="U8" s="135">
         <v>50</v>
       </c>
       <c r="V8" s="79">
@@ -11610,13 +11634,13 @@
       <c r="C9" s="82" t="s">
         <v>53</v>
       </c>
-      <c r="D9" s="107">
+      <c r="D9" s="106">
         <f>D8-D5</f>
-        <v>0</v>
-      </c>
-      <c r="E9" s="107">
+        <v>-165</v>
+      </c>
+      <c r="E9" s="106">
         <f>E8-E5</f>
-        <v>0</v>
+        <v>-143</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>5</v>
@@ -11636,7 +11660,7 @@
       <c r="T9" s="79" t="s">
         <v>24</v>
       </c>
-      <c r="U9" s="136">
+      <c r="U9" s="135">
         <v>50</v>
       </c>
       <c r="V9" s="79">
@@ -11652,7 +11676,7 @@
         <v>1</v>
       </c>
       <c r="Z9" s="79">
-        <f t="shared" ref="Z9:Z13" si="1">SUM(U9:Y9)</f>
+        <f t="shared" ref="Z9:Z13" si="2">SUM(U9:Y9)</f>
         <v>80</v>
       </c>
     </row>
@@ -11675,7 +11699,7 @@
       <c r="T10" s="79" t="s">
         <v>82</v>
       </c>
-      <c r="U10" s="136"/>
+      <c r="U10" s="135"/>
       <c r="V10" s="79">
         <v>3</v>
       </c>
@@ -11687,19 +11711,19 @@
       </c>
       <c r="Y10" s="79"/>
       <c r="Z10" s="79">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>24</v>
       </c>
     </row>
     <row r="11" spans="3:26" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C11" s="171" t="s">
+      <c r="C11" s="170" t="s">
         <v>60</v>
       </c>
-      <c r="D11" s="171"/>
-      <c r="F11" s="171" t="s">
+      <c r="D11" s="170"/>
+      <c r="F11" s="170" t="s">
         <v>69</v>
       </c>
-      <c r="G11" s="171"/>
+      <c r="G11" s="170"/>
       <c r="K11" s="1" t="s">
         <v>7</v>
       </c>
@@ -11718,7 +11742,7 @@
       <c r="T11" s="79" t="s">
         <v>80</v>
       </c>
-      <c r="U11" s="136"/>
+      <c r="U11" s="135"/>
       <c r="V11" s="79"/>
       <c r="W11" s="79"/>
       <c r="X11" s="79">
@@ -11728,7 +11752,7 @@
         <v>1</v>
       </c>
       <c r="Z11" s="79">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
     </row>
@@ -11744,7 +11768,7 @@
       </c>
       <c r="G12" s="91">
         <f>D12+G5</f>
-        <v>4200</v>
+        <v>4608</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>11</v>
@@ -11768,7 +11792,7 @@
       <c r="T12" s="79" t="s">
         <v>83</v>
       </c>
-      <c r="U12" s="136"/>
+      <c r="U12" s="135"/>
       <c r="V12" s="79"/>
       <c r="W12" s="79"/>
       <c r="X12" s="79">
@@ -11778,7 +11802,7 @@
         <v>1</v>
       </c>
       <c r="Z12" s="79">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
     </row>
@@ -11795,64 +11819,64 @@
       </c>
       <c r="G13" s="91">
         <f>G12*40</f>
-        <v>168000</v>
-      </c>
-      <c r="S13" s="166" t="s">
+        <v>184320</v>
+      </c>
+      <c r="S13" s="165" t="s">
         <v>86</v>
       </c>
-      <c r="T13" s="166"/>
-      <c r="U13" s="136">
+      <c r="T13" s="165"/>
+      <c r="U13" s="135">
         <f>SUM(U8:U12)</f>
         <v>100</v>
       </c>
       <c r="V13" s="79">
-        <f t="shared" ref="V13:Y13" si="2">SUM(V8:V12)</f>
+        <f t="shared" ref="V13:Y13" si="3">SUM(V8:V12)</f>
         <v>9</v>
       </c>
       <c r="W13" s="79">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="X13" s="79">
+        <f t="shared" si="3"/>
+        <v>77</v>
+      </c>
+      <c r="Y13" s="79">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="Z13" s="5">
         <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-      <c r="X13" s="79">
-        <f t="shared" si="2"/>
-        <v>77</v>
-      </c>
-      <c r="Y13" s="79">
-        <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-      <c r="Z13" s="5">
-        <f t="shared" si="1"/>
         <v>192</v>
       </c>
     </row>
     <row r="16" spans="3:26" ht="24" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="K16" s="118" t="s">
+      <c r="K16" s="117" t="s">
         <v>75</v>
       </c>
-      <c r="L16" s="118" t="s">
+      <c r="L16" s="117" t="s">
         <v>8</v>
       </c>
-      <c r="M16" s="118" t="s">
+      <c r="M16" s="117" t="s">
         <v>62</v>
       </c>
-      <c r="N16" s="118" t="s">
+      <c r="N16" s="117" t="s">
         <v>74</v>
       </c>
-      <c r="O16" s="118" t="s">
+      <c r="O16" s="117" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="17" spans="4:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="K17" s="114" t="s">
+      <c r="K17" s="113" t="s">
         <v>1</v>
       </c>
-      <c r="L17" s="116">
+      <c r="L17" s="115">
         <v>70</v>
       </c>
-      <c r="M17" s="115"/>
-      <c r="N17" s="122"/>
-      <c r="O17" s="123">
+      <c r="M17" s="114"/>
+      <c r="N17" s="121"/>
+      <c r="O17" s="122">
         <f>N17-M5</f>
         <v>0</v>
       </c>
@@ -11861,12 +11885,12 @@
       <c r="K18" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="L18" s="117">
+      <c r="L18" s="116">
         <v>70</v>
       </c>
       <c r="M18" s="5"/>
       <c r="N18" s="5"/>
-      <c r="O18" s="123">
+      <c r="O18" s="122">
         <f>N18-M6</f>
         <v>0</v>
       </c>
@@ -11878,34 +11902,34 @@
       <c r="K19" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="L19" s="117">
+      <c r="L19" s="116">
         <v>70</v>
       </c>
       <c r="M19" s="5"/>
       <c r="N19" s="5"/>
-      <c r="O19" s="123">
-        <f t="shared" ref="O19:O23" si="3">N19-M7</f>
+      <c r="O19" s="122">
+        <f t="shared" ref="O19:O23" si="4">N19-M7</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="4:15" ht="24" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="D20" s="167" t="s">
+      <c r="D20" s="166" t="s">
         <v>67</v>
       </c>
-      <c r="E20" s="167"/>
-      <c r="F20" s="167"/>
-      <c r="G20" s="167"/>
-      <c r="H20" s="167"/>
+      <c r="E20" s="166"/>
+      <c r="F20" s="166"/>
+      <c r="G20" s="166"/>
+      <c r="H20" s="166"/>
       <c r="K20" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="L20" s="117">
+      <c r="L20" s="116">
         <v>120</v>
       </c>
       <c r="M20" s="5"/>
       <c r="N20" s="5"/>
-      <c r="O20" s="123">
-        <f t="shared" si="3"/>
+      <c r="O20" s="122">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -11928,13 +11952,13 @@
       <c r="K21" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="L21" s="117">
+      <c r="L21" s="116">
         <v>120</v>
       </c>
       <c r="M21" s="5"/>
       <c r="N21" s="5"/>
-      <c r="O21" s="123">
-        <f t="shared" si="3"/>
+      <c r="O21" s="122">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -11947,20 +11971,20 @@
       </c>
       <c r="F22" s="5"/>
       <c r="G22" s="6">
-        <f t="shared" ref="G22:G28" si="4">F22/40</f>
+        <f t="shared" ref="G22:G28" si="5">F22/40</f>
         <v>0</v>
       </c>
       <c r="H22" s="81"/>
       <c r="K22" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="L22" s="117">
+      <c r="L22" s="116">
         <v>120</v>
       </c>
       <c r="M22" s="5"/>
       <c r="N22" s="5"/>
-      <c r="O22" s="123">
-        <f t="shared" si="3"/>
+      <c r="O22" s="122">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -11973,20 +11997,20 @@
       </c>
       <c r="F23" s="5"/>
       <c r="G23" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="H23" s="81"/>
       <c r="K23" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="L23" s="117">
+      <c r="L23" s="116">
         <v>60</v>
       </c>
       <c r="M23" s="5"/>
       <c r="N23" s="5"/>
-      <c r="O23" s="123">
-        <f t="shared" si="3"/>
+      <c r="O23" s="122">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -11999,23 +12023,23 @@
       </c>
       <c r="F24" s="5"/>
       <c r="G24" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="H24" s="81"/>
-      <c r="K24" s="119" t="s">
+      <c r="K24" s="118" t="s">
         <v>72</v>
       </c>
-      <c r="L24" s="120"/>
-      <c r="M24" s="121">
+      <c r="L24" s="119"/>
+      <c r="M24" s="120">
         <f>SUM(M17:M23)</f>
         <v>0</v>
       </c>
-      <c r="N24" s="121">
+      <c r="N24" s="120">
         <f>SUM(N17:N23)</f>
         <v>0</v>
       </c>
-      <c r="O24" s="118">
+      <c r="O24" s="117">
         <f>SUM(O17:O23)</f>
         <v>0</v>
       </c>
@@ -12029,23 +12053,23 @@
       </c>
       <c r="F25" s="5"/>
       <c r="G25" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="H25" s="81"/>
-      <c r="K25" s="119" t="s">
+      <c r="K25" s="118" t="s">
         <v>73</v>
       </c>
-      <c r="L25" s="120"/>
-      <c r="M25" s="121">
+      <c r="L25" s="119"/>
+      <c r="M25" s="120">
         <f>M24/40</f>
         <v>0</v>
       </c>
-      <c r="N25" s="121">
+      <c r="N25" s="120">
         <f>N24/40</f>
         <v>0</v>
       </c>
-      <c r="O25" s="118">
+      <c r="O25" s="117">
         <f>O24/40</f>
         <v>0</v>
       </c>
@@ -12059,7 +12083,7 @@
       </c>
       <c r="F26" s="5"/>
       <c r="G26" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="H26" s="81"/>
@@ -12073,7 +12097,7 @@
       </c>
       <c r="F27" s="5"/>
       <c r="G27" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="H27" s="81"/>
@@ -12087,7 +12111,7 @@
       </c>
       <c r="F28" s="5"/>
       <c r="G28" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="H28" s="81"/>

--- a/Aug_2026/daily Reports/LMT Orders.xlsx
+++ b/Aug_2026/daily Reports/LMT Orders.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95D145A1-2F42-44A1-961C-E82EC9A71606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A7D609A-98DC-4067-B714-28E8CC9BB07D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="106">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -317,6 +317,30 @@
   <si>
     <t xml:space="preserve">Lutaf Mart </t>
   </si>
+  <si>
+    <t>Imperia Departmental Store</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rainbow Shadra </t>
+  </si>
+  <si>
+    <t>Rainbow Shikhupura</t>
+  </si>
+  <si>
+    <t>Rainbow Gujranwala</t>
+  </si>
+  <si>
+    <t>Zubaida Associates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gourmet Behria Town </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gourmet Foods </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gorrmet Behria Town </t>
+  </si>
 </sst>
 </file>
 
@@ -1567,6 +1591,45 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1601,45 +1664,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2204,14 +2228,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="140">
+      <c r="B1" s="153">
         <f ca="1">TODAY()</f>
-        <v>46241</v>
-      </c>
-      <c r="C1" s="140"/>
-      <c r="D1" s="140"/>
-      <c r="E1" s="140"/>
-      <c r="F1" s="140"/>
+        <v>46244</v>
+      </c>
+      <c r="C1" s="153"/>
+      <c r="D1" s="153"/>
+      <c r="E1" s="153"/>
+      <c r="F1" s="153"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
       <c r="I1" s="10"/>
@@ -2233,10 +2257,10 @@
       <c r="Y1" s="10"/>
     </row>
     <row r="2" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="162" t="s">
+      <c r="A2" s="150" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="141" t="s">
+      <c r="B2" s="154" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2269,13 +2293,13 @@
       <c r="L2" s="15">
         <v>120</v>
       </c>
-      <c r="M2" s="154"/>
-      <c r="N2" s="155"/>
-      <c r="O2" s="156"/>
-      <c r="P2" s="157" t="s">
+      <c r="M2" s="142"/>
+      <c r="N2" s="143"/>
+      <c r="O2" s="144"/>
+      <c r="P2" s="145" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="158"/>
+      <c r="Q2" s="146"/>
       <c r="R2" s="18">
         <v>0.05</v>
       </c>
@@ -2294,8 +2318,8 @@
       <c r="Y2" s="20"/>
     </row>
     <row r="3" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="162"/>
-      <c r="B3" s="142"/>
+      <c r="A3" s="150"/>
+      <c r="B3" s="155"/>
       <c r="C3" s="23" t="s">
         <v>15</v>
       </c>
@@ -2326,29 +2350,29 @@
       <c r="L3" s="29">
         <v>72.64</v>
       </c>
-      <c r="M3" s="159" t="s">
+      <c r="M3" s="147" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="160"/>
-      <c r="O3" s="161"/>
+      <c r="N3" s="148"/>
+      <c r="O3" s="149"/>
       <c r="P3" s="71"/>
       <c r="Q3" s="72"/>
-      <c r="R3" s="144" t="s">
+      <c r="R3" s="157" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="145"/>
-      <c r="T3" s="145"/>
-      <c r="U3" s="146"/>
-      <c r="V3" s="147" t="s">
+      <c r="S3" s="158"/>
+      <c r="T3" s="158"/>
+      <c r="U3" s="159"/>
+      <c r="V3" s="160" t="s">
         <v>17</v>
       </c>
-      <c r="W3" s="148"/>
-      <c r="X3" s="148"/>
-      <c r="Y3" s="149"/>
+      <c r="W3" s="161"/>
+      <c r="X3" s="161"/>
+      <c r="Y3" s="162"/>
     </row>
     <row r="4" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="162"/>
-      <c r="B4" s="143"/>
+      <c r="A4" s="150"/>
+      <c r="B4" s="156"/>
       <c r="C4" s="30" t="s">
         <v>18</v>
       </c>
@@ -3070,23 +3094,39 @@
       </c>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A13" s="78"/>
+      <c r="A13" s="78">
+        <v>46241</v>
+      </c>
       <c r="B13" s="47">
         <v>9</v>
       </c>
-      <c r="C13" s="57"/>
+      <c r="C13" s="57" t="s">
+        <v>25</v>
+      </c>
       <c r="D13" s="74"/>
       <c r="E13" s="75"/>
       <c r="F13" s="76"/>
-      <c r="G13" s="50"/>
-      <c r="H13" s="75"/>
-      <c r="I13" s="49"/>
-      <c r="J13" s="50"/>
-      <c r="K13" s="75"/>
-      <c r="L13" s="76"/>
+      <c r="G13" s="50">
+        <v>160</v>
+      </c>
+      <c r="H13" s="75">
+        <v>280</v>
+      </c>
+      <c r="I13" s="49">
+        <v>160</v>
+      </c>
+      <c r="J13" s="50">
+        <v>240</v>
+      </c>
+      <c r="K13" s="75">
+        <v>160</v>
+      </c>
+      <c r="L13" s="76">
+        <v>400</v>
+      </c>
       <c r="M13" s="48">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="N13" s="39">
         <f t="shared" si="18"/>
@@ -3098,11 +3138,11 @@
       </c>
       <c r="P13" s="73">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="Q13" s="40">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="R13" s="51" t="e">
         <f t="shared" si="4"/>
@@ -3138,23 +3178,37 @@
       </c>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A14" s="78"/>
+      <c r="A14" s="78">
+        <v>46241</v>
+      </c>
       <c r="B14" s="47">
         <v>10</v>
       </c>
-      <c r="C14" s="57"/>
+      <c r="C14" s="57" t="s">
+        <v>104</v>
+      </c>
       <c r="D14" s="74"/>
       <c r="E14" s="75"/>
       <c r="F14" s="76"/>
-      <c r="G14" s="50"/>
-      <c r="H14" s="75"/>
+      <c r="G14" s="50">
+        <v>120</v>
+      </c>
+      <c r="H14" s="75">
+        <v>120</v>
+      </c>
       <c r="I14" s="49"/>
-      <c r="J14" s="50"/>
-      <c r="K14" s="75"/>
-      <c r="L14" s="76"/>
+      <c r="J14" s="50">
+        <v>140</v>
+      </c>
+      <c r="K14" s="75">
+        <v>120</v>
+      </c>
+      <c r="L14" s="76">
+        <v>160</v>
+      </c>
       <c r="M14" s="48">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="N14" s="39">
         <f t="shared" si="18"/>
@@ -3166,11 +3220,11 @@
       </c>
       <c r="P14" s="73">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q14" s="40">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="R14" s="51" t="e">
         <f t="shared" si="4"/>
@@ -3206,23 +3260,41 @@
       </c>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A15" s="78"/>
+      <c r="A15" s="78">
+        <v>46241</v>
+      </c>
       <c r="B15" s="47">
         <v>11</v>
       </c>
-      <c r="C15" s="57"/>
-      <c r="D15" s="74"/>
+      <c r="C15" s="57" t="s">
+        <v>105</v>
+      </c>
+      <c r="D15" s="74">
+        <v>3</v>
+      </c>
       <c r="E15" s="75"/>
       <c r="F15" s="76"/>
-      <c r="G15" s="50"/>
-      <c r="H15" s="75"/>
-      <c r="I15" s="49"/>
-      <c r="J15" s="50"/>
-      <c r="K15" s="75"/>
-      <c r="L15" s="76"/>
+      <c r="G15" s="50">
+        <v>1</v>
+      </c>
+      <c r="H15" s="75">
+        <v>3</v>
+      </c>
+      <c r="I15" s="49">
+        <v>1</v>
+      </c>
+      <c r="J15" s="50">
+        <v>3</v>
+      </c>
+      <c r="K15" s="75">
+        <v>1</v>
+      </c>
+      <c r="L15" s="76">
+        <v>1</v>
+      </c>
       <c r="M15" s="48">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>0.32500000000000001</v>
       </c>
       <c r="N15" s="39">
         <f t="shared" si="18"/>
@@ -3234,11 +3306,11 @@
       </c>
       <c r="P15" s="73">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="Q15" s="40">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="R15" s="51" t="e">
         <f t="shared" si="4"/>
@@ -3274,23 +3346,41 @@
       </c>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A16" s="78"/>
+      <c r="A16" s="78">
+        <v>46242</v>
+      </c>
       <c r="B16" s="47">
         <v>12</v>
       </c>
-      <c r="C16" s="57"/>
-      <c r="D16" s="74"/>
+      <c r="C16" s="57" t="s">
+        <v>103</v>
+      </c>
+      <c r="D16" s="74">
+        <v>120</v>
+      </c>
       <c r="E16" s="75"/>
       <c r="F16" s="76"/>
-      <c r="G16" s="50"/>
-      <c r="H16" s="75"/>
-      <c r="I16" s="49"/>
-      <c r="J16" s="50"/>
-      <c r="K16" s="75"/>
-      <c r="L16" s="76"/>
+      <c r="G16" s="50">
+        <v>120</v>
+      </c>
+      <c r="H16" s="75">
+        <v>120</v>
+      </c>
+      <c r="I16" s="49">
+        <v>120</v>
+      </c>
+      <c r="J16" s="50">
+        <v>120</v>
+      </c>
+      <c r="K16" s="75">
+        <v>120</v>
+      </c>
+      <c r="L16" s="76">
+        <v>120</v>
+      </c>
       <c r="M16" s="48">
         <f t="shared" ref="M16:M17" si="21">SUM(D16:L16)/40</f>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="N16" s="39">
         <f t="shared" si="18"/>
@@ -3302,11 +3392,11 @@
       </c>
       <c r="P16" s="73">
         <f t="shared" ref="P16:P17" si="22">SUM(G16:I16)/20</f>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Q16" s="40">
         <f t="shared" ref="Q16:Q17" si="23">SUM(J16:L16)/20</f>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="R16" s="51" t="e">
         <f t="shared" si="4"/>
@@ -3342,23 +3432,39 @@
       </c>
     </row>
     <row r="17" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A17" s="78"/>
+      <c r="A17" s="78">
+        <v>46242</v>
+      </c>
       <c r="B17" s="47">
         <v>13</v>
       </c>
-      <c r="C17" s="57"/>
+      <c r="C17" s="57" t="s">
+        <v>98</v>
+      </c>
       <c r="D17" s="74"/>
       <c r="E17" s="75"/>
       <c r="F17" s="76"/>
-      <c r="G17" s="50"/>
-      <c r="H17" s="75"/>
-      <c r="I17" s="49"/>
-      <c r="J17" s="50"/>
-      <c r="K17" s="75"/>
-      <c r="L17" s="76"/>
+      <c r="G17" s="50">
+        <v>24</v>
+      </c>
+      <c r="H17" s="75">
+        <v>4</v>
+      </c>
+      <c r="I17" s="49">
+        <v>39</v>
+      </c>
+      <c r="J17" s="50">
+        <v>38</v>
+      </c>
+      <c r="K17" s="75">
+        <v>77</v>
+      </c>
+      <c r="L17" s="76">
+        <v>80</v>
+      </c>
       <c r="M17" s="48">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="N17" s="39">
         <f t="shared" si="18"/>
@@ -3370,11 +3476,11 @@
       </c>
       <c r="P17" s="73">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="Q17" s="40">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>9.75</v>
       </c>
       <c r="R17" s="51" t="e">
         <f t="shared" si="4"/>
@@ -3410,23 +3516,39 @@
       </c>
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A18" s="78"/>
+      <c r="A18" s="78">
+        <v>46242</v>
+      </c>
       <c r="B18" s="47">
         <v>14</v>
       </c>
-      <c r="C18" s="57"/>
+      <c r="C18" s="57" t="s">
+        <v>99</v>
+      </c>
       <c r="D18" s="74"/>
       <c r="E18" s="75"/>
       <c r="F18" s="76"/>
-      <c r="G18" s="50"/>
-      <c r="H18" s="75"/>
-      <c r="I18" s="49"/>
-      <c r="J18" s="50"/>
-      <c r="K18" s="75"/>
-      <c r="L18" s="76"/>
+      <c r="G18" s="50">
+        <v>80</v>
+      </c>
+      <c r="H18" s="75">
+        <v>120</v>
+      </c>
+      <c r="I18" s="49">
+        <v>200</v>
+      </c>
+      <c r="J18" s="50">
+        <v>160</v>
+      </c>
+      <c r="K18" s="75">
+        <v>39</v>
+      </c>
+      <c r="L18" s="76">
+        <v>280</v>
+      </c>
       <c r="M18" s="48">
         <f t="shared" ref="M18:M20" si="29">SUM(D18:L18)/40</f>
-        <v>0</v>
+        <v>21.975000000000001</v>
       </c>
       <c r="N18" s="39">
         <f t="shared" si="18"/>
@@ -3438,11 +3560,11 @@
       </c>
       <c r="P18" s="73">
         <f t="shared" ref="P18:P20" si="30">SUM(G18:I18)/20</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Q18" s="40">
         <f t="shared" ref="Q18:Q20" si="31">SUM(J18:L18)/20</f>
-        <v>0</v>
+        <v>23.95</v>
       </c>
       <c r="R18" s="51" t="e">
         <f t="shared" si="4"/>
@@ -3478,23 +3600,39 @@
       </c>
     </row>
     <row r="19" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A19" s="78"/>
+      <c r="A19" s="78">
+        <v>46242</v>
+      </c>
       <c r="B19" s="47">
         <v>15</v>
       </c>
-      <c r="C19" s="57"/>
+      <c r="C19" s="57" t="s">
+        <v>100</v>
+      </c>
       <c r="D19" s="74"/>
       <c r="E19" s="75"/>
       <c r="F19" s="76"/>
-      <c r="G19" s="50"/>
-      <c r="H19" s="75"/>
-      <c r="I19" s="49"/>
-      <c r="J19" s="50"/>
-      <c r="K19" s="75"/>
-      <c r="L19" s="76"/>
+      <c r="G19" s="50">
+        <v>40</v>
+      </c>
+      <c r="H19" s="75">
+        <v>40</v>
+      </c>
+      <c r="I19" s="49">
+        <v>120</v>
+      </c>
+      <c r="J19" s="50">
+        <v>120</v>
+      </c>
+      <c r="K19" s="75">
+        <v>80</v>
+      </c>
+      <c r="L19" s="76">
+        <v>120</v>
+      </c>
       <c r="M19" s="48">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="N19" s="39">
         <f t="shared" si="18"/>
@@ -3506,11 +3644,11 @@
       </c>
       <c r="P19" s="73">
         <f t="shared" si="30"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q19" s="40">
         <f t="shared" si="31"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="R19" s="51" t="e">
         <f t="shared" si="4"/>
@@ -3546,23 +3684,37 @@
       </c>
     </row>
     <row r="20" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A20" s="78"/>
+      <c r="A20" s="78">
+        <v>46242</v>
+      </c>
       <c r="B20" s="47">
         <v>16</v>
       </c>
-      <c r="C20" s="57"/>
+      <c r="C20" s="57" t="s">
+        <v>101</v>
+      </c>
       <c r="D20" s="74"/>
       <c r="E20" s="75"/>
       <c r="F20" s="76"/>
       <c r="G20" s="50"/>
-      <c r="H20" s="75"/>
-      <c r="I20" s="49"/>
-      <c r="J20" s="50"/>
-      <c r="K20" s="75"/>
-      <c r="L20" s="76"/>
+      <c r="H20" s="75">
+        <v>120</v>
+      </c>
+      <c r="I20" s="49">
+        <v>120</v>
+      </c>
+      <c r="J20" s="50">
+        <v>120</v>
+      </c>
+      <c r="K20" s="75">
+        <v>120</v>
+      </c>
+      <c r="L20" s="76">
+        <v>120</v>
+      </c>
       <c r="M20" s="48">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="N20" s="39">
         <f t="shared" si="18"/>
@@ -3574,11 +3726,11 @@
       </c>
       <c r="P20" s="73">
         <f t="shared" si="30"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q20" s="40">
         <f t="shared" si="31"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="R20" s="51" t="e">
         <f t="shared" si="4"/>
@@ -3614,23 +3766,39 @@
       </c>
     </row>
     <row r="21" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A21" s="78"/>
+      <c r="A21" s="78">
+        <v>46242</v>
+      </c>
       <c r="B21" s="47">
         <v>17</v>
       </c>
-      <c r="C21" s="57"/>
+      <c r="C21" s="57" t="s">
+        <v>102</v>
+      </c>
       <c r="D21" s="74"/>
       <c r="E21" s="75"/>
       <c r="F21" s="76"/>
-      <c r="G21" s="50"/>
-      <c r="H21" s="75"/>
-      <c r="I21" s="49"/>
-      <c r="J21" s="50"/>
-      <c r="K21" s="75"/>
-      <c r="L21" s="76"/>
+      <c r="G21" s="50">
+        <v>600</v>
+      </c>
+      <c r="H21" s="75">
+        <v>600</v>
+      </c>
+      <c r="I21" s="49">
+        <v>2800</v>
+      </c>
+      <c r="J21" s="50">
+        <v>600</v>
+      </c>
+      <c r="K21" s="75">
+        <v>1000</v>
+      </c>
+      <c r="L21" s="76">
+        <v>2000</v>
+      </c>
       <c r="M21" s="48">
         <f t="shared" ref="M21:M23" si="37">SUM(D21:L21)/40</f>
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="N21" s="39">
         <f t="shared" si="18"/>
@@ -3642,11 +3810,11 @@
       </c>
       <c r="P21" s="73">
         <f t="shared" ref="P21:P23" si="38">SUM(G21:I21)/20</f>
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="Q21" s="40">
         <f t="shared" ref="Q21:Q23" si="39">SUM(J21:L21)/20</f>
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="R21" s="51" t="e">
         <f t="shared" si="4"/>
@@ -10895,13 +11063,13 @@
     </row>
     <row r="132" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A132" s="78"/>
-      <c r="B132" s="150" t="s">
+      <c r="B132" s="163" t="s">
         <v>11</v>
       </c>
-      <c r="C132" s="151"/>
+      <c r="C132" s="164"/>
       <c r="D132" s="84">
         <f t="shared" ref="D132:L132" si="104">SUM(D6:D60)</f>
-        <v>1880</v>
+        <v>2003</v>
       </c>
       <c r="E132" s="84">
         <f t="shared" si="104"/>
@@ -10913,31 +11081,31 @@
       </c>
       <c r="G132" s="84">
         <f t="shared" si="104"/>
-        <v>758</v>
+        <v>1903</v>
       </c>
       <c r="H132" s="84">
         <f t="shared" si="104"/>
-        <v>600</v>
+        <v>2007</v>
       </c>
       <c r="I132" s="84">
         <f t="shared" si="104"/>
-        <v>799</v>
+        <v>4359</v>
       </c>
       <c r="J132" s="84">
         <f t="shared" si="104"/>
-        <v>1560</v>
+        <v>3101</v>
       </c>
       <c r="K132" s="84">
         <f t="shared" si="104"/>
-        <v>1640</v>
+        <v>3357</v>
       </c>
       <c r="L132" s="84">
         <f t="shared" si="104"/>
-        <v>2278</v>
+        <v>5559</v>
       </c>
       <c r="M132" s="48">
         <f t="shared" ref="M132:M135" si="105">SUM(D132:L132)/40</f>
-        <v>237.875</v>
+        <v>557.22500000000002</v>
       </c>
       <c r="N132" s="39">
         <f t="shared" si="18"/>
@@ -10949,11 +11117,11 @@
       </c>
       <c r="P132" s="73">
         <f t="shared" ref="P132:P136" si="106">SUM(G132:I132)/20</f>
-        <v>107.85</v>
+        <v>413.45</v>
       </c>
       <c r="Q132" s="40">
         <f t="shared" ref="Q132:Q136" si="107">SUM(J132:L132)/20</f>
-        <v>273.89999999999998</v>
+        <v>600.85</v>
       </c>
       <c r="R132" s="51" t="e">
         <f t="shared" si="4"/>
@@ -11162,10 +11330,10 @@
       </c>
     </row>
     <row r="136" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B136" s="163" t="s">
+      <c r="B136" s="151" t="s">
         <v>71</v>
       </c>
-      <c r="C136" s="164"/>
+      <c r="C136" s="152"/>
       <c r="D136" s="83">
         <f>SUM(D134:D135)</f>
         <v>0</v>
@@ -11256,13 +11424,13 @@
       </c>
     </row>
     <row r="137" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B137" s="152" t="s">
+      <c r="B137" s="140" t="s">
         <v>11</v>
       </c>
-      <c r="C137" s="153"/>
+      <c r="C137" s="141"/>
       <c r="D137" s="85">
         <f>SUM(D132,D136)</f>
-        <v>1880</v>
+        <v>2003</v>
       </c>
       <c r="E137" s="85">
         <f t="shared" ref="E137:L137" si="112">SUM(E132,E136)</f>
@@ -11274,31 +11442,31 @@
       </c>
       <c r="G137" s="85">
         <f t="shared" si="112"/>
-        <v>758</v>
+        <v>1903</v>
       </c>
       <c r="H137" s="85">
         <f t="shared" si="112"/>
-        <v>600</v>
+        <v>2007</v>
       </c>
       <c r="I137" s="85">
         <f t="shared" si="112"/>
-        <v>799</v>
+        <v>4359</v>
       </c>
       <c r="J137" s="85">
         <f t="shared" si="112"/>
-        <v>1560</v>
+        <v>3101</v>
       </c>
       <c r="K137" s="85">
         <f t="shared" si="112"/>
-        <v>1640</v>
+        <v>3357</v>
       </c>
       <c r="L137" s="85">
         <f t="shared" si="112"/>
-        <v>2278</v>
+        <v>5559</v>
       </c>
       <c r="M137" s="60">
         <f t="shared" si="0"/>
-        <v>237.875</v>
+        <v>557.22500000000002</v>
       </c>
       <c r="N137" s="63">
         <f>SUM(N5:N136)</f>
@@ -11310,11 +11478,11 @@
       </c>
       <c r="P137" s="62">
         <f t="shared" si="113"/>
-        <v>221.7</v>
+        <v>832.9</v>
       </c>
       <c r="Q137" s="64">
         <f t="shared" si="113"/>
-        <v>551.79999999999995</v>
+        <v>1205.6999999999998</v>
       </c>
       <c r="R137" s="65" t="e">
         <f t="shared" si="113"/>
@@ -11351,17 +11519,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="R3:U3"/>
+    <mergeCell ref="V3:Y3"/>
+    <mergeCell ref="B132:C132"/>
     <mergeCell ref="B137:C137"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="P2:Q2"/>
     <mergeCell ref="M3:O3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B136:C136"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="R3:U3"/>
-    <mergeCell ref="V3:Y3"/>
-    <mergeCell ref="B132:C132"/>
   </mergeCells>
   <conditionalFormatting sqref="C45:C59">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>

--- a/Aug_2026/daily Reports/LMT Orders.xlsx
+++ b/Aug_2026/daily Reports/LMT Orders.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A7D609A-98DC-4067-B714-28E8CC9BB07D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DC7164B-940B-4FCE-A2EA-A0F7B4DB111A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="112">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -341,6 +341,24 @@
   <si>
     <t xml:space="preserve">Gorrmet Behria Town </t>
   </si>
+  <si>
+    <t>Green Velly</t>
+  </si>
+  <si>
+    <t>Rainbow Defence Road</t>
+  </si>
+  <si>
+    <t>Rainbow EME</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rainbow Wapda Town </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rainbow Model Town </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rainbow Behria Town </t>
+  </si>
 </sst>
 </file>
 
@@ -1228,7 +1246,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="174">
+  <cellXfs count="181">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1591,6 +1609,53 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="16" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1628,42 +1693,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2228,14 +2257,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="153">
+      <c r="B1" s="147">
         <f ca="1">TODAY()</f>
-        <v>46244</v>
-      </c>
-      <c r="C1" s="153"/>
-      <c r="D1" s="153"/>
-      <c r="E1" s="153"/>
-      <c r="F1" s="153"/>
+        <v>46246</v>
+      </c>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
       <c r="I1" s="10"/>
@@ -2257,10 +2286,10 @@
       <c r="Y1" s="10"/>
     </row>
     <row r="2" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="150" t="s">
+      <c r="A2" s="169" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="154" t="s">
+      <c r="B2" s="148" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2293,13 +2322,13 @@
       <c r="L2" s="15">
         <v>120</v>
       </c>
-      <c r="M2" s="142"/>
-      <c r="N2" s="143"/>
-      <c r="O2" s="144"/>
-      <c r="P2" s="145" t="s">
+      <c r="M2" s="161"/>
+      <c r="N2" s="162"/>
+      <c r="O2" s="163"/>
+      <c r="P2" s="164" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="146"/>
+      <c r="Q2" s="165"/>
       <c r="R2" s="18">
         <v>0.05</v>
       </c>
@@ -2318,8 +2347,8 @@
       <c r="Y2" s="20"/>
     </row>
     <row r="3" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="150"/>
-      <c r="B3" s="155"/>
+      <c r="A3" s="169"/>
+      <c r="B3" s="149"/>
       <c r="C3" s="23" t="s">
         <v>15</v>
       </c>
@@ -2350,29 +2379,29 @@
       <c r="L3" s="29">
         <v>72.64</v>
       </c>
-      <c r="M3" s="147" t="s">
+      <c r="M3" s="166" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="148"/>
-      <c r="O3" s="149"/>
+      <c r="N3" s="167"/>
+      <c r="O3" s="168"/>
       <c r="P3" s="71"/>
       <c r="Q3" s="72"/>
-      <c r="R3" s="157" t="s">
+      <c r="R3" s="151" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="158"/>
-      <c r="T3" s="158"/>
-      <c r="U3" s="159"/>
-      <c r="V3" s="160" t="s">
+      <c r="S3" s="152"/>
+      <c r="T3" s="152"/>
+      <c r="U3" s="153"/>
+      <c r="V3" s="154" t="s">
         <v>17</v>
       </c>
-      <c r="W3" s="161"/>
-      <c r="X3" s="161"/>
-      <c r="Y3" s="162"/>
+      <c r="W3" s="155"/>
+      <c r="X3" s="155"/>
+      <c r="Y3" s="156"/>
     </row>
     <row r="4" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="150"/>
-      <c r="B4" s="156"/>
+      <c r="A4" s="169"/>
+      <c r="B4" s="150"/>
       <c r="C4" s="30" t="s">
         <v>18</v>
       </c>
@@ -3346,36 +3375,36 @@
       </c>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A16" s="78">
-        <v>46242</v>
-      </c>
-      <c r="B16" s="47">
+      <c r="A16" s="140">
+        <v>46241</v>
+      </c>
+      <c r="B16" s="141">
         <v>12</v>
       </c>
-      <c r="C16" s="57" t="s">
+      <c r="C16" s="142" t="s">
         <v>103</v>
       </c>
-      <c r="D16" s="74">
+      <c r="D16" s="143">
         <v>120</v>
       </c>
-      <c r="E16" s="75"/>
-      <c r="F16" s="76"/>
-      <c r="G16" s="50">
+      <c r="E16" s="144"/>
+      <c r="F16" s="145"/>
+      <c r="G16" s="146">
         <v>120</v>
       </c>
-      <c r="H16" s="75">
+      <c r="H16" s="144">
         <v>120</v>
       </c>
-      <c r="I16" s="49">
+      <c r="I16" s="56">
         <v>120</v>
       </c>
-      <c r="J16" s="50">
+      <c r="J16" s="146">
         <v>120</v>
       </c>
-      <c r="K16" s="75">
+      <c r="K16" s="144">
         <v>120</v>
       </c>
-      <c r="L16" s="76">
+      <c r="L16" s="145">
         <v>120</v>
       </c>
       <c r="M16" s="48">
@@ -3432,34 +3461,34 @@
       </c>
     </row>
     <row r="17" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A17" s="78">
+      <c r="A17" s="140">
         <v>46242</v>
       </c>
-      <c r="B17" s="47">
+      <c r="B17" s="141">
         <v>13</v>
       </c>
-      <c r="C17" s="57" t="s">
+      <c r="C17" s="142" t="s">
         <v>98</v>
       </c>
-      <c r="D17" s="74"/>
-      <c r="E17" s="75"/>
-      <c r="F17" s="76"/>
-      <c r="G17" s="50">
+      <c r="D17" s="143"/>
+      <c r="E17" s="144"/>
+      <c r="F17" s="145"/>
+      <c r="G17" s="146">
         <v>24</v>
       </c>
-      <c r="H17" s="75">
+      <c r="H17" s="144">
         <v>4</v>
       </c>
-      <c r="I17" s="49">
+      <c r="I17" s="56">
         <v>39</v>
       </c>
-      <c r="J17" s="50">
+      <c r="J17" s="146">
         <v>38</v>
       </c>
-      <c r="K17" s="75">
+      <c r="K17" s="144">
         <v>77</v>
       </c>
-      <c r="L17" s="76">
+      <c r="L17" s="145">
         <v>80</v>
       </c>
       <c r="M17" s="48">
@@ -3516,34 +3545,34 @@
       </c>
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A18" s="78">
+      <c r="A18" s="140">
         <v>46242</v>
       </c>
-      <c r="B18" s="47">
+      <c r="B18" s="141">
         <v>14</v>
       </c>
-      <c r="C18" s="57" t="s">
+      <c r="C18" s="142" t="s">
         <v>99</v>
       </c>
-      <c r="D18" s="74"/>
-      <c r="E18" s="75"/>
-      <c r="F18" s="76"/>
-      <c r="G18" s="50">
+      <c r="D18" s="143"/>
+      <c r="E18" s="144"/>
+      <c r="F18" s="145"/>
+      <c r="G18" s="146">
         <v>80</v>
       </c>
-      <c r="H18" s="75">
+      <c r="H18" s="144">
         <v>120</v>
       </c>
-      <c r="I18" s="49">
+      <c r="I18" s="56">
         <v>200</v>
       </c>
-      <c r="J18" s="50">
+      <c r="J18" s="146">
         <v>160</v>
       </c>
-      <c r="K18" s="75">
+      <c r="K18" s="144">
         <v>39</v>
       </c>
-      <c r="L18" s="76">
+      <c r="L18" s="145">
         <v>280</v>
       </c>
       <c r="M18" s="48">
@@ -3600,34 +3629,34 @@
       </c>
     </row>
     <row r="19" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A19" s="78">
+      <c r="A19" s="140">
         <v>46242</v>
       </c>
-      <c r="B19" s="47">
+      <c r="B19" s="141">
         <v>15</v>
       </c>
-      <c r="C19" s="57" t="s">
+      <c r="C19" s="142" t="s">
         <v>100</v>
       </c>
-      <c r="D19" s="74"/>
-      <c r="E19" s="75"/>
-      <c r="F19" s="76"/>
-      <c r="G19" s="50">
+      <c r="D19" s="143"/>
+      <c r="E19" s="144"/>
+      <c r="F19" s="145"/>
+      <c r="G19" s="146">
         <v>40</v>
       </c>
-      <c r="H19" s="75">
+      <c r="H19" s="144">
         <v>40</v>
       </c>
-      <c r="I19" s="49">
+      <c r="I19" s="56">
         <v>120</v>
       </c>
-      <c r="J19" s="50">
+      <c r="J19" s="146">
         <v>120</v>
       </c>
-      <c r="K19" s="75">
+      <c r="K19" s="144">
         <v>80</v>
       </c>
-      <c r="L19" s="76">
+      <c r="L19" s="145">
         <v>120</v>
       </c>
       <c r="M19" s="48">
@@ -3684,32 +3713,32 @@
       </c>
     </row>
     <row r="20" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A20" s="78">
+      <c r="A20" s="140">
         <v>46242</v>
       </c>
-      <c r="B20" s="47">
+      <c r="B20" s="141">
         <v>16</v>
       </c>
-      <c r="C20" s="57" t="s">
+      <c r="C20" s="142" t="s">
         <v>101</v>
       </c>
-      <c r="D20" s="74"/>
-      <c r="E20" s="75"/>
-      <c r="F20" s="76"/>
-      <c r="G20" s="50"/>
-      <c r="H20" s="75">
+      <c r="D20" s="143"/>
+      <c r="E20" s="144"/>
+      <c r="F20" s="145"/>
+      <c r="G20" s="146"/>
+      <c r="H20" s="144">
         <v>120</v>
       </c>
-      <c r="I20" s="49">
+      <c r="I20" s="56">
         <v>120</v>
       </c>
-      <c r="J20" s="50">
+      <c r="J20" s="146">
         <v>120</v>
       </c>
-      <c r="K20" s="75">
+      <c r="K20" s="144">
         <v>120</v>
       </c>
-      <c r="L20" s="76">
+      <c r="L20" s="145">
         <v>120</v>
       </c>
       <c r="M20" s="48">
@@ -3766,34 +3795,34 @@
       </c>
     </row>
     <row r="21" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A21" s="78">
+      <c r="A21" s="140">
         <v>46242</v>
       </c>
-      <c r="B21" s="47">
+      <c r="B21" s="141">
         <v>17</v>
       </c>
-      <c r="C21" s="57" t="s">
+      <c r="C21" s="142" t="s">
         <v>102</v>
       </c>
-      <c r="D21" s="74"/>
-      <c r="E21" s="75"/>
-      <c r="F21" s="76"/>
-      <c r="G21" s="50">
+      <c r="D21" s="143"/>
+      <c r="E21" s="144"/>
+      <c r="F21" s="145"/>
+      <c r="G21" s="146">
         <v>600</v>
       </c>
-      <c r="H21" s="75">
+      <c r="H21" s="144">
         <v>600</v>
       </c>
-      <c r="I21" s="49">
+      <c r="I21" s="56">
         <v>2800</v>
       </c>
-      <c r="J21" s="50">
+      <c r="J21" s="146">
         <v>600</v>
       </c>
-      <c r="K21" s="75">
+      <c r="K21" s="144">
         <v>1000</v>
       </c>
-      <c r="L21" s="76">
+      <c r="L21" s="145">
         <v>2000</v>
       </c>
       <c r="M21" s="48">
@@ -3850,23 +3879,39 @@
       </c>
     </row>
     <row r="22" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A22" s="78"/>
+      <c r="A22" s="78">
+        <v>46244</v>
+      </c>
       <c r="B22" s="47">
         <v>18</v>
       </c>
-      <c r="C22" s="57"/>
+      <c r="C22" s="57" t="s">
+        <v>106</v>
+      </c>
       <c r="D22" s="74"/>
       <c r="E22" s="75"/>
       <c r="F22" s="76"/>
-      <c r="G22" s="50"/>
-      <c r="H22" s="75"/>
-      <c r="I22" s="49"/>
-      <c r="J22" s="50"/>
-      <c r="K22" s="75"/>
-      <c r="L22" s="76"/>
+      <c r="G22" s="50">
+        <v>120</v>
+      </c>
+      <c r="H22" s="75">
+        <v>120</v>
+      </c>
+      <c r="I22" s="49">
+        <v>120</v>
+      </c>
+      <c r="J22" s="50">
+        <v>80</v>
+      </c>
+      <c r="K22" s="75">
+        <v>80</v>
+      </c>
+      <c r="L22" s="76">
+        <v>80</v>
+      </c>
       <c r="M22" s="48">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="N22" s="39">
         <f t="shared" si="18"/>
@@ -3878,11 +3923,11 @@
       </c>
       <c r="P22" s="73">
         <f t="shared" si="38"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Q22" s="40">
         <f t="shared" si="39"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="R22" s="51" t="e">
         <f t="shared" si="4"/>
@@ -3918,23 +3963,37 @@
       </c>
     </row>
     <row r="23" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A23" s="78"/>
+      <c r="A23" s="78">
+        <v>46244</v>
+      </c>
       <c r="B23" s="47">
         <v>19</v>
       </c>
-      <c r="C23" s="57"/>
+      <c r="C23" s="57" t="s">
+        <v>107</v>
+      </c>
       <c r="D23" s="74"/>
       <c r="E23" s="75"/>
       <c r="F23" s="76"/>
       <c r="G23" s="50"/>
-      <c r="H23" s="75"/>
-      <c r="I23" s="49"/>
-      <c r="J23" s="50"/>
-      <c r="K23" s="75"/>
-      <c r="L23" s="76"/>
+      <c r="H23" s="75">
+        <v>160</v>
+      </c>
+      <c r="I23" s="49">
+        <v>200</v>
+      </c>
+      <c r="J23" s="50">
+        <v>200</v>
+      </c>
+      <c r="K23" s="75">
+        <v>240</v>
+      </c>
+      <c r="L23" s="76">
+        <v>280</v>
+      </c>
       <c r="M23" s="48">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="N23" s="39">
         <f t="shared" si="18"/>
@@ -3946,11 +4005,11 @@
       </c>
       <c r="P23" s="73">
         <f t="shared" si="38"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Q23" s="40">
         <f t="shared" si="39"/>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="R23" s="51" t="e">
         <f t="shared" si="4"/>
@@ -3986,23 +4045,37 @@
       </c>
     </row>
     <row r="24" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A24" s="78"/>
+      <c r="A24" s="78">
+        <v>46244</v>
+      </c>
       <c r="B24" s="47">
         <v>20</v>
       </c>
-      <c r="C24" s="57"/>
+      <c r="C24" s="57" t="s">
+        <v>108</v>
+      </c>
       <c r="D24" s="74"/>
       <c r="E24" s="75"/>
       <c r="F24" s="76"/>
       <c r="G24" s="50"/>
-      <c r="H24" s="75"/>
-      <c r="I24" s="49"/>
-      <c r="J24" s="50"/>
-      <c r="K24" s="75"/>
-      <c r="L24" s="76"/>
+      <c r="H24" s="75">
+        <v>80</v>
+      </c>
+      <c r="I24" s="49">
+        <v>120</v>
+      </c>
+      <c r="J24" s="50">
+        <v>40</v>
+      </c>
+      <c r="K24" s="75">
+        <v>40</v>
+      </c>
+      <c r="L24" s="76">
+        <v>120</v>
+      </c>
       <c r="M24" s="48">
         <f t="shared" ref="M24:M27" si="47">SUM(D24:L24)/40</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N24" s="39">
         <f t="shared" si="18"/>
@@ -4014,11 +4087,11 @@
       </c>
       <c r="P24" s="73">
         <f t="shared" ref="P24:P27" si="48">SUM(G24:I24)/20</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q24" s="40">
         <f t="shared" ref="Q24:Q27" si="49">SUM(J24:L24)/20</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R24" s="51" t="e">
         <f t="shared" si="4"/>
@@ -4054,23 +4127,37 @@
       </c>
     </row>
     <row r="25" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A25" s="78"/>
+      <c r="A25" s="78">
+        <v>46244</v>
+      </c>
       <c r="B25" s="47">
         <v>21</v>
       </c>
-      <c r="C25" s="57"/>
+      <c r="C25" s="57" t="s">
+        <v>109</v>
+      </c>
       <c r="D25" s="74"/>
       <c r="E25" s="75"/>
       <c r="F25" s="76"/>
-      <c r="G25" s="50"/>
+      <c r="G25" s="50">
+        <v>80</v>
+      </c>
       <c r="H25" s="75"/>
-      <c r="I25" s="49"/>
-      <c r="J25" s="50"/>
-      <c r="K25" s="75"/>
-      <c r="L25" s="76"/>
+      <c r="I25" s="49">
+        <v>200</v>
+      </c>
+      <c r="J25" s="50">
+        <v>40</v>
+      </c>
+      <c r="K25" s="75">
+        <v>80</v>
+      </c>
+      <c r="L25" s="76">
+        <v>280</v>
+      </c>
       <c r="M25" s="48">
         <f t="shared" si="47"/>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="N25" s="39">
         <f t="shared" si="18"/>
@@ -4082,11 +4169,11 @@
       </c>
       <c r="P25" s="73">
         <f t="shared" si="48"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q25" s="40">
         <f t="shared" si="49"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="R25" s="51" t="e">
         <f t="shared" si="4"/>
@@ -4122,23 +4209,37 @@
       </c>
     </row>
     <row r="26" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A26" s="78"/>
+      <c r="A26" s="78">
+        <v>46244</v>
+      </c>
       <c r="B26" s="47">
         <v>22</v>
       </c>
-      <c r="C26" s="57"/>
+      <c r="C26" s="57" t="s">
+        <v>110</v>
+      </c>
       <c r="D26" s="74"/>
       <c r="E26" s="75"/>
       <c r="F26" s="76"/>
       <c r="G26" s="50"/>
-      <c r="H26" s="75"/>
-      <c r="I26" s="49"/>
-      <c r="J26" s="50"/>
-      <c r="K26" s="75"/>
-      <c r="L26" s="76"/>
+      <c r="H26" s="75">
+        <v>80</v>
+      </c>
+      <c r="I26" s="49">
+        <v>120</v>
+      </c>
+      <c r="J26" s="50">
+        <v>40</v>
+      </c>
+      <c r="K26" s="75">
+        <v>80</v>
+      </c>
+      <c r="L26" s="76">
+        <v>40</v>
+      </c>
       <c r="M26" s="48">
         <f t="shared" si="47"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N26" s="39">
         <f t="shared" si="18"/>
@@ -4150,11 +4251,11 @@
       </c>
       <c r="P26" s="73">
         <f t="shared" si="48"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q26" s="40">
         <f t="shared" si="49"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R26" s="51" t="e">
         <f t="shared" si="4"/>
@@ -4190,23 +4291,37 @@
       </c>
     </row>
     <row r="27" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A27" s="78"/>
-      <c r="B27" s="47">
+      <c r="A27" s="140">
+        <v>46245</v>
+      </c>
+      <c r="B27" s="141">
         <v>23</v>
       </c>
-      <c r="C27" s="57"/>
-      <c r="D27" s="74"/>
-      <c r="E27" s="75"/>
-      <c r="F27" s="76"/>
-      <c r="G27" s="50"/>
-      <c r="H27" s="75"/>
-      <c r="I27" s="49"/>
-      <c r="J27" s="50"/>
-      <c r="K27" s="75"/>
-      <c r="L27" s="76"/>
+      <c r="C27" s="142" t="s">
+        <v>96</v>
+      </c>
+      <c r="D27" s="143"/>
+      <c r="E27" s="144"/>
+      <c r="F27" s="145"/>
+      <c r="G27" s="146">
+        <v>39</v>
+      </c>
+      <c r="H27" s="144">
+        <v>80</v>
+      </c>
+      <c r="I27" s="56"/>
+      <c r="J27" s="146">
+        <v>40</v>
+      </c>
+      <c r="K27" s="144">
+        <v>80</v>
+      </c>
+      <c r="L27" s="145">
+        <v>40</v>
+      </c>
       <c r="M27" s="48">
         <f t="shared" si="47"/>
-        <v>0</v>
+        <v>6.9749999999999996</v>
       </c>
       <c r="N27" s="39">
         <f t="shared" si="18"/>
@@ -4218,11 +4333,11 @@
       </c>
       <c r="P27" s="73">
         <f t="shared" si="48"/>
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="Q27" s="40">
         <f t="shared" si="49"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R27" s="51" t="e">
         <f t="shared" si="4"/>
@@ -4258,23 +4373,39 @@
       </c>
     </row>
     <row r="28" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A28" s="78"/>
-      <c r="B28" s="47">
+      <c r="A28" s="140">
+        <v>46245</v>
+      </c>
+      <c r="B28" s="141">
         <v>24</v>
       </c>
-      <c r="C28" s="57"/>
-      <c r="D28" s="74"/>
-      <c r="E28" s="75"/>
-      <c r="F28" s="76"/>
-      <c r="G28" s="50"/>
-      <c r="H28" s="75"/>
-      <c r="I28" s="49"/>
-      <c r="J28" s="50"/>
-      <c r="K28" s="75"/>
-      <c r="L28" s="76"/>
+      <c r="C28" s="142" t="s">
+        <v>111</v>
+      </c>
+      <c r="D28" s="143"/>
+      <c r="E28" s="144"/>
+      <c r="F28" s="145"/>
+      <c r="G28" s="146">
+        <v>40</v>
+      </c>
+      <c r="H28" s="144">
+        <v>40</v>
+      </c>
+      <c r="I28" s="56">
+        <v>120</v>
+      </c>
+      <c r="J28" s="146">
+        <v>120</v>
+      </c>
+      <c r="K28" s="144">
+        <v>120</v>
+      </c>
+      <c r="L28" s="145">
+        <v>120</v>
+      </c>
       <c r="M28" s="48">
         <f t="shared" ref="M28:M60" si="52">SUM(D28:L28)/40</f>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N28" s="39">
         <f t="shared" si="18"/>
@@ -4286,11 +4417,11 @@
       </c>
       <c r="P28" s="73">
         <f t="shared" ref="P28:P60" si="53">SUM(G28:I28)/20</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q28" s="40">
         <f t="shared" ref="Q28:Q60" si="54">SUM(J28:L28)/20</f>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="R28" s="51" t="e">
         <f t="shared" si="4"/>
@@ -11063,10 +11194,10 @@
     </row>
     <row r="132" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A132" s="78"/>
-      <c r="B132" s="163" t="s">
+      <c r="B132" s="157" t="s">
         <v>11</v>
       </c>
-      <c r="C132" s="164"/>
+      <c r="C132" s="158"/>
       <c r="D132" s="84">
         <f t="shared" ref="D132:L132" si="104">SUM(D6:D60)</f>
         <v>2003</v>
@@ -11081,31 +11212,31 @@
       </c>
       <c r="G132" s="84">
         <f t="shared" si="104"/>
-        <v>1903</v>
+        <v>2182</v>
       </c>
       <c r="H132" s="84">
         <f t="shared" si="104"/>
-        <v>2007</v>
+        <v>2567</v>
       </c>
       <c r="I132" s="84">
         <f t="shared" si="104"/>
-        <v>4359</v>
+        <v>5239</v>
       </c>
       <c r="J132" s="84">
         <f t="shared" si="104"/>
-        <v>3101</v>
+        <v>3661</v>
       </c>
       <c r="K132" s="84">
         <f t="shared" si="104"/>
-        <v>3357</v>
+        <v>4077</v>
       </c>
       <c r="L132" s="84">
         <f t="shared" si="104"/>
-        <v>5559</v>
+        <v>6519</v>
       </c>
       <c r="M132" s="48">
         <f t="shared" ref="M132:M135" si="105">SUM(D132:L132)/40</f>
-        <v>557.22500000000002</v>
+        <v>656.2</v>
       </c>
       <c r="N132" s="39">
         <f t="shared" si="18"/>
@@ -11117,11 +11248,11 @@
       </c>
       <c r="P132" s="73">
         <f t="shared" ref="P132:P136" si="106">SUM(G132:I132)/20</f>
-        <v>413.45</v>
+        <v>499.4</v>
       </c>
       <c r="Q132" s="40">
         <f t="shared" ref="Q132:Q136" si="107">SUM(J132:L132)/20</f>
-        <v>600.85</v>
+        <v>712.85</v>
       </c>
       <c r="R132" s="51" t="e">
         <f t="shared" si="4"/>
@@ -11330,10 +11461,10 @@
       </c>
     </row>
     <row r="136" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B136" s="151" t="s">
+      <c r="B136" s="170" t="s">
         <v>71</v>
       </c>
-      <c r="C136" s="152"/>
+      <c r="C136" s="171"/>
       <c r="D136" s="83">
         <f>SUM(D134:D135)</f>
         <v>0</v>
@@ -11424,10 +11555,10 @@
       </c>
     </row>
     <row r="137" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B137" s="140" t="s">
+      <c r="B137" s="159" t="s">
         <v>11</v>
       </c>
-      <c r="C137" s="141"/>
+      <c r="C137" s="160"/>
       <c r="D137" s="85">
         <f>SUM(D132,D136)</f>
         <v>2003</v>
@@ -11442,31 +11573,31 @@
       </c>
       <c r="G137" s="85">
         <f t="shared" si="112"/>
-        <v>1903</v>
+        <v>2182</v>
       </c>
       <c r="H137" s="85">
         <f t="shared" si="112"/>
-        <v>2007</v>
+        <v>2567</v>
       </c>
       <c r="I137" s="85">
         <f t="shared" si="112"/>
-        <v>4359</v>
+        <v>5239</v>
       </c>
       <c r="J137" s="85">
         <f t="shared" si="112"/>
-        <v>3101</v>
+        <v>3661</v>
       </c>
       <c r="K137" s="85">
         <f t="shared" si="112"/>
-        <v>3357</v>
+        <v>4077</v>
       </c>
       <c r="L137" s="85">
         <f t="shared" si="112"/>
-        <v>5559</v>
+        <v>6519</v>
       </c>
       <c r="M137" s="60">
         <f t="shared" si="0"/>
-        <v>557.22500000000002</v>
+        <v>656.2</v>
       </c>
       <c r="N137" s="63">
         <f>SUM(N5:N136)</f>
@@ -11478,11 +11609,11 @@
       </c>
       <c r="P137" s="62">
         <f t="shared" si="113"/>
-        <v>832.9</v>
+        <v>1004.8</v>
       </c>
       <c r="Q137" s="64">
         <f t="shared" si="113"/>
-        <v>1205.6999999999998</v>
+        <v>1429.6999999999998</v>
       </c>
       <c r="R137" s="65" t="e">
         <f t="shared" si="113"/>
@@ -11519,17 +11650,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="R3:U3"/>
-    <mergeCell ref="V3:Y3"/>
-    <mergeCell ref="B132:C132"/>
     <mergeCell ref="B137:C137"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="P2:Q2"/>
     <mergeCell ref="M3:O3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B136:C136"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="R3:U3"/>
+    <mergeCell ref="V3:Y3"/>
+    <mergeCell ref="B132:C132"/>
   </mergeCells>
   <conditionalFormatting sqref="C45:C59">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
@@ -11565,25 +11696,25 @@
   <sheetData>
     <row r="2" spans="3:26" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="3:26" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C3" s="167" t="s">
+      <c r="C3" s="174" t="s">
         <v>49</v>
       </c>
-      <c r="D3" s="168"/>
-      <c r="E3" s="168"/>
-      <c r="F3" s="168"/>
-      <c r="G3" s="169"/>
-      <c r="H3" s="171" t="s">
+      <c r="D3" s="175"/>
+      <c r="E3" s="175"/>
+      <c r="F3" s="175"/>
+      <c r="G3" s="176"/>
+      <c r="H3" s="178" t="s">
         <v>63</v>
       </c>
-      <c r="I3" s="172"/>
-      <c r="K3" s="173" t="s">
+      <c r="I3" s="179"/>
+      <c r="K3" s="180" t="s">
         <v>67</v>
       </c>
-      <c r="L3" s="173"/>
-      <c r="M3" s="173"/>
-      <c r="N3" s="173"/>
-      <c r="O3" s="173"/>
-      <c r="P3" s="173"/>
+      <c r="L3" s="180"/>
+      <c r="M3" s="180"/>
+      <c r="N3" s="180"/>
+      <c r="O3" s="180"/>
+      <c r="P3" s="180"/>
     </row>
     <row r="4" spans="3:26" ht="29.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C4" s="99"/>
@@ -11629,24 +11760,24 @@
         <v>50</v>
       </c>
       <c r="D5" s="88">
-        <v>165</v>
+        <v>337</v>
       </c>
       <c r="E5" s="79">
-        <v>143</v>
+        <v>567</v>
       </c>
       <c r="F5" s="79">
         <v>100</v>
       </c>
       <c r="G5" s="102">
         <f>SUM(D5:F5)</f>
-        <v>408</v>
+        <v>1004</v>
       </c>
       <c r="H5" s="95">
         <v>10000</v>
       </c>
       <c r="I5" s="96">
         <f>G5-H5</f>
-        <v>-9592</v>
+        <v>-8996</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>1</v>
@@ -11667,11 +11798,11 @@
       </c>
       <c r="D6" s="104">
         <f>D5*40</f>
-        <v>6600</v>
+        <v>13480</v>
       </c>
       <c r="E6" s="104">
         <f t="shared" ref="E6:F6" si="1">E5*40</f>
-        <v>5720</v>
+        <v>22680</v>
       </c>
       <c r="F6" s="104">
         <f t="shared" si="1"/>
@@ -11679,7 +11810,7 @@
       </c>
       <c r="G6" s="105">
         <f>SUM(D6:F6)</f>
-        <v>16320</v>
+        <v>40160</v>
       </c>
       <c r="H6" s="97">
         <f>H5*40</f>
@@ -11687,7 +11818,7 @@
       </c>
       <c r="I6" s="98">
         <f>G6-H6</f>
-        <v>-383680</v>
+        <v>-359840</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>2</v>
@@ -11804,11 +11935,11 @@
       </c>
       <c r="D9" s="106">
         <f>D8-D5</f>
-        <v>-165</v>
+        <v>-337</v>
       </c>
       <c r="E9" s="106">
         <f>E8-E5</f>
-        <v>-143</v>
+        <v>-567</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>5</v>
@@ -11884,14 +12015,14 @@
       </c>
     </row>
     <row r="11" spans="3:26" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C11" s="170" t="s">
+      <c r="C11" s="177" t="s">
         <v>60</v>
       </c>
-      <c r="D11" s="170"/>
-      <c r="F11" s="170" t="s">
+      <c r="D11" s="177"/>
+      <c r="F11" s="177" t="s">
         <v>69</v>
       </c>
-      <c r="G11" s="170"/>
+      <c r="G11" s="177"/>
       <c r="K11" s="1" t="s">
         <v>7</v>
       </c>
@@ -11936,7 +12067,7 @@
       </c>
       <c r="G12" s="91">
         <f>D12+G5</f>
-        <v>4608</v>
+        <v>5204</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>11</v>
@@ -11987,12 +12118,12 @@
       </c>
       <c r="G13" s="91">
         <f>G12*40</f>
-        <v>184320</v>
-      </c>
-      <c r="S13" s="165" t="s">
+        <v>208160</v>
+      </c>
+      <c r="S13" s="172" t="s">
         <v>86</v>
       </c>
-      <c r="T13" s="165"/>
+      <c r="T13" s="172"/>
       <c r="U13" s="135">
         <f>SUM(U8:U12)</f>
         <v>100</v>
@@ -12081,13 +12212,13 @@
       </c>
     </row>
     <row r="20" spans="4:15" ht="24" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="D20" s="166" t="s">
+      <c r="D20" s="173" t="s">
         <v>67</v>
       </c>
-      <c r="E20" s="166"/>
-      <c r="F20" s="166"/>
-      <c r="G20" s="166"/>
-      <c r="H20" s="166"/>
+      <c r="E20" s="173"/>
+      <c r="F20" s="173"/>
+      <c r="G20" s="173"/>
+      <c r="H20" s="173"/>
       <c r="K20" s="1" t="s">
         <v>4</v>
       </c>

--- a/Aug_2026/daily Reports/LMT Orders.xlsx
+++ b/Aug_2026/daily Reports/LMT Orders.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DC7164B-940B-4FCE-A2EA-A0F7B4DB111A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15766488-7FF7-492E-A89E-EF0EE2036AC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="115">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -358,6 +358,15 @@
   </si>
   <si>
     <t xml:space="preserve">Rainbow Behria Town </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Euro Rachna Block </t>
+  </si>
+  <si>
+    <t>HKB</t>
+  </si>
+  <si>
+    <t>Rainbow Barki Road</t>
   </si>
 </sst>
 </file>
@@ -4457,23 +4466,41 @@
       </c>
     </row>
     <row r="29" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A29" s="78"/>
+      <c r="A29" s="140">
+        <v>46246</v>
+      </c>
       <c r="B29" s="47">
         <v>25</v>
       </c>
-      <c r="C29" s="57"/>
-      <c r="D29" s="74"/>
+      <c r="C29" s="57" t="s">
+        <v>54</v>
+      </c>
+      <c r="D29" s="74">
+        <v>40</v>
+      </c>
       <c r="E29" s="75"/>
       <c r="F29" s="76"/>
-      <c r="G29" s="50"/>
-      <c r="H29" s="75"/>
-      <c r="I29" s="49"/>
-      <c r="J29" s="50"/>
-      <c r="K29" s="75"/>
-      <c r="L29" s="76"/>
+      <c r="G29" s="50">
+        <v>40</v>
+      </c>
+      <c r="H29" s="75">
+        <v>40</v>
+      </c>
+      <c r="I29" s="49">
+        <v>40</v>
+      </c>
+      <c r="J29" s="50">
+        <v>20</v>
+      </c>
+      <c r="K29" s="75">
+        <v>20</v>
+      </c>
+      <c r="L29" s="76">
+        <v>20</v>
+      </c>
       <c r="M29" s="48">
         <f t="shared" ref="M29" si="60">SUM(D29:L29)/40</f>
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N29" s="39">
         <f t="shared" si="18"/>
@@ -4485,11 +4512,11 @@
       </c>
       <c r="P29" s="73">
         <f t="shared" ref="P29" si="61">SUM(G29:I29)/20</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q29" s="40">
         <f t="shared" ref="Q29" si="62">SUM(J29:L29)/20</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R29" s="51" t="e">
         <f t="shared" si="4"/>
@@ -4525,23 +4552,39 @@
       </c>
     </row>
     <row r="30" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A30" s="78"/>
+      <c r="A30" s="140">
+        <v>46246</v>
+      </c>
       <c r="B30" s="47">
         <v>26</v>
       </c>
-      <c r="C30" s="57"/>
+      <c r="C30" s="57" t="s">
+        <v>112</v>
+      </c>
       <c r="D30" s="74"/>
       <c r="E30" s="75"/>
       <c r="F30" s="76"/>
-      <c r="G30" s="50"/>
-      <c r="H30" s="75"/>
-      <c r="I30" s="49"/>
-      <c r="J30" s="50"/>
-      <c r="K30" s="75"/>
-      <c r="L30" s="76"/>
+      <c r="G30" s="50">
+        <v>200</v>
+      </c>
+      <c r="H30" s="75">
+        <v>200</v>
+      </c>
+      <c r="I30" s="49">
+        <v>200</v>
+      </c>
+      <c r="J30" s="50">
+        <v>200</v>
+      </c>
+      <c r="K30" s="75">
+        <v>200</v>
+      </c>
+      <c r="L30" s="76">
+        <v>200</v>
+      </c>
       <c r="M30" s="48">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="N30" s="39">
         <f t="shared" si="18"/>
@@ -4553,11 +4596,11 @@
       </c>
       <c r="P30" s="73">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="Q30" s="40">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="R30" s="51" t="e">
         <f t="shared" si="4"/>
@@ -4593,23 +4636,39 @@
       </c>
     </row>
     <row r="31" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A31" s="78"/>
+      <c r="A31" s="140">
+        <v>46246</v>
+      </c>
       <c r="B31" s="47">
         <v>27</v>
       </c>
-      <c r="C31" s="57"/>
+      <c r="C31" s="57" t="s">
+        <v>113</v>
+      </c>
       <c r="D31" s="74"/>
       <c r="E31" s="75"/>
       <c r="F31" s="76"/>
-      <c r="G31" s="50"/>
-      <c r="H31" s="75"/>
-      <c r="I31" s="49"/>
-      <c r="J31" s="50"/>
-      <c r="K31" s="75"/>
-      <c r="L31" s="76"/>
+      <c r="G31" s="50">
+        <v>40</v>
+      </c>
+      <c r="H31" s="75">
+        <v>40</v>
+      </c>
+      <c r="I31" s="49">
+        <v>40</v>
+      </c>
+      <c r="J31" s="50">
+        <v>40</v>
+      </c>
+      <c r="K31" s="75">
+        <v>40</v>
+      </c>
+      <c r="L31" s="76">
+        <v>40</v>
+      </c>
       <c r="M31" s="48">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N31" s="39">
         <f t="shared" si="18"/>
@@ -4621,11 +4680,11 @@
       </c>
       <c r="P31" s="73">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q31" s="40">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R31" s="51" t="e">
         <f t="shared" si="4"/>
@@ -4661,23 +4720,41 @@
       </c>
     </row>
     <row r="32" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A32" s="78"/>
+      <c r="A32" s="140">
+        <v>46246</v>
+      </c>
       <c r="B32" s="47">
         <v>28</v>
       </c>
-      <c r="C32" s="57"/>
-      <c r="D32" s="74"/>
+      <c r="C32" s="57" t="s">
+        <v>33</v>
+      </c>
+      <c r="D32" s="74">
+        <v>4000</v>
+      </c>
       <c r="E32" s="75"/>
       <c r="F32" s="76"/>
-      <c r="G32" s="50"/>
-      <c r="H32" s="75"/>
-      <c r="I32" s="49"/>
-      <c r="J32" s="50"/>
-      <c r="K32" s="75"/>
-      <c r="L32" s="76"/>
+      <c r="G32" s="50">
+        <v>1600</v>
+      </c>
+      <c r="H32" s="75">
+        <v>1600</v>
+      </c>
+      <c r="I32" s="49">
+        <v>800</v>
+      </c>
+      <c r="J32" s="50">
+        <v>4000</v>
+      </c>
+      <c r="K32" s="75">
+        <v>3200</v>
+      </c>
+      <c r="L32" s="76">
+        <v>2800</v>
+      </c>
       <c r="M32" s="48">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="N32" s="39">
         <f t="shared" si="18"/>
@@ -4689,11 +4766,11 @@
       </c>
       <c r="P32" s="73">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="Q32" s="40">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="R32" s="51" t="e">
         <f t="shared" si="4"/>
@@ -4729,23 +4806,35 @@
       </c>
     </row>
     <row r="33" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A33" s="78"/>
+      <c r="A33" s="140">
+        <v>46246</v>
+      </c>
       <c r="B33" s="47">
         <v>29</v>
       </c>
-      <c r="C33" s="57"/>
+      <c r="C33" s="57" t="s">
+        <v>114</v>
+      </c>
       <c r="D33" s="74"/>
       <c r="E33" s="75"/>
       <c r="F33" s="76"/>
       <c r="G33" s="50"/>
       <c r="H33" s="75"/>
-      <c r="I33" s="49"/>
-      <c r="J33" s="50"/>
-      <c r="K33" s="75"/>
-      <c r="L33" s="76"/>
+      <c r="I33" s="49">
+        <v>200</v>
+      </c>
+      <c r="J33" s="50">
+        <v>40</v>
+      </c>
+      <c r="K33" s="75">
+        <v>40</v>
+      </c>
+      <c r="L33" s="76">
+        <v>120</v>
+      </c>
       <c r="M33" s="48">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N33" s="39">
         <f t="shared" si="18"/>
@@ -4757,11 +4846,11 @@
       </c>
       <c r="P33" s="73">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q33" s="40">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R33" s="51" t="e">
         <f t="shared" si="4"/>
@@ -4797,23 +4886,35 @@
       </c>
     </row>
     <row r="34" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A34" s="78"/>
+      <c r="A34" s="140">
+        <v>46246</v>
+      </c>
       <c r="B34" s="47">
         <v>30</v>
       </c>
-      <c r="C34" s="57"/>
+      <c r="C34" s="57" t="s">
+        <v>92</v>
+      </c>
       <c r="D34" s="74"/>
       <c r="E34" s="75"/>
       <c r="F34" s="76"/>
-      <c r="G34" s="50"/>
+      <c r="G34" s="50">
+        <v>200</v>
+      </c>
       <c r="H34" s="75"/>
-      <c r="I34" s="49"/>
-      <c r="J34" s="50"/>
+      <c r="I34" s="49">
+        <v>160</v>
+      </c>
+      <c r="J34" s="50">
+        <v>120</v>
+      </c>
       <c r="K34" s="75"/>
-      <c r="L34" s="76"/>
+      <c r="L34" s="76">
+        <v>160</v>
+      </c>
       <c r="M34" s="48">
         <f t="shared" ref="M34:M46" si="68">SUM(D34:L34)/40</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="N34" s="39">
         <f t="shared" si="18"/>
@@ -4825,11 +4926,11 @@
       </c>
       <c r="P34" s="73">
         <f t="shared" ref="P34:P46" si="69">SUM(G34:I34)/20</f>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Q34" s="40">
         <f t="shared" ref="Q34:Q46" si="70">SUM(J34:L34)/20</f>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="R34" s="51" t="e">
         <f t="shared" si="4"/>
@@ -4865,23 +4966,39 @@
       </c>
     </row>
     <row r="35" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A35" s="78"/>
+      <c r="A35" s="140">
+        <v>46246</v>
+      </c>
       <c r="B35" s="47">
         <v>31</v>
       </c>
-      <c r="C35" s="57"/>
+      <c r="C35" s="57" t="s">
+        <v>104</v>
+      </c>
       <c r="D35" s="74"/>
       <c r="E35" s="75"/>
       <c r="F35" s="76"/>
-      <c r="G35" s="50"/>
-      <c r="H35" s="75"/>
-      <c r="I35" s="49"/>
-      <c r="J35" s="50"/>
-      <c r="K35" s="75"/>
-      <c r="L35" s="76"/>
+      <c r="G35" s="50">
+        <v>120</v>
+      </c>
+      <c r="H35" s="75">
+        <v>80</v>
+      </c>
+      <c r="I35" s="49">
+        <v>40</v>
+      </c>
+      <c r="J35" s="50">
+        <v>140</v>
+      </c>
+      <c r="K35" s="75">
+        <v>120</v>
+      </c>
+      <c r="L35" s="76">
+        <v>180</v>
+      </c>
       <c r="M35" s="48">
         <f t="shared" si="68"/>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="N35" s="39">
         <f t="shared" si="18"/>
@@ -4893,11 +5010,11 @@
       </c>
       <c r="P35" s="73">
         <f t="shared" si="69"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q35" s="40">
         <f t="shared" si="70"/>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="R35" s="51" t="e">
         <f t="shared" si="4"/>
@@ -11200,7 +11317,7 @@
       <c r="C132" s="158"/>
       <c r="D132" s="84">
         <f t="shared" ref="D132:L132" si="104">SUM(D6:D60)</f>
-        <v>2003</v>
+        <v>6043</v>
       </c>
       <c r="E132" s="84">
         <f t="shared" si="104"/>
@@ -11212,31 +11329,31 @@
       </c>
       <c r="G132" s="84">
         <f t="shared" si="104"/>
-        <v>2182</v>
+        <v>4382</v>
       </c>
       <c r="H132" s="84">
         <f t="shared" si="104"/>
-        <v>2567</v>
+        <v>4527</v>
       </c>
       <c r="I132" s="84">
         <f t="shared" si="104"/>
-        <v>5239</v>
+        <v>6719</v>
       </c>
       <c r="J132" s="84">
         <f t="shared" si="104"/>
-        <v>3661</v>
+        <v>8221</v>
       </c>
       <c r="K132" s="84">
         <f t="shared" si="104"/>
-        <v>4077</v>
+        <v>7697</v>
       </c>
       <c r="L132" s="84">
         <f t="shared" si="104"/>
-        <v>6519</v>
+        <v>10039</v>
       </c>
       <c r="M132" s="48">
         <f t="shared" ref="M132:M135" si="105">SUM(D132:L132)/40</f>
-        <v>656.2</v>
+        <v>1190.7</v>
       </c>
       <c r="N132" s="39">
         <f t="shared" si="18"/>
@@ -11248,11 +11365,11 @@
       </c>
       <c r="P132" s="73">
         <f t="shared" ref="P132:P136" si="106">SUM(G132:I132)/20</f>
-        <v>499.4</v>
+        <v>781.4</v>
       </c>
       <c r="Q132" s="40">
         <f t="shared" ref="Q132:Q136" si="107">SUM(J132:L132)/20</f>
-        <v>712.85</v>
+        <v>1297.8499999999999</v>
       </c>
       <c r="R132" s="51" t="e">
         <f t="shared" si="4"/>
@@ -11561,7 +11678,7 @@
       <c r="C137" s="160"/>
       <c r="D137" s="85">
         <f>SUM(D132,D136)</f>
-        <v>2003</v>
+        <v>6043</v>
       </c>
       <c r="E137" s="85">
         <f t="shared" ref="E137:L137" si="112">SUM(E132,E136)</f>
@@ -11573,31 +11690,31 @@
       </c>
       <c r="G137" s="85">
         <f t="shared" si="112"/>
-        <v>2182</v>
+        <v>4382</v>
       </c>
       <c r="H137" s="85">
         <f t="shared" si="112"/>
-        <v>2567</v>
+        <v>4527</v>
       </c>
       <c r="I137" s="85">
         <f t="shared" si="112"/>
-        <v>5239</v>
+        <v>6719</v>
       </c>
       <c r="J137" s="85">
         <f t="shared" si="112"/>
-        <v>3661</v>
+        <v>8221</v>
       </c>
       <c r="K137" s="85">
         <f t="shared" si="112"/>
-        <v>4077</v>
+        <v>7697</v>
       </c>
       <c r="L137" s="85">
         <f t="shared" si="112"/>
-        <v>6519</v>
+        <v>10039</v>
       </c>
       <c r="M137" s="60">
         <f t="shared" si="0"/>
-        <v>656.2</v>
+        <v>1190.7</v>
       </c>
       <c r="N137" s="63">
         <f>SUM(N5:N136)</f>
@@ -11609,11 +11726,11 @@
       </c>
       <c r="P137" s="62">
         <f t="shared" si="113"/>
-        <v>1004.8</v>
+        <v>1568.8</v>
       </c>
       <c r="Q137" s="64">
         <f t="shared" si="113"/>
-        <v>1429.6999999999998</v>
+        <v>2599.6999999999998</v>
       </c>
       <c r="R137" s="65" t="e">
         <f t="shared" si="113"/>

--- a/Aug_2026/daily Reports/LMT Orders.xlsx
+++ b/Aug_2026/daily Reports/LMT Orders.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15766488-7FF7-492E-A89E-EF0EE2036AC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FFD1C9F-B857-40C1-8729-98697714846C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="117">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -169,9 +169,6 @@
   </si>
   <si>
     <t xml:space="preserve">Total </t>
-  </si>
-  <si>
-    <t>Elite Secondary MTD</t>
   </si>
   <si>
     <t>CTN'S</t>
@@ -368,6 +365,15 @@
   <si>
     <t>Rainbow Barki Road</t>
   </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Euro Fateh Ghar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jalal Sons </t>
+  </si>
 </sst>
 </file>
 
@@ -1629,6 +1635,45 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1663,45 +1708,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2067,7 +2073,7 @@
     <row r="7" spans="2:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="8" spans="2:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="2:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -2084,7 +2090,7 @@
         <v>14</v>
       </c>
       <c r="F9" s="92" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.35">
@@ -2194,17 +2200,17 @@
     </row>
     <row r="19" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B19" s="125" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="124" t="s">
         <v>54</v>
-      </c>
-      <c r="C19" s="124" t="s">
-        <v>55</v>
       </c>
       <c r="D19" s="124"/>
       <c r="E19" s="124"/>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B20" s="125" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C20" s="124"/>
       <c r="D20" s="124"/>
@@ -2212,7 +2218,7 @@
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B21" s="125" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C21" s="124"/>
       <c r="D21" s="124"/>
@@ -2220,7 +2226,7 @@
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B22" s="125" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C22" s="124"/>
       <c r="D22" s="124"/>
@@ -2228,10 +2234,10 @@
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B23" s="125" t="s">
+        <v>64</v>
+      </c>
+      <c r="C23" s="124" t="s">
         <v>65</v>
-      </c>
-      <c r="C23" s="124" t="s">
-        <v>66</v>
       </c>
       <c r="D23" s="126">
         <v>3277876231301</v>
@@ -2240,14 +2246,14 @@
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B24" s="125" t="s">
+        <v>76</v>
+      </c>
+      <c r="C24" s="124" t="s">
         <v>77</v>
-      </c>
-      <c r="C24" s="124" t="s">
-        <v>78</v>
       </c>
       <c r="D24" s="124"/>
       <c r="E24" s="124" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -2266,14 +2272,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="147">
+      <c r="B1" s="160">
         <f ca="1">TODAY()</f>
-        <v>46246</v>
-      </c>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="147"/>
+        <v>46247</v>
+      </c>
+      <c r="C1" s="160"/>
+      <c r="D1" s="160"/>
+      <c r="E1" s="160"/>
+      <c r="F1" s="160"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
       <c r="I1" s="10"/>
@@ -2295,10 +2301,10 @@
       <c r="Y1" s="10"/>
     </row>
     <row r="2" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="169" t="s">
+      <c r="A2" s="157" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="148" t="s">
+      <c r="B2" s="161" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2331,13 +2337,13 @@
       <c r="L2" s="15">
         <v>120</v>
       </c>
-      <c r="M2" s="161"/>
-      <c r="N2" s="162"/>
-      <c r="O2" s="163"/>
-      <c r="P2" s="164" t="s">
+      <c r="M2" s="149"/>
+      <c r="N2" s="150"/>
+      <c r="O2" s="151"/>
+      <c r="P2" s="152" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="165"/>
+      <c r="Q2" s="153"/>
       <c r="R2" s="18">
         <v>0.05</v>
       </c>
@@ -2356,8 +2362,8 @@
       <c r="Y2" s="20"/>
     </row>
     <row r="3" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="169"/>
-      <c r="B3" s="149"/>
+      <c r="A3" s="157"/>
+      <c r="B3" s="162"/>
       <c r="C3" s="23" t="s">
         <v>15</v>
       </c>
@@ -2388,29 +2394,29 @@
       <c r="L3" s="29">
         <v>72.64</v>
       </c>
-      <c r="M3" s="166" t="s">
+      <c r="M3" s="154" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="167"/>
-      <c r="O3" s="168"/>
+      <c r="N3" s="155"/>
+      <c r="O3" s="156"/>
       <c r="P3" s="71"/>
       <c r="Q3" s="72"/>
-      <c r="R3" s="151" t="s">
+      <c r="R3" s="164" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="152"/>
-      <c r="T3" s="152"/>
-      <c r="U3" s="153"/>
-      <c r="V3" s="154" t="s">
+      <c r="S3" s="165"/>
+      <c r="T3" s="165"/>
+      <c r="U3" s="166"/>
+      <c r="V3" s="167" t="s">
         <v>17</v>
       </c>
-      <c r="W3" s="155"/>
-      <c r="X3" s="155"/>
-      <c r="Y3" s="156"/>
+      <c r="W3" s="168"/>
+      <c r="X3" s="168"/>
+      <c r="Y3" s="169"/>
     </row>
     <row r="4" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="169"/>
-      <c r="B4" s="150"/>
+      <c r="A4" s="157"/>
+      <c r="B4" s="163"/>
       <c r="C4" s="30" t="s">
         <v>18</v>
       </c>
@@ -2489,7 +2495,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="130" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D5" s="131"/>
       <c r="E5" s="132"/>
@@ -2567,7 +2573,7 @@
         <v>2</v>
       </c>
       <c r="C6" s="57" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D6" s="74"/>
       <c r="E6" s="75"/>
@@ -2651,7 +2657,7 @@
         <v>3</v>
       </c>
       <c r="C7" s="57" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D7" s="74"/>
       <c r="E7" s="75"/>
@@ -2729,7 +2735,7 @@
         <v>4</v>
       </c>
       <c r="C8" s="57" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D8" s="74"/>
       <c r="E8" s="75"/>
@@ -2809,7 +2815,7 @@
         <v>5</v>
       </c>
       <c r="C9" s="57" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D9" s="74"/>
       <c r="E9" s="75"/>
@@ -2893,7 +2899,7 @@
         <v>6</v>
       </c>
       <c r="C10" s="57" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D10" s="74">
         <v>80</v>
@@ -2973,7 +2979,7 @@
         <v>7</v>
       </c>
       <c r="C11" s="57" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D11" s="74">
         <v>200</v>
@@ -3059,7 +3065,7 @@
         <v>8</v>
       </c>
       <c r="C12" s="57" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D12" s="74">
         <v>1600</v>
@@ -3223,7 +3229,7 @@
         <v>10</v>
       </c>
       <c r="C14" s="57" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D14" s="74"/>
       <c r="E14" s="75"/>
@@ -3305,7 +3311,7 @@
         <v>11</v>
       </c>
       <c r="C15" s="57" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D15" s="74">
         <v>3</v>
@@ -3391,7 +3397,7 @@
         <v>12</v>
       </c>
       <c r="C16" s="142" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D16" s="143">
         <v>120</v>
@@ -3477,7 +3483,7 @@
         <v>13</v>
       </c>
       <c r="C17" s="142" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D17" s="143"/>
       <c r="E17" s="144"/>
@@ -3561,7 +3567,7 @@
         <v>14</v>
       </c>
       <c r="C18" s="142" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D18" s="143"/>
       <c r="E18" s="144"/>
@@ -3645,7 +3651,7 @@
         <v>15</v>
       </c>
       <c r="C19" s="142" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D19" s="143"/>
       <c r="E19" s="144"/>
@@ -3729,7 +3735,7 @@
         <v>16</v>
       </c>
       <c r="C20" s="142" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D20" s="143"/>
       <c r="E20" s="144"/>
@@ -3811,7 +3817,7 @@
         <v>17</v>
       </c>
       <c r="C21" s="142" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D21" s="143"/>
       <c r="E21" s="144"/>
@@ -3895,7 +3901,7 @@
         <v>18</v>
       </c>
       <c r="C22" s="57" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D22" s="74"/>
       <c r="E22" s="75"/>
@@ -3979,7 +3985,7 @@
         <v>19</v>
       </c>
       <c r="C23" s="57" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D23" s="74"/>
       <c r="E23" s="75"/>
@@ -4061,7 +4067,7 @@
         <v>20</v>
       </c>
       <c r="C24" s="57" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D24" s="74"/>
       <c r="E24" s="75"/>
@@ -4143,7 +4149,7 @@
         <v>21</v>
       </c>
       <c r="C25" s="57" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D25" s="74"/>
       <c r="E25" s="75"/>
@@ -4225,7 +4231,7 @@
         <v>22</v>
       </c>
       <c r="C26" s="57" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D26" s="74"/>
       <c r="E26" s="75"/>
@@ -4300,32 +4306,32 @@
       </c>
     </row>
     <row r="27" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A27" s="140">
+      <c r="A27" s="78">
         <v>46245</v>
       </c>
-      <c r="B27" s="141">
+      <c r="B27" s="47">
         <v>23</v>
       </c>
-      <c r="C27" s="142" t="s">
-        <v>96</v>
-      </c>
-      <c r="D27" s="143"/>
-      <c r="E27" s="144"/>
-      <c r="F27" s="145"/>
-      <c r="G27" s="146">
+      <c r="C27" s="57" t="s">
+        <v>95</v>
+      </c>
+      <c r="D27" s="74"/>
+      <c r="E27" s="75"/>
+      <c r="F27" s="76"/>
+      <c r="G27" s="50">
         <v>39</v>
       </c>
-      <c r="H27" s="144">
+      <c r="H27" s="75">
         <v>80</v>
       </c>
-      <c r="I27" s="56"/>
-      <c r="J27" s="146">
+      <c r="I27" s="49"/>
+      <c r="J27" s="50">
         <v>40</v>
       </c>
-      <c r="K27" s="144">
+      <c r="K27" s="75">
         <v>80</v>
       </c>
-      <c r="L27" s="145">
+      <c r="L27" s="76">
         <v>40</v>
       </c>
       <c r="M27" s="48">
@@ -4382,34 +4388,34 @@
       </c>
     </row>
     <row r="28" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A28" s="140">
+      <c r="A28" s="78">
         <v>46245</v>
       </c>
-      <c r="B28" s="141">
+      <c r="B28" s="47">
         <v>24</v>
       </c>
-      <c r="C28" s="142" t="s">
-        <v>111</v>
-      </c>
-      <c r="D28" s="143"/>
-      <c r="E28" s="144"/>
-      <c r="F28" s="145"/>
-      <c r="G28" s="146">
+      <c r="C28" s="57" t="s">
+        <v>110</v>
+      </c>
+      <c r="D28" s="74"/>
+      <c r="E28" s="75"/>
+      <c r="F28" s="76"/>
+      <c r="G28" s="50">
         <v>40</v>
       </c>
-      <c r="H28" s="144">
+      <c r="H28" s="75">
         <v>40</v>
       </c>
-      <c r="I28" s="56">
+      <c r="I28" s="49">
         <v>120</v>
       </c>
-      <c r="J28" s="146">
+      <c r="J28" s="50">
         <v>120</v>
       </c>
-      <c r="K28" s="144">
+      <c r="K28" s="75">
         <v>120</v>
       </c>
-      <c r="L28" s="145">
+      <c r="L28" s="76">
         <v>120</v>
       </c>
       <c r="M28" s="48">
@@ -4473,29 +4479,29 @@
         <v>25</v>
       </c>
       <c r="C29" s="57" t="s">
-        <v>54</v>
-      </c>
-      <c r="D29" s="74">
+        <v>53</v>
+      </c>
+      <c r="D29" s="143">
         <v>40</v>
       </c>
-      <c r="E29" s="75"/>
-      <c r="F29" s="76"/>
-      <c r="G29" s="50">
+      <c r="E29" s="144"/>
+      <c r="F29" s="145"/>
+      <c r="G29" s="146">
         <v>40</v>
       </c>
-      <c r="H29" s="75">
+      <c r="H29" s="144">
         <v>40</v>
       </c>
-      <c r="I29" s="49">
+      <c r="I29" s="56">
         <v>40</v>
       </c>
-      <c r="J29" s="50">
+      <c r="J29" s="146">
         <v>20</v>
       </c>
-      <c r="K29" s="75">
+      <c r="K29" s="144">
         <v>20</v>
       </c>
-      <c r="L29" s="76">
+      <c r="L29" s="145">
         <v>20</v>
       </c>
       <c r="M29" s="48">
@@ -4559,27 +4565,27 @@
         <v>26</v>
       </c>
       <c r="C30" s="57" t="s">
-        <v>112</v>
-      </c>
-      <c r="D30" s="74"/>
-      <c r="E30" s="75"/>
-      <c r="F30" s="76"/>
-      <c r="G30" s="50">
+        <v>111</v>
+      </c>
+      <c r="D30" s="143"/>
+      <c r="E30" s="144"/>
+      <c r="F30" s="145"/>
+      <c r="G30" s="146">
         <v>200</v>
       </c>
-      <c r="H30" s="75">
+      <c r="H30" s="144">
         <v>200</v>
       </c>
-      <c r="I30" s="49">
+      <c r="I30" s="56">
         <v>200</v>
       </c>
-      <c r="J30" s="50">
+      <c r="J30" s="146">
         <v>200</v>
       </c>
-      <c r="K30" s="75">
+      <c r="K30" s="144">
         <v>200</v>
       </c>
-      <c r="L30" s="76">
+      <c r="L30" s="145">
         <v>200</v>
       </c>
       <c r="M30" s="48">
@@ -4643,27 +4649,27 @@
         <v>27</v>
       </c>
       <c r="C31" s="57" t="s">
-        <v>113</v>
-      </c>
-      <c r="D31" s="74"/>
-      <c r="E31" s="75"/>
-      <c r="F31" s="76"/>
-      <c r="G31" s="50">
+        <v>112</v>
+      </c>
+      <c r="D31" s="143"/>
+      <c r="E31" s="144"/>
+      <c r="F31" s="145"/>
+      <c r="G31" s="146">
         <v>40</v>
       </c>
-      <c r="H31" s="75">
+      <c r="H31" s="144">
         <v>40</v>
       </c>
-      <c r="I31" s="49">
+      <c r="I31" s="56">
         <v>40</v>
       </c>
-      <c r="J31" s="50">
+      <c r="J31" s="146">
         <v>40</v>
       </c>
-      <c r="K31" s="75">
+      <c r="K31" s="144">
         <v>40</v>
       </c>
-      <c r="L31" s="76">
+      <c r="L31" s="145">
         <v>40</v>
       </c>
       <c r="M31" s="48">
@@ -4727,34 +4733,28 @@
         <v>28</v>
       </c>
       <c r="C32" s="57" t="s">
-        <v>33</v>
-      </c>
-      <c r="D32" s="74">
-        <v>4000</v>
-      </c>
-      <c r="E32" s="75"/>
-      <c r="F32" s="76"/>
-      <c r="G32" s="50">
-        <v>1600</v>
-      </c>
-      <c r="H32" s="75">
-        <v>1600</v>
-      </c>
-      <c r="I32" s="49">
-        <v>800</v>
-      </c>
-      <c r="J32" s="50">
-        <v>4000</v>
-      </c>
-      <c r="K32" s="75">
-        <v>3200</v>
-      </c>
-      <c r="L32" s="76">
-        <v>2800</v>
+        <v>91</v>
+      </c>
+      <c r="D32" s="143"/>
+      <c r="E32" s="144"/>
+      <c r="F32" s="145"/>
+      <c r="G32" s="146">
+        <v>200</v>
+      </c>
+      <c r="H32" s="144"/>
+      <c r="I32" s="56">
+        <v>160</v>
+      </c>
+      <c r="J32" s="146">
+        <v>120</v>
+      </c>
+      <c r="K32" s="144"/>
+      <c r="L32" s="145">
+        <v>160</v>
       </c>
       <c r="M32" s="48">
         <f t="shared" si="52"/>
-        <v>450</v>
+        <v>16</v>
       </c>
       <c r="N32" s="39">
         <f t="shared" si="18"/>
@@ -4766,11 +4766,11 @@
       </c>
       <c r="P32" s="73">
         <f t="shared" si="53"/>
-        <v>200</v>
+        <v>18</v>
       </c>
       <c r="Q32" s="40">
         <f t="shared" si="54"/>
-        <v>500</v>
+        <v>14</v>
       </c>
       <c r="R32" s="51" t="e">
         <f t="shared" si="4"/>
@@ -4813,28 +4813,32 @@
         <v>29</v>
       </c>
       <c r="C33" s="57" t="s">
-        <v>114</v>
-      </c>
-      <c r="D33" s="74"/>
-      <c r="E33" s="75"/>
-      <c r="F33" s="76"/>
-      <c r="G33" s="50"/>
-      <c r="H33" s="75"/>
-      <c r="I33" s="49">
-        <v>200</v>
-      </c>
-      <c r="J33" s="50">
+        <v>103</v>
+      </c>
+      <c r="D33" s="143"/>
+      <c r="E33" s="144"/>
+      <c r="F33" s="145"/>
+      <c r="G33" s="146">
+        <v>120</v>
+      </c>
+      <c r="H33" s="144">
+        <v>80</v>
+      </c>
+      <c r="I33" s="56">
         <v>40</v>
       </c>
-      <c r="K33" s="75">
-        <v>40</v>
-      </c>
-      <c r="L33" s="76">
+      <c r="J33" s="146">
+        <v>140</v>
+      </c>
+      <c r="K33" s="144">
         <v>120</v>
+      </c>
+      <c r="L33" s="145">
+        <v>180</v>
       </c>
       <c r="M33" s="48">
         <f t="shared" si="52"/>
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="N33" s="39">
         <f t="shared" si="18"/>
@@ -4846,11 +4850,11 @@
       </c>
       <c r="P33" s="73">
         <f t="shared" si="53"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Q33" s="40">
         <f t="shared" si="54"/>
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="R33" s="51" t="e">
         <f t="shared" si="4"/>
@@ -4893,28 +4897,34 @@
         <v>30</v>
       </c>
       <c r="C34" s="57" t="s">
-        <v>92</v>
-      </c>
-      <c r="D34" s="74"/>
+        <v>33</v>
+      </c>
+      <c r="D34" s="74">
+        <v>4000</v>
+      </c>
       <c r="E34" s="75"/>
       <c r="F34" s="76"/>
       <c r="G34" s="50">
-        <v>200</v>
-      </c>
-      <c r="H34" s="75"/>
+        <v>1600</v>
+      </c>
+      <c r="H34" s="75">
+        <v>1600</v>
+      </c>
       <c r="I34" s="49">
-        <v>160</v>
+        <v>800</v>
       </c>
       <c r="J34" s="50">
-        <v>120</v>
-      </c>
-      <c r="K34" s="75"/>
+        <v>4000</v>
+      </c>
+      <c r="K34" s="75">
+        <v>3200</v>
+      </c>
       <c r="L34" s="76">
-        <v>160</v>
+        <v>2800</v>
       </c>
       <c r="M34" s="48">
         <f t="shared" ref="M34:M46" si="68">SUM(D34:L34)/40</f>
-        <v>16</v>
+        <v>450</v>
       </c>
       <c r="N34" s="39">
         <f t="shared" si="18"/>
@@ -4926,11 +4936,11 @@
       </c>
       <c r="P34" s="73">
         <f t="shared" ref="P34:P46" si="69">SUM(G34:I34)/20</f>
-        <v>18</v>
+        <v>200</v>
       </c>
       <c r="Q34" s="40">
         <f t="shared" ref="Q34:Q46" si="70">SUM(J34:L34)/20</f>
-        <v>14</v>
+        <v>500</v>
       </c>
       <c r="R34" s="51" t="e">
         <f t="shared" si="4"/>
@@ -4966,39 +4976,35 @@
       </c>
     </row>
     <row r="35" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A35" s="140">
-        <v>46246</v>
+      <c r="A35" s="78">
+        <v>46247</v>
       </c>
       <c r="B35" s="47">
         <v>31</v>
       </c>
       <c r="C35" s="57" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="D35" s="74"/>
       <c r="E35" s="75"/>
       <c r="F35" s="76"/>
-      <c r="G35" s="50">
+      <c r="G35" s="50"/>
+      <c r="H35" s="75"/>
+      <c r="I35" s="49">
+        <v>200</v>
+      </c>
+      <c r="J35" s="50">
+        <v>40</v>
+      </c>
+      <c r="K35" s="75">
+        <v>40</v>
+      </c>
+      <c r="L35" s="76">
         <v>120</v>
-      </c>
-      <c r="H35" s="75">
-        <v>80</v>
-      </c>
-      <c r="I35" s="49">
-        <v>40</v>
-      </c>
-      <c r="J35" s="50">
-        <v>140</v>
-      </c>
-      <c r="K35" s="75">
-        <v>120</v>
-      </c>
-      <c r="L35" s="76">
-        <v>180</v>
       </c>
       <c r="M35" s="48">
         <f t="shared" si="68"/>
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="N35" s="39">
         <f t="shared" si="18"/>
@@ -5010,11 +5016,11 @@
       </c>
       <c r="P35" s="73">
         <f t="shared" si="69"/>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Q35" s="40">
         <f t="shared" si="70"/>
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="R35" s="51" t="e">
         <f t="shared" si="4"/>
@@ -5050,23 +5056,41 @@
       </c>
     </row>
     <row r="36" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A36" s="78"/>
+      <c r="A36" s="78">
+        <v>46247</v>
+      </c>
       <c r="B36" s="47">
         <v>32</v>
       </c>
-      <c r="C36" s="57"/>
-      <c r="D36" s="74"/>
+      <c r="C36" s="57" t="s">
+        <v>115</v>
+      </c>
+      <c r="D36" s="74">
+        <v>40</v>
+      </c>
       <c r="E36" s="75"/>
       <c r="F36" s="76"/>
-      <c r="G36" s="50"/>
-      <c r="H36" s="75"/>
-      <c r="I36" s="49"/>
-      <c r="J36" s="50"/>
-      <c r="K36" s="75"/>
-      <c r="L36" s="76"/>
+      <c r="G36" s="50">
+        <v>40</v>
+      </c>
+      <c r="H36" s="75">
+        <v>40</v>
+      </c>
+      <c r="I36" s="49">
+        <v>40</v>
+      </c>
+      <c r="J36" s="50">
+        <v>40</v>
+      </c>
+      <c r="K36" s="75">
+        <v>40</v>
+      </c>
+      <c r="L36" s="76">
+        <v>40</v>
+      </c>
       <c r="M36" s="48">
         <f t="shared" si="68"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N36" s="39">
         <f t="shared" si="18"/>
@@ -5078,11 +5102,11 @@
       </c>
       <c r="P36" s="73">
         <f t="shared" si="69"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q36" s="40">
         <f t="shared" si="70"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R36" s="51" t="e">
         <f t="shared" si="4"/>
@@ -5118,23 +5142,39 @@
       </c>
     </row>
     <row r="37" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A37" s="78"/>
+      <c r="A37" s="78">
+        <v>46247</v>
+      </c>
       <c r="B37" s="47">
         <v>33</v>
       </c>
-      <c r="C37" s="57"/>
+      <c r="C37" s="57" t="s">
+        <v>116</v>
+      </c>
       <c r="D37" s="74"/>
       <c r="E37" s="75"/>
       <c r="F37" s="76"/>
-      <c r="G37" s="50"/>
-      <c r="H37" s="75"/>
-      <c r="I37" s="49"/>
-      <c r="J37" s="50"/>
-      <c r="K37" s="75"/>
-      <c r="L37" s="76"/>
+      <c r="G37" s="50">
+        <v>40</v>
+      </c>
+      <c r="H37" s="75">
+        <v>40</v>
+      </c>
+      <c r="I37" s="49">
+        <v>40</v>
+      </c>
+      <c r="J37" s="50">
+        <v>40</v>
+      </c>
+      <c r="K37" s="75">
+        <v>40</v>
+      </c>
+      <c r="L37" s="76">
+        <v>40</v>
+      </c>
       <c r="M37" s="48">
         <f t="shared" si="68"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N37" s="39">
         <f t="shared" si="18"/>
@@ -5146,11 +5186,11 @@
       </c>
       <c r="P37" s="73">
         <f t="shared" si="69"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q37" s="40">
         <f t="shared" si="70"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R37" s="51" t="e">
         <f t="shared" si="4"/>
@@ -11311,13 +11351,13 @@
     </row>
     <row r="132" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A132" s="78"/>
-      <c r="B132" s="157" t="s">
+      <c r="B132" s="170" t="s">
         <v>11</v>
       </c>
-      <c r="C132" s="158"/>
+      <c r="C132" s="171"/>
       <c r="D132" s="84">
         <f t="shared" ref="D132:L132" si="104">SUM(D6:D60)</f>
-        <v>6043</v>
+        <v>6083</v>
       </c>
       <c r="E132" s="84">
         <f t="shared" si="104"/>
@@ -11329,31 +11369,31 @@
       </c>
       <c r="G132" s="84">
         <f t="shared" si="104"/>
-        <v>4382</v>
+        <v>4462</v>
       </c>
       <c r="H132" s="84">
         <f t="shared" si="104"/>
-        <v>4527</v>
+        <v>4607</v>
       </c>
       <c r="I132" s="84">
         <f t="shared" si="104"/>
-        <v>6719</v>
+        <v>6799</v>
       </c>
       <c r="J132" s="84">
         <f t="shared" si="104"/>
-        <v>8221</v>
+        <v>8301</v>
       </c>
       <c r="K132" s="84">
         <f t="shared" si="104"/>
-        <v>7697</v>
+        <v>7777</v>
       </c>
       <c r="L132" s="84">
         <f t="shared" si="104"/>
-        <v>10039</v>
+        <v>10119</v>
       </c>
       <c r="M132" s="48">
         <f t="shared" ref="M132:M135" si="105">SUM(D132:L132)/40</f>
-        <v>1190.7</v>
+        <v>1203.7</v>
       </c>
       <c r="N132" s="39">
         <f t="shared" si="18"/>
@@ -11365,11 +11405,11 @@
       </c>
       <c r="P132" s="73">
         <f t="shared" ref="P132:P136" si="106">SUM(G132:I132)/20</f>
-        <v>781.4</v>
+        <v>793.4</v>
       </c>
       <c r="Q132" s="40">
         <f t="shared" ref="Q132:Q136" si="107">SUM(J132:L132)/20</f>
-        <v>1297.8499999999999</v>
+        <v>1309.8499999999999</v>
       </c>
       <c r="R132" s="51" t="e">
         <f t="shared" si="4"/>
@@ -11410,7 +11450,7 @@
         <v>0</v>
       </c>
       <c r="C133" s="57" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D133" s="108"/>
       <c r="E133" s="109"/>
@@ -11578,10 +11618,10 @@
       </c>
     </row>
     <row r="136" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B136" s="170" t="s">
-        <v>71</v>
-      </c>
-      <c r="C136" s="171"/>
+      <c r="B136" s="158" t="s">
+        <v>70</v>
+      </c>
+      <c r="C136" s="159"/>
       <c r="D136" s="83">
         <f>SUM(D134:D135)</f>
         <v>0</v>
@@ -11672,13 +11712,13 @@
       </c>
     </row>
     <row r="137" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B137" s="159" t="s">
+      <c r="B137" s="147" t="s">
         <v>11</v>
       </c>
-      <c r="C137" s="160"/>
+      <c r="C137" s="148"/>
       <c r="D137" s="85">
         <f>SUM(D132,D136)</f>
-        <v>6043</v>
+        <v>6083</v>
       </c>
       <c r="E137" s="85">
         <f t="shared" ref="E137:L137" si="112">SUM(E132,E136)</f>
@@ -11690,31 +11730,31 @@
       </c>
       <c r="G137" s="85">
         <f t="shared" si="112"/>
-        <v>4382</v>
+        <v>4462</v>
       </c>
       <c r="H137" s="85">
         <f t="shared" si="112"/>
-        <v>4527</v>
+        <v>4607</v>
       </c>
       <c r="I137" s="85">
         <f t="shared" si="112"/>
-        <v>6719</v>
+        <v>6799</v>
       </c>
       <c r="J137" s="85">
         <f t="shared" si="112"/>
-        <v>8221</v>
+        <v>8301</v>
       </c>
       <c r="K137" s="85">
         <f t="shared" si="112"/>
-        <v>7697</v>
+        <v>7777</v>
       </c>
       <c r="L137" s="85">
         <f t="shared" si="112"/>
-        <v>10039</v>
+        <v>10119</v>
       </c>
       <c r="M137" s="60">
         <f t="shared" si="0"/>
-        <v>1190.7</v>
+        <v>1203.7</v>
       </c>
       <c r="N137" s="63">
         <f>SUM(N5:N136)</f>
@@ -11726,11 +11766,11 @@
       </c>
       <c r="P137" s="62">
         <f t="shared" si="113"/>
-        <v>1568.8</v>
+        <v>1592.8</v>
       </c>
       <c r="Q137" s="64">
         <f t="shared" si="113"/>
-        <v>2599.6999999999998</v>
+        <v>2623.7</v>
       </c>
       <c r="R137" s="65" t="e">
         <f t="shared" si="113"/>
@@ -11767,17 +11807,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="R3:U3"/>
+    <mergeCell ref="V3:Y3"/>
+    <mergeCell ref="B132:C132"/>
     <mergeCell ref="B137:C137"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="P2:Q2"/>
     <mergeCell ref="M3:O3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B136:C136"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="R3:U3"/>
-    <mergeCell ref="V3:Y3"/>
-    <mergeCell ref="B132:C132"/>
   </mergeCells>
   <conditionalFormatting sqref="C45:C59">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
@@ -11814,18 +11854,18 @@
     <row r="2" spans="3:26" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="3:26" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C3" s="174" t="s">
-        <v>49</v>
+        <v>114</v>
       </c>
       <c r="D3" s="175"/>
       <c r="E3" s="175"/>
       <c r="F3" s="175"/>
       <c r="G3" s="176"/>
       <c r="H3" s="178" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I3" s="179"/>
       <c r="K3" s="180" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="L3" s="180"/>
       <c r="M3" s="180"/>
@@ -11842,16 +11882,16 @@
         <v>47</v>
       </c>
       <c r="F4" s="80" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G4" s="100" t="s">
         <v>48</v>
       </c>
       <c r="H4" s="93" t="s">
+        <v>62</v>
+      </c>
+      <c r="I4" s="94" t="s">
         <v>63</v>
-      </c>
-      <c r="I4" s="94" t="s">
-        <v>64</v>
       </c>
       <c r="K4" s="3" t="s">
         <v>0</v>
@@ -11866,35 +11906,35 @@
         <v>10</v>
       </c>
       <c r="O4" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="P4" s="138" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="3:26" ht="32" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C5" s="101" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D5" s="88">
-        <v>337</v>
+        <v>366</v>
       </c>
       <c r="E5" s="79">
-        <v>567</v>
+        <v>641</v>
       </c>
       <c r="F5" s="79">
-        <v>100</v>
+        <v>550</v>
       </c>
       <c r="G5" s="102">
         <f>SUM(D5:F5)</f>
-        <v>1004</v>
+        <v>1557</v>
       </c>
       <c r="H5" s="95">
         <v>10000</v>
       </c>
       <c r="I5" s="96">
         <f>G5-H5</f>
-        <v>-8996</v>
+        <v>-8443</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>1</v>
@@ -11911,23 +11951,23 @@
     </row>
     <row r="6" spans="3:26" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="C6" s="103" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D6" s="104">
         <f>D5*40</f>
-        <v>13480</v>
+        <v>14640</v>
       </c>
       <c r="E6" s="104">
         <f t="shared" ref="E6:F6" si="1">E5*40</f>
-        <v>22680</v>
+        <v>25640</v>
       </c>
       <c r="F6" s="104">
         <f t="shared" si="1"/>
-        <v>4000</v>
+        <v>22000</v>
       </c>
       <c r="G6" s="105">
         <f>SUM(D6:F6)</f>
-        <v>40160</v>
+        <v>62280</v>
       </c>
       <c r="H6" s="97">
         <f>H5*40</f>
@@ -11935,7 +11975,7 @@
       </c>
       <c r="I6" s="98">
         <f>G6-H6</f>
-        <v>-359840</v>
+        <v>-337720</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>2</v>
@@ -11982,33 +12022,33 @@
       </c>
       <c r="O7" s="81"/>
       <c r="S7" s="136" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="T7" s="136" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="U7" s="77" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="V7" s="136" t="s">
+        <v>84</v>
+      </c>
+      <c r="W7" s="136" t="s">
+        <v>83</v>
+      </c>
+      <c r="X7" s="136" t="s">
+        <v>83</v>
+      </c>
+      <c r="Y7" s="136" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z7" s="136" t="s">
         <v>85</v>
-      </c>
-      <c r="W7" s="136" t="s">
-        <v>84</v>
-      </c>
-      <c r="X7" s="136" t="s">
-        <v>84</v>
-      </c>
-      <c r="Y7" s="136" t="s">
-        <v>84</v>
-      </c>
-      <c r="Z7" s="136" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="8" spans="3:26" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="C8" s="82" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K8" s="1" t="s">
         <v>4</v>
@@ -12026,7 +12066,7 @@
         <v>120</v>
       </c>
       <c r="T8" s="79" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="U8" s="135">
         <v>50</v>
@@ -12048,15 +12088,15 @@
     </row>
     <row r="9" spans="3:26" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="C9" s="82" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D9" s="106">
         <f>D8-D5</f>
-        <v>-337</v>
+        <v>-366</v>
       </c>
       <c r="E9" s="106">
         <f>E8-E5</f>
-        <v>-567</v>
+        <v>-641</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>5</v>
@@ -12113,7 +12153,7 @@
         <v>120</v>
       </c>
       <c r="T10" s="79" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="U10" s="135"/>
       <c r="V10" s="79">
@@ -12133,11 +12173,11 @@
     </row>
     <row r="11" spans="3:26" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="C11" s="177" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D11" s="177"/>
       <c r="F11" s="177" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G11" s="177"/>
       <c r="K11" s="1" t="s">
@@ -12156,7 +12196,7 @@
         <v>70</v>
       </c>
       <c r="T11" s="79" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="U11" s="135"/>
       <c r="V11" s="79"/>
@@ -12174,17 +12214,17 @@
     </row>
     <row r="12" spans="3:26" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="C12" s="89" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D12" s="87">
         <v>4200</v>
       </c>
       <c r="F12" s="89" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G12" s="91">
         <f>D12+G5</f>
-        <v>5204</v>
+        <v>5757</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>11</v>
@@ -12206,7 +12246,7 @@
         <v>70</v>
       </c>
       <c r="T12" s="79" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U12" s="135"/>
       <c r="V12" s="79"/>
@@ -12224,21 +12264,21 @@
     </row>
     <row r="13" spans="3:26" ht="18.5" x14ac:dyDescent="0.35">
       <c r="C13" s="90" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D13" s="91">
         <f>D12*40</f>
         <v>168000</v>
       </c>
       <c r="F13" s="90" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G13" s="91">
         <f>G12*40</f>
-        <v>208160</v>
+        <v>230280</v>
       </c>
       <c r="S13" s="172" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="T13" s="172"/>
       <c r="U13" s="135">
@@ -12268,19 +12308,19 @@
     </row>
     <row r="16" spans="3:26" ht="24" thickBot="1" x14ac:dyDescent="0.6">
       <c r="K16" s="117" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L16" s="117" t="s">
         <v>8</v>
       </c>
       <c r="M16" s="117" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N16" s="117" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O16" s="117" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" spans="4:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
@@ -12313,7 +12353,7 @@
     </row>
     <row r="19" spans="4:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="F19" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K19" s="1" t="s">
         <v>3</v>
@@ -12330,7 +12370,7 @@
     </row>
     <row r="20" spans="4:15" ht="24" thickBot="1" x14ac:dyDescent="0.6">
       <c r="D20" s="173" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E20" s="173"/>
       <c r="F20" s="173"/>
@@ -12363,7 +12403,7 @@
         <v>10</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K21" s="1" t="s">
         <v>5</v>
@@ -12444,7 +12484,7 @@
       </c>
       <c r="H24" s="81"/>
       <c r="K24" s="118" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L24" s="119"/>
       <c r="M24" s="120">
@@ -12474,7 +12514,7 @@
       </c>
       <c r="H25" s="81"/>
       <c r="K25" s="118" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L25" s="119"/>
       <c r="M25" s="120">

--- a/Aug_2026/daily Reports/LMT Orders.xlsx
+++ b/Aug_2026/daily Reports/LMT Orders.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FFD1C9F-B857-40C1-8729-98697714846C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28F28180-5C85-4877-AB2F-38D34BF5526A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="118">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -366,13 +366,16 @@
     <t>Rainbow Barki Road</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
     <t>Euro Fateh Ghar</t>
   </si>
   <si>
     <t xml:space="preserve">Jalal Sons </t>
+  </si>
+  <si>
+    <t>Gourmet Barkii Road As</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Till To Date </t>
   </si>
 </sst>
 </file>
@@ -1635,6 +1638,42 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1672,42 +1711,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2264,7 +2267,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Y137"/>
+  <dimension ref="A1:Y138"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="30.90625" bestFit="1" customWidth="1"/>
@@ -2272,14 +2275,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="160">
+      <c r="B1" s="147">
         <f ca="1">TODAY()</f>
-        <v>46247</v>
-      </c>
-      <c r="C1" s="160"/>
-      <c r="D1" s="160"/>
-      <c r="E1" s="160"/>
-      <c r="F1" s="160"/>
+        <v>46249</v>
+      </c>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
       <c r="I1" s="10"/>
@@ -2301,10 +2304,10 @@
       <c r="Y1" s="10"/>
     </row>
     <row r="2" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="157" t="s">
+      <c r="A2" s="169" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="161" t="s">
+      <c r="B2" s="148" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2337,13 +2340,13 @@
       <c r="L2" s="15">
         <v>120</v>
       </c>
-      <c r="M2" s="149"/>
-      <c r="N2" s="150"/>
-      <c r="O2" s="151"/>
-      <c r="P2" s="152" t="s">
+      <c r="M2" s="161"/>
+      <c r="N2" s="162"/>
+      <c r="O2" s="163"/>
+      <c r="P2" s="164" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="153"/>
+      <c r="Q2" s="165"/>
       <c r="R2" s="18">
         <v>0.05</v>
       </c>
@@ -2362,8 +2365,8 @@
       <c r="Y2" s="20"/>
     </row>
     <row r="3" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="157"/>
-      <c r="B3" s="162"/>
+      <c r="A3" s="169"/>
+      <c r="B3" s="149"/>
       <c r="C3" s="23" t="s">
         <v>15</v>
       </c>
@@ -2394,29 +2397,29 @@
       <c r="L3" s="29">
         <v>72.64</v>
       </c>
-      <c r="M3" s="154" t="s">
+      <c r="M3" s="166" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="155"/>
-      <c r="O3" s="156"/>
+      <c r="N3" s="167"/>
+      <c r="O3" s="168"/>
       <c r="P3" s="71"/>
       <c r="Q3" s="72"/>
-      <c r="R3" s="164" t="s">
+      <c r="R3" s="151" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="165"/>
-      <c r="T3" s="165"/>
-      <c r="U3" s="166"/>
-      <c r="V3" s="167" t="s">
+      <c r="S3" s="152"/>
+      <c r="T3" s="152"/>
+      <c r="U3" s="153"/>
+      <c r="V3" s="154" t="s">
         <v>17</v>
       </c>
-      <c r="W3" s="168"/>
-      <c r="X3" s="168"/>
-      <c r="Y3" s="169"/>
+      <c r="W3" s="155"/>
+      <c r="X3" s="155"/>
+      <c r="Y3" s="156"/>
     </row>
     <row r="4" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="157"/>
-      <c r="B4" s="163"/>
+      <c r="A4" s="169"/>
+      <c r="B4" s="150"/>
       <c r="C4" s="30" t="s">
         <v>18</v>
       </c>
@@ -2597,7 +2600,7 @@
         <v>200</v>
       </c>
       <c r="M6" s="48">
-        <f t="shared" ref="M6:M137" si="0">SUM(D6:L6)/40</f>
+        <f t="shared" ref="M6:M138" si="0">SUM(D6:L6)/40</f>
         <v>24</v>
       </c>
       <c r="N6" s="39">
@@ -2605,7 +2608,7 @@
         <v>0</v>
       </c>
       <c r="O6" s="49">
-        <f t="shared" ref="O6:O136" si="1">SUMPRODUCT($D$3:$L$3,$D$6:$L$6)/1000</f>
+        <f t="shared" ref="O6:O137" si="1">SUMPRODUCT($D$3:$L$3,$D$6:$L$6)/1000</f>
         <v>62.470500000000001</v>
       </c>
       <c r="P6" s="73">
@@ -2617,15 +2620,15 @@
         <v>30</v>
       </c>
       <c r="R6" s="51" t="e">
-        <f t="shared" ref="R6:R136" si="4">SUMPRODUCT($D$4:$F$4,$D$6:$F$6)*$R$3</f>
+        <f t="shared" ref="R6:R137" si="4">SUMPRODUCT($D$4:$F$4,$D$6:$F$6)*$R$3</f>
         <v>#VALUE!</v>
       </c>
       <c r="S6" s="52">
-        <f t="shared" ref="S6:S136" si="5">SUMPRODUCT($G$4:$I$4,$G$6:$I$6)*$S$3</f>
+        <f t="shared" ref="S6:S137" si="5">SUMPRODUCT($G$4:$I$4,$G$6:$I$6)*$S$3</f>
         <v>0</v>
       </c>
       <c r="T6" s="52">
-        <f t="shared" ref="T6:T136" si="6">SUMPRODUCT($J$4:$L$4,$J$6:$L$6)*$T$3</f>
+        <f t="shared" ref="T6:T137" si="6">SUMPRODUCT($J$4:$L$4,$J$6:$L$6)*$T$3</f>
         <v>0</v>
       </c>
       <c r="U6" s="53" t="e">
@@ -2759,7 +2762,7 @@
         <v>15.9</v>
       </c>
       <c r="N8" s="39">
-        <f t="shared" ref="N8:N136" si="18">SUMPRODUCT($D$4:$L$4,$D$6:$L$6)</f>
+        <f t="shared" ref="N8:N137" si="18">SUMPRODUCT($D$4:$L$4,$D$6:$L$6)</f>
         <v>0</v>
       </c>
       <c r="O8" s="49">
@@ -3201,7 +3204,7 @@
         <v>0</v>
       </c>
       <c r="U13" s="53" t="e">
-        <f t="shared" ref="U13:U136" si="19">SUM(R13:T13)</f>
+        <f t="shared" ref="U13:U137" si="19">SUM(R13:T13)</f>
         <v>#VALUE!</v>
       </c>
       <c r="V13" s="54" t="e">
@@ -3217,7 +3220,7 @@
         <v>0</v>
       </c>
       <c r="Y13" s="56" t="e">
-        <f t="shared" ref="Y13:Y136" si="20">SUM(V13:X13)</f>
+        <f t="shared" ref="Y13:Y137" si="20">SUM(V13:X13)</f>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -3889,7 +3892,7 @@
         <v>0</v>
       </c>
       <c r="Y21" s="56" t="e">
-        <f t="shared" ref="Y21:Y132" si="44">SUM(V21:X21)</f>
+        <f t="shared" ref="Y21:Y133" si="44">SUM(V21:X21)</f>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -4419,7 +4422,7 @@
         <v>120</v>
       </c>
       <c r="M28" s="48">
-        <f t="shared" ref="M28:M60" si="52">SUM(D28:L28)/40</f>
+        <f t="shared" ref="M28:M61" si="52">SUM(D28:L28)/40</f>
         <v>14</v>
       </c>
       <c r="N28" s="39">
@@ -4431,11 +4434,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P28" s="73">
-        <f t="shared" ref="P28:P60" si="53">SUM(G28:I28)/20</f>
+        <f t="shared" ref="P28:P61" si="53">SUM(G28:I28)/20</f>
         <v>10</v>
       </c>
       <c r="Q28" s="40">
-        <f t="shared" ref="Q28:Q60" si="54">SUM(J28:L28)/20</f>
+        <f t="shared" ref="Q28:Q61" si="54">SUM(J28:L28)/20</f>
         <v>18</v>
       </c>
       <c r="R28" s="51" t="e">
@@ -4451,23 +4454,23 @@
         <v>0</v>
       </c>
       <c r="U28" s="53" t="e">
-        <f t="shared" ref="U28:U60" si="55">SUM(R28:T28)</f>
+        <f t="shared" ref="U28:U61" si="55">SUM(R28:T28)</f>
         <v>#VALUE!</v>
       </c>
       <c r="V28" s="54" t="e">
-        <f t="shared" ref="V28:V60" si="56">SUM(D28:F28)*$V$3</f>
+        <f t="shared" ref="V28:V61" si="56">SUM(D28:F28)*$V$3</f>
         <v>#VALUE!</v>
       </c>
       <c r="W28" s="55">
-        <f t="shared" ref="W28:W60" si="57">SUM(G28:I28)*$W$3</f>
+        <f t="shared" ref="W28:W61" si="57">SUM(G28:I28)*$W$3</f>
         <v>0</v>
       </c>
       <c r="X28" s="55">
-        <f t="shared" ref="X28:X60" si="58">SUM(J28:L28)*$X$3</f>
+        <f t="shared" ref="X28:X61" si="58">SUM(J28:L28)*$X$3</f>
         <v>0</v>
       </c>
       <c r="Y28" s="56" t="e">
-        <f t="shared" ref="Y28:Y60" si="59">SUM(V28:X28)</f>
+        <f t="shared" ref="Y28:Y61" si="59">SUM(V28:X28)</f>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -4923,7 +4926,7 @@
         <v>2800</v>
       </c>
       <c r="M34" s="48">
-        <f t="shared" ref="M34:M46" si="68">SUM(D34:L34)/40</f>
+        <f t="shared" ref="M34:M47" si="68">SUM(D34:L34)/40</f>
         <v>450</v>
       </c>
       <c r="N34" s="39">
@@ -4935,11 +4938,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P34" s="73">
-        <f t="shared" ref="P34:P46" si="69">SUM(G34:I34)/20</f>
+        <f t="shared" ref="P34:P47" si="69">SUM(G34:I34)/20</f>
         <v>200</v>
       </c>
       <c r="Q34" s="40">
-        <f t="shared" ref="Q34:Q46" si="70">SUM(J34:L34)/20</f>
+        <f t="shared" ref="Q34:Q47" si="70">SUM(J34:L34)/20</f>
         <v>500</v>
       </c>
       <c r="R34" s="51" t="e">
@@ -4955,129 +4958,86 @@
         <v>0</v>
       </c>
       <c r="U34" s="53" t="e">
-        <f t="shared" ref="U34:U45" si="71">SUM(R34:T34)</f>
+        <f t="shared" ref="U34:U46" si="71">SUM(R34:T34)</f>
         <v>#VALUE!</v>
       </c>
       <c r="V34" s="54" t="e">
-        <f t="shared" ref="V34:V45" si="72">SUM(D34:F34)*$V$3</f>
+        <f t="shared" ref="V34:V46" si="72">SUM(D34:F34)*$V$3</f>
         <v>#VALUE!</v>
       </c>
       <c r="W34" s="55">
-        <f t="shared" ref="W34:W46" si="73">SUM(G34:I34)*$W$3</f>
+        <f t="shared" ref="W34:W47" si="73">SUM(G34:I34)*$W$3</f>
         <v>0</v>
       </c>
       <c r="X34" s="55">
-        <f t="shared" ref="X34:X46" si="74">SUM(J34:L34)*$X$3</f>
+        <f t="shared" ref="X34:X47" si="74">SUM(J34:L34)*$X$3</f>
         <v>0</v>
       </c>
       <c r="Y34" s="56" t="e">
-        <f t="shared" ref="Y34:Y45" si="75">SUM(V34:X34)</f>
+        <f t="shared" ref="Y34:Y46" si="75">SUM(V34:X34)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="35" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A35" s="78">
-        <v>46247</v>
-      </c>
-      <c r="B35" s="47">
-        <v>31</v>
-      </c>
+      <c r="A35" s="140">
+        <v>46246</v>
+      </c>
+      <c r="B35" s="47"/>
       <c r="C35" s="57" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D35" s="74"/>
       <c r="E35" s="75"/>
       <c r="F35" s="76"/>
       <c r="G35" s="50"/>
       <c r="H35" s="75"/>
-      <c r="I35" s="49">
-        <v>200</v>
-      </c>
+      <c r="I35" s="49"/>
       <c r="J35" s="50">
-        <v>40</v>
+        <v>880</v>
       </c>
       <c r="K35" s="75">
-        <v>40</v>
+        <v>640</v>
       </c>
       <c r="L35" s="76">
-        <v>120</v>
-      </c>
-      <c r="M35" s="48">
-        <f t="shared" si="68"/>
-        <v>10</v>
-      </c>
-      <c r="N35" s="39">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="O35" s="49">
-        <f t="shared" si="1"/>
-        <v>62.470500000000001</v>
-      </c>
-      <c r="P35" s="73">
-        <f t="shared" si="69"/>
-        <v>10</v>
-      </c>
+        <v>880</v>
+      </c>
+      <c r="M35" s="48"/>
+      <c r="N35" s="39"/>
+      <c r="O35" s="49"/>
+      <c r="P35" s="73"/>
       <c r="Q35" s="40">
         <f t="shared" si="70"/>
-        <v>10</v>
-      </c>
-      <c r="R35" s="51" t="e">
-        <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S35" s="52">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="T35" s="52">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="U35" s="53" t="e">
-        <f t="shared" si="71"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V35" s="54" t="e">
-        <f t="shared" si="72"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W35" s="55">
-        <f t="shared" si="73"/>
-        <v>0</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="R35" s="51"/>
+      <c r="S35" s="52"/>
+      <c r="T35" s="52"/>
+      <c r="U35" s="53"/>
+      <c r="V35" s="54"/>
+      <c r="W35" s="55"/>
       <c r="X35" s="55">
         <f t="shared" si="74"/>
         <v>0</v>
       </c>
-      <c r="Y35" s="56" t="e">
-        <f t="shared" si="75"/>
-        <v>#VALUE!</v>
-      </c>
+      <c r="Y35" s="56"/>
     </row>
     <row r="36" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A36" s="78">
         <v>46247</v>
       </c>
       <c r="B36" s="47">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C36" s="57" t="s">
-        <v>115</v>
-      </c>
-      <c r="D36" s="74">
-        <v>40</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="D36" s="74"/>
       <c r="E36" s="75"/>
       <c r="F36" s="76"/>
-      <c r="G36" s="50">
-        <v>40</v>
-      </c>
-      <c r="H36" s="75">
-        <v>40</v>
-      </c>
+      <c r="G36" s="50"/>
+      <c r="H36" s="75"/>
       <c r="I36" s="49">
-        <v>40</v>
+        <v>200</v>
       </c>
       <c r="J36" s="50">
         <v>40</v>
@@ -5086,11 +5046,11 @@
         <v>40</v>
       </c>
       <c r="L36" s="76">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="M36" s="48">
         <f t="shared" si="68"/>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="N36" s="39">
         <f t="shared" si="18"/>
@@ -5102,11 +5062,11 @@
       </c>
       <c r="P36" s="73">
         <f t="shared" si="69"/>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Q36" s="40">
         <f t="shared" si="70"/>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R36" s="51" t="e">
         <f t="shared" si="4"/>
@@ -5146,12 +5106,14 @@
         <v>46247</v>
       </c>
       <c r="B37" s="47">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C37" s="57" t="s">
-        <v>116</v>
-      </c>
-      <c r="D37" s="74"/>
+        <v>114</v>
+      </c>
+      <c r="D37" s="74">
+        <v>40</v>
+      </c>
       <c r="E37" s="75"/>
       <c r="F37" s="76"/>
       <c r="G37" s="50">
@@ -5174,7 +5136,7 @@
       </c>
       <c r="M37" s="48">
         <f t="shared" si="68"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N37" s="39">
         <f t="shared" si="18"/>
@@ -5226,23 +5188,39 @@
       </c>
     </row>
     <row r="38" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A38" s="78"/>
+      <c r="A38" s="78">
+        <v>46247</v>
+      </c>
       <c r="B38" s="47">
-        <v>34</v>
-      </c>
-      <c r="C38" s="57"/>
+        <v>33</v>
+      </c>
+      <c r="C38" s="57" t="s">
+        <v>115</v>
+      </c>
       <c r="D38" s="74"/>
       <c r="E38" s="75"/>
       <c r="F38" s="76"/>
-      <c r="G38" s="50"/>
-      <c r="H38" s="75"/>
-      <c r="I38" s="49"/>
-      <c r="J38" s="50"/>
-      <c r="K38" s="75"/>
-      <c r="L38" s="76"/>
+      <c r="G38" s="50">
+        <v>40</v>
+      </c>
+      <c r="H38" s="75">
+        <v>40</v>
+      </c>
+      <c r="I38" s="49">
+        <v>40</v>
+      </c>
+      <c r="J38" s="50">
+        <v>40</v>
+      </c>
+      <c r="K38" s="75">
+        <v>40</v>
+      </c>
+      <c r="L38" s="76">
+        <v>40</v>
+      </c>
       <c r="M38" s="48">
         <f t="shared" si="68"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N38" s="39">
         <f t="shared" si="18"/>
@@ -5254,11 +5232,11 @@
       </c>
       <c r="P38" s="73">
         <f t="shared" si="69"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q38" s="40">
         <f t="shared" si="70"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R38" s="51" t="e">
         <f t="shared" si="4"/>
@@ -5296,7 +5274,7 @@
     <row r="39" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A39" s="78"/>
       <c r="B39" s="47">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C39" s="57"/>
       <c r="D39" s="74"/>
@@ -5364,7 +5342,7 @@
     <row r="40" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A40" s="78"/>
       <c r="B40" s="47">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C40" s="57"/>
       <c r="D40" s="74"/>
@@ -5432,7 +5410,7 @@
     <row r="41" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A41" s="78"/>
       <c r="B41" s="47">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C41" s="57"/>
       <c r="D41" s="74"/>
@@ -5500,7 +5478,7 @@
     <row r="42" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A42" s="78"/>
       <c r="B42" s="47">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C42" s="57"/>
       <c r="D42" s="74"/>
@@ -5568,7 +5546,7 @@
     <row r="43" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A43" s="78"/>
       <c r="B43" s="47">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C43" s="57"/>
       <c r="D43" s="74"/>
@@ -5636,7 +5614,7 @@
     <row r="44" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A44" s="78"/>
       <c r="B44" s="47">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C44" s="57"/>
       <c r="D44" s="74"/>
@@ -5704,7 +5682,7 @@
     <row r="45" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A45" s="78"/>
       <c r="B45" s="47">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C45" s="57"/>
       <c r="D45" s="74"/>
@@ -5772,7 +5750,7 @@
     <row r="46" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A46" s="78"/>
       <c r="B46" s="47">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C46" s="57"/>
       <c r="D46" s="74"/>
@@ -5804,11 +5782,26 @@
         <f t="shared" si="70"/>
         <v>0</v>
       </c>
-      <c r="R46" s="51"/>
-      <c r="S46" s="52"/>
-      <c r="T46" s="52"/>
-      <c r="U46" s="53"/>
-      <c r="V46" s="54"/>
+      <c r="R46" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S46" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T46" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U46" s="53" t="e">
+        <f t="shared" si="71"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V46" s="54" t="e">
+        <f t="shared" si="72"/>
+        <v>#VALUE!</v>
+      </c>
       <c r="W46" s="55">
         <f t="shared" si="73"/>
         <v>0</v>
@@ -5817,12 +5810,15 @@
         <f t="shared" si="74"/>
         <v>0</v>
       </c>
-      <c r="Y46" s="56"/>
+      <c r="Y46" s="56" t="e">
+        <f t="shared" si="75"/>
+        <v>#VALUE!</v>
+      </c>
     </row>
     <row r="47" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A47" s="78"/>
       <c r="B47" s="47">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C47" s="57"/>
       <c r="D47" s="74"/>
@@ -5835,7 +5831,7 @@
       <c r="K47" s="75"/>
       <c r="L47" s="76"/>
       <c r="M47" s="48">
-        <f t="shared" ref="M47:M59" si="76">SUM(D47:L47)/40</f>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="N47" s="39">
@@ -5847,11 +5843,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P47" s="73">
-        <f t="shared" ref="P47:P59" si="77">SUM(G47:I47)/20</f>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="Q47" s="40">
-        <f t="shared" ref="Q47:Q59" si="78">SUM(J47:L47)/20</f>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="R47" s="51"/>
@@ -5860,11 +5856,11 @@
       <c r="U47" s="53"/>
       <c r="V47" s="54"/>
       <c r="W47" s="55">
-        <f t="shared" ref="W47:W59" si="79">SUM(G47:I47)*$W$3</f>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="X47" s="55">
-        <f t="shared" ref="X47:X59" si="80">SUM(J47:L47)*$X$3</f>
+        <f t="shared" si="74"/>
         <v>0</v>
       </c>
       <c r="Y47" s="56"/>
@@ -5872,7 +5868,7 @@
     <row r="48" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A48" s="78"/>
       <c r="B48" s="47">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C48" s="57"/>
       <c r="D48" s="74"/>
@@ -5885,7 +5881,7 @@
       <c r="K48" s="75"/>
       <c r="L48" s="76"/>
       <c r="M48" s="48">
-        <f t="shared" si="76"/>
+        <f t="shared" ref="M48:M60" si="76">SUM(D48:L48)/40</f>
         <v>0</v>
       </c>
       <c r="N48" s="39">
@@ -5897,11 +5893,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P48" s="73">
-        <f t="shared" si="77"/>
+        <f t="shared" ref="P48:P60" si="77">SUM(G48:I48)/20</f>
         <v>0</v>
       </c>
       <c r="Q48" s="40">
-        <f t="shared" si="78"/>
+        <f t="shared" ref="Q48:Q60" si="78">SUM(J48:L48)/20</f>
         <v>0</v>
       </c>
       <c r="R48" s="51"/>
@@ -5910,11 +5906,11 @@
       <c r="U48" s="53"/>
       <c r="V48" s="54"/>
       <c r="W48" s="55">
-        <f t="shared" si="79"/>
+        <f t="shared" ref="W48:W60" si="79">SUM(G48:I48)*$W$3</f>
         <v>0</v>
       </c>
       <c r="X48" s="55">
-        <f t="shared" si="80"/>
+        <f t="shared" ref="X48:X60" si="80">SUM(J48:L48)*$X$3</f>
         <v>0</v>
       </c>
       <c r="Y48" s="56"/>
@@ -5922,7 +5918,7 @@
     <row r="49" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A49" s="78"/>
       <c r="B49" s="47">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C49" s="57"/>
       <c r="D49" s="74"/>
@@ -5972,7 +5968,7 @@
     <row r="50" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A50" s="78"/>
       <c r="B50" s="47">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C50" s="57"/>
       <c r="D50" s="74"/>
@@ -6022,7 +6018,7 @@
     <row r="51" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A51" s="78"/>
       <c r="B51" s="47">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C51" s="57"/>
       <c r="D51" s="74"/>
@@ -6072,7 +6068,7 @@
     <row r="52" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A52" s="78"/>
       <c r="B52" s="47">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C52" s="57"/>
       <c r="D52" s="74"/>
@@ -6122,7 +6118,7 @@
     <row r="53" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A53" s="78"/>
       <c r="B53" s="47">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C53" s="57"/>
       <c r="D53" s="74"/>
@@ -6172,7 +6168,7 @@
     <row r="54" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A54" s="78"/>
       <c r="B54" s="47">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C54" s="57"/>
       <c r="D54" s="74"/>
@@ -6222,7 +6218,7 @@
     <row r="55" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A55" s="78"/>
       <c r="B55" s="47">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C55" s="57"/>
       <c r="D55" s="74"/>
@@ -6272,7 +6268,7 @@
     <row r="56" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A56" s="78"/>
       <c r="B56" s="47">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C56" s="57"/>
       <c r="D56" s="74"/>
@@ -6322,19 +6318,19 @@
     <row r="57" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A57" s="78"/>
       <c r="B57" s="47">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C57" s="57"/>
-      <c r="D57" s="75"/>
+      <c r="D57" s="74"/>
       <c r="E57" s="75"/>
-      <c r="F57" s="75"/>
-      <c r="G57" s="75"/>
+      <c r="F57" s="76"/>
+      <c r="G57" s="50"/>
       <c r="H57" s="75"/>
-      <c r="I57" s="127"/>
-      <c r="J57" s="75"/>
+      <c r="I57" s="49"/>
+      <c r="J57" s="50"/>
       <c r="K57" s="75"/>
-      <c r="L57" s="75"/>
-      <c r="M57" s="129">
+      <c r="L57" s="76"/>
+      <c r="M57" s="48">
         <f t="shared" si="76"/>
         <v>0</v>
       </c>
@@ -6372,7 +6368,7 @@
     <row r="58" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A58" s="78"/>
       <c r="B58" s="47">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C58" s="57"/>
       <c r="D58" s="75"/>
@@ -6422,7 +6418,7 @@
     <row r="59" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A59" s="78"/>
       <c r="B59" s="47">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C59" s="57"/>
       <c r="D59" s="75"/>
@@ -6472,7 +6468,7 @@
     <row r="60" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A60" s="78"/>
       <c r="B60" s="47">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C60" s="57"/>
       <c r="D60" s="75"/>
@@ -6485,7 +6481,7 @@
       <c r="K60" s="75"/>
       <c r="L60" s="75"/>
       <c r="M60" s="129">
-        <f t="shared" si="52"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="N60" s="39">
@@ -6497,52 +6493,34 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P60" s="73">
-        <f t="shared" si="53"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="Q60" s="40">
-        <f t="shared" si="54"/>
-        <v>0</v>
-      </c>
-      <c r="R60" s="51" t="e">
-        <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S60" s="52">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="T60" s="52">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="U60" s="53" t="e">
-        <f t="shared" si="55"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V60" s="54" t="e">
-        <f t="shared" si="56"/>
-        <v>#VALUE!</v>
-      </c>
+        <f t="shared" si="78"/>
+        <v>0</v>
+      </c>
+      <c r="R60" s="51"/>
+      <c r="S60" s="52"/>
+      <c r="T60" s="52"/>
+      <c r="U60" s="53"/>
+      <c r="V60" s="54"/>
       <c r="W60" s="55">
-        <f t="shared" si="57"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="X60" s="55">
-        <f t="shared" si="58"/>
-        <v>0</v>
-      </c>
-      <c r="Y60" s="56" t="e">
-        <f t="shared" si="59"/>
-        <v>#VALUE!</v>
-      </c>
+        <f t="shared" si="80"/>
+        <v>0</v>
+      </c>
+      <c r="Y60" s="56"/>
     </row>
     <row r="61" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A61" s="78"/>
       <c r="B61" s="47">
-        <v>57</v>
-      </c>
-      <c r="C61" s="128"/>
+        <v>56</v>
+      </c>
+      <c r="C61" s="57"/>
       <c r="D61" s="75"/>
       <c r="E61" s="75"/>
       <c r="F61" s="75"/>
@@ -6553,7 +6531,7 @@
       <c r="K61" s="75"/>
       <c r="L61" s="75"/>
       <c r="M61" s="129">
-        <f t="shared" ref="M61:M83" si="81">SUM(D61:L61)/40</f>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="N61" s="39">
@@ -6565,11 +6543,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P61" s="73">
-        <f t="shared" ref="P61:P78" si="82">SUM(G61:I61)/20</f>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="Q61" s="40">
-        <f t="shared" ref="Q61:Q78" si="83">SUM(J61:L61)/20</f>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="R61" s="51" t="e">
@@ -6585,30 +6563,30 @@
         <v>0</v>
       </c>
       <c r="U61" s="53" t="e">
-        <f t="shared" ref="U61:U78" si="84">SUM(R61:T61)</f>
+        <f t="shared" si="55"/>
         <v>#VALUE!</v>
       </c>
       <c r="V61" s="54" t="e">
-        <f t="shared" ref="V61:V78" si="85">SUM(D61:F61)*$V$3</f>
+        <f t="shared" si="56"/>
         <v>#VALUE!</v>
       </c>
       <c r="W61" s="55">
-        <f t="shared" ref="W61:W78" si="86">SUM(G61:I61)*$W$3</f>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="X61" s="55">
-        <f t="shared" ref="X61:X78" si="87">SUM(J61:L61)*$X$3</f>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="Y61" s="56" t="e">
-        <f t="shared" ref="Y61:Y78" si="88">SUM(V61:X61)</f>
+        <f t="shared" si="59"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="62" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A62" s="78"/>
       <c r="B62" s="47">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C62" s="128"/>
       <c r="D62" s="75"/>
@@ -6621,7 +6599,7 @@
       <c r="K62" s="75"/>
       <c r="L62" s="75"/>
       <c r="M62" s="129">
-        <f t="shared" si="81"/>
+        <f t="shared" ref="M62:M84" si="81">SUM(D62:L62)/40</f>
         <v>0</v>
       </c>
       <c r="N62" s="39">
@@ -6633,11 +6611,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P62" s="73">
-        <f t="shared" si="82"/>
+        <f t="shared" ref="P62:P79" si="82">SUM(G62:I62)/20</f>
         <v>0</v>
       </c>
       <c r="Q62" s="40">
-        <f t="shared" si="83"/>
+        <f t="shared" ref="Q62:Q79" si="83">SUM(J62:L62)/20</f>
         <v>0</v>
       </c>
       <c r="R62" s="51" t="e">
@@ -6653,30 +6631,30 @@
         <v>0</v>
       </c>
       <c r="U62" s="53" t="e">
-        <f t="shared" si="84"/>
+        <f t="shared" ref="U62:U79" si="84">SUM(R62:T62)</f>
         <v>#VALUE!</v>
       </c>
       <c r="V62" s="54" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" ref="V62:V79" si="85">SUM(D62:F62)*$V$3</f>
         <v>#VALUE!</v>
       </c>
       <c r="W62" s="55">
-        <f t="shared" si="86"/>
+        <f t="shared" ref="W62:W79" si="86">SUM(G62:I62)*$W$3</f>
         <v>0</v>
       </c>
       <c r="X62" s="55">
-        <f t="shared" si="87"/>
+        <f t="shared" ref="X62:X79" si="87">SUM(J62:L62)*$X$3</f>
         <v>0</v>
       </c>
       <c r="Y62" s="56" t="e">
-        <f t="shared" si="88"/>
+        <f t="shared" ref="Y62:Y79" si="88">SUM(V62:X62)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="63" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A63" s="78"/>
       <c r="B63" s="47">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C63" s="128"/>
       <c r="D63" s="75"/>
@@ -6744,7 +6722,7 @@
     <row r="64" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A64" s="78"/>
       <c r="B64" s="47">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C64" s="128"/>
       <c r="D64" s="75"/>
@@ -6812,7 +6790,7 @@
     <row r="65" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A65" s="78"/>
       <c r="B65" s="47">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C65" s="128"/>
       <c r="D65" s="75"/>
@@ -6880,7 +6858,7 @@
     <row r="66" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A66" s="78"/>
       <c r="B66" s="47">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C66" s="128"/>
       <c r="D66" s="75"/>
@@ -6948,7 +6926,7 @@
     <row r="67" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A67" s="78"/>
       <c r="B67" s="47">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C67" s="128"/>
       <c r="D67" s="75"/>
@@ -7016,7 +6994,7 @@
     <row r="68" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A68" s="78"/>
       <c r="B68" s="47">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C68" s="128"/>
       <c r="D68" s="75"/>
@@ -7084,7 +7062,7 @@
     <row r="69" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A69" s="78"/>
       <c r="B69" s="47">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C69" s="128"/>
       <c r="D69" s="75"/>
@@ -7152,7 +7130,7 @@
     <row r="70" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A70" s="78"/>
       <c r="B70" s="47">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C70" s="128"/>
       <c r="D70" s="75"/>
@@ -7220,7 +7198,7 @@
     <row r="71" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A71" s="78"/>
       <c r="B71" s="47">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C71" s="128"/>
       <c r="D71" s="75"/>
@@ -7288,7 +7266,7 @@
     <row r="72" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A72" s="78"/>
       <c r="B72" s="47">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C72" s="128"/>
       <c r="D72" s="75"/>
@@ -7356,7 +7334,7 @@
     <row r="73" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A73" s="78"/>
       <c r="B73" s="47">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C73" s="128"/>
       <c r="D73" s="75"/>
@@ -7424,12 +7402,12 @@
     <row r="74" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A74" s="78"/>
       <c r="B74" s="47">
-        <v>70</v>
-      </c>
-      <c r="C74" s="139"/>
+        <v>69</v>
+      </c>
+      <c r="C74" s="128"/>
       <c r="D74" s="75"/>
       <c r="E74" s="75"/>
-      <c r="F74" s="50"/>
+      <c r="F74" s="75"/>
       <c r="G74" s="75"/>
       <c r="H74" s="75"/>
       <c r="I74" s="127"/>
@@ -7492,11 +7470,11 @@
     <row r="75" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A75" s="78"/>
       <c r="B75" s="47">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C75" s="139"/>
       <c r="D75" s="75"/>
-      <c r="E75" s="50"/>
+      <c r="E75" s="75"/>
       <c r="F75" s="50"/>
       <c r="G75" s="75"/>
       <c r="H75" s="75"/>
@@ -7560,7 +7538,7 @@
     <row r="76" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A76" s="78"/>
       <c r="B76" s="47">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C76" s="139"/>
       <c r="D76" s="75"/>
@@ -7628,18 +7606,18 @@
     <row r="77" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A77" s="78"/>
       <c r="B77" s="47">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C77" s="139"/>
       <c r="D77" s="75"/>
       <c r="E77" s="50"/>
       <c r="F77" s="50"/>
-      <c r="G77" s="50"/>
-      <c r="H77" s="50"/>
-      <c r="I77" s="129"/>
-      <c r="J77" s="50"/>
-      <c r="K77" s="50"/>
-      <c r="L77" s="50"/>
+      <c r="G77" s="75"/>
+      <c r="H77" s="75"/>
+      <c r="I77" s="127"/>
+      <c r="J77" s="75"/>
+      <c r="K77" s="75"/>
+      <c r="L77" s="75"/>
       <c r="M77" s="129">
         <f t="shared" si="81"/>
         <v>0</v>
@@ -7696,7 +7674,7 @@
     <row r="78" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A78" s="78"/>
       <c r="B78" s="47">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C78" s="139"/>
       <c r="D78" s="75"/>
@@ -7764,10 +7742,10 @@
     <row r="79" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A79" s="78"/>
       <c r="B79" s="47">
-        <v>75</v>
-      </c>
-      <c r="C79" s="128"/>
-      <c r="D79" s="50"/>
+        <v>74</v>
+      </c>
+      <c r="C79" s="139"/>
+      <c r="D79" s="75"/>
       <c r="E79" s="50"/>
       <c r="F79" s="50"/>
       <c r="G79" s="50"/>
@@ -7789,11 +7767,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P79" s="73">
-        <f t="shared" ref="P79:P83" si="89">SUM(G79:I79)/20</f>
+        <f t="shared" si="82"/>
         <v>0</v>
       </c>
       <c r="Q79" s="40">
-        <f t="shared" ref="Q79:Q83" si="90">SUM(J79:L79)/20</f>
+        <f t="shared" si="83"/>
         <v>0</v>
       </c>
       <c r="R79" s="51" t="e">
@@ -7809,30 +7787,30 @@
         <v>0</v>
       </c>
       <c r="U79" s="53" t="e">
-        <f t="shared" ref="U79:U83" si="91">SUM(R79:T79)</f>
+        <f t="shared" si="84"/>
         <v>#VALUE!</v>
       </c>
       <c r="V79" s="54" t="e">
-        <f t="shared" ref="V79:V83" si="92">SUM(D79:F79)*$V$3</f>
+        <f t="shared" si="85"/>
         <v>#VALUE!</v>
       </c>
       <c r="W79" s="55">
-        <f t="shared" ref="W79:W83" si="93">SUM(G79:I79)*$W$3</f>
+        <f t="shared" si="86"/>
         <v>0</v>
       </c>
       <c r="X79" s="55">
-        <f t="shared" ref="X79:X83" si="94">SUM(J79:L79)*$X$3</f>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="Y79" s="56" t="e">
-        <f t="shared" ref="Y79:Y83" si="95">SUM(V79:X79)</f>
+        <f t="shared" si="88"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="80" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A80" s="78"/>
       <c r="B80" s="47">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C80" s="128"/>
       <c r="D80" s="50"/>
@@ -7857,11 +7835,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P80" s="73">
-        <f t="shared" si="89"/>
+        <f t="shared" ref="P80:P84" si="89">SUM(G80:I80)/20</f>
         <v>0</v>
       </c>
       <c r="Q80" s="40">
-        <f t="shared" si="90"/>
+        <f t="shared" ref="Q80:Q84" si="90">SUM(J80:L80)/20</f>
         <v>0</v>
       </c>
       <c r="R80" s="51" t="e">
@@ -7877,30 +7855,30 @@
         <v>0</v>
       </c>
       <c r="U80" s="53" t="e">
-        <f t="shared" si="91"/>
+        <f t="shared" ref="U80:U84" si="91">SUM(R80:T80)</f>
         <v>#VALUE!</v>
       </c>
       <c r="V80" s="54" t="e">
-        <f t="shared" si="92"/>
+        <f t="shared" ref="V80:V84" si="92">SUM(D80:F80)*$V$3</f>
         <v>#VALUE!</v>
       </c>
       <c r="W80" s="55">
-        <f t="shared" si="93"/>
+        <f t="shared" ref="W80:W84" si="93">SUM(G80:I80)*$W$3</f>
         <v>0</v>
       </c>
       <c r="X80" s="55">
-        <f t="shared" si="94"/>
+        <f t="shared" ref="X80:X84" si="94">SUM(J80:L80)*$X$3</f>
         <v>0</v>
       </c>
       <c r="Y80" s="56" t="e">
-        <f t="shared" si="95"/>
+        <f t="shared" ref="Y80:Y84" si="95">SUM(V80:X80)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="81" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A81" s="78"/>
       <c r="B81" s="47">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C81" s="128"/>
       <c r="D81" s="50"/>
@@ -7968,7 +7946,7 @@
     <row r="82" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A82" s="78"/>
       <c r="B82" s="47">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C82" s="128"/>
       <c r="D82" s="50"/>
@@ -8036,7 +8014,7 @@
     <row r="83" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A83" s="78"/>
       <c r="B83" s="47">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C83" s="128"/>
       <c r="D83" s="50"/>
@@ -8104,7 +8082,7 @@
     <row r="84" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A84" s="78"/>
       <c r="B84" s="47">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C84" s="128"/>
       <c r="D84" s="50"/>
@@ -8117,7 +8095,7 @@
       <c r="K84" s="50"/>
       <c r="L84" s="50"/>
       <c r="M84" s="129">
-        <f t="shared" ref="M84:M131" si="96">SUM(D84:L84)/40</f>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="N84" s="39">
@@ -8129,11 +8107,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P84" s="73">
-        <f t="shared" ref="P84:P131" si="97">SUM(G84:I84)/20</f>
+        <f t="shared" si="89"/>
         <v>0</v>
       </c>
       <c r="Q84" s="40">
-        <f t="shared" ref="Q84:Q131" si="98">SUM(J84:L84)/20</f>
+        <f t="shared" si="90"/>
         <v>0</v>
       </c>
       <c r="R84" s="51" t="e">
@@ -8149,30 +8127,30 @@
         <v>0</v>
       </c>
       <c r="U84" s="53" t="e">
-        <f t="shared" ref="U84:U131" si="99">SUM(R84:T84)</f>
+        <f t="shared" si="91"/>
         <v>#VALUE!</v>
       </c>
       <c r="V84" s="54" t="e">
-        <f t="shared" ref="V84:V131" si="100">SUM(D84:F84)*$V$3</f>
+        <f t="shared" si="92"/>
         <v>#VALUE!</v>
       </c>
       <c r="W84" s="55">
-        <f t="shared" ref="W84:W131" si="101">SUM(G84:I84)*$W$3</f>
+        <f t="shared" si="93"/>
         <v>0</v>
       </c>
       <c r="X84" s="55">
-        <f t="shared" ref="X84:X131" si="102">SUM(J84:L84)*$X$3</f>
+        <f t="shared" si="94"/>
         <v>0</v>
       </c>
       <c r="Y84" s="56" t="e">
-        <f t="shared" ref="Y84:Y131" si="103">SUM(V84:X84)</f>
+        <f t="shared" si="95"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="85" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A85" s="78"/>
       <c r="B85" s="47">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C85" s="128"/>
       <c r="D85" s="50"/>
@@ -8185,7 +8163,7 @@
       <c r="K85" s="50"/>
       <c r="L85" s="50"/>
       <c r="M85" s="129">
-        <f t="shared" si="96"/>
+        <f t="shared" ref="M85:M132" si="96">SUM(D85:L85)/40</f>
         <v>0</v>
       </c>
       <c r="N85" s="39">
@@ -8197,11 +8175,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P85" s="73">
-        <f t="shared" si="97"/>
+        <f t="shared" ref="P85:P132" si="97">SUM(G85:I85)/20</f>
         <v>0</v>
       </c>
       <c r="Q85" s="40">
-        <f t="shared" si="98"/>
+        <f t="shared" ref="Q85:Q132" si="98">SUM(J85:L85)/20</f>
         <v>0</v>
       </c>
       <c r="R85" s="51" t="e">
@@ -8217,30 +8195,30 @@
         <v>0</v>
       </c>
       <c r="U85" s="53" t="e">
-        <f t="shared" si="99"/>
+        <f t="shared" ref="U85:U132" si="99">SUM(R85:T85)</f>
         <v>#VALUE!</v>
       </c>
       <c r="V85" s="54" t="e">
-        <f t="shared" si="100"/>
+        <f t="shared" ref="V85:V132" si="100">SUM(D85:F85)*$V$3</f>
         <v>#VALUE!</v>
       </c>
       <c r="W85" s="55">
-        <f t="shared" si="101"/>
+        <f t="shared" ref="W85:W132" si="101">SUM(G85:I85)*$W$3</f>
         <v>0</v>
       </c>
       <c r="X85" s="55">
-        <f t="shared" si="102"/>
+        <f t="shared" ref="X85:X132" si="102">SUM(J85:L85)*$X$3</f>
         <v>0</v>
       </c>
       <c r="Y85" s="56" t="e">
-        <f t="shared" si="103"/>
+        <f t="shared" ref="Y85:Y132" si="103">SUM(V85:X85)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="86" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A86" s="78"/>
       <c r="B86" s="47">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C86" s="128"/>
       <c r="D86" s="50"/>
@@ -8308,7 +8286,7 @@
     <row r="87" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A87" s="78"/>
       <c r="B87" s="47">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C87" s="128"/>
       <c r="D87" s="50"/>
@@ -8376,7 +8354,7 @@
     <row r="88" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A88" s="78"/>
       <c r="B88" s="47">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C88" s="128"/>
       <c r="D88" s="50"/>
@@ -8444,7 +8422,7 @@
     <row r="89" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A89" s="78"/>
       <c r="B89" s="47">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C89" s="128"/>
       <c r="D89" s="50"/>
@@ -8512,7 +8490,7 @@
     <row r="90" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A90" s="78"/>
       <c r="B90" s="47">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C90" s="128"/>
       <c r="D90" s="50"/>
@@ -8580,7 +8558,7 @@
     <row r="91" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A91" s="78"/>
       <c r="B91" s="47">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C91" s="128"/>
       <c r="D91" s="50"/>
@@ -8648,7 +8626,7 @@
     <row r="92" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A92" s="78"/>
       <c r="B92" s="47">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C92" s="128"/>
       <c r="D92" s="50"/>
@@ -8716,7 +8694,7 @@
     <row r="93" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A93" s="78"/>
       <c r="B93" s="47">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C93" s="128"/>
       <c r="D93" s="50"/>
@@ -8784,7 +8762,7 @@
     <row r="94" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A94" s="78"/>
       <c r="B94" s="47">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C94" s="128"/>
       <c r="D94" s="50"/>
@@ -8852,7 +8830,7 @@
     <row r="95" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A95" s="78"/>
       <c r="B95" s="47">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C95" s="128"/>
       <c r="D95" s="50"/>
@@ -8920,7 +8898,7 @@
     <row r="96" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A96" s="78"/>
       <c r="B96" s="47">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C96" s="128"/>
       <c r="D96" s="50"/>
@@ -8988,7 +8966,7 @@
     <row r="97" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A97" s="78"/>
       <c r="B97" s="47">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C97" s="128"/>
       <c r="D97" s="50"/>
@@ -9056,7 +9034,7 @@
     <row r="98" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A98" s="78"/>
       <c r="B98" s="47">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C98" s="128"/>
       <c r="D98" s="50"/>
@@ -9124,7 +9102,7 @@
     <row r="99" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A99" s="78"/>
       <c r="B99" s="47">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C99" s="128"/>
       <c r="D99" s="50"/>
@@ -9192,7 +9170,7 @@
     <row r="100" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A100" s="78"/>
       <c r="B100" s="47">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C100" s="128"/>
       <c r="D100" s="50"/>
@@ -9260,7 +9238,7 @@
     <row r="101" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A101" s="78"/>
       <c r="B101" s="47">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C101" s="128"/>
       <c r="D101" s="50"/>
@@ -9328,7 +9306,7 @@
     <row r="102" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A102" s="78"/>
       <c r="B102" s="47">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C102" s="128"/>
       <c r="D102" s="50"/>
@@ -9396,7 +9374,7 @@
     <row r="103" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A103" s="78"/>
       <c r="B103" s="47">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C103" s="128"/>
       <c r="D103" s="50"/>
@@ -9464,7 +9442,7 @@
     <row r="104" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A104" s="78"/>
       <c r="B104" s="47">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C104" s="128"/>
       <c r="D104" s="50"/>
@@ -9532,7 +9510,7 @@
     <row r="105" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A105" s="78"/>
       <c r="B105" s="47">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C105" s="128"/>
       <c r="D105" s="50"/>
@@ -9600,7 +9578,7 @@
     <row r="106" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A106" s="78"/>
       <c r="B106" s="47">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C106" s="128"/>
       <c r="D106" s="50"/>
@@ -9668,7 +9646,7 @@
     <row r="107" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A107" s="78"/>
       <c r="B107" s="47">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C107" s="128"/>
       <c r="D107" s="50"/>
@@ -9736,7 +9714,7 @@
     <row r="108" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A108" s="78"/>
       <c r="B108" s="47">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C108" s="128"/>
       <c r="D108" s="50"/>
@@ -9804,7 +9782,7 @@
     <row r="109" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A109" s="78"/>
       <c r="B109" s="47">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C109" s="128"/>
       <c r="D109" s="50"/>
@@ -9872,7 +9850,7 @@
     <row r="110" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A110" s="78"/>
       <c r="B110" s="47">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C110" s="128"/>
       <c r="D110" s="50"/>
@@ -9940,7 +9918,7 @@
     <row r="111" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A111" s="78"/>
       <c r="B111" s="47">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C111" s="128"/>
       <c r="D111" s="50"/>
@@ -10008,7 +9986,7 @@
     <row r="112" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A112" s="78"/>
       <c r="B112" s="47">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C112" s="128"/>
       <c r="D112" s="50"/>
@@ -10076,7 +10054,7 @@
     <row r="113" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A113" s="78"/>
       <c r="B113" s="47">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C113" s="128"/>
       <c r="D113" s="50"/>
@@ -10144,7 +10122,7 @@
     <row r="114" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A114" s="78"/>
       <c r="B114" s="47">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C114" s="128"/>
       <c r="D114" s="50"/>
@@ -10212,7 +10190,7 @@
     <row r="115" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A115" s="78"/>
       <c r="B115" s="47">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C115" s="128"/>
       <c r="D115" s="50"/>
@@ -10280,7 +10258,7 @@
     <row r="116" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A116" s="78"/>
       <c r="B116" s="47">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C116" s="128"/>
       <c r="D116" s="50"/>
@@ -10348,7 +10326,7 @@
     <row r="117" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A117" s="78"/>
       <c r="B117" s="47">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C117" s="128"/>
       <c r="D117" s="50"/>
@@ -10416,7 +10394,7 @@
     <row r="118" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A118" s="78"/>
       <c r="B118" s="47">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C118" s="128"/>
       <c r="D118" s="50"/>
@@ -10484,7 +10462,7 @@
     <row r="119" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A119" s="78"/>
       <c r="B119" s="47">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C119" s="128"/>
       <c r="D119" s="50"/>
@@ -10552,7 +10530,7 @@
     <row r="120" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A120" s="78"/>
       <c r="B120" s="47">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C120" s="128"/>
       <c r="D120" s="50"/>
@@ -10620,7 +10598,7 @@
     <row r="121" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A121" s="78"/>
       <c r="B121" s="47">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C121" s="128"/>
       <c r="D121" s="50"/>
@@ -10688,7 +10666,7 @@
     <row r="122" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A122" s="78"/>
       <c r="B122" s="47">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C122" s="128"/>
       <c r="D122" s="50"/>
@@ -10756,7 +10734,7 @@
     <row r="123" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A123" s="78"/>
       <c r="B123" s="47">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C123" s="128"/>
       <c r="D123" s="50"/>
@@ -10823,7 +10801,9 @@
     </row>
     <row r="124" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A124" s="78"/>
-      <c r="B124" s="107"/>
+      <c r="B124" s="47">
+        <v>119</v>
+      </c>
       <c r="C124" s="128"/>
       <c r="D124" s="50"/>
       <c r="E124" s="50"/>
@@ -11351,209 +11331,206 @@
     </row>
     <row r="132" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A132" s="78"/>
-      <c r="B132" s="170" t="s">
+      <c r="B132" s="107"/>
+      <c r="C132" s="128"/>
+      <c r="D132" s="50"/>
+      <c r="E132" s="50"/>
+      <c r="F132" s="50"/>
+      <c r="G132" s="50"/>
+      <c r="H132" s="50"/>
+      <c r="I132" s="129"/>
+      <c r="J132" s="50"/>
+      <c r="K132" s="50"/>
+      <c r="L132" s="50"/>
+      <c r="M132" s="129">
+        <f t="shared" si="96"/>
+        <v>0</v>
+      </c>
+      <c r="N132" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O132" s="49">
+        <f t="shared" si="1"/>
+        <v>62.470500000000001</v>
+      </c>
+      <c r="P132" s="73">
+        <f t="shared" si="97"/>
+        <v>0</v>
+      </c>
+      <c r="Q132" s="40">
+        <f t="shared" si="98"/>
+        <v>0</v>
+      </c>
+      <c r="R132" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S132" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T132" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U132" s="53" t="e">
+        <f t="shared" si="99"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V132" s="54" t="e">
+        <f t="shared" si="100"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W132" s="55">
+        <f t="shared" si="101"/>
+        <v>0</v>
+      </c>
+      <c r="X132" s="55">
+        <f t="shared" si="102"/>
+        <v>0</v>
+      </c>
+      <c r="Y132" s="56" t="e">
+        <f t="shared" si="103"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="133" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A133" s="78"/>
+      <c r="B133" s="157" t="s">
         <v>11</v>
       </c>
-      <c r="C132" s="171"/>
-      <c r="D132" s="84">
-        <f t="shared" ref="D132:L132" si="104">SUM(D6:D60)</f>
+      <c r="C133" s="158"/>
+      <c r="D133" s="84">
+        <f t="shared" ref="D133:L133" si="104">SUM(D6:D61)</f>
         <v>6083</v>
       </c>
-      <c r="E132" s="84">
+      <c r="E133" s="84">
         <f t="shared" si="104"/>
         <v>0</v>
       </c>
-      <c r="F132" s="84">
+      <c r="F133" s="84">
         <f t="shared" si="104"/>
         <v>0</v>
       </c>
-      <c r="G132" s="84">
+      <c r="G133" s="84">
         <f t="shared" si="104"/>
         <v>4462</v>
       </c>
-      <c r="H132" s="84">
+      <c r="H133" s="84">
         <f t="shared" si="104"/>
         <v>4607</v>
       </c>
-      <c r="I132" s="84">
+      <c r="I133" s="84">
         <f t="shared" si="104"/>
         <v>6799</v>
       </c>
-      <c r="J132" s="84">
+      <c r="J133" s="84">
         <f t="shared" si="104"/>
-        <v>8301</v>
-      </c>
-      <c r="K132" s="84">
+        <v>9181</v>
+      </c>
+      <c r="K133" s="84">
         <f t="shared" si="104"/>
-        <v>7777</v>
-      </c>
-      <c r="L132" s="84">
+        <v>8417</v>
+      </c>
+      <c r="L133" s="84">
         <f t="shared" si="104"/>
-        <v>10119</v>
-      </c>
-      <c r="M132" s="48">
-        <f t="shared" ref="M132:M135" si="105">SUM(D132:L132)/40</f>
-        <v>1203.7</v>
-      </c>
-      <c r="N132" s="39">
+        <v>10999</v>
+      </c>
+      <c r="M133" s="48">
+        <f t="shared" ref="M133:M136" si="105">SUM(D133:L133)/40</f>
+        <v>1263.7</v>
+      </c>
+      <c r="N133" s="39">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="O132" s="49">
-        <f t="shared" si="1"/>
-        <v>62.470500000000001</v>
-      </c>
-      <c r="P132" s="73">
-        <f t="shared" ref="P132:P136" si="106">SUM(G132:I132)/20</f>
+      <c r="O133" s="49">
+        <f t="shared" si="1"/>
+        <v>62.470500000000001</v>
+      </c>
+      <c r="P133" s="73">
+        <f t="shared" ref="P133:P137" si="106">SUM(G133:I133)/20</f>
         <v>793.4</v>
       </c>
-      <c r="Q132" s="40">
-        <f t="shared" ref="Q132:Q136" si="107">SUM(J132:L132)/20</f>
-        <v>1309.8499999999999</v>
-      </c>
-      <c r="R132" s="51" t="e">
+      <c r="Q133" s="40">
+        <f t="shared" ref="Q133:Q137" si="107">SUM(J133:L133)/20</f>
+        <v>1429.85</v>
+      </c>
+      <c r="R133" s="51" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
-      <c r="S132" s="52">
+      <c r="S133" s="52">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="T132" s="52">
+      <c r="T133" s="52">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="U132" s="53" t="e">
+      <c r="U133" s="53" t="e">
         <f t="shared" si="19"/>
         <v>#VALUE!</v>
       </c>
-      <c r="V132" s="54" t="e">
-        <f t="shared" ref="V132:V136" si="108">SUM(D132:F132)*$V$3</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W132" s="55">
-        <f t="shared" ref="W132:W136" si="109">SUM(G132:I132)*$W$3</f>
-        <v>0</v>
-      </c>
-      <c r="X132" s="55">
-        <f t="shared" ref="X132:X136" si="110">SUM(J132:L132)*$X$3</f>
-        <v>0</v>
-      </c>
-      <c r="Y132" s="56" t="e">
+      <c r="V133" s="54" t="e">
+        <f t="shared" ref="V133:V137" si="108">SUM(D133:F133)*$V$3</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W133" s="55">
+        <f t="shared" ref="W133:W137" si="109">SUM(G133:I133)*$W$3</f>
+        <v>0</v>
+      </c>
+      <c r="X133" s="55">
+        <f t="shared" ref="X133:X137" si="110">SUM(J133:L133)*$X$3</f>
+        <v>0</v>
+      </c>
+      <c r="Y133" s="56" t="e">
         <f t="shared" si="44"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="133" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A133" s="78"/>
-      <c r="B133" s="107">
-        <v>0</v>
-      </c>
-      <c r="C133" s="57" t="s">
-        <v>69</v>
-      </c>
-      <c r="D133" s="108"/>
-      <c r="E133" s="109"/>
-      <c r="F133" s="110"/>
-      <c r="G133" s="109"/>
-      <c r="H133" s="109"/>
-      <c r="I133" s="110"/>
-      <c r="J133" s="109"/>
-      <c r="K133" s="109"/>
-      <c r="L133" s="110"/>
-      <c r="M133" s="111">
-        <f>SUM(D133:L133)</f>
-        <v>0</v>
-      </c>
-      <c r="N133" s="39"/>
-      <c r="O133" s="49"/>
-      <c r="P133" s="73"/>
-      <c r="Q133" s="40"/>
-      <c r="R133" s="51"/>
-      <c r="S133" s="52"/>
-      <c r="T133" s="52"/>
-      <c r="U133" s="53"/>
-      <c r="V133" s="54"/>
-      <c r="W133" s="55"/>
-      <c r="X133" s="55"/>
-      <c r="Y133" s="56"/>
     </row>
     <row r="134" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A134" s="78"/>
-      <c r="B134" s="47">
+      <c r="B134" s="107">
+        <v>0</v>
+      </c>
+      <c r="C134" s="57" t="s">
+        <v>69</v>
+      </c>
+      <c r="D134" s="108"/>
+      <c r="E134" s="109"/>
+      <c r="F134" s="110"/>
+      <c r="G134" s="109"/>
+      <c r="H134" s="109"/>
+      <c r="I134" s="110"/>
+      <c r="J134" s="109"/>
+      <c r="K134" s="109"/>
+      <c r="L134" s="110"/>
+      <c r="M134" s="111">
+        <f>SUM(D134:L134)</f>
+        <v>0</v>
+      </c>
+      <c r="N134" s="39"/>
+      <c r="O134" s="49"/>
+      <c r="P134" s="73"/>
+      <c r="Q134" s="40"/>
+      <c r="R134" s="51"/>
+      <c r="S134" s="52"/>
+      <c r="T134" s="52"/>
+      <c r="U134" s="53"/>
+      <c r="V134" s="54"/>
+      <c r="W134" s="55"/>
+      <c r="X134" s="55"/>
+      <c r="Y134" s="56"/>
+    </row>
+    <row r="135" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A135" s="78"/>
+      <c r="B135" s="47">
         <v>1</v>
       </c>
-      <c r="C134" s="57" t="s">
+      <c r="C135" s="57" t="s">
         <v>33</v>
-      </c>
-      <c r="D134" s="74"/>
-      <c r="E134" s="75"/>
-      <c r="F134" s="76"/>
-      <c r="G134" s="50"/>
-      <c r="H134" s="75"/>
-      <c r="I134" s="49"/>
-      <c r="J134" s="50"/>
-      <c r="K134" s="75"/>
-      <c r="L134" s="76"/>
-      <c r="M134" s="48">
-        <f t="shared" si="105"/>
-        <v>0</v>
-      </c>
-      <c r="N134" s="39">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="O134" s="49">
-        <f t="shared" si="1"/>
-        <v>62.470500000000001</v>
-      </c>
-      <c r="P134" s="73">
-        <f t="shared" si="106"/>
-        <v>0</v>
-      </c>
-      <c r="Q134" s="40">
-        <f t="shared" si="107"/>
-        <v>0</v>
-      </c>
-      <c r="R134" s="51" t="e">
-        <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S134" s="52">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="T134" s="52">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="U134" s="53" t="e">
-        <f t="shared" si="19"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V134" s="54" t="e">
-        <f t="shared" si="108"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W134" s="55">
-        <f t="shared" si="109"/>
-        <v>0</v>
-      </c>
-      <c r="X134" s="55">
-        <f t="shared" si="110"/>
-        <v>0</v>
-      </c>
-      <c r="Y134" s="56" t="e">
-        <f t="shared" si="20"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="135" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="B135" s="47">
-        <v>2</v>
-      </c>
-      <c r="C135" s="57" t="s">
-        <v>26</v>
       </c>
       <c r="D135" s="74"/>
       <c r="E135" s="75"/>
@@ -11617,56 +11594,31 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="136" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B136" s="158" t="s">
-        <v>70</v>
-      </c>
-      <c r="C136" s="159"/>
-      <c r="D136" s="83">
-        <f>SUM(D134:D135)</f>
-        <v>0</v>
-      </c>
-      <c r="E136" s="83">
-        <f t="shared" ref="E136:L136" si="111">SUM(E134:E135)</f>
-        <v>0</v>
-      </c>
-      <c r="F136" s="83">
-        <f t="shared" si="111"/>
-        <v>0</v>
-      </c>
-      <c r="G136" s="83">
-        <f t="shared" si="111"/>
-        <v>0</v>
-      </c>
-      <c r="H136" s="83">
-        <f t="shared" si="111"/>
-        <v>0</v>
-      </c>
-      <c r="I136" s="83">
-        <f t="shared" si="111"/>
-        <v>0</v>
-      </c>
-      <c r="J136" s="83">
-        <f t="shared" si="111"/>
-        <v>0</v>
-      </c>
-      <c r="K136" s="83">
-        <f t="shared" si="111"/>
-        <v>0</v>
-      </c>
-      <c r="L136" s="83">
-        <f t="shared" si="111"/>
-        <v>0</v>
-      </c>
-      <c r="M136" s="112">
-        <f>SUM(M133:M135)</f>
-        <v>0</v>
-      </c>
-      <c r="N136" s="59">
+    <row r="136" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="B136" s="47">
+        <v>2</v>
+      </c>
+      <c r="C136" s="57" t="s">
+        <v>26</v>
+      </c>
+      <c r="D136" s="74"/>
+      <c r="E136" s="75"/>
+      <c r="F136" s="76"/>
+      <c r="G136" s="50"/>
+      <c r="H136" s="75"/>
+      <c r="I136" s="49"/>
+      <c r="J136" s="50"/>
+      <c r="K136" s="75"/>
+      <c r="L136" s="76"/>
+      <c r="M136" s="48">
+        <f t="shared" si="105"/>
+        <v>0</v>
+      </c>
+      <c r="N136" s="39">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="O136" s="58">
+      <c r="O136" s="49">
         <f t="shared" si="1"/>
         <v>62.470500000000001</v>
       </c>
@@ -11712,114 +11664,208 @@
       </c>
     </row>
     <row r="137" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B137" s="147" t="s">
+      <c r="B137" s="170" t="s">
+        <v>70</v>
+      </c>
+      <c r="C137" s="171"/>
+      <c r="D137" s="83">
+        <f>SUM(D135:D136)</f>
+        <v>0</v>
+      </c>
+      <c r="E137" s="83">
+        <f t="shared" ref="E137:L137" si="111">SUM(E135:E136)</f>
+        <v>0</v>
+      </c>
+      <c r="F137" s="83">
+        <f t="shared" si="111"/>
+        <v>0</v>
+      </c>
+      <c r="G137" s="83">
+        <f t="shared" si="111"/>
+        <v>0</v>
+      </c>
+      <c r="H137" s="83">
+        <f t="shared" si="111"/>
+        <v>0</v>
+      </c>
+      <c r="I137" s="83">
+        <f t="shared" si="111"/>
+        <v>0</v>
+      </c>
+      <c r="J137" s="83">
+        <f t="shared" si="111"/>
+        <v>0</v>
+      </c>
+      <c r="K137" s="83">
+        <f t="shared" si="111"/>
+        <v>0</v>
+      </c>
+      <c r="L137" s="83">
+        <f t="shared" si="111"/>
+        <v>0</v>
+      </c>
+      <c r="M137" s="112">
+        <f>SUM(M134:M136)</f>
+        <v>0</v>
+      </c>
+      <c r="N137" s="59">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O137" s="58">
+        <f t="shared" si="1"/>
+        <v>62.470500000000001</v>
+      </c>
+      <c r="P137" s="73">
+        <f t="shared" si="106"/>
+        <v>0</v>
+      </c>
+      <c r="Q137" s="40">
+        <f t="shared" si="107"/>
+        <v>0</v>
+      </c>
+      <c r="R137" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S137" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T137" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U137" s="53" t="e">
+        <f t="shared" si="19"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V137" s="54" t="e">
+        <f t="shared" si="108"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W137" s="55">
+        <f t="shared" si="109"/>
+        <v>0</v>
+      </c>
+      <c r="X137" s="55">
+        <f t="shared" si="110"/>
+        <v>0</v>
+      </c>
+      <c r="Y137" s="56" t="e">
+        <f t="shared" si="20"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="138" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B138" s="159" t="s">
         <v>11</v>
       </c>
-      <c r="C137" s="148"/>
-      <c r="D137" s="85">
-        <f>SUM(D132,D136)</f>
+      <c r="C138" s="160"/>
+      <c r="D138" s="85">
+        <f>SUM(D133,D137)</f>
         <v>6083</v>
       </c>
-      <c r="E137" s="85">
-        <f t="shared" ref="E137:L137" si="112">SUM(E132,E136)</f>
-        <v>0</v>
-      </c>
-      <c r="F137" s="85">
+      <c r="E138" s="85">
+        <f t="shared" ref="E138:L138" si="112">SUM(E133,E137)</f>
+        <v>0</v>
+      </c>
+      <c r="F138" s="85">
         <f t="shared" si="112"/>
         <v>0</v>
       </c>
-      <c r="G137" s="85">
+      <c r="G138" s="85">
         <f t="shared" si="112"/>
         <v>4462</v>
       </c>
-      <c r="H137" s="85">
+      <c r="H138" s="85">
         <f t="shared" si="112"/>
         <v>4607</v>
       </c>
-      <c r="I137" s="85">
+      <c r="I138" s="85">
         <f t="shared" si="112"/>
         <v>6799</v>
       </c>
-      <c r="J137" s="85">
+      <c r="J138" s="85">
         <f t="shared" si="112"/>
-        <v>8301</v>
-      </c>
-      <c r="K137" s="85">
+        <v>9181</v>
+      </c>
+      <c r="K138" s="85">
         <f t="shared" si="112"/>
-        <v>7777</v>
-      </c>
-      <c r="L137" s="85">
+        <v>8417</v>
+      </c>
+      <c r="L138" s="85">
         <f t="shared" si="112"/>
-        <v>10119</v>
-      </c>
-      <c r="M137" s="60">
+        <v>10999</v>
+      </c>
+      <c r="M138" s="60">
         <f t="shared" si="0"/>
-        <v>1203.7</v>
-      </c>
-      <c r="N137" s="63">
-        <f>SUM(N5:N136)</f>
-        <v>0</v>
-      </c>
-      <c r="O137" s="61">
-        <f t="shared" ref="O137:Y137" si="113">SUM(O5:O136)</f>
+        <v>1263.7</v>
+      </c>
+      <c r="N138" s="63">
+        <f>SUM(N5:N137)</f>
+        <v>0</v>
+      </c>
+      <c r="O138" s="61">
+        <f t="shared" ref="O138:Y138" si="113">SUM(O5:O137)</f>
         <v>8183.6355000000185</v>
       </c>
-      <c r="P137" s="62">
+      <c r="P138" s="62">
         <f t="shared" si="113"/>
         <v>1592.8</v>
       </c>
-      <c r="Q137" s="64">
+      <c r="Q138" s="64">
         <f t="shared" si="113"/>
-        <v>2623.7</v>
-      </c>
-      <c r="R137" s="65" t="e">
+        <v>2863.7</v>
+      </c>
+      <c r="R138" s="65" t="e">
         <f t="shared" si="113"/>
         <v>#VALUE!</v>
       </c>
-      <c r="S137" s="66">
+      <c r="S138" s="66">
         <f t="shared" si="113"/>
         <v>0</v>
       </c>
-      <c r="T137" s="66">
+      <c r="T138" s="66">
         <f t="shared" si="113"/>
         <v>0</v>
       </c>
-      <c r="U137" s="67" t="e">
+      <c r="U138" s="67" t="e">
         <f t="shared" si="113"/>
         <v>#VALUE!</v>
       </c>
-      <c r="V137" s="68" t="e">
+      <c r="V138" s="68" t="e">
         <f t="shared" si="113"/>
         <v>#VALUE!</v>
       </c>
-      <c r="W137" s="69">
+      <c r="W138" s="69">
         <f t="shared" si="113"/>
         <v>0</v>
       </c>
-      <c r="X137" s="69">
+      <c r="X138" s="69">
         <f t="shared" si="113"/>
         <v>0</v>
       </c>
-      <c r="Y137" s="70" t="e">
+      <c r="Y138" s="70" t="e">
         <f t="shared" si="113"/>
         <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B138:C138"/>
+    <mergeCell ref="M2:O2"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="M3:O3"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="B137:C137"/>
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="R3:U3"/>
     <mergeCell ref="V3:Y3"/>
-    <mergeCell ref="B132:C132"/>
-    <mergeCell ref="B137:C137"/>
-    <mergeCell ref="M2:O2"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="M3:O3"/>
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="B136:C136"/>
+    <mergeCell ref="B133:C133"/>
   </mergeCells>
-  <conditionalFormatting sqref="C45:C59">
+  <conditionalFormatting sqref="C46:C60">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11854,7 +11900,7 @@
     <row r="2" spans="3:26" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="3:26" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C3" s="174" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D3" s="175"/>
       <c r="E3" s="175"/>
@@ -11917,24 +11963,24 @@
         <v>49</v>
       </c>
       <c r="D5" s="88">
-        <v>366</v>
+        <v>392</v>
       </c>
       <c r="E5" s="79">
-        <v>641</v>
+        <v>724</v>
       </c>
       <c r="F5" s="79">
-        <v>550</v>
+        <v>600</v>
       </c>
       <c r="G5" s="102">
         <f>SUM(D5:F5)</f>
-        <v>1557</v>
+        <v>1716</v>
       </c>
       <c r="H5" s="95">
         <v>10000</v>
       </c>
       <c r="I5" s="96">
         <f>G5-H5</f>
-        <v>-8443</v>
+        <v>-8284</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>1</v>
@@ -11955,19 +12001,19 @@
       </c>
       <c r="D6" s="104">
         <f>D5*40</f>
-        <v>14640</v>
+        <v>15680</v>
       </c>
       <c r="E6" s="104">
         <f t="shared" ref="E6:F6" si="1">E5*40</f>
-        <v>25640</v>
+        <v>28960</v>
       </c>
       <c r="F6" s="104">
         <f t="shared" si="1"/>
-        <v>22000</v>
+        <v>24000</v>
       </c>
       <c r="G6" s="105">
         <f>SUM(D6:F6)</f>
-        <v>62280</v>
+        <v>68640</v>
       </c>
       <c r="H6" s="97">
         <f>H5*40</f>
@@ -11975,7 +12021,7 @@
       </c>
       <c r="I6" s="98">
         <f>G6-H6</f>
-        <v>-337720</v>
+        <v>-331360</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>2</v>
@@ -12092,11 +12138,11 @@
       </c>
       <c r="D9" s="106">
         <f>D8-D5</f>
-        <v>-366</v>
+        <v>-392</v>
       </c>
       <c r="E9" s="106">
         <f>E8-E5</f>
-        <v>-641</v>
+        <v>-724</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>5</v>
@@ -12224,7 +12270,7 @@
       </c>
       <c r="G12" s="91">
         <f>D12+G5</f>
-        <v>5757</v>
+        <v>5916</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>11</v>
@@ -12275,7 +12321,7 @@
       </c>
       <c r="G13" s="91">
         <f>G12*40</f>
-        <v>230280</v>
+        <v>236640</v>
       </c>
       <c r="S13" s="172" t="s">
         <v>85</v>

--- a/Aug_2026/daily Reports/LMT Orders.xlsx
+++ b/Aug_2026/daily Reports/LMT Orders.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28F28180-5C85-4877-AB2F-38D34BF5526A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26F9212D-A787-43EB-93A4-8837CB21D008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="121">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -377,6 +377,15 @@
   <si>
     <t xml:space="preserve">Till To Date </t>
   </si>
+  <si>
+    <t xml:space="preserve">Arshad Sons </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Euro Model Town </t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 Season </t>
+  </si>
 </sst>
 </file>
 
@@ -1264,7 +1273,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="181">
+  <cellXfs count="189">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1739,6 +1748,20 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2277,7 +2300,7 @@
     <row r="1" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B1" s="147">
         <f ca="1">TODAY()</f>
-        <v>46249</v>
+        <v>46252</v>
       </c>
       <c r="C1" s="147"/>
       <c r="D1" s="147"/>
@@ -4475,36 +4498,36 @@
       </c>
     </row>
     <row r="29" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A29" s="140">
+      <c r="A29" s="181">
         <v>46246</v>
       </c>
-      <c r="B29" s="47">
+      <c r="B29" s="182">
         <v>25</v>
       </c>
-      <c r="C29" s="57" t="s">
+      <c r="C29" s="183" t="s">
         <v>53</v>
       </c>
-      <c r="D29" s="143">
+      <c r="D29" s="184">
         <v>40</v>
       </c>
-      <c r="E29" s="144"/>
-      <c r="F29" s="145"/>
-      <c r="G29" s="146">
+      <c r="E29" s="185"/>
+      <c r="F29" s="186"/>
+      <c r="G29" s="187">
         <v>40</v>
       </c>
-      <c r="H29" s="144">
+      <c r="H29" s="185">
         <v>40</v>
       </c>
-      <c r="I29" s="56">
+      <c r="I29" s="188">
         <v>40</v>
       </c>
-      <c r="J29" s="146">
+      <c r="J29" s="187">
         <v>20</v>
       </c>
-      <c r="K29" s="144">
+      <c r="K29" s="185">
         <v>20</v>
       </c>
-      <c r="L29" s="145">
+      <c r="L29" s="186">
         <v>20</v>
       </c>
       <c r="M29" s="48">
@@ -4561,34 +4584,34 @@
       </c>
     </row>
     <row r="30" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A30" s="140">
+      <c r="A30" s="181">
         <v>46246</v>
       </c>
-      <c r="B30" s="47">
+      <c r="B30" s="182">
         <v>26</v>
       </c>
-      <c r="C30" s="57" t="s">
+      <c r="C30" s="183" t="s">
         <v>111</v>
       </c>
-      <c r="D30" s="143"/>
-      <c r="E30" s="144"/>
-      <c r="F30" s="145"/>
-      <c r="G30" s="146">
+      <c r="D30" s="184"/>
+      <c r="E30" s="185"/>
+      <c r="F30" s="186"/>
+      <c r="G30" s="187">
         <v>200</v>
       </c>
-      <c r="H30" s="144">
+      <c r="H30" s="185">
         <v>200</v>
       </c>
-      <c r="I30" s="56">
+      <c r="I30" s="188">
         <v>200</v>
       </c>
-      <c r="J30" s="146">
+      <c r="J30" s="187">
         <v>200</v>
       </c>
-      <c r="K30" s="144">
+      <c r="K30" s="185">
         <v>200</v>
       </c>
-      <c r="L30" s="145">
+      <c r="L30" s="186">
         <v>200</v>
       </c>
       <c r="M30" s="48">
@@ -4645,34 +4668,34 @@
       </c>
     </row>
     <row r="31" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A31" s="140">
+      <c r="A31" s="181">
         <v>46246</v>
       </c>
-      <c r="B31" s="47">
+      <c r="B31" s="182">
         <v>27</v>
       </c>
-      <c r="C31" s="57" t="s">
+      <c r="C31" s="183" t="s">
         <v>112</v>
       </c>
-      <c r="D31" s="143"/>
-      <c r="E31" s="144"/>
-      <c r="F31" s="145"/>
-      <c r="G31" s="146">
+      <c r="D31" s="184"/>
+      <c r="E31" s="185"/>
+      <c r="F31" s="186"/>
+      <c r="G31" s="187">
         <v>40</v>
       </c>
-      <c r="H31" s="144">
+      <c r="H31" s="185">
         <v>40</v>
       </c>
-      <c r="I31" s="56">
+      <c r="I31" s="188">
         <v>40</v>
       </c>
-      <c r="J31" s="146">
+      <c r="J31" s="187">
         <v>40</v>
       </c>
-      <c r="K31" s="144">
+      <c r="K31" s="185">
         <v>40</v>
       </c>
-      <c r="L31" s="145">
+      <c r="L31" s="186">
         <v>40</v>
       </c>
       <c r="M31" s="48">
@@ -4729,30 +4752,30 @@
       </c>
     </row>
     <row r="32" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A32" s="140">
+      <c r="A32" s="181">
         <v>46246</v>
       </c>
       <c r="B32" s="47">
         <v>28</v>
       </c>
-      <c r="C32" s="57" t="s">
+      <c r="C32" s="183" t="s">
         <v>91</v>
       </c>
-      <c r="D32" s="143"/>
-      <c r="E32" s="144"/>
-      <c r="F32" s="145"/>
-      <c r="G32" s="146">
+      <c r="D32" s="184"/>
+      <c r="E32" s="185"/>
+      <c r="F32" s="186"/>
+      <c r="G32" s="187">
         <v>200</v>
       </c>
-      <c r="H32" s="144"/>
-      <c r="I32" s="56">
+      <c r="H32" s="185"/>
+      <c r="I32" s="188">
         <v>160</v>
       </c>
-      <c r="J32" s="146">
+      <c r="J32" s="187">
         <v>120</v>
       </c>
-      <c r="K32" s="144"/>
-      <c r="L32" s="145">
+      <c r="K32" s="185"/>
+      <c r="L32" s="186">
         <v>160</v>
       </c>
       <c r="M32" s="48">
@@ -4809,34 +4832,34 @@
       </c>
     </row>
     <row r="33" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A33" s="140">
+      <c r="A33" s="181">
         <v>46246</v>
       </c>
       <c r="B33" s="47">
         <v>29</v>
       </c>
-      <c r="C33" s="57" t="s">
+      <c r="C33" s="183" t="s">
         <v>103</v>
       </c>
-      <c r="D33" s="143"/>
-      <c r="E33" s="144"/>
-      <c r="F33" s="145"/>
-      <c r="G33" s="146">
+      <c r="D33" s="184"/>
+      <c r="E33" s="185"/>
+      <c r="F33" s="186"/>
+      <c r="G33" s="187">
         <v>120</v>
       </c>
-      <c r="H33" s="144">
+      <c r="H33" s="185">
         <v>80</v>
       </c>
-      <c r="I33" s="56">
+      <c r="I33" s="188">
         <v>40</v>
       </c>
-      <c r="J33" s="146">
+      <c r="J33" s="187">
         <v>140</v>
       </c>
-      <c r="K33" s="144">
+      <c r="K33" s="185">
         <v>120</v>
       </c>
-      <c r="L33" s="145">
+      <c r="L33" s="186">
         <v>180</v>
       </c>
       <c r="M33" s="48">
@@ -4893,36 +4916,36 @@
       </c>
     </row>
     <row r="34" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A34" s="140">
+      <c r="A34" s="181">
         <v>46246</v>
       </c>
       <c r="B34" s="47">
         <v>30</v>
       </c>
-      <c r="C34" s="57" t="s">
+      <c r="C34" s="183" t="s">
         <v>33</v>
       </c>
-      <c r="D34" s="74">
+      <c r="D34" s="184">
         <v>4000</v>
       </c>
-      <c r="E34" s="75"/>
-      <c r="F34" s="76"/>
-      <c r="G34" s="50">
+      <c r="E34" s="185"/>
+      <c r="F34" s="186"/>
+      <c r="G34" s="187">
         <v>1600</v>
       </c>
-      <c r="H34" s="75">
+      <c r="H34" s="185">
         <v>1600</v>
       </c>
-      <c r="I34" s="49">
+      <c r="I34" s="188">
         <v>800</v>
       </c>
-      <c r="J34" s="50">
+      <c r="J34" s="187">
         <v>4000</v>
       </c>
-      <c r="K34" s="75">
+      <c r="K34" s="185">
         <v>3200</v>
       </c>
-      <c r="L34" s="76">
+      <c r="L34" s="186">
         <v>2800</v>
       </c>
       <c r="M34" s="48">
@@ -4979,73 +5002,108 @@
       </c>
     </row>
     <row r="35" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A35" s="140">
+      <c r="A35" s="181">
         <v>46246</v>
       </c>
-      <c r="B35" s="47"/>
-      <c r="C35" s="57" t="s">
+      <c r="B35" s="47">
+        <v>31</v>
+      </c>
+      <c r="C35" s="183" t="s">
         <v>116</v>
       </c>
-      <c r="D35" s="74"/>
-      <c r="E35" s="75"/>
-      <c r="F35" s="76"/>
-      <c r="G35" s="50"/>
-      <c r="H35" s="75"/>
-      <c r="I35" s="49"/>
-      <c r="J35" s="50">
+      <c r="D35" s="184"/>
+      <c r="E35" s="185"/>
+      <c r="F35" s="186"/>
+      <c r="G35" s="187"/>
+      <c r="H35" s="185"/>
+      <c r="I35" s="188"/>
+      <c r="J35" s="187">
         <v>880</v>
       </c>
-      <c r="K35" s="75">
+      <c r="K35" s="185">
         <v>640</v>
       </c>
-      <c r="L35" s="76">
+      <c r="L35" s="186">
         <v>880</v>
       </c>
-      <c r="M35" s="48"/>
-      <c r="N35" s="39"/>
-      <c r="O35" s="49"/>
-      <c r="P35" s="73"/>
+      <c r="M35" s="48">
+        <f t="shared" si="68"/>
+        <v>60</v>
+      </c>
+      <c r="N35" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O35" s="49">
+        <f t="shared" si="1"/>
+        <v>62.470500000000001</v>
+      </c>
+      <c r="P35" s="73">
+        <f t="shared" ref="P35" si="76">SUM(G35:I35)/20</f>
+        <v>0</v>
+      </c>
       <c r="Q35" s="40">
-        <f t="shared" si="70"/>
+        <f t="shared" ref="Q35" si="77">SUM(J35:L35)/20</f>
         <v>120</v>
       </c>
-      <c r="R35" s="51"/>
-      <c r="S35" s="52"/>
-      <c r="T35" s="52"/>
-      <c r="U35" s="53"/>
-      <c r="V35" s="54"/>
-      <c r="W35" s="55"/>
+      <c r="R35" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S35" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T35" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U35" s="53" t="e">
+        <f t="shared" ref="U35" si="78">SUM(R35:T35)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V35" s="54" t="e">
+        <f t="shared" ref="V35" si="79">SUM(D35:F35)*$V$3</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W35" s="55">
+        <f t="shared" ref="W35" si="80">SUM(G35:I35)*$W$3</f>
+        <v>0</v>
+      </c>
       <c r="X35" s="55">
-        <f t="shared" si="74"/>
-        <v>0</v>
-      </c>
-      <c r="Y35" s="56"/>
+        <f t="shared" ref="X35" si="81">SUM(J35:L35)*$X$3</f>
+        <v>0</v>
+      </c>
+      <c r="Y35" s="56" t="e">
+        <f t="shared" ref="Y35" si="82">SUM(V35:X35)</f>
+        <v>#VALUE!</v>
+      </c>
     </row>
     <row r="36" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A36" s="78">
+      <c r="A36" s="181">
         <v>46247</v>
       </c>
       <c r="B36" s="47">
-        <v>31</v>
-      </c>
-      <c r="C36" s="57" t="s">
+        <v>32</v>
+      </c>
+      <c r="C36" s="183" t="s">
         <v>113</v>
       </c>
-      <c r="D36" s="74"/>
-      <c r="E36" s="75"/>
-      <c r="F36" s="76"/>
-      <c r="G36" s="50"/>
-      <c r="H36" s="75"/>
-      <c r="I36" s="49">
+      <c r="D36" s="184"/>
+      <c r="E36" s="185"/>
+      <c r="F36" s="186"/>
+      <c r="G36" s="187"/>
+      <c r="H36" s="185"/>
+      <c r="I36" s="188">
         <v>200</v>
       </c>
-      <c r="J36" s="50">
+      <c r="J36" s="187">
         <v>40</v>
       </c>
-      <c r="K36" s="75">
+      <c r="K36" s="185">
         <v>40</v>
       </c>
-      <c r="L36" s="76">
+      <c r="L36" s="186">
         <v>120</v>
       </c>
       <c r="M36" s="48">
@@ -5106,7 +5164,7 @@
         <v>46247</v>
       </c>
       <c r="B37" s="47">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C37" s="57" t="s">
         <v>114</v>
@@ -5192,7 +5250,7 @@
         <v>46247</v>
       </c>
       <c r="B38" s="47">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C38" s="57" t="s">
         <v>115</v>
@@ -5272,23 +5330,41 @@
       </c>
     </row>
     <row r="39" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A39" s="78"/>
-      <c r="B39" s="47">
-        <v>34</v>
-      </c>
-      <c r="C39" s="57"/>
-      <c r="D39" s="74"/>
-      <c r="E39" s="75"/>
-      <c r="F39" s="76"/>
-      <c r="G39" s="50"/>
-      <c r="H39" s="75"/>
-      <c r="I39" s="49"/>
-      <c r="J39" s="50"/>
-      <c r="K39" s="75"/>
-      <c r="L39" s="76"/>
+      <c r="A39" s="140">
+        <v>46249</v>
+      </c>
+      <c r="B39" s="182">
+        <v>35</v>
+      </c>
+      <c r="C39" s="142" t="s">
+        <v>118</v>
+      </c>
+      <c r="D39" s="143">
+        <v>40</v>
+      </c>
+      <c r="E39" s="144"/>
+      <c r="F39" s="145"/>
+      <c r="G39" s="146">
+        <v>20</v>
+      </c>
+      <c r="H39" s="144">
+        <v>20</v>
+      </c>
+      <c r="I39" s="56">
+        <v>40</v>
+      </c>
+      <c r="J39" s="146">
+        <v>40</v>
+      </c>
+      <c r="K39" s="144">
+        <v>20</v>
+      </c>
+      <c r="L39" s="145">
+        <v>20</v>
+      </c>
       <c r="M39" s="48">
         <f t="shared" si="68"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N39" s="39">
         <f t="shared" si="18"/>
@@ -5300,11 +5376,11 @@
       </c>
       <c r="P39" s="73">
         <f t="shared" si="69"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q39" s="40">
         <f t="shared" si="70"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R39" s="51" t="e">
         <f t="shared" si="4"/>
@@ -5340,23 +5416,41 @@
       </c>
     </row>
     <row r="40" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A40" s="78"/>
-      <c r="B40" s="47">
-        <v>35</v>
-      </c>
-      <c r="C40" s="57"/>
-      <c r="D40" s="74"/>
-      <c r="E40" s="75"/>
-      <c r="F40" s="76"/>
-      <c r="G40" s="50"/>
-      <c r="H40" s="75"/>
-      <c r="I40" s="49"/>
-      <c r="J40" s="50"/>
-      <c r="K40" s="75"/>
-      <c r="L40" s="76"/>
+      <c r="A40" s="140">
+        <v>46249</v>
+      </c>
+      <c r="B40" s="182">
+        <v>36</v>
+      </c>
+      <c r="C40" s="142" t="s">
+        <v>119</v>
+      </c>
+      <c r="D40" s="143">
+        <v>80</v>
+      </c>
+      <c r="E40" s="144"/>
+      <c r="F40" s="145"/>
+      <c r="G40" s="146">
+        <v>103</v>
+      </c>
+      <c r="H40" s="144">
+        <v>104</v>
+      </c>
+      <c r="I40" s="56">
+        <v>38</v>
+      </c>
+      <c r="J40" s="146">
+        <v>68</v>
+      </c>
+      <c r="K40" s="144">
+        <v>93</v>
+      </c>
+      <c r="L40" s="145">
+        <v>33</v>
+      </c>
       <c r="M40" s="48">
         <f t="shared" si="68"/>
-        <v>0</v>
+        <v>12.975</v>
       </c>
       <c r="N40" s="39">
         <f t="shared" si="18"/>
@@ -5368,11 +5462,11 @@
       </c>
       <c r="P40" s="73">
         <f t="shared" si="69"/>
-        <v>0</v>
+        <v>12.25</v>
       </c>
       <c r="Q40" s="40">
         <f t="shared" si="70"/>
-        <v>0</v>
+        <v>9.6999999999999993</v>
       </c>
       <c r="R40" s="51" t="e">
         <f t="shared" si="4"/>
@@ -5408,23 +5502,37 @@
       </c>
     </row>
     <row r="41" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A41" s="78"/>
-      <c r="B41" s="47">
-        <v>36</v>
-      </c>
-      <c r="C41" s="57"/>
-      <c r="D41" s="74"/>
-      <c r="E41" s="75"/>
-      <c r="F41" s="76"/>
-      <c r="G41" s="50"/>
-      <c r="H41" s="75"/>
-      <c r="I41" s="49"/>
-      <c r="J41" s="50"/>
-      <c r="K41" s="75"/>
-      <c r="L41" s="76"/>
+      <c r="A41" s="140">
+        <v>46249</v>
+      </c>
+      <c r="B41" s="182">
+        <v>37</v>
+      </c>
+      <c r="C41" s="142" t="s">
+        <v>120</v>
+      </c>
+      <c r="D41" s="143"/>
+      <c r="E41" s="144"/>
+      <c r="F41" s="145"/>
+      <c r="G41" s="146">
+        <v>120</v>
+      </c>
+      <c r="H41" s="144">
+        <v>200</v>
+      </c>
+      <c r="I41" s="56">
+        <v>200</v>
+      </c>
+      <c r="J41" s="146"/>
+      <c r="K41" s="144">
+        <v>200</v>
+      </c>
+      <c r="L41" s="145">
+        <v>200</v>
+      </c>
       <c r="M41" s="48">
         <f t="shared" si="68"/>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="N41" s="39">
         <f t="shared" si="18"/>
@@ -5436,11 +5544,11 @@
       </c>
       <c r="P41" s="73">
         <f t="shared" si="69"/>
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="Q41" s="40">
         <f t="shared" si="70"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="R41" s="51" t="e">
         <f t="shared" si="4"/>
@@ -5476,23 +5584,39 @@
       </c>
     </row>
     <row r="42" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A42" s="78"/>
+      <c r="A42" s="78">
+        <v>46251</v>
+      </c>
       <c r="B42" s="47">
-        <v>37</v>
-      </c>
-      <c r="C42" s="57"/>
+        <v>38</v>
+      </c>
+      <c r="C42" s="57" t="s">
+        <v>115</v>
+      </c>
       <c r="D42" s="74"/>
       <c r="E42" s="75"/>
       <c r="F42" s="76"/>
-      <c r="G42" s="50"/>
-      <c r="H42" s="75"/>
-      <c r="I42" s="49"/>
-      <c r="J42" s="50"/>
-      <c r="K42" s="75"/>
-      <c r="L42" s="76"/>
+      <c r="G42" s="50">
+        <v>40</v>
+      </c>
+      <c r="H42" s="75">
+        <v>40</v>
+      </c>
+      <c r="I42" s="49">
+        <v>40</v>
+      </c>
+      <c r="J42" s="50">
+        <v>40</v>
+      </c>
+      <c r="K42" s="75">
+        <v>40</v>
+      </c>
+      <c r="L42" s="76">
+        <v>40</v>
+      </c>
       <c r="M42" s="48">
         <f t="shared" si="68"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N42" s="39">
         <f t="shared" si="18"/>
@@ -5504,11 +5628,11 @@
       </c>
       <c r="P42" s="73">
         <f t="shared" si="69"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q42" s="40">
         <f t="shared" si="70"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R42" s="51" t="e">
         <f t="shared" si="4"/>
@@ -5546,7 +5670,7 @@
     <row r="43" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A43" s="78"/>
       <c r="B43" s="47">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C43" s="57"/>
       <c r="D43" s="74"/>
@@ -5614,7 +5738,7 @@
     <row r="44" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A44" s="78"/>
       <c r="B44" s="47">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C44" s="57"/>
       <c r="D44" s="74"/>
@@ -5682,7 +5806,7 @@
     <row r="45" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A45" s="78"/>
       <c r="B45" s="47">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C45" s="57"/>
       <c r="D45" s="74"/>
@@ -5750,7 +5874,7 @@
     <row r="46" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A46" s="78"/>
       <c r="B46" s="47">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C46" s="57"/>
       <c r="D46" s="74"/>
@@ -5818,7 +5942,7 @@
     <row r="47" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A47" s="78"/>
       <c r="B47" s="47">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C47" s="57"/>
       <c r="D47" s="74"/>
@@ -5868,7 +5992,7 @@
     <row r="48" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A48" s="78"/>
       <c r="B48" s="47">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C48" s="57"/>
       <c r="D48" s="74"/>
@@ -5881,7 +6005,7 @@
       <c r="K48" s="75"/>
       <c r="L48" s="76"/>
       <c r="M48" s="48">
-        <f t="shared" ref="M48:M60" si="76">SUM(D48:L48)/40</f>
+        <f t="shared" ref="M48:M60" si="83">SUM(D48:L48)/40</f>
         <v>0</v>
       </c>
       <c r="N48" s="39">
@@ -5893,11 +6017,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P48" s="73">
-        <f t="shared" ref="P48:P60" si="77">SUM(G48:I48)/20</f>
+        <f t="shared" ref="P48:P60" si="84">SUM(G48:I48)/20</f>
         <v>0</v>
       </c>
       <c r="Q48" s="40">
-        <f t="shared" ref="Q48:Q60" si="78">SUM(J48:L48)/20</f>
+        <f t="shared" ref="Q48:Q60" si="85">SUM(J48:L48)/20</f>
         <v>0</v>
       </c>
       <c r="R48" s="51"/>
@@ -5906,19 +6030,19 @@
       <c r="U48" s="53"/>
       <c r="V48" s="54"/>
       <c r="W48" s="55">
-        <f t="shared" ref="W48:W60" si="79">SUM(G48:I48)*$W$3</f>
+        <f t="shared" ref="W48:W60" si="86">SUM(G48:I48)*$W$3</f>
         <v>0</v>
       </c>
       <c r="X48" s="55">
-        <f t="shared" ref="X48:X60" si="80">SUM(J48:L48)*$X$3</f>
+        <f t="shared" ref="X48:X60" si="87">SUM(J48:L48)*$X$3</f>
         <v>0</v>
       </c>
       <c r="Y48" s="56"/>
     </row>
     <row r="49" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A49" s="78"/>
-      <c r="B49" s="47">
-        <v>44</v>
+      <c r="B49" s="182">
+        <v>45</v>
       </c>
       <c r="C49" s="57"/>
       <c r="D49" s="74"/>
@@ -5931,7 +6055,7 @@
       <c r="K49" s="75"/>
       <c r="L49" s="76"/>
       <c r="M49" s="48">
-        <f t="shared" si="76"/>
+        <f t="shared" si="83"/>
         <v>0</v>
       </c>
       <c r="N49" s="39">
@@ -5943,11 +6067,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P49" s="73">
-        <f t="shared" si="77"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="Q49" s="40">
-        <f t="shared" si="78"/>
+        <f t="shared" si="85"/>
         <v>0</v>
       </c>
       <c r="R49" s="51"/>
@@ -5956,19 +6080,19 @@
       <c r="U49" s="53"/>
       <c r="V49" s="54"/>
       <c r="W49" s="55">
-        <f t="shared" si="79"/>
+        <f t="shared" si="86"/>
         <v>0</v>
       </c>
       <c r="X49" s="55">
-        <f t="shared" si="80"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="Y49" s="56"/>
     </row>
     <row r="50" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A50" s="78"/>
-      <c r="B50" s="47">
-        <v>45</v>
+      <c r="B50" s="182">
+        <v>46</v>
       </c>
       <c r="C50" s="57"/>
       <c r="D50" s="74"/>
@@ -5981,7 +6105,7 @@
       <c r="K50" s="75"/>
       <c r="L50" s="76"/>
       <c r="M50" s="48">
-        <f t="shared" si="76"/>
+        <f t="shared" si="83"/>
         <v>0</v>
       </c>
       <c r="N50" s="39">
@@ -5993,11 +6117,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P50" s="73">
-        <f t="shared" si="77"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="Q50" s="40">
-        <f t="shared" si="78"/>
+        <f t="shared" si="85"/>
         <v>0</v>
       </c>
       <c r="R50" s="51"/>
@@ -6006,19 +6130,19 @@
       <c r="U50" s="53"/>
       <c r="V50" s="54"/>
       <c r="W50" s="55">
-        <f t="shared" si="79"/>
+        <f t="shared" si="86"/>
         <v>0</v>
       </c>
       <c r="X50" s="55">
-        <f t="shared" si="80"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="Y50" s="56"/>
     </row>
     <row r="51" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A51" s="78"/>
-      <c r="B51" s="47">
-        <v>46</v>
+      <c r="B51" s="182">
+        <v>47</v>
       </c>
       <c r="C51" s="57"/>
       <c r="D51" s="74"/>
@@ -6031,7 +6155,7 @@
       <c r="K51" s="75"/>
       <c r="L51" s="76"/>
       <c r="M51" s="48">
-        <f t="shared" si="76"/>
+        <f t="shared" si="83"/>
         <v>0</v>
       </c>
       <c r="N51" s="39">
@@ -6043,11 +6167,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P51" s="73">
-        <f t="shared" si="77"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="Q51" s="40">
-        <f t="shared" si="78"/>
+        <f t="shared" si="85"/>
         <v>0</v>
       </c>
       <c r="R51" s="51"/>
@@ -6056,11 +6180,11 @@
       <c r="U51" s="53"/>
       <c r="V51" s="54"/>
       <c r="W51" s="55">
-        <f t="shared" si="79"/>
+        <f t="shared" si="86"/>
         <v>0</v>
       </c>
       <c r="X51" s="55">
-        <f t="shared" si="80"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="Y51" s="56"/>
@@ -6068,7 +6192,7 @@
     <row r="52" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A52" s="78"/>
       <c r="B52" s="47">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C52" s="57"/>
       <c r="D52" s="74"/>
@@ -6081,7 +6205,7 @@
       <c r="K52" s="75"/>
       <c r="L52" s="76"/>
       <c r="M52" s="48">
-        <f t="shared" si="76"/>
+        <f t="shared" si="83"/>
         <v>0</v>
       </c>
       <c r="N52" s="39">
@@ -6093,11 +6217,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P52" s="73">
-        <f t="shared" si="77"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="Q52" s="40">
-        <f t="shared" si="78"/>
+        <f t="shared" si="85"/>
         <v>0</v>
       </c>
       <c r="R52" s="51"/>
@@ -6106,11 +6230,11 @@
       <c r="U52" s="53"/>
       <c r="V52" s="54"/>
       <c r="W52" s="55">
-        <f t="shared" si="79"/>
+        <f t="shared" si="86"/>
         <v>0</v>
       </c>
       <c r="X52" s="55">
-        <f t="shared" si="80"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="Y52" s="56"/>
@@ -6118,7 +6242,7 @@
     <row r="53" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A53" s="78"/>
       <c r="B53" s="47">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C53" s="57"/>
       <c r="D53" s="74"/>
@@ -6131,7 +6255,7 @@
       <c r="K53" s="75"/>
       <c r="L53" s="76"/>
       <c r="M53" s="48">
-        <f t="shared" si="76"/>
+        <f t="shared" si="83"/>
         <v>0</v>
       </c>
       <c r="N53" s="39">
@@ -6143,11 +6267,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P53" s="73">
-        <f t="shared" si="77"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="Q53" s="40">
-        <f t="shared" si="78"/>
+        <f t="shared" si="85"/>
         <v>0</v>
       </c>
       <c r="R53" s="51"/>
@@ -6156,11 +6280,11 @@
       <c r="U53" s="53"/>
       <c r="V53" s="54"/>
       <c r="W53" s="55">
-        <f t="shared" si="79"/>
+        <f t="shared" si="86"/>
         <v>0</v>
       </c>
       <c r="X53" s="55">
-        <f t="shared" si="80"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="Y53" s="56"/>
@@ -6168,7 +6292,7 @@
     <row r="54" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A54" s="78"/>
       <c r="B54" s="47">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C54" s="57"/>
       <c r="D54" s="74"/>
@@ -6181,7 +6305,7 @@
       <c r="K54" s="75"/>
       <c r="L54" s="76"/>
       <c r="M54" s="48">
-        <f t="shared" si="76"/>
+        <f t="shared" si="83"/>
         <v>0</v>
       </c>
       <c r="N54" s="39">
@@ -6193,11 +6317,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P54" s="73">
-        <f t="shared" si="77"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="Q54" s="40">
-        <f t="shared" si="78"/>
+        <f t="shared" si="85"/>
         <v>0</v>
       </c>
       <c r="R54" s="51"/>
@@ -6206,11 +6330,11 @@
       <c r="U54" s="53"/>
       <c r="V54" s="54"/>
       <c r="W54" s="55">
-        <f t="shared" si="79"/>
+        <f t="shared" si="86"/>
         <v>0</v>
       </c>
       <c r="X54" s="55">
-        <f t="shared" si="80"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="Y54" s="56"/>
@@ -6218,7 +6342,7 @@
     <row r="55" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A55" s="78"/>
       <c r="B55" s="47">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C55" s="57"/>
       <c r="D55" s="74"/>
@@ -6231,7 +6355,7 @@
       <c r="K55" s="75"/>
       <c r="L55" s="76"/>
       <c r="M55" s="48">
-        <f t="shared" si="76"/>
+        <f t="shared" si="83"/>
         <v>0</v>
       </c>
       <c r="N55" s="39">
@@ -6243,11 +6367,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P55" s="73">
-        <f t="shared" si="77"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="Q55" s="40">
-        <f t="shared" si="78"/>
+        <f t="shared" si="85"/>
         <v>0</v>
       </c>
       <c r="R55" s="51"/>
@@ -6256,11 +6380,11 @@
       <c r="U55" s="53"/>
       <c r="V55" s="54"/>
       <c r="W55" s="55">
-        <f t="shared" si="79"/>
+        <f t="shared" si="86"/>
         <v>0</v>
       </c>
       <c r="X55" s="55">
-        <f t="shared" si="80"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="Y55" s="56"/>
@@ -6268,7 +6392,7 @@
     <row r="56" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A56" s="78"/>
       <c r="B56" s="47">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C56" s="57"/>
       <c r="D56" s="74"/>
@@ -6281,7 +6405,7 @@
       <c r="K56" s="75"/>
       <c r="L56" s="76"/>
       <c r="M56" s="48">
-        <f t="shared" si="76"/>
+        <f t="shared" si="83"/>
         <v>0</v>
       </c>
       <c r="N56" s="39">
@@ -6293,11 +6417,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P56" s="73">
-        <f t="shared" si="77"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="Q56" s="40">
-        <f t="shared" si="78"/>
+        <f t="shared" si="85"/>
         <v>0</v>
       </c>
       <c r="R56" s="51"/>
@@ -6306,11 +6430,11 @@
       <c r="U56" s="53"/>
       <c r="V56" s="54"/>
       <c r="W56" s="55">
-        <f t="shared" si="79"/>
+        <f t="shared" si="86"/>
         <v>0</v>
       </c>
       <c r="X56" s="55">
-        <f t="shared" si="80"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="Y56" s="56"/>
@@ -6318,7 +6442,7 @@
     <row r="57" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A57" s="78"/>
       <c r="B57" s="47">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C57" s="57"/>
       <c r="D57" s="74"/>
@@ -6331,7 +6455,7 @@
       <c r="K57" s="75"/>
       <c r="L57" s="76"/>
       <c r="M57" s="48">
-        <f t="shared" si="76"/>
+        <f t="shared" si="83"/>
         <v>0</v>
       </c>
       <c r="N57" s="39">
@@ -6343,11 +6467,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P57" s="73">
-        <f t="shared" si="77"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="Q57" s="40">
-        <f t="shared" si="78"/>
+        <f t="shared" si="85"/>
         <v>0</v>
       </c>
       <c r="R57" s="51"/>
@@ -6356,11 +6480,11 @@
       <c r="U57" s="53"/>
       <c r="V57" s="54"/>
       <c r="W57" s="55">
-        <f t="shared" si="79"/>
+        <f t="shared" si="86"/>
         <v>0</v>
       </c>
       <c r="X57" s="55">
-        <f t="shared" si="80"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="Y57" s="56"/>
@@ -6368,7 +6492,7 @@
     <row r="58" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A58" s="78"/>
       <c r="B58" s="47">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C58" s="57"/>
       <c r="D58" s="75"/>
@@ -6381,7 +6505,7 @@
       <c r="K58" s="75"/>
       <c r="L58" s="75"/>
       <c r="M58" s="129">
-        <f t="shared" si="76"/>
+        <f t="shared" si="83"/>
         <v>0</v>
       </c>
       <c r="N58" s="39">
@@ -6393,11 +6517,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P58" s="73">
-        <f t="shared" si="77"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="Q58" s="40">
-        <f t="shared" si="78"/>
+        <f t="shared" si="85"/>
         <v>0</v>
       </c>
       <c r="R58" s="51"/>
@@ -6406,19 +6530,19 @@
       <c r="U58" s="53"/>
       <c r="V58" s="54"/>
       <c r="W58" s="55">
-        <f t="shared" si="79"/>
+        <f t="shared" si="86"/>
         <v>0</v>
       </c>
       <c r="X58" s="55">
-        <f t="shared" si="80"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="Y58" s="56"/>
     </row>
     <row r="59" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A59" s="78"/>
-      <c r="B59" s="47">
-        <v>54</v>
+      <c r="B59" s="182">
+        <v>55</v>
       </c>
       <c r="C59" s="57"/>
       <c r="D59" s="75"/>
@@ -6431,7 +6555,7 @@
       <c r="K59" s="75"/>
       <c r="L59" s="75"/>
       <c r="M59" s="129">
-        <f t="shared" si="76"/>
+        <f t="shared" si="83"/>
         <v>0</v>
       </c>
       <c r="N59" s="39">
@@ -6443,11 +6567,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P59" s="73">
-        <f t="shared" si="77"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="Q59" s="40">
-        <f t="shared" si="78"/>
+        <f t="shared" si="85"/>
         <v>0</v>
       </c>
       <c r="R59" s="51"/>
@@ -6456,19 +6580,19 @@
       <c r="U59" s="53"/>
       <c r="V59" s="54"/>
       <c r="W59" s="55">
-        <f t="shared" si="79"/>
+        <f t="shared" si="86"/>
         <v>0</v>
       </c>
       <c r="X59" s="55">
-        <f t="shared" si="80"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="Y59" s="56"/>
     </row>
     <row r="60" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A60" s="78"/>
-      <c r="B60" s="47">
-        <v>55</v>
+      <c r="B60" s="182">
+        <v>56</v>
       </c>
       <c r="C60" s="57"/>
       <c r="D60" s="75"/>
@@ -6481,7 +6605,7 @@
       <c r="K60" s="75"/>
       <c r="L60" s="75"/>
       <c r="M60" s="129">
-        <f t="shared" si="76"/>
+        <f t="shared" si="83"/>
         <v>0</v>
       </c>
       <c r="N60" s="39">
@@ -6493,11 +6617,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P60" s="73">
-        <f t="shared" si="77"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="Q60" s="40">
-        <f t="shared" si="78"/>
+        <f t="shared" si="85"/>
         <v>0</v>
       </c>
       <c r="R60" s="51"/>
@@ -6506,19 +6630,19 @@
       <c r="U60" s="53"/>
       <c r="V60" s="54"/>
       <c r="W60" s="55">
-        <f t="shared" si="79"/>
+        <f t="shared" si="86"/>
         <v>0</v>
       </c>
       <c r="X60" s="55">
-        <f t="shared" si="80"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="Y60" s="56"/>
     </row>
     <row r="61" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A61" s="78"/>
-      <c r="B61" s="47">
-        <v>56</v>
+      <c r="B61" s="182">
+        <v>57</v>
       </c>
       <c r="C61" s="57"/>
       <c r="D61" s="75"/>
@@ -6586,7 +6710,7 @@
     <row r="62" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A62" s="78"/>
       <c r="B62" s="47">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C62" s="128"/>
       <c r="D62" s="75"/>
@@ -6599,7 +6723,7 @@
       <c r="K62" s="75"/>
       <c r="L62" s="75"/>
       <c r="M62" s="129">
-        <f t="shared" ref="M62:M84" si="81">SUM(D62:L62)/40</f>
+        <f t="shared" ref="M62:M84" si="88">SUM(D62:L62)/40</f>
         <v>0</v>
       </c>
       <c r="N62" s="39">
@@ -6611,11 +6735,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P62" s="73">
-        <f t="shared" ref="P62:P79" si="82">SUM(G62:I62)/20</f>
+        <f t="shared" ref="P62:P79" si="89">SUM(G62:I62)/20</f>
         <v>0</v>
       </c>
       <c r="Q62" s="40">
-        <f t="shared" ref="Q62:Q79" si="83">SUM(J62:L62)/20</f>
+        <f t="shared" ref="Q62:Q79" si="90">SUM(J62:L62)/20</f>
         <v>0</v>
       </c>
       <c r="R62" s="51" t="e">
@@ -6631,30 +6755,30 @@
         <v>0</v>
       </c>
       <c r="U62" s="53" t="e">
-        <f t="shared" ref="U62:U79" si="84">SUM(R62:T62)</f>
+        <f t="shared" ref="U62:U79" si="91">SUM(R62:T62)</f>
         <v>#VALUE!</v>
       </c>
       <c r="V62" s="54" t="e">
-        <f t="shared" ref="V62:V79" si="85">SUM(D62:F62)*$V$3</f>
+        <f t="shared" ref="V62:V79" si="92">SUM(D62:F62)*$V$3</f>
         <v>#VALUE!</v>
       </c>
       <c r="W62" s="55">
-        <f t="shared" ref="W62:W79" si="86">SUM(G62:I62)*$W$3</f>
+        <f t="shared" ref="W62:W79" si="93">SUM(G62:I62)*$W$3</f>
         <v>0</v>
       </c>
       <c r="X62" s="55">
-        <f t="shared" ref="X62:X79" si="87">SUM(J62:L62)*$X$3</f>
+        <f t="shared" ref="X62:X79" si="94">SUM(J62:L62)*$X$3</f>
         <v>0</v>
       </c>
       <c r="Y62" s="56" t="e">
-        <f t="shared" ref="Y62:Y79" si="88">SUM(V62:X62)</f>
+        <f t="shared" ref="Y62:Y79" si="95">SUM(V62:X62)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="63" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A63" s="78"/>
       <c r="B63" s="47">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C63" s="128"/>
       <c r="D63" s="75"/>
@@ -6667,7 +6791,7 @@
       <c r="K63" s="75"/>
       <c r="L63" s="75"/>
       <c r="M63" s="129">
-        <f t="shared" si="81"/>
+        <f t="shared" si="88"/>
         <v>0</v>
       </c>
       <c r="N63" s="39">
@@ -6679,11 +6803,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P63" s="73">
-        <f t="shared" si="82"/>
+        <f t="shared" si="89"/>
         <v>0</v>
       </c>
       <c r="Q63" s="40">
-        <f t="shared" si="83"/>
+        <f t="shared" si="90"/>
         <v>0</v>
       </c>
       <c r="R63" s="51" t="e">
@@ -6699,30 +6823,30 @@
         <v>0</v>
       </c>
       <c r="U63" s="53" t="e">
-        <f t="shared" si="84"/>
+        <f t="shared" si="91"/>
         <v>#VALUE!</v>
       </c>
       <c r="V63" s="54" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>#VALUE!</v>
       </c>
       <c r="W63" s="55">
-        <f t="shared" si="86"/>
+        <f t="shared" si="93"/>
         <v>0</v>
       </c>
       <c r="X63" s="55">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>0</v>
       </c>
       <c r="Y63" s="56" t="e">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="64" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A64" s="78"/>
       <c r="B64" s="47">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C64" s="128"/>
       <c r="D64" s="75"/>
@@ -6735,7 +6859,7 @@
       <c r="K64" s="75"/>
       <c r="L64" s="75"/>
       <c r="M64" s="129">
-        <f t="shared" si="81"/>
+        <f t="shared" si="88"/>
         <v>0</v>
       </c>
       <c r="N64" s="39">
@@ -6747,11 +6871,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P64" s="73">
-        <f t="shared" si="82"/>
+        <f t="shared" si="89"/>
         <v>0</v>
       </c>
       <c r="Q64" s="40">
-        <f t="shared" si="83"/>
+        <f t="shared" si="90"/>
         <v>0</v>
       </c>
       <c r="R64" s="51" t="e">
@@ -6767,30 +6891,30 @@
         <v>0</v>
       </c>
       <c r="U64" s="53" t="e">
-        <f t="shared" si="84"/>
+        <f t="shared" si="91"/>
         <v>#VALUE!</v>
       </c>
       <c r="V64" s="54" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>#VALUE!</v>
       </c>
       <c r="W64" s="55">
-        <f t="shared" si="86"/>
+        <f t="shared" si="93"/>
         <v>0</v>
       </c>
       <c r="X64" s="55">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>0</v>
       </c>
       <c r="Y64" s="56" t="e">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="65" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A65" s="78"/>
       <c r="B65" s="47">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C65" s="128"/>
       <c r="D65" s="75"/>
@@ -6803,7 +6927,7 @@
       <c r="K65" s="75"/>
       <c r="L65" s="75"/>
       <c r="M65" s="129">
-        <f t="shared" si="81"/>
+        <f t="shared" si="88"/>
         <v>0</v>
       </c>
       <c r="N65" s="39">
@@ -6815,11 +6939,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P65" s="73">
-        <f t="shared" si="82"/>
+        <f t="shared" si="89"/>
         <v>0</v>
       </c>
       <c r="Q65" s="40">
-        <f t="shared" si="83"/>
+        <f t="shared" si="90"/>
         <v>0</v>
       </c>
       <c r="R65" s="51" t="e">
@@ -6835,30 +6959,30 @@
         <v>0</v>
       </c>
       <c r="U65" s="53" t="e">
-        <f t="shared" si="84"/>
+        <f t="shared" si="91"/>
         <v>#VALUE!</v>
       </c>
       <c r="V65" s="54" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>#VALUE!</v>
       </c>
       <c r="W65" s="55">
-        <f t="shared" si="86"/>
+        <f t="shared" si="93"/>
         <v>0</v>
       </c>
       <c r="X65" s="55">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>0</v>
       </c>
       <c r="Y65" s="56" t="e">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="66" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A66" s="78"/>
       <c r="B66" s="47">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C66" s="128"/>
       <c r="D66" s="75"/>
@@ -6871,7 +6995,7 @@
       <c r="K66" s="75"/>
       <c r="L66" s="75"/>
       <c r="M66" s="129">
-        <f t="shared" si="81"/>
+        <f t="shared" si="88"/>
         <v>0</v>
       </c>
       <c r="N66" s="39">
@@ -6883,11 +7007,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P66" s="73">
-        <f t="shared" si="82"/>
+        <f t="shared" si="89"/>
         <v>0</v>
       </c>
       <c r="Q66" s="40">
-        <f t="shared" si="83"/>
+        <f t="shared" si="90"/>
         <v>0</v>
       </c>
       <c r="R66" s="51" t="e">
@@ -6903,30 +7027,30 @@
         <v>0</v>
       </c>
       <c r="U66" s="53" t="e">
-        <f t="shared" si="84"/>
+        <f t="shared" si="91"/>
         <v>#VALUE!</v>
       </c>
       <c r="V66" s="54" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>#VALUE!</v>
       </c>
       <c r="W66" s="55">
-        <f t="shared" si="86"/>
+        <f t="shared" si="93"/>
         <v>0</v>
       </c>
       <c r="X66" s="55">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>0</v>
       </c>
       <c r="Y66" s="56" t="e">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="67" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A67" s="78"/>
       <c r="B67" s="47">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C67" s="128"/>
       <c r="D67" s="75"/>
@@ -6939,7 +7063,7 @@
       <c r="K67" s="75"/>
       <c r="L67" s="75"/>
       <c r="M67" s="129">
-        <f t="shared" si="81"/>
+        <f t="shared" si="88"/>
         <v>0</v>
       </c>
       <c r="N67" s="39">
@@ -6951,11 +7075,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P67" s="73">
-        <f t="shared" si="82"/>
+        <f t="shared" si="89"/>
         <v>0</v>
       </c>
       <c r="Q67" s="40">
-        <f t="shared" si="83"/>
+        <f t="shared" si="90"/>
         <v>0</v>
       </c>
       <c r="R67" s="51" t="e">
@@ -6971,30 +7095,30 @@
         <v>0</v>
       </c>
       <c r="U67" s="53" t="e">
-        <f t="shared" si="84"/>
+        <f t="shared" si="91"/>
         <v>#VALUE!</v>
       </c>
       <c r="V67" s="54" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>#VALUE!</v>
       </c>
       <c r="W67" s="55">
-        <f t="shared" si="86"/>
+        <f t="shared" si="93"/>
         <v>0</v>
       </c>
       <c r="X67" s="55">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>0</v>
       </c>
       <c r="Y67" s="56" t="e">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="68" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A68" s="78"/>
       <c r="B68" s="47">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C68" s="128"/>
       <c r="D68" s="75"/>
@@ -7007,7 +7131,7 @@
       <c r="K68" s="75"/>
       <c r="L68" s="75"/>
       <c r="M68" s="129">
-        <f t="shared" si="81"/>
+        <f t="shared" si="88"/>
         <v>0</v>
       </c>
       <c r="N68" s="39">
@@ -7019,11 +7143,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P68" s="73">
-        <f t="shared" si="82"/>
+        <f t="shared" si="89"/>
         <v>0</v>
       </c>
       <c r="Q68" s="40">
-        <f t="shared" si="83"/>
+        <f t="shared" si="90"/>
         <v>0</v>
       </c>
       <c r="R68" s="51" t="e">
@@ -7039,30 +7163,30 @@
         <v>0</v>
       </c>
       <c r="U68" s="53" t="e">
-        <f t="shared" si="84"/>
+        <f t="shared" si="91"/>
         <v>#VALUE!</v>
       </c>
       <c r="V68" s="54" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>#VALUE!</v>
       </c>
       <c r="W68" s="55">
-        <f t="shared" si="86"/>
+        <f t="shared" si="93"/>
         <v>0</v>
       </c>
       <c r="X68" s="55">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>0</v>
       </c>
       <c r="Y68" s="56" t="e">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="69" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A69" s="78"/>
-      <c r="B69" s="47">
-        <v>64</v>
+      <c r="B69" s="182">
+        <v>65</v>
       </c>
       <c r="C69" s="128"/>
       <c r="D69" s="75"/>
@@ -7075,7 +7199,7 @@
       <c r="K69" s="75"/>
       <c r="L69" s="75"/>
       <c r="M69" s="129">
-        <f t="shared" si="81"/>
+        <f t="shared" si="88"/>
         <v>0</v>
       </c>
       <c r="N69" s="39">
@@ -7087,11 +7211,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P69" s="73">
-        <f t="shared" si="82"/>
+        <f t="shared" si="89"/>
         <v>0</v>
       </c>
       <c r="Q69" s="40">
-        <f t="shared" si="83"/>
+        <f t="shared" si="90"/>
         <v>0</v>
       </c>
       <c r="R69" s="51" t="e">
@@ -7107,30 +7231,30 @@
         <v>0</v>
       </c>
       <c r="U69" s="53" t="e">
-        <f t="shared" si="84"/>
+        <f t="shared" si="91"/>
         <v>#VALUE!</v>
       </c>
       <c r="V69" s="54" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>#VALUE!</v>
       </c>
       <c r="W69" s="55">
-        <f t="shared" si="86"/>
+        <f t="shared" si="93"/>
         <v>0</v>
       </c>
       <c r="X69" s="55">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>0</v>
       </c>
       <c r="Y69" s="56" t="e">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="70" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A70" s="78"/>
-      <c r="B70" s="47">
-        <v>65</v>
+      <c r="B70" s="182">
+        <v>66</v>
       </c>
       <c r="C70" s="128"/>
       <c r="D70" s="75"/>
@@ -7143,7 +7267,7 @@
       <c r="K70" s="75"/>
       <c r="L70" s="75"/>
       <c r="M70" s="129">
-        <f t="shared" si="81"/>
+        <f t="shared" si="88"/>
         <v>0</v>
       </c>
       <c r="N70" s="39">
@@ -7155,11 +7279,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P70" s="73">
-        <f t="shared" si="82"/>
+        <f t="shared" si="89"/>
         <v>0</v>
       </c>
       <c r="Q70" s="40">
-        <f t="shared" si="83"/>
+        <f t="shared" si="90"/>
         <v>0</v>
       </c>
       <c r="R70" s="51" t="e">
@@ -7175,30 +7299,30 @@
         <v>0</v>
       </c>
       <c r="U70" s="53" t="e">
-        <f t="shared" si="84"/>
+        <f t="shared" si="91"/>
         <v>#VALUE!</v>
       </c>
       <c r="V70" s="54" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>#VALUE!</v>
       </c>
       <c r="W70" s="55">
-        <f t="shared" si="86"/>
+        <f t="shared" si="93"/>
         <v>0</v>
       </c>
       <c r="X70" s="55">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>0</v>
       </c>
       <c r="Y70" s="56" t="e">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="71" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A71" s="78"/>
-      <c r="B71" s="47">
-        <v>66</v>
+      <c r="B71" s="182">
+        <v>67</v>
       </c>
       <c r="C71" s="128"/>
       <c r="D71" s="75"/>
@@ -7211,7 +7335,7 @@
       <c r="K71" s="75"/>
       <c r="L71" s="75"/>
       <c r="M71" s="129">
-        <f t="shared" si="81"/>
+        <f t="shared" si="88"/>
         <v>0</v>
       </c>
       <c r="N71" s="39">
@@ -7223,11 +7347,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P71" s="73">
-        <f t="shared" si="82"/>
+        <f t="shared" si="89"/>
         <v>0</v>
       </c>
       <c r="Q71" s="40">
-        <f t="shared" si="83"/>
+        <f t="shared" si="90"/>
         <v>0</v>
       </c>
       <c r="R71" s="51" t="e">
@@ -7243,30 +7367,30 @@
         <v>0</v>
       </c>
       <c r="U71" s="53" t="e">
-        <f t="shared" si="84"/>
+        <f t="shared" si="91"/>
         <v>#VALUE!</v>
       </c>
       <c r="V71" s="54" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>#VALUE!</v>
       </c>
       <c r="W71" s="55">
-        <f t="shared" si="86"/>
+        <f t="shared" si="93"/>
         <v>0</v>
       </c>
       <c r="X71" s="55">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>0</v>
       </c>
       <c r="Y71" s="56" t="e">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="72" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A72" s="78"/>
       <c r="B72" s="47">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C72" s="128"/>
       <c r="D72" s="75"/>
@@ -7279,7 +7403,7 @@
       <c r="K72" s="75"/>
       <c r="L72" s="75"/>
       <c r="M72" s="129">
-        <f t="shared" si="81"/>
+        <f t="shared" si="88"/>
         <v>0</v>
       </c>
       <c r="N72" s="39">
@@ -7291,11 +7415,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P72" s="73">
-        <f t="shared" si="82"/>
+        <f t="shared" si="89"/>
         <v>0</v>
       </c>
       <c r="Q72" s="40">
-        <f t="shared" si="83"/>
+        <f t="shared" si="90"/>
         <v>0</v>
       </c>
       <c r="R72" s="51" t="e">
@@ -7311,30 +7435,30 @@
         <v>0</v>
       </c>
       <c r="U72" s="53" t="e">
-        <f t="shared" si="84"/>
+        <f t="shared" si="91"/>
         <v>#VALUE!</v>
       </c>
       <c r="V72" s="54" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>#VALUE!</v>
       </c>
       <c r="W72" s="55">
-        <f t="shared" si="86"/>
+        <f t="shared" si="93"/>
         <v>0</v>
       </c>
       <c r="X72" s="55">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>0</v>
       </c>
       <c r="Y72" s="56" t="e">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="73" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A73" s="78"/>
       <c r="B73" s="47">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C73" s="128"/>
       <c r="D73" s="75"/>
@@ -7347,7 +7471,7 @@
       <c r="K73" s="75"/>
       <c r="L73" s="75"/>
       <c r="M73" s="129">
-        <f t="shared" si="81"/>
+        <f t="shared" si="88"/>
         <v>0</v>
       </c>
       <c r="N73" s="39">
@@ -7359,11 +7483,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P73" s="73">
-        <f t="shared" si="82"/>
+        <f t="shared" si="89"/>
         <v>0</v>
       </c>
       <c r="Q73" s="40">
-        <f t="shared" si="83"/>
+        <f t="shared" si="90"/>
         <v>0</v>
       </c>
       <c r="R73" s="51" t="e">
@@ -7379,30 +7503,30 @@
         <v>0</v>
       </c>
       <c r="U73" s="53" t="e">
-        <f t="shared" si="84"/>
+        <f t="shared" si="91"/>
         <v>#VALUE!</v>
       </c>
       <c r="V73" s="54" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>#VALUE!</v>
       </c>
       <c r="W73" s="55">
-        <f t="shared" si="86"/>
+        <f t="shared" si="93"/>
         <v>0</v>
       </c>
       <c r="X73" s="55">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>0</v>
       </c>
       <c r="Y73" s="56" t="e">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="74" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A74" s="78"/>
       <c r="B74" s="47">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C74" s="128"/>
       <c r="D74" s="75"/>
@@ -7415,7 +7539,7 @@
       <c r="K74" s="75"/>
       <c r="L74" s="75"/>
       <c r="M74" s="129">
-        <f t="shared" si="81"/>
+        <f t="shared" si="88"/>
         <v>0</v>
       </c>
       <c r="N74" s="39">
@@ -7427,11 +7551,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P74" s="73">
-        <f t="shared" si="82"/>
+        <f t="shared" si="89"/>
         <v>0</v>
       </c>
       <c r="Q74" s="40">
-        <f t="shared" si="83"/>
+        <f t="shared" si="90"/>
         <v>0</v>
       </c>
       <c r="R74" s="51" t="e">
@@ -7447,30 +7571,30 @@
         <v>0</v>
       </c>
       <c r="U74" s="53" t="e">
-        <f t="shared" si="84"/>
+        <f t="shared" si="91"/>
         <v>#VALUE!</v>
       </c>
       <c r="V74" s="54" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>#VALUE!</v>
       </c>
       <c r="W74" s="55">
-        <f t="shared" si="86"/>
+        <f t="shared" si="93"/>
         <v>0</v>
       </c>
       <c r="X74" s="55">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>0</v>
       </c>
       <c r="Y74" s="56" t="e">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="75" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A75" s="78"/>
       <c r="B75" s="47">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C75" s="139"/>
       <c r="D75" s="75"/>
@@ -7483,7 +7607,7 @@
       <c r="K75" s="75"/>
       <c r="L75" s="75"/>
       <c r="M75" s="129">
-        <f t="shared" si="81"/>
+        <f t="shared" si="88"/>
         <v>0</v>
       </c>
       <c r="N75" s="39">
@@ -7495,11 +7619,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P75" s="73">
-        <f t="shared" si="82"/>
+        <f t="shared" si="89"/>
         <v>0</v>
       </c>
       <c r="Q75" s="40">
-        <f t="shared" si="83"/>
+        <f t="shared" si="90"/>
         <v>0</v>
       </c>
       <c r="R75" s="51" t="e">
@@ -7515,30 +7639,30 @@
         <v>0</v>
       </c>
       <c r="U75" s="53" t="e">
-        <f t="shared" si="84"/>
+        <f t="shared" si="91"/>
         <v>#VALUE!</v>
       </c>
       <c r="V75" s="54" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>#VALUE!</v>
       </c>
       <c r="W75" s="55">
-        <f t="shared" si="86"/>
+        <f t="shared" si="93"/>
         <v>0</v>
       </c>
       <c r="X75" s="55">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>0</v>
       </c>
       <c r="Y75" s="56" t="e">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="76" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A76" s="78"/>
       <c r="B76" s="47">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C76" s="139"/>
       <c r="D76" s="75"/>
@@ -7551,7 +7675,7 @@
       <c r="K76" s="75"/>
       <c r="L76" s="75"/>
       <c r="M76" s="129">
-        <f t="shared" si="81"/>
+        <f t="shared" si="88"/>
         <v>0</v>
       </c>
       <c r="N76" s="39">
@@ -7563,11 +7687,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P76" s="73">
-        <f t="shared" si="82"/>
+        <f t="shared" si="89"/>
         <v>0</v>
       </c>
       <c r="Q76" s="40">
-        <f t="shared" si="83"/>
+        <f t="shared" si="90"/>
         <v>0</v>
       </c>
       <c r="R76" s="51" t="e">
@@ -7583,30 +7707,30 @@
         <v>0</v>
       </c>
       <c r="U76" s="53" t="e">
-        <f t="shared" si="84"/>
+        <f t="shared" si="91"/>
         <v>#VALUE!</v>
       </c>
       <c r="V76" s="54" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>#VALUE!</v>
       </c>
       <c r="W76" s="55">
-        <f t="shared" si="86"/>
+        <f t="shared" si="93"/>
         <v>0</v>
       </c>
       <c r="X76" s="55">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>0</v>
       </c>
       <c r="Y76" s="56" t="e">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="77" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A77" s="78"/>
       <c r="B77" s="47">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C77" s="139"/>
       <c r="D77" s="75"/>
@@ -7619,7 +7743,7 @@
       <c r="K77" s="75"/>
       <c r="L77" s="75"/>
       <c r="M77" s="129">
-        <f t="shared" si="81"/>
+        <f t="shared" si="88"/>
         <v>0</v>
       </c>
       <c r="N77" s="39">
@@ -7631,11 +7755,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P77" s="73">
-        <f t="shared" si="82"/>
+        <f t="shared" si="89"/>
         <v>0</v>
       </c>
       <c r="Q77" s="40">
-        <f t="shared" si="83"/>
+        <f t="shared" si="90"/>
         <v>0</v>
       </c>
       <c r="R77" s="51" t="e">
@@ -7651,30 +7775,30 @@
         <v>0</v>
       </c>
       <c r="U77" s="53" t="e">
-        <f t="shared" si="84"/>
+        <f t="shared" si="91"/>
         <v>#VALUE!</v>
       </c>
       <c r="V77" s="54" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>#VALUE!</v>
       </c>
       <c r="W77" s="55">
-        <f t="shared" si="86"/>
+        <f t="shared" si="93"/>
         <v>0</v>
       </c>
       <c r="X77" s="55">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>0</v>
       </c>
       <c r="Y77" s="56" t="e">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="78" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A78" s="78"/>
       <c r="B78" s="47">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C78" s="139"/>
       <c r="D78" s="75"/>
@@ -7687,7 +7811,7 @@
       <c r="K78" s="50"/>
       <c r="L78" s="50"/>
       <c r="M78" s="129">
-        <f t="shared" si="81"/>
+        <f t="shared" si="88"/>
         <v>0</v>
       </c>
       <c r="N78" s="39">
@@ -7699,11 +7823,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P78" s="73">
-        <f t="shared" si="82"/>
+        <f t="shared" si="89"/>
         <v>0</v>
       </c>
       <c r="Q78" s="40">
-        <f t="shared" si="83"/>
+        <f t="shared" si="90"/>
         <v>0</v>
       </c>
       <c r="R78" s="51" t="e">
@@ -7719,30 +7843,30 @@
         <v>0</v>
       </c>
       <c r="U78" s="53" t="e">
-        <f t="shared" si="84"/>
+        <f t="shared" si="91"/>
         <v>#VALUE!</v>
       </c>
       <c r="V78" s="54" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>#VALUE!</v>
       </c>
       <c r="W78" s="55">
-        <f t="shared" si="86"/>
+        <f t="shared" si="93"/>
         <v>0</v>
       </c>
       <c r="X78" s="55">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>0</v>
       </c>
       <c r="Y78" s="56" t="e">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="79" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A79" s="78"/>
-      <c r="B79" s="47">
-        <v>74</v>
+      <c r="B79" s="182">
+        <v>75</v>
       </c>
       <c r="C79" s="139"/>
       <c r="D79" s="75"/>
@@ -7755,7 +7879,7 @@
       <c r="K79" s="50"/>
       <c r="L79" s="50"/>
       <c r="M79" s="129">
-        <f t="shared" si="81"/>
+        <f t="shared" si="88"/>
         <v>0</v>
       </c>
       <c r="N79" s="39">
@@ -7767,11 +7891,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P79" s="73">
-        <f t="shared" si="82"/>
+        <f t="shared" si="89"/>
         <v>0</v>
       </c>
       <c r="Q79" s="40">
-        <f t="shared" si="83"/>
+        <f t="shared" si="90"/>
         <v>0</v>
       </c>
       <c r="R79" s="51" t="e">
@@ -7787,30 +7911,30 @@
         <v>0</v>
       </c>
       <c r="U79" s="53" t="e">
-        <f t="shared" si="84"/>
+        <f t="shared" si="91"/>
         <v>#VALUE!</v>
       </c>
       <c r="V79" s="54" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>#VALUE!</v>
       </c>
       <c r="W79" s="55">
-        <f t="shared" si="86"/>
+        <f t="shared" si="93"/>
         <v>0</v>
       </c>
       <c r="X79" s="55">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>0</v>
       </c>
       <c r="Y79" s="56" t="e">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="80" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A80" s="78"/>
-      <c r="B80" s="47">
-        <v>75</v>
+      <c r="B80" s="182">
+        <v>76</v>
       </c>
       <c r="C80" s="128"/>
       <c r="D80" s="50"/>
@@ -7823,7 +7947,7 @@
       <c r="K80" s="50"/>
       <c r="L80" s="50"/>
       <c r="M80" s="129">
-        <f t="shared" si="81"/>
+        <f t="shared" si="88"/>
         <v>0</v>
       </c>
       <c r="N80" s="39">
@@ -7835,11 +7959,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P80" s="73">
-        <f t="shared" ref="P80:P84" si="89">SUM(G80:I80)/20</f>
+        <f t="shared" ref="P80:P84" si="96">SUM(G80:I80)/20</f>
         <v>0</v>
       </c>
       <c r="Q80" s="40">
-        <f t="shared" ref="Q80:Q84" si="90">SUM(J80:L80)/20</f>
+        <f t="shared" ref="Q80:Q84" si="97">SUM(J80:L80)/20</f>
         <v>0</v>
       </c>
       <c r="R80" s="51" t="e">
@@ -7855,30 +7979,30 @@
         <v>0</v>
       </c>
       <c r="U80" s="53" t="e">
-        <f t="shared" ref="U80:U84" si="91">SUM(R80:T80)</f>
+        <f t="shared" ref="U80:U84" si="98">SUM(R80:T80)</f>
         <v>#VALUE!</v>
       </c>
       <c r="V80" s="54" t="e">
-        <f t="shared" ref="V80:V84" si="92">SUM(D80:F80)*$V$3</f>
+        <f t="shared" ref="V80:V84" si="99">SUM(D80:F80)*$V$3</f>
         <v>#VALUE!</v>
       </c>
       <c r="W80" s="55">
-        <f t="shared" ref="W80:W84" si="93">SUM(G80:I80)*$W$3</f>
+        <f t="shared" ref="W80:W84" si="100">SUM(G80:I80)*$W$3</f>
         <v>0</v>
       </c>
       <c r="X80" s="55">
-        <f t="shared" ref="X80:X84" si="94">SUM(J80:L80)*$X$3</f>
+        <f t="shared" ref="X80:X84" si="101">SUM(J80:L80)*$X$3</f>
         <v>0</v>
       </c>
       <c r="Y80" s="56" t="e">
-        <f t="shared" ref="Y80:Y84" si="95">SUM(V80:X80)</f>
+        <f t="shared" ref="Y80:Y84" si="102">SUM(V80:X80)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="81" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A81" s="78"/>
-      <c r="B81" s="47">
-        <v>76</v>
+      <c r="B81" s="182">
+        <v>77</v>
       </c>
       <c r="C81" s="128"/>
       <c r="D81" s="50"/>
@@ -7891,7 +8015,7 @@
       <c r="K81" s="50"/>
       <c r="L81" s="50"/>
       <c r="M81" s="129">
-        <f t="shared" si="81"/>
+        <f t="shared" si="88"/>
         <v>0</v>
       </c>
       <c r="N81" s="39">
@@ -7903,11 +8027,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P81" s="73">
-        <f t="shared" si="89"/>
+        <f t="shared" si="96"/>
         <v>0</v>
       </c>
       <c r="Q81" s="40">
-        <f t="shared" si="90"/>
+        <f t="shared" si="97"/>
         <v>0</v>
       </c>
       <c r="R81" s="51" t="e">
@@ -7923,30 +8047,30 @@
         <v>0</v>
       </c>
       <c r="U81" s="53" t="e">
-        <f t="shared" si="91"/>
+        <f t="shared" si="98"/>
         <v>#VALUE!</v>
       </c>
       <c r="V81" s="54" t="e">
-        <f t="shared" si="92"/>
+        <f t="shared" si="99"/>
         <v>#VALUE!</v>
       </c>
       <c r="W81" s="55">
-        <f t="shared" si="93"/>
+        <f t="shared" si="100"/>
         <v>0</v>
       </c>
       <c r="X81" s="55">
-        <f t="shared" si="94"/>
+        <f t="shared" si="101"/>
         <v>0</v>
       </c>
       <c r="Y81" s="56" t="e">
-        <f t="shared" si="95"/>
+        <f t="shared" si="102"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="82" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A82" s="78"/>
       <c r="B82" s="47">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C82" s="128"/>
       <c r="D82" s="50"/>
@@ -7959,7 +8083,7 @@
       <c r="K82" s="50"/>
       <c r="L82" s="50"/>
       <c r="M82" s="129">
-        <f t="shared" si="81"/>
+        <f t="shared" si="88"/>
         <v>0</v>
       </c>
       <c r="N82" s="39">
@@ -7971,11 +8095,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P82" s="73">
-        <f t="shared" si="89"/>
+        <f t="shared" si="96"/>
         <v>0</v>
       </c>
       <c r="Q82" s="40">
-        <f t="shared" si="90"/>
+        <f t="shared" si="97"/>
         <v>0</v>
       </c>
       <c r="R82" s="51" t="e">
@@ -7991,30 +8115,30 @@
         <v>0</v>
       </c>
       <c r="U82" s="53" t="e">
-        <f t="shared" si="91"/>
+        <f t="shared" si="98"/>
         <v>#VALUE!</v>
       </c>
       <c r="V82" s="54" t="e">
-        <f t="shared" si="92"/>
+        <f t="shared" si="99"/>
         <v>#VALUE!</v>
       </c>
       <c r="W82" s="55">
-        <f t="shared" si="93"/>
+        <f t="shared" si="100"/>
         <v>0</v>
       </c>
       <c r="X82" s="55">
-        <f t="shared" si="94"/>
+        <f t="shared" si="101"/>
         <v>0</v>
       </c>
       <c r="Y82" s="56" t="e">
-        <f t="shared" si="95"/>
+        <f t="shared" si="102"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="83" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A83" s="78"/>
       <c r="B83" s="47">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C83" s="128"/>
       <c r="D83" s="50"/>
@@ -8027,7 +8151,7 @@
       <c r="K83" s="50"/>
       <c r="L83" s="50"/>
       <c r="M83" s="129">
-        <f t="shared" si="81"/>
+        <f t="shared" si="88"/>
         <v>0</v>
       </c>
       <c r="N83" s="39">
@@ -8039,11 +8163,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P83" s="73">
-        <f t="shared" si="89"/>
+        <f t="shared" si="96"/>
         <v>0</v>
       </c>
       <c r="Q83" s="40">
-        <f t="shared" si="90"/>
+        <f t="shared" si="97"/>
         <v>0</v>
       </c>
       <c r="R83" s="51" t="e">
@@ -8059,30 +8183,30 @@
         <v>0</v>
       </c>
       <c r="U83" s="53" t="e">
-        <f t="shared" si="91"/>
+        <f t="shared" si="98"/>
         <v>#VALUE!</v>
       </c>
       <c r="V83" s="54" t="e">
-        <f t="shared" si="92"/>
+        <f t="shared" si="99"/>
         <v>#VALUE!</v>
       </c>
       <c r="W83" s="55">
-        <f t="shared" si="93"/>
+        <f t="shared" si="100"/>
         <v>0</v>
       </c>
       <c r="X83" s="55">
-        <f t="shared" si="94"/>
+        <f t="shared" si="101"/>
         <v>0</v>
       </c>
       <c r="Y83" s="56" t="e">
-        <f t="shared" si="95"/>
+        <f t="shared" si="102"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="84" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A84" s="78"/>
       <c r="B84" s="47">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C84" s="128"/>
       <c r="D84" s="50"/>
@@ -8095,7 +8219,7 @@
       <c r="K84" s="50"/>
       <c r="L84" s="50"/>
       <c r="M84" s="129">
-        <f t="shared" si="81"/>
+        <f t="shared" si="88"/>
         <v>0</v>
       </c>
       <c r="N84" s="39">
@@ -8107,11 +8231,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P84" s="73">
-        <f t="shared" si="89"/>
+        <f t="shared" si="96"/>
         <v>0</v>
       </c>
       <c r="Q84" s="40">
-        <f t="shared" si="90"/>
+        <f t="shared" si="97"/>
         <v>0</v>
       </c>
       <c r="R84" s="51" t="e">
@@ -8127,30 +8251,30 @@
         <v>0</v>
       </c>
       <c r="U84" s="53" t="e">
-        <f t="shared" si="91"/>
+        <f t="shared" si="98"/>
         <v>#VALUE!</v>
       </c>
       <c r="V84" s="54" t="e">
-        <f t="shared" si="92"/>
+        <f t="shared" si="99"/>
         <v>#VALUE!</v>
       </c>
       <c r="W84" s="55">
-        <f t="shared" si="93"/>
+        <f t="shared" si="100"/>
         <v>0</v>
       </c>
       <c r="X84" s="55">
-        <f t="shared" si="94"/>
+        <f t="shared" si="101"/>
         <v>0</v>
       </c>
       <c r="Y84" s="56" t="e">
-        <f t="shared" si="95"/>
+        <f t="shared" si="102"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="85" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A85" s="78"/>
       <c r="B85" s="47">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C85" s="128"/>
       <c r="D85" s="50"/>
@@ -8163,7 +8287,7 @@
       <c r="K85" s="50"/>
       <c r="L85" s="50"/>
       <c r="M85" s="129">
-        <f t="shared" ref="M85:M132" si="96">SUM(D85:L85)/40</f>
+        <f t="shared" ref="M85:M132" si="103">SUM(D85:L85)/40</f>
         <v>0</v>
       </c>
       <c r="N85" s="39">
@@ -8175,11 +8299,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P85" s="73">
-        <f t="shared" ref="P85:P132" si="97">SUM(G85:I85)/20</f>
+        <f t="shared" ref="P85:P132" si="104">SUM(G85:I85)/20</f>
         <v>0</v>
       </c>
       <c r="Q85" s="40">
-        <f t="shared" ref="Q85:Q132" si="98">SUM(J85:L85)/20</f>
+        <f t="shared" ref="Q85:Q132" si="105">SUM(J85:L85)/20</f>
         <v>0</v>
       </c>
       <c r="R85" s="51" t="e">
@@ -8195,30 +8319,30 @@
         <v>0</v>
       </c>
       <c r="U85" s="53" t="e">
-        <f t="shared" ref="U85:U132" si="99">SUM(R85:T85)</f>
+        <f t="shared" ref="U85:U132" si="106">SUM(R85:T85)</f>
         <v>#VALUE!</v>
       </c>
       <c r="V85" s="54" t="e">
-        <f t="shared" ref="V85:V132" si="100">SUM(D85:F85)*$V$3</f>
+        <f t="shared" ref="V85:V132" si="107">SUM(D85:F85)*$V$3</f>
         <v>#VALUE!</v>
       </c>
       <c r="W85" s="55">
-        <f t="shared" ref="W85:W132" si="101">SUM(G85:I85)*$W$3</f>
+        <f t="shared" ref="W85:W132" si="108">SUM(G85:I85)*$W$3</f>
         <v>0</v>
       </c>
       <c r="X85" s="55">
-        <f t="shared" ref="X85:X132" si="102">SUM(J85:L85)*$X$3</f>
+        <f t="shared" ref="X85:X132" si="109">SUM(J85:L85)*$X$3</f>
         <v>0</v>
       </c>
       <c r="Y85" s="56" t="e">
-        <f t="shared" ref="Y85:Y132" si="103">SUM(V85:X85)</f>
+        <f t="shared" ref="Y85:Y132" si="110">SUM(V85:X85)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="86" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A86" s="78"/>
       <c r="B86" s="47">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C86" s="128"/>
       <c r="D86" s="50"/>
@@ -8231,7 +8355,7 @@
       <c r="K86" s="50"/>
       <c r="L86" s="50"/>
       <c r="M86" s="129">
-        <f t="shared" si="96"/>
+        <f t="shared" si="103"/>
         <v>0</v>
       </c>
       <c r="N86" s="39">
@@ -8243,11 +8367,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P86" s="73">
-        <f t="shared" si="97"/>
+        <f t="shared" si="104"/>
         <v>0</v>
       </c>
       <c r="Q86" s="40">
-        <f t="shared" si="98"/>
+        <f t="shared" si="105"/>
         <v>0</v>
       </c>
       <c r="R86" s="51" t="e">
@@ -8263,30 +8387,30 @@
         <v>0</v>
       </c>
       <c r="U86" s="53" t="e">
-        <f t="shared" si="99"/>
+        <f t="shared" si="106"/>
         <v>#VALUE!</v>
       </c>
       <c r="V86" s="54" t="e">
-        <f t="shared" si="100"/>
+        <f t="shared" si="107"/>
         <v>#VALUE!</v>
       </c>
       <c r="W86" s="55">
-        <f t="shared" si="101"/>
+        <f t="shared" si="108"/>
         <v>0</v>
       </c>
       <c r="X86" s="55">
-        <f t="shared" si="102"/>
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
       <c r="Y86" s="56" t="e">
-        <f t="shared" si="103"/>
+        <f t="shared" si="110"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="87" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A87" s="78"/>
       <c r="B87" s="47">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C87" s="128"/>
       <c r="D87" s="50"/>
@@ -8299,7 +8423,7 @@
       <c r="K87" s="50"/>
       <c r="L87" s="50"/>
       <c r="M87" s="129">
-        <f t="shared" si="96"/>
+        <f t="shared" si="103"/>
         <v>0</v>
       </c>
       <c r="N87" s="39">
@@ -8311,11 +8435,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P87" s="73">
-        <f t="shared" si="97"/>
+        <f t="shared" si="104"/>
         <v>0</v>
       </c>
       <c r="Q87" s="40">
-        <f t="shared" si="98"/>
+        <f t="shared" si="105"/>
         <v>0</v>
       </c>
       <c r="R87" s="51" t="e">
@@ -8331,30 +8455,30 @@
         <v>0</v>
       </c>
       <c r="U87" s="53" t="e">
-        <f t="shared" si="99"/>
+        <f t="shared" si="106"/>
         <v>#VALUE!</v>
       </c>
       <c r="V87" s="54" t="e">
-        <f t="shared" si="100"/>
+        <f t="shared" si="107"/>
         <v>#VALUE!</v>
       </c>
       <c r="W87" s="55">
-        <f t="shared" si="101"/>
+        <f t="shared" si="108"/>
         <v>0</v>
       </c>
       <c r="X87" s="55">
-        <f t="shared" si="102"/>
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
       <c r="Y87" s="56" t="e">
-        <f t="shared" si="103"/>
+        <f t="shared" si="110"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="88" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A88" s="78"/>
       <c r="B88" s="47">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C88" s="128"/>
       <c r="D88" s="50"/>
@@ -8367,7 +8491,7 @@
       <c r="K88" s="50"/>
       <c r="L88" s="50"/>
       <c r="M88" s="129">
-        <f t="shared" si="96"/>
+        <f t="shared" si="103"/>
         <v>0</v>
       </c>
       <c r="N88" s="39">
@@ -8379,11 +8503,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P88" s="73">
-        <f t="shared" si="97"/>
+        <f t="shared" si="104"/>
         <v>0</v>
       </c>
       <c r="Q88" s="40">
-        <f t="shared" si="98"/>
+        <f t="shared" si="105"/>
         <v>0</v>
       </c>
       <c r="R88" s="51" t="e">
@@ -8399,30 +8523,30 @@
         <v>0</v>
       </c>
       <c r="U88" s="53" t="e">
-        <f t="shared" si="99"/>
+        <f t="shared" si="106"/>
         <v>#VALUE!</v>
       </c>
       <c r="V88" s="54" t="e">
-        <f t="shared" si="100"/>
+        <f t="shared" si="107"/>
         <v>#VALUE!</v>
       </c>
       <c r="W88" s="55">
-        <f t="shared" si="101"/>
+        <f t="shared" si="108"/>
         <v>0</v>
       </c>
       <c r="X88" s="55">
-        <f t="shared" si="102"/>
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
       <c r="Y88" s="56" t="e">
-        <f t="shared" si="103"/>
+        <f t="shared" si="110"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="89" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A89" s="78"/>
-      <c r="B89" s="47">
-        <v>84</v>
+      <c r="B89" s="182">
+        <v>85</v>
       </c>
       <c r="C89" s="128"/>
       <c r="D89" s="50"/>
@@ -8435,7 +8559,7 @@
       <c r="K89" s="50"/>
       <c r="L89" s="50"/>
       <c r="M89" s="129">
-        <f t="shared" si="96"/>
+        <f t="shared" si="103"/>
         <v>0</v>
       </c>
       <c r="N89" s="39">
@@ -8447,11 +8571,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P89" s="73">
-        <f t="shared" si="97"/>
+        <f t="shared" si="104"/>
         <v>0</v>
       </c>
       <c r="Q89" s="40">
-        <f t="shared" si="98"/>
+        <f t="shared" si="105"/>
         <v>0</v>
       </c>
       <c r="R89" s="51" t="e">
@@ -8467,30 +8591,30 @@
         <v>0</v>
       </c>
       <c r="U89" s="53" t="e">
-        <f t="shared" si="99"/>
+        <f t="shared" si="106"/>
         <v>#VALUE!</v>
       </c>
       <c r="V89" s="54" t="e">
-        <f t="shared" si="100"/>
+        <f t="shared" si="107"/>
         <v>#VALUE!</v>
       </c>
       <c r="W89" s="55">
-        <f t="shared" si="101"/>
+        <f t="shared" si="108"/>
         <v>0</v>
       </c>
       <c r="X89" s="55">
-        <f t="shared" si="102"/>
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
       <c r="Y89" s="56" t="e">
-        <f t="shared" si="103"/>
+        <f t="shared" si="110"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="90" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A90" s="78"/>
-      <c r="B90" s="47">
-        <v>85</v>
+      <c r="B90" s="182">
+        <v>86</v>
       </c>
       <c r="C90" s="128"/>
       <c r="D90" s="50"/>
@@ -8503,7 +8627,7 @@
       <c r="K90" s="50"/>
       <c r="L90" s="50"/>
       <c r="M90" s="129">
-        <f t="shared" si="96"/>
+        <f t="shared" si="103"/>
         <v>0</v>
       </c>
       <c r="N90" s="39">
@@ -8515,11 +8639,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P90" s="73">
-        <f t="shared" si="97"/>
+        <f t="shared" si="104"/>
         <v>0</v>
       </c>
       <c r="Q90" s="40">
-        <f t="shared" si="98"/>
+        <f t="shared" si="105"/>
         <v>0</v>
       </c>
       <c r="R90" s="51" t="e">
@@ -8535,30 +8659,30 @@
         <v>0</v>
       </c>
       <c r="U90" s="53" t="e">
-        <f t="shared" si="99"/>
+        <f t="shared" si="106"/>
         <v>#VALUE!</v>
       </c>
       <c r="V90" s="54" t="e">
-        <f t="shared" si="100"/>
+        <f t="shared" si="107"/>
         <v>#VALUE!</v>
       </c>
       <c r="W90" s="55">
-        <f t="shared" si="101"/>
+        <f t="shared" si="108"/>
         <v>0</v>
       </c>
       <c r="X90" s="55">
-        <f t="shared" si="102"/>
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
       <c r="Y90" s="56" t="e">
-        <f t="shared" si="103"/>
+        <f t="shared" si="110"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="91" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A91" s="78"/>
-      <c r="B91" s="47">
-        <v>86</v>
+      <c r="B91" s="182">
+        <v>87</v>
       </c>
       <c r="C91" s="128"/>
       <c r="D91" s="50"/>
@@ -8571,7 +8695,7 @@
       <c r="K91" s="50"/>
       <c r="L91" s="50"/>
       <c r="M91" s="129">
-        <f t="shared" si="96"/>
+        <f t="shared" si="103"/>
         <v>0</v>
       </c>
       <c r="N91" s="39">
@@ -8583,11 +8707,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P91" s="73">
-        <f t="shared" si="97"/>
+        <f t="shared" si="104"/>
         <v>0</v>
       </c>
       <c r="Q91" s="40">
-        <f t="shared" si="98"/>
+        <f t="shared" si="105"/>
         <v>0</v>
       </c>
       <c r="R91" s="51" t="e">
@@ -8603,30 +8727,30 @@
         <v>0</v>
       </c>
       <c r="U91" s="53" t="e">
-        <f t="shared" si="99"/>
+        <f t="shared" si="106"/>
         <v>#VALUE!</v>
       </c>
       <c r="V91" s="54" t="e">
-        <f t="shared" si="100"/>
+        <f t="shared" si="107"/>
         <v>#VALUE!</v>
       </c>
       <c r="W91" s="55">
-        <f t="shared" si="101"/>
+        <f t="shared" si="108"/>
         <v>0</v>
       </c>
       <c r="X91" s="55">
-        <f t="shared" si="102"/>
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
       <c r="Y91" s="56" t="e">
-        <f t="shared" si="103"/>
+        <f t="shared" si="110"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="92" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A92" s="78"/>
       <c r="B92" s="47">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C92" s="128"/>
       <c r="D92" s="50"/>
@@ -8639,7 +8763,7 @@
       <c r="K92" s="50"/>
       <c r="L92" s="50"/>
       <c r="M92" s="129">
-        <f t="shared" si="96"/>
+        <f t="shared" si="103"/>
         <v>0</v>
       </c>
       <c r="N92" s="39">
@@ -8651,11 +8775,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P92" s="73">
-        <f t="shared" si="97"/>
+        <f t="shared" si="104"/>
         <v>0</v>
       </c>
       <c r="Q92" s="40">
-        <f t="shared" si="98"/>
+        <f t="shared" si="105"/>
         <v>0</v>
       </c>
       <c r="R92" s="51" t="e">
@@ -8671,30 +8795,30 @@
         <v>0</v>
       </c>
       <c r="U92" s="53" t="e">
-        <f t="shared" si="99"/>
+        <f t="shared" si="106"/>
         <v>#VALUE!</v>
       </c>
       <c r="V92" s="54" t="e">
-        <f t="shared" si="100"/>
+        <f t="shared" si="107"/>
         <v>#VALUE!</v>
       </c>
       <c r="W92" s="55">
-        <f t="shared" si="101"/>
+        <f t="shared" si="108"/>
         <v>0</v>
       </c>
       <c r="X92" s="55">
-        <f t="shared" si="102"/>
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
       <c r="Y92" s="56" t="e">
-        <f t="shared" si="103"/>
+        <f t="shared" si="110"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="93" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A93" s="78"/>
       <c r="B93" s="47">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C93" s="128"/>
       <c r="D93" s="50"/>
@@ -8707,7 +8831,7 @@
       <c r="K93" s="50"/>
       <c r="L93" s="50"/>
       <c r="M93" s="129">
-        <f t="shared" si="96"/>
+        <f t="shared" si="103"/>
         <v>0</v>
       </c>
       <c r="N93" s="39">
@@ -8719,11 +8843,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P93" s="73">
-        <f t="shared" si="97"/>
+        <f t="shared" si="104"/>
         <v>0</v>
       </c>
       <c r="Q93" s="40">
-        <f t="shared" si="98"/>
+        <f t="shared" si="105"/>
         <v>0</v>
       </c>
       <c r="R93" s="51" t="e">
@@ -8739,30 +8863,30 @@
         <v>0</v>
       </c>
       <c r="U93" s="53" t="e">
-        <f t="shared" si="99"/>
+        <f t="shared" si="106"/>
         <v>#VALUE!</v>
       </c>
       <c r="V93" s="54" t="e">
-        <f t="shared" si="100"/>
+        <f t="shared" si="107"/>
         <v>#VALUE!</v>
       </c>
       <c r="W93" s="55">
-        <f t="shared" si="101"/>
+        <f t="shared" si="108"/>
         <v>0</v>
       </c>
       <c r="X93" s="55">
-        <f t="shared" si="102"/>
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
       <c r="Y93" s="56" t="e">
-        <f t="shared" si="103"/>
+        <f t="shared" si="110"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="94" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A94" s="78"/>
       <c r="B94" s="47">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C94" s="128"/>
       <c r="D94" s="50"/>
@@ -8775,7 +8899,7 @@
       <c r="K94" s="50"/>
       <c r="L94" s="50"/>
       <c r="M94" s="129">
-        <f t="shared" si="96"/>
+        <f t="shared" si="103"/>
         <v>0</v>
       </c>
       <c r="N94" s="39">
@@ -8787,11 +8911,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P94" s="73">
-        <f t="shared" si="97"/>
+        <f t="shared" si="104"/>
         <v>0</v>
       </c>
       <c r="Q94" s="40">
-        <f t="shared" si="98"/>
+        <f t="shared" si="105"/>
         <v>0</v>
       </c>
       <c r="R94" s="51" t="e">
@@ -8807,30 +8931,30 @@
         <v>0</v>
       </c>
       <c r="U94" s="53" t="e">
-        <f t="shared" si="99"/>
+        <f t="shared" si="106"/>
         <v>#VALUE!</v>
       </c>
       <c r="V94" s="54" t="e">
-        <f t="shared" si="100"/>
+        <f t="shared" si="107"/>
         <v>#VALUE!</v>
       </c>
       <c r="W94" s="55">
-        <f t="shared" si="101"/>
+        <f t="shared" si="108"/>
         <v>0</v>
       </c>
       <c r="X94" s="55">
-        <f t="shared" si="102"/>
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
       <c r="Y94" s="56" t="e">
-        <f t="shared" si="103"/>
+        <f t="shared" si="110"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="95" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A95" s="78"/>
       <c r="B95" s="47">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C95" s="128"/>
       <c r="D95" s="50"/>
@@ -8843,7 +8967,7 @@
       <c r="K95" s="50"/>
       <c r="L95" s="50"/>
       <c r="M95" s="129">
-        <f t="shared" si="96"/>
+        <f t="shared" si="103"/>
         <v>0</v>
       </c>
       <c r="N95" s="39">
@@ -8855,11 +8979,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P95" s="73">
-        <f t="shared" si="97"/>
+        <f t="shared" si="104"/>
         <v>0</v>
       </c>
       <c r="Q95" s="40">
-        <f t="shared" si="98"/>
+        <f t="shared" si="105"/>
         <v>0</v>
       </c>
       <c r="R95" s="51" t="e">
@@ -8875,30 +8999,30 @@
         <v>0</v>
       </c>
       <c r="U95" s="53" t="e">
-        <f t="shared" si="99"/>
+        <f t="shared" si="106"/>
         <v>#VALUE!</v>
       </c>
       <c r="V95" s="54" t="e">
-        <f t="shared" si="100"/>
+        <f t="shared" si="107"/>
         <v>#VALUE!</v>
       </c>
       <c r="W95" s="55">
-        <f t="shared" si="101"/>
+        <f t="shared" si="108"/>
         <v>0</v>
       </c>
       <c r="X95" s="55">
-        <f t="shared" si="102"/>
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
       <c r="Y95" s="56" t="e">
-        <f t="shared" si="103"/>
+        <f t="shared" si="110"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="96" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A96" s="78"/>
       <c r="B96" s="47">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C96" s="128"/>
       <c r="D96" s="50"/>
@@ -8911,7 +9035,7 @@
       <c r="K96" s="50"/>
       <c r="L96" s="50"/>
       <c r="M96" s="129">
-        <f t="shared" si="96"/>
+        <f t="shared" si="103"/>
         <v>0</v>
       </c>
       <c r="N96" s="39">
@@ -8923,11 +9047,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P96" s="73">
-        <f t="shared" si="97"/>
+        <f t="shared" si="104"/>
         <v>0</v>
       </c>
       <c r="Q96" s="40">
-        <f t="shared" si="98"/>
+        <f t="shared" si="105"/>
         <v>0</v>
       </c>
       <c r="R96" s="51" t="e">
@@ -8943,30 +9067,30 @@
         <v>0</v>
       </c>
       <c r="U96" s="53" t="e">
-        <f t="shared" si="99"/>
+        <f t="shared" si="106"/>
         <v>#VALUE!</v>
       </c>
       <c r="V96" s="54" t="e">
-        <f t="shared" si="100"/>
+        <f t="shared" si="107"/>
         <v>#VALUE!</v>
       </c>
       <c r="W96" s="55">
-        <f t="shared" si="101"/>
+        <f t="shared" si="108"/>
         <v>0</v>
       </c>
       <c r="X96" s="55">
-        <f t="shared" si="102"/>
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
       <c r="Y96" s="56" t="e">
-        <f t="shared" si="103"/>
+        <f t="shared" si="110"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="97" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A97" s="78"/>
       <c r="B97" s="47">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C97" s="128"/>
       <c r="D97" s="50"/>
@@ -8979,7 +9103,7 @@
       <c r="K97" s="50"/>
       <c r="L97" s="50"/>
       <c r="M97" s="129">
-        <f t="shared" si="96"/>
+        <f t="shared" si="103"/>
         <v>0</v>
       </c>
       <c r="N97" s="39">
@@ -8991,11 +9115,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P97" s="73">
-        <f t="shared" si="97"/>
+        <f t="shared" si="104"/>
         <v>0</v>
       </c>
       <c r="Q97" s="40">
-        <f t="shared" si="98"/>
+        <f t="shared" si="105"/>
         <v>0</v>
       </c>
       <c r="R97" s="51" t="e">
@@ -9011,30 +9135,30 @@
         <v>0</v>
       </c>
       <c r="U97" s="53" t="e">
-        <f t="shared" si="99"/>
+        <f t="shared" si="106"/>
         <v>#VALUE!</v>
       </c>
       <c r="V97" s="54" t="e">
-        <f t="shared" si="100"/>
+        <f t="shared" si="107"/>
         <v>#VALUE!</v>
       </c>
       <c r="W97" s="55">
-        <f t="shared" si="101"/>
+        <f t="shared" si="108"/>
         <v>0</v>
       </c>
       <c r="X97" s="55">
-        <f t="shared" si="102"/>
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
       <c r="Y97" s="56" t="e">
-        <f t="shared" si="103"/>
+        <f t="shared" si="110"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="98" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A98" s="78"/>
       <c r="B98" s="47">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C98" s="128"/>
       <c r="D98" s="50"/>
@@ -9047,7 +9171,7 @@
       <c r="K98" s="50"/>
       <c r="L98" s="50"/>
       <c r="M98" s="129">
-        <f t="shared" si="96"/>
+        <f t="shared" si="103"/>
         <v>0</v>
       </c>
       <c r="N98" s="39">
@@ -9059,11 +9183,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P98" s="73">
-        <f t="shared" si="97"/>
+        <f t="shared" si="104"/>
         <v>0</v>
       </c>
       <c r="Q98" s="40">
-        <f t="shared" si="98"/>
+        <f t="shared" si="105"/>
         <v>0</v>
       </c>
       <c r="R98" s="51" t="e">
@@ -9079,30 +9203,30 @@
         <v>0</v>
       </c>
       <c r="U98" s="53" t="e">
-        <f t="shared" si="99"/>
+        <f t="shared" si="106"/>
         <v>#VALUE!</v>
       </c>
       <c r="V98" s="54" t="e">
-        <f t="shared" si="100"/>
+        <f t="shared" si="107"/>
         <v>#VALUE!</v>
       </c>
       <c r="W98" s="55">
-        <f t="shared" si="101"/>
+        <f t="shared" si="108"/>
         <v>0</v>
       </c>
       <c r="X98" s="55">
-        <f t="shared" si="102"/>
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
       <c r="Y98" s="56" t="e">
-        <f t="shared" si="103"/>
+        <f t="shared" si="110"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="99" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A99" s="78"/>
-      <c r="B99" s="47">
-        <v>94</v>
+      <c r="B99" s="182">
+        <v>95</v>
       </c>
       <c r="C99" s="128"/>
       <c r="D99" s="50"/>
@@ -9115,7 +9239,7 @@
       <c r="K99" s="50"/>
       <c r="L99" s="50"/>
       <c r="M99" s="129">
-        <f t="shared" si="96"/>
+        <f t="shared" si="103"/>
         <v>0</v>
       </c>
       <c r="N99" s="39">
@@ -9127,11 +9251,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P99" s="73">
-        <f t="shared" si="97"/>
+        <f t="shared" si="104"/>
         <v>0</v>
       </c>
       <c r="Q99" s="40">
-        <f t="shared" si="98"/>
+        <f t="shared" si="105"/>
         <v>0</v>
       </c>
       <c r="R99" s="51" t="e">
@@ -9147,30 +9271,30 @@
         <v>0</v>
       </c>
       <c r="U99" s="53" t="e">
-        <f t="shared" si="99"/>
+        <f t="shared" si="106"/>
         <v>#VALUE!</v>
       </c>
       <c r="V99" s="54" t="e">
-        <f t="shared" si="100"/>
+        <f t="shared" si="107"/>
         <v>#VALUE!</v>
       </c>
       <c r="W99" s="55">
-        <f t="shared" si="101"/>
+        <f t="shared" si="108"/>
         <v>0</v>
       </c>
       <c r="X99" s="55">
-        <f t="shared" si="102"/>
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
       <c r="Y99" s="56" t="e">
-        <f t="shared" si="103"/>
+        <f t="shared" si="110"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="100" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A100" s="78"/>
-      <c r="B100" s="47">
-        <v>95</v>
+      <c r="B100" s="182">
+        <v>96</v>
       </c>
       <c r="C100" s="128"/>
       <c r="D100" s="50"/>
@@ -9183,7 +9307,7 @@
       <c r="K100" s="50"/>
       <c r="L100" s="50"/>
       <c r="M100" s="129">
-        <f t="shared" si="96"/>
+        <f t="shared" si="103"/>
         <v>0</v>
       </c>
       <c r="N100" s="39">
@@ -9195,11 +9319,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P100" s="73">
-        <f t="shared" si="97"/>
+        <f t="shared" si="104"/>
         <v>0</v>
       </c>
       <c r="Q100" s="40">
-        <f t="shared" si="98"/>
+        <f t="shared" si="105"/>
         <v>0</v>
       </c>
       <c r="R100" s="51" t="e">
@@ -9215,30 +9339,30 @@
         <v>0</v>
       </c>
       <c r="U100" s="53" t="e">
-        <f t="shared" si="99"/>
+        <f t="shared" si="106"/>
         <v>#VALUE!</v>
       </c>
       <c r="V100" s="54" t="e">
-        <f t="shared" si="100"/>
+        <f t="shared" si="107"/>
         <v>#VALUE!</v>
       </c>
       <c r="W100" s="55">
-        <f t="shared" si="101"/>
+        <f t="shared" si="108"/>
         <v>0</v>
       </c>
       <c r="X100" s="55">
-        <f t="shared" si="102"/>
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
       <c r="Y100" s="56" t="e">
-        <f t="shared" si="103"/>
+        <f t="shared" si="110"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="101" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A101" s="78"/>
-      <c r="B101" s="47">
-        <v>96</v>
+      <c r="B101" s="182">
+        <v>97</v>
       </c>
       <c r="C101" s="128"/>
       <c r="D101" s="50"/>
@@ -9251,7 +9375,7 @@
       <c r="K101" s="50"/>
       <c r="L101" s="50"/>
       <c r="M101" s="129">
-        <f t="shared" si="96"/>
+        <f t="shared" si="103"/>
         <v>0</v>
       </c>
       <c r="N101" s="39">
@@ -9263,11 +9387,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P101" s="73">
-        <f t="shared" si="97"/>
+        <f t="shared" si="104"/>
         <v>0</v>
       </c>
       <c r="Q101" s="40">
-        <f t="shared" si="98"/>
+        <f t="shared" si="105"/>
         <v>0</v>
       </c>
       <c r="R101" s="51" t="e">
@@ -9283,30 +9407,30 @@
         <v>0</v>
       </c>
       <c r="U101" s="53" t="e">
-        <f t="shared" si="99"/>
+        <f t="shared" si="106"/>
         <v>#VALUE!</v>
       </c>
       <c r="V101" s="54" t="e">
-        <f t="shared" si="100"/>
+        <f t="shared" si="107"/>
         <v>#VALUE!</v>
       </c>
       <c r="W101" s="55">
-        <f t="shared" si="101"/>
+        <f t="shared" si="108"/>
         <v>0</v>
       </c>
       <c r="X101" s="55">
-        <f t="shared" si="102"/>
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
       <c r="Y101" s="56" t="e">
-        <f t="shared" si="103"/>
+        <f t="shared" si="110"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="102" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A102" s="78"/>
       <c r="B102" s="47">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C102" s="128"/>
       <c r="D102" s="50"/>
@@ -9319,7 +9443,7 @@
       <c r="K102" s="50"/>
       <c r="L102" s="50"/>
       <c r="M102" s="129">
-        <f t="shared" si="96"/>
+        <f t="shared" si="103"/>
         <v>0</v>
       </c>
       <c r="N102" s="39">
@@ -9331,11 +9455,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P102" s="73">
-        <f t="shared" si="97"/>
+        <f t="shared" si="104"/>
         <v>0</v>
       </c>
       <c r="Q102" s="40">
-        <f t="shared" si="98"/>
+        <f t="shared" si="105"/>
         <v>0</v>
       </c>
       <c r="R102" s="51" t="e">
@@ -9351,30 +9475,30 @@
         <v>0</v>
       </c>
       <c r="U102" s="53" t="e">
-        <f t="shared" si="99"/>
+        <f t="shared" si="106"/>
         <v>#VALUE!</v>
       </c>
       <c r="V102" s="54" t="e">
-        <f t="shared" si="100"/>
+        <f t="shared" si="107"/>
         <v>#VALUE!</v>
       </c>
       <c r="W102" s="55">
-        <f t="shared" si="101"/>
+        <f t="shared" si="108"/>
         <v>0</v>
       </c>
       <c r="X102" s="55">
-        <f t="shared" si="102"/>
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
       <c r="Y102" s="56" t="e">
-        <f t="shared" si="103"/>
+        <f t="shared" si="110"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="103" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A103" s="78"/>
       <c r="B103" s="47">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C103" s="128"/>
       <c r="D103" s="50"/>
@@ -9387,7 +9511,7 @@
       <c r="K103" s="50"/>
       <c r="L103" s="50"/>
       <c r="M103" s="129">
-        <f t="shared" si="96"/>
+        <f t="shared" si="103"/>
         <v>0</v>
       </c>
       <c r="N103" s="39">
@@ -9399,11 +9523,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P103" s="73">
-        <f t="shared" si="97"/>
+        <f t="shared" si="104"/>
         <v>0</v>
       </c>
       <c r="Q103" s="40">
-        <f t="shared" si="98"/>
+        <f t="shared" si="105"/>
         <v>0</v>
       </c>
       <c r="R103" s="51" t="e">
@@ -9419,30 +9543,30 @@
         <v>0</v>
       </c>
       <c r="U103" s="53" t="e">
-        <f t="shared" si="99"/>
+        <f t="shared" si="106"/>
         <v>#VALUE!</v>
       </c>
       <c r="V103" s="54" t="e">
-        <f t="shared" si="100"/>
+        <f t="shared" si="107"/>
         <v>#VALUE!</v>
       </c>
       <c r="W103" s="55">
-        <f t="shared" si="101"/>
+        <f t="shared" si="108"/>
         <v>0</v>
       </c>
       <c r="X103" s="55">
-        <f t="shared" si="102"/>
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
       <c r="Y103" s="56" t="e">
-        <f t="shared" si="103"/>
+        <f t="shared" si="110"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="104" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A104" s="78"/>
       <c r="B104" s="47">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C104" s="128"/>
       <c r="D104" s="50"/>
@@ -9455,7 +9579,7 @@
       <c r="K104" s="50"/>
       <c r="L104" s="50"/>
       <c r="M104" s="129">
-        <f t="shared" si="96"/>
+        <f t="shared" si="103"/>
         <v>0</v>
       </c>
       <c r="N104" s="39">
@@ -9467,11 +9591,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P104" s="73">
-        <f t="shared" si="97"/>
+        <f t="shared" si="104"/>
         <v>0</v>
       </c>
       <c r="Q104" s="40">
-        <f t="shared" si="98"/>
+        <f t="shared" si="105"/>
         <v>0</v>
       </c>
       <c r="R104" s="51" t="e">
@@ -9487,30 +9611,30 @@
         <v>0</v>
       </c>
       <c r="U104" s="53" t="e">
-        <f t="shared" si="99"/>
+        <f t="shared" si="106"/>
         <v>#VALUE!</v>
       </c>
       <c r="V104" s="54" t="e">
-        <f t="shared" si="100"/>
+        <f t="shared" si="107"/>
         <v>#VALUE!</v>
       </c>
       <c r="W104" s="55">
-        <f t="shared" si="101"/>
+        <f t="shared" si="108"/>
         <v>0</v>
       </c>
       <c r="X104" s="55">
-        <f t="shared" si="102"/>
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
       <c r="Y104" s="56" t="e">
-        <f t="shared" si="103"/>
+        <f t="shared" si="110"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="105" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A105" s="78"/>
       <c r="B105" s="47">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C105" s="128"/>
       <c r="D105" s="50"/>
@@ -9523,7 +9647,7 @@
       <c r="K105" s="50"/>
       <c r="L105" s="50"/>
       <c r="M105" s="129">
-        <f t="shared" si="96"/>
+        <f t="shared" si="103"/>
         <v>0</v>
       </c>
       <c r="N105" s="39">
@@ -9535,11 +9659,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P105" s="73">
-        <f t="shared" si="97"/>
+        <f t="shared" si="104"/>
         <v>0</v>
       </c>
       <c r="Q105" s="40">
-        <f t="shared" si="98"/>
+        <f t="shared" si="105"/>
         <v>0</v>
       </c>
       <c r="R105" s="51" t="e">
@@ -9555,30 +9679,30 @@
         <v>0</v>
       </c>
       <c r="U105" s="53" t="e">
-        <f t="shared" si="99"/>
+        <f t="shared" si="106"/>
         <v>#VALUE!</v>
       </c>
       <c r="V105" s="54" t="e">
-        <f t="shared" si="100"/>
+        <f t="shared" si="107"/>
         <v>#VALUE!</v>
       </c>
       <c r="W105" s="55">
-        <f t="shared" si="101"/>
+        <f t="shared" si="108"/>
         <v>0</v>
       </c>
       <c r="X105" s="55">
-        <f t="shared" si="102"/>
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
       <c r="Y105" s="56" t="e">
-        <f t="shared" si="103"/>
+        <f t="shared" si="110"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="106" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A106" s="78"/>
       <c r="B106" s="47">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C106" s="128"/>
       <c r="D106" s="50"/>
@@ -9591,7 +9715,7 @@
       <c r="K106" s="50"/>
       <c r="L106" s="50"/>
       <c r="M106" s="129">
-        <f t="shared" si="96"/>
+        <f t="shared" si="103"/>
         <v>0</v>
       </c>
       <c r="N106" s="39">
@@ -9603,11 +9727,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P106" s="73">
-        <f t="shared" si="97"/>
+        <f t="shared" si="104"/>
         <v>0</v>
       </c>
       <c r="Q106" s="40">
-        <f t="shared" si="98"/>
+        <f t="shared" si="105"/>
         <v>0</v>
       </c>
       <c r="R106" s="51" t="e">
@@ -9623,30 +9747,30 @@
         <v>0</v>
       </c>
       <c r="U106" s="53" t="e">
-        <f t="shared" si="99"/>
+        <f t="shared" si="106"/>
         <v>#VALUE!</v>
       </c>
       <c r="V106" s="54" t="e">
-        <f t="shared" si="100"/>
+        <f t="shared" si="107"/>
         <v>#VALUE!</v>
       </c>
       <c r="W106" s="55">
-        <f t="shared" si="101"/>
+        <f t="shared" si="108"/>
         <v>0</v>
       </c>
       <c r="X106" s="55">
-        <f t="shared" si="102"/>
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
       <c r="Y106" s="56" t="e">
-        <f t="shared" si="103"/>
+        <f t="shared" si="110"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="107" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A107" s="78"/>
       <c r="B107" s="47">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C107" s="128"/>
       <c r="D107" s="50"/>
@@ -9659,7 +9783,7 @@
       <c r="K107" s="50"/>
       <c r="L107" s="50"/>
       <c r="M107" s="129">
-        <f t="shared" si="96"/>
+        <f t="shared" si="103"/>
         <v>0</v>
       </c>
       <c r="N107" s="39">
@@ -9671,11 +9795,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P107" s="73">
-        <f t="shared" si="97"/>
+        <f t="shared" si="104"/>
         <v>0</v>
       </c>
       <c r="Q107" s="40">
-        <f t="shared" si="98"/>
+        <f t="shared" si="105"/>
         <v>0</v>
       </c>
       <c r="R107" s="51" t="e">
@@ -9691,30 +9815,30 @@
         <v>0</v>
       </c>
       <c r="U107" s="53" t="e">
-        <f t="shared" si="99"/>
+        <f t="shared" si="106"/>
         <v>#VALUE!</v>
       </c>
       <c r="V107" s="54" t="e">
-        <f t="shared" si="100"/>
+        <f t="shared" si="107"/>
         <v>#VALUE!</v>
       </c>
       <c r="W107" s="55">
-        <f t="shared" si="101"/>
+        <f t="shared" si="108"/>
         <v>0</v>
       </c>
       <c r="X107" s="55">
-        <f t="shared" si="102"/>
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
       <c r="Y107" s="56" t="e">
-        <f t="shared" si="103"/>
+        <f t="shared" si="110"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="108" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A108" s="78"/>
       <c r="B108" s="47">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C108" s="128"/>
       <c r="D108" s="50"/>
@@ -9727,7 +9851,7 @@
       <c r="K108" s="50"/>
       <c r="L108" s="50"/>
       <c r="M108" s="129">
-        <f t="shared" si="96"/>
+        <f t="shared" si="103"/>
         <v>0</v>
       </c>
       <c r="N108" s="39">
@@ -9739,11 +9863,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P108" s="73">
-        <f t="shared" si="97"/>
+        <f t="shared" si="104"/>
         <v>0</v>
       </c>
       <c r="Q108" s="40">
-        <f t="shared" si="98"/>
+        <f t="shared" si="105"/>
         <v>0</v>
       </c>
       <c r="R108" s="51" t="e">
@@ -9759,30 +9883,30 @@
         <v>0</v>
       </c>
       <c r="U108" s="53" t="e">
-        <f t="shared" si="99"/>
+        <f t="shared" si="106"/>
         <v>#VALUE!</v>
       </c>
       <c r="V108" s="54" t="e">
-        <f t="shared" si="100"/>
+        <f t="shared" si="107"/>
         <v>#VALUE!</v>
       </c>
       <c r="W108" s="55">
-        <f t="shared" si="101"/>
+        <f t="shared" si="108"/>
         <v>0</v>
       </c>
       <c r="X108" s="55">
-        <f t="shared" si="102"/>
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
       <c r="Y108" s="56" t="e">
-        <f t="shared" si="103"/>
+        <f t="shared" si="110"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="109" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A109" s="78"/>
-      <c r="B109" s="47">
-        <v>104</v>
+      <c r="B109" s="182">
+        <v>105</v>
       </c>
       <c r="C109" s="128"/>
       <c r="D109" s="50"/>
@@ -9795,7 +9919,7 @@
       <c r="K109" s="50"/>
       <c r="L109" s="50"/>
       <c r="M109" s="129">
-        <f t="shared" si="96"/>
+        <f t="shared" si="103"/>
         <v>0</v>
       </c>
       <c r="N109" s="39">
@@ -9807,11 +9931,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P109" s="73">
-        <f t="shared" si="97"/>
+        <f t="shared" si="104"/>
         <v>0</v>
       </c>
       <c r="Q109" s="40">
-        <f t="shared" si="98"/>
+        <f t="shared" si="105"/>
         <v>0</v>
       </c>
       <c r="R109" s="51" t="e">
@@ -9827,30 +9951,30 @@
         <v>0</v>
       </c>
       <c r="U109" s="53" t="e">
-        <f t="shared" si="99"/>
+        <f t="shared" si="106"/>
         <v>#VALUE!</v>
       </c>
       <c r="V109" s="54" t="e">
-        <f t="shared" si="100"/>
+        <f t="shared" si="107"/>
         <v>#VALUE!</v>
       </c>
       <c r="W109" s="55">
-        <f t="shared" si="101"/>
+        <f t="shared" si="108"/>
         <v>0</v>
       </c>
       <c r="X109" s="55">
-        <f t="shared" si="102"/>
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
       <c r="Y109" s="56" t="e">
-        <f t="shared" si="103"/>
+        <f t="shared" si="110"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="110" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A110" s="78"/>
-      <c r="B110" s="47">
-        <v>105</v>
+      <c r="B110" s="182">
+        <v>106</v>
       </c>
       <c r="C110" s="128"/>
       <c r="D110" s="50"/>
@@ -9863,7 +9987,7 @@
       <c r="K110" s="50"/>
       <c r="L110" s="50"/>
       <c r="M110" s="129">
-        <f t="shared" si="96"/>
+        <f t="shared" si="103"/>
         <v>0</v>
       </c>
       <c r="N110" s="39">
@@ -9875,11 +9999,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P110" s="73">
-        <f t="shared" si="97"/>
+        <f t="shared" si="104"/>
         <v>0</v>
       </c>
       <c r="Q110" s="40">
-        <f t="shared" si="98"/>
+        <f t="shared" si="105"/>
         <v>0</v>
       </c>
       <c r="R110" s="51" t="e">
@@ -9895,30 +10019,30 @@
         <v>0</v>
       </c>
       <c r="U110" s="53" t="e">
-        <f t="shared" si="99"/>
+        <f t="shared" si="106"/>
         <v>#VALUE!</v>
       </c>
       <c r="V110" s="54" t="e">
-        <f t="shared" si="100"/>
+        <f t="shared" si="107"/>
         <v>#VALUE!</v>
       </c>
       <c r="W110" s="55">
-        <f t="shared" si="101"/>
+        <f t="shared" si="108"/>
         <v>0</v>
       </c>
       <c r="X110" s="55">
-        <f t="shared" si="102"/>
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
       <c r="Y110" s="56" t="e">
-        <f t="shared" si="103"/>
+        <f t="shared" si="110"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="111" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A111" s="78"/>
-      <c r="B111" s="47">
-        <v>106</v>
+      <c r="B111" s="182">
+        <v>107</v>
       </c>
       <c r="C111" s="128"/>
       <c r="D111" s="50"/>
@@ -9931,7 +10055,7 @@
       <c r="K111" s="50"/>
       <c r="L111" s="50"/>
       <c r="M111" s="129">
-        <f t="shared" si="96"/>
+        <f t="shared" si="103"/>
         <v>0</v>
       </c>
       <c r="N111" s="39">
@@ -9943,11 +10067,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P111" s="73">
-        <f t="shared" si="97"/>
+        <f t="shared" si="104"/>
         <v>0</v>
       </c>
       <c r="Q111" s="40">
-        <f t="shared" si="98"/>
+        <f t="shared" si="105"/>
         <v>0</v>
       </c>
       <c r="R111" s="51" t="e">
@@ -9963,30 +10087,30 @@
         <v>0</v>
       </c>
       <c r="U111" s="53" t="e">
-        <f t="shared" si="99"/>
+        <f t="shared" si="106"/>
         <v>#VALUE!</v>
       </c>
       <c r="V111" s="54" t="e">
-        <f t="shared" si="100"/>
+        <f t="shared" si="107"/>
         <v>#VALUE!</v>
       </c>
       <c r="W111" s="55">
-        <f t="shared" si="101"/>
+        <f t="shared" si="108"/>
         <v>0</v>
       </c>
       <c r="X111" s="55">
-        <f t="shared" si="102"/>
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
       <c r="Y111" s="56" t="e">
-        <f t="shared" si="103"/>
+        <f t="shared" si="110"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="112" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A112" s="78"/>
       <c r="B112" s="47">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C112" s="128"/>
       <c r="D112" s="50"/>
@@ -9999,7 +10123,7 @@
       <c r="K112" s="50"/>
       <c r="L112" s="50"/>
       <c r="M112" s="129">
-        <f t="shared" si="96"/>
+        <f t="shared" si="103"/>
         <v>0</v>
       </c>
       <c r="N112" s="39">
@@ -10011,11 +10135,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P112" s="73">
-        <f t="shared" si="97"/>
+        <f t="shared" si="104"/>
         <v>0</v>
       </c>
       <c r="Q112" s="40">
-        <f t="shared" si="98"/>
+        <f t="shared" si="105"/>
         <v>0</v>
       </c>
       <c r="R112" s="51" t="e">
@@ -10031,30 +10155,30 @@
         <v>0</v>
       </c>
       <c r="U112" s="53" t="e">
-        <f t="shared" si="99"/>
+        <f t="shared" si="106"/>
         <v>#VALUE!</v>
       </c>
       <c r="V112" s="54" t="e">
-        <f t="shared" si="100"/>
+        <f t="shared" si="107"/>
         <v>#VALUE!</v>
       </c>
       <c r="W112" s="55">
-        <f t="shared" si="101"/>
+        <f t="shared" si="108"/>
         <v>0</v>
       </c>
       <c r="X112" s="55">
-        <f t="shared" si="102"/>
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
       <c r="Y112" s="56" t="e">
-        <f t="shared" si="103"/>
+        <f t="shared" si="110"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="113" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A113" s="78"/>
       <c r="B113" s="47">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C113" s="128"/>
       <c r="D113" s="50"/>
@@ -10067,7 +10191,7 @@
       <c r="K113" s="50"/>
       <c r="L113" s="50"/>
       <c r="M113" s="129">
-        <f t="shared" si="96"/>
+        <f t="shared" si="103"/>
         <v>0</v>
       </c>
       <c r="N113" s="39">
@@ -10079,11 +10203,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P113" s="73">
-        <f t="shared" si="97"/>
+        <f t="shared" si="104"/>
         <v>0</v>
       </c>
       <c r="Q113" s="40">
-        <f t="shared" si="98"/>
+        <f t="shared" si="105"/>
         <v>0</v>
       </c>
       <c r="R113" s="51" t="e">
@@ -10099,30 +10223,30 @@
         <v>0</v>
       </c>
       <c r="U113" s="53" t="e">
-        <f t="shared" si="99"/>
+        <f t="shared" si="106"/>
         <v>#VALUE!</v>
       </c>
       <c r="V113" s="54" t="e">
-        <f t="shared" si="100"/>
+        <f t="shared" si="107"/>
         <v>#VALUE!</v>
       </c>
       <c r="W113" s="55">
-        <f t="shared" si="101"/>
+        <f t="shared" si="108"/>
         <v>0</v>
       </c>
       <c r="X113" s="55">
-        <f t="shared" si="102"/>
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
       <c r="Y113" s="56" t="e">
-        <f t="shared" si="103"/>
+        <f t="shared" si="110"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="114" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A114" s="78"/>
       <c r="B114" s="47">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C114" s="128"/>
       <c r="D114" s="50"/>
@@ -10135,7 +10259,7 @@
       <c r="K114" s="50"/>
       <c r="L114" s="50"/>
       <c r="M114" s="129">
-        <f t="shared" si="96"/>
+        <f t="shared" si="103"/>
         <v>0</v>
       </c>
       <c r="N114" s="39">
@@ -10147,11 +10271,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P114" s="73">
-        <f t="shared" si="97"/>
+        <f t="shared" si="104"/>
         <v>0</v>
       </c>
       <c r="Q114" s="40">
-        <f t="shared" si="98"/>
+        <f t="shared" si="105"/>
         <v>0</v>
       </c>
       <c r="R114" s="51" t="e">
@@ -10167,30 +10291,30 @@
         <v>0</v>
       </c>
       <c r="U114" s="53" t="e">
-        <f t="shared" si="99"/>
+        <f t="shared" si="106"/>
         <v>#VALUE!</v>
       </c>
       <c r="V114" s="54" t="e">
-        <f t="shared" si="100"/>
+        <f t="shared" si="107"/>
         <v>#VALUE!</v>
       </c>
       <c r="W114" s="55">
-        <f t="shared" si="101"/>
+        <f t="shared" si="108"/>
         <v>0</v>
       </c>
       <c r="X114" s="55">
-        <f t="shared" si="102"/>
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
       <c r="Y114" s="56" t="e">
-        <f t="shared" si="103"/>
+        <f t="shared" si="110"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="115" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A115" s="78"/>
       <c r="B115" s="47">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C115" s="128"/>
       <c r="D115" s="50"/>
@@ -10203,7 +10327,7 @@
       <c r="K115" s="50"/>
       <c r="L115" s="50"/>
       <c r="M115" s="129">
-        <f t="shared" si="96"/>
+        <f t="shared" si="103"/>
         <v>0</v>
       </c>
       <c r="N115" s="39">
@@ -10215,11 +10339,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P115" s="73">
-        <f t="shared" si="97"/>
+        <f t="shared" si="104"/>
         <v>0</v>
       </c>
       <c r="Q115" s="40">
-        <f t="shared" si="98"/>
+        <f t="shared" si="105"/>
         <v>0</v>
       </c>
       <c r="R115" s="51" t="e">
@@ -10235,30 +10359,30 @@
         <v>0</v>
       </c>
       <c r="U115" s="53" t="e">
-        <f t="shared" si="99"/>
+        <f t="shared" si="106"/>
         <v>#VALUE!</v>
       </c>
       <c r="V115" s="54" t="e">
-        <f t="shared" si="100"/>
+        <f t="shared" si="107"/>
         <v>#VALUE!</v>
       </c>
       <c r="W115" s="55">
-        <f t="shared" si="101"/>
+        <f t="shared" si="108"/>
         <v>0</v>
       </c>
       <c r="X115" s="55">
-        <f t="shared" si="102"/>
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
       <c r="Y115" s="56" t="e">
-        <f t="shared" si="103"/>
+        <f t="shared" si="110"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="116" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A116" s="78"/>
       <c r="B116" s="47">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C116" s="128"/>
       <c r="D116" s="50"/>
@@ -10271,7 +10395,7 @@
       <c r="K116" s="50"/>
       <c r="L116" s="50"/>
       <c r="M116" s="129">
-        <f t="shared" si="96"/>
+        <f t="shared" si="103"/>
         <v>0</v>
       </c>
       <c r="N116" s="39">
@@ -10283,11 +10407,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P116" s="73">
-        <f t="shared" si="97"/>
+        <f t="shared" si="104"/>
         <v>0</v>
       </c>
       <c r="Q116" s="40">
-        <f t="shared" si="98"/>
+        <f t="shared" si="105"/>
         <v>0</v>
       </c>
       <c r="R116" s="51" t="e">
@@ -10303,30 +10427,30 @@
         <v>0</v>
       </c>
       <c r="U116" s="53" t="e">
-        <f t="shared" si="99"/>
+        <f t="shared" si="106"/>
         <v>#VALUE!</v>
       </c>
       <c r="V116" s="54" t="e">
-        <f t="shared" si="100"/>
+        <f t="shared" si="107"/>
         <v>#VALUE!</v>
       </c>
       <c r="W116" s="55">
-        <f t="shared" si="101"/>
+        <f t="shared" si="108"/>
         <v>0</v>
       </c>
       <c r="X116" s="55">
-        <f t="shared" si="102"/>
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
       <c r="Y116" s="56" t="e">
-        <f t="shared" si="103"/>
+        <f t="shared" si="110"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="117" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A117" s="78"/>
       <c r="B117" s="47">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C117" s="128"/>
       <c r="D117" s="50"/>
@@ -10339,7 +10463,7 @@
       <c r="K117" s="50"/>
       <c r="L117" s="50"/>
       <c r="M117" s="129">
-        <f t="shared" si="96"/>
+        <f t="shared" si="103"/>
         <v>0</v>
       </c>
       <c r="N117" s="39">
@@ -10351,11 +10475,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P117" s="73">
-        <f t="shared" si="97"/>
+        <f t="shared" si="104"/>
         <v>0</v>
       </c>
       <c r="Q117" s="40">
-        <f t="shared" si="98"/>
+        <f t="shared" si="105"/>
         <v>0</v>
       </c>
       <c r="R117" s="51" t="e">
@@ -10371,30 +10495,30 @@
         <v>0</v>
       </c>
       <c r="U117" s="53" t="e">
-        <f t="shared" si="99"/>
+        <f t="shared" si="106"/>
         <v>#VALUE!</v>
       </c>
       <c r="V117" s="54" t="e">
-        <f t="shared" si="100"/>
+        <f t="shared" si="107"/>
         <v>#VALUE!</v>
       </c>
       <c r="W117" s="55">
-        <f t="shared" si="101"/>
+        <f t="shared" si="108"/>
         <v>0</v>
       </c>
       <c r="X117" s="55">
-        <f t="shared" si="102"/>
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
       <c r="Y117" s="56" t="e">
-        <f t="shared" si="103"/>
+        <f t="shared" si="110"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="118" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A118" s="78"/>
       <c r="B118" s="47">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C118" s="128"/>
       <c r="D118" s="50"/>
@@ -10407,7 +10531,7 @@
       <c r="K118" s="50"/>
       <c r="L118" s="50"/>
       <c r="M118" s="129">
-        <f t="shared" si="96"/>
+        <f t="shared" si="103"/>
         <v>0</v>
       </c>
       <c r="N118" s="39">
@@ -10419,11 +10543,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P118" s="73">
-        <f t="shared" si="97"/>
+        <f t="shared" si="104"/>
         <v>0</v>
       </c>
       <c r="Q118" s="40">
-        <f t="shared" si="98"/>
+        <f t="shared" si="105"/>
         <v>0</v>
       </c>
       <c r="R118" s="51" t="e">
@@ -10439,30 +10563,30 @@
         <v>0</v>
       </c>
       <c r="U118" s="53" t="e">
-        <f t="shared" si="99"/>
+        <f t="shared" si="106"/>
         <v>#VALUE!</v>
       </c>
       <c r="V118" s="54" t="e">
-        <f t="shared" si="100"/>
+        <f t="shared" si="107"/>
         <v>#VALUE!</v>
       </c>
       <c r="W118" s="55">
-        <f t="shared" si="101"/>
+        <f t="shared" si="108"/>
         <v>0</v>
       </c>
       <c r="X118" s="55">
-        <f t="shared" si="102"/>
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
       <c r="Y118" s="56" t="e">
-        <f t="shared" si="103"/>
+        <f t="shared" si="110"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="119" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A119" s="78"/>
-      <c r="B119" s="47">
-        <v>114</v>
+      <c r="B119" s="182">
+        <v>115</v>
       </c>
       <c r="C119" s="128"/>
       <c r="D119" s="50"/>
@@ -10475,7 +10599,7 @@
       <c r="K119" s="50"/>
       <c r="L119" s="50"/>
       <c r="M119" s="129">
-        <f t="shared" si="96"/>
+        <f t="shared" si="103"/>
         <v>0</v>
       </c>
       <c r="N119" s="39">
@@ -10487,11 +10611,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P119" s="73">
-        <f t="shared" si="97"/>
+        <f t="shared" si="104"/>
         <v>0</v>
       </c>
       <c r="Q119" s="40">
-        <f t="shared" si="98"/>
+        <f t="shared" si="105"/>
         <v>0</v>
       </c>
       <c r="R119" s="51" t="e">
@@ -10507,30 +10631,30 @@
         <v>0</v>
       </c>
       <c r="U119" s="53" t="e">
-        <f t="shared" si="99"/>
+        <f t="shared" si="106"/>
         <v>#VALUE!</v>
       </c>
       <c r="V119" s="54" t="e">
-        <f t="shared" si="100"/>
+        <f t="shared" si="107"/>
         <v>#VALUE!</v>
       </c>
       <c r="W119" s="55">
-        <f t="shared" si="101"/>
+        <f t="shared" si="108"/>
         <v>0</v>
       </c>
       <c r="X119" s="55">
-        <f t="shared" si="102"/>
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
       <c r="Y119" s="56" t="e">
-        <f t="shared" si="103"/>
+        <f t="shared" si="110"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="120" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A120" s="78"/>
-      <c r="B120" s="47">
-        <v>115</v>
+      <c r="B120" s="182">
+        <v>116</v>
       </c>
       <c r="C120" s="128"/>
       <c r="D120" s="50"/>
@@ -10543,7 +10667,7 @@
       <c r="K120" s="50"/>
       <c r="L120" s="50"/>
       <c r="M120" s="129">
-        <f t="shared" si="96"/>
+        <f t="shared" si="103"/>
         <v>0</v>
       </c>
       <c r="N120" s="39">
@@ -10555,11 +10679,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P120" s="73">
-        <f t="shared" si="97"/>
+        <f t="shared" si="104"/>
         <v>0</v>
       </c>
       <c r="Q120" s="40">
-        <f t="shared" si="98"/>
+        <f t="shared" si="105"/>
         <v>0</v>
       </c>
       <c r="R120" s="51" t="e">
@@ -10575,30 +10699,30 @@
         <v>0</v>
       </c>
       <c r="U120" s="53" t="e">
-        <f t="shared" si="99"/>
+        <f t="shared" si="106"/>
         <v>#VALUE!</v>
       </c>
       <c r="V120" s="54" t="e">
-        <f t="shared" si="100"/>
+        <f t="shared" si="107"/>
         <v>#VALUE!</v>
       </c>
       <c r="W120" s="55">
-        <f t="shared" si="101"/>
+        <f t="shared" si="108"/>
         <v>0</v>
       </c>
       <c r="X120" s="55">
-        <f t="shared" si="102"/>
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
       <c r="Y120" s="56" t="e">
-        <f t="shared" si="103"/>
+        <f t="shared" si="110"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="121" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A121" s="78"/>
-      <c r="B121" s="47">
-        <v>116</v>
+      <c r="B121" s="182">
+        <v>117</v>
       </c>
       <c r="C121" s="128"/>
       <c r="D121" s="50"/>
@@ -10611,7 +10735,7 @@
       <c r="K121" s="50"/>
       <c r="L121" s="50"/>
       <c r="M121" s="129">
-        <f t="shared" si="96"/>
+        <f t="shared" si="103"/>
         <v>0</v>
       </c>
       <c r="N121" s="39">
@@ -10623,11 +10747,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P121" s="73">
-        <f t="shared" si="97"/>
+        <f t="shared" si="104"/>
         <v>0</v>
       </c>
       <c r="Q121" s="40">
-        <f t="shared" si="98"/>
+        <f t="shared" si="105"/>
         <v>0</v>
       </c>
       <c r="R121" s="51" t="e">
@@ -10643,30 +10767,30 @@
         <v>0</v>
       </c>
       <c r="U121" s="53" t="e">
-        <f t="shared" si="99"/>
+        <f t="shared" si="106"/>
         <v>#VALUE!</v>
       </c>
       <c r="V121" s="54" t="e">
-        <f t="shared" si="100"/>
+        <f t="shared" si="107"/>
         <v>#VALUE!</v>
       </c>
       <c r="W121" s="55">
-        <f t="shared" si="101"/>
+        <f t="shared" si="108"/>
         <v>0</v>
       </c>
       <c r="X121" s="55">
-        <f t="shared" si="102"/>
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
       <c r="Y121" s="56" t="e">
-        <f t="shared" si="103"/>
+        <f t="shared" si="110"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="122" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A122" s="78"/>
       <c r="B122" s="47">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C122" s="128"/>
       <c r="D122" s="50"/>
@@ -10679,7 +10803,7 @@
       <c r="K122" s="50"/>
       <c r="L122" s="50"/>
       <c r="M122" s="129">
-        <f t="shared" si="96"/>
+        <f t="shared" si="103"/>
         <v>0</v>
       </c>
       <c r="N122" s="39">
@@ -10691,11 +10815,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P122" s="73">
-        <f t="shared" si="97"/>
+        <f t="shared" si="104"/>
         <v>0</v>
       </c>
       <c r="Q122" s="40">
-        <f t="shared" si="98"/>
+        <f t="shared" si="105"/>
         <v>0</v>
       </c>
       <c r="R122" s="51" t="e">
@@ -10711,30 +10835,30 @@
         <v>0</v>
       </c>
       <c r="U122" s="53" t="e">
-        <f t="shared" si="99"/>
+        <f t="shared" si="106"/>
         <v>#VALUE!</v>
       </c>
       <c r="V122" s="54" t="e">
-        <f t="shared" si="100"/>
+        <f t="shared" si="107"/>
         <v>#VALUE!</v>
       </c>
       <c r="W122" s="55">
-        <f t="shared" si="101"/>
+        <f t="shared" si="108"/>
         <v>0</v>
       </c>
       <c r="X122" s="55">
-        <f t="shared" si="102"/>
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
       <c r="Y122" s="56" t="e">
-        <f t="shared" si="103"/>
+        <f t="shared" si="110"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="123" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A123" s="78"/>
       <c r="B123" s="47">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C123" s="128"/>
       <c r="D123" s="50"/>
@@ -10747,7 +10871,7 @@
       <c r="K123" s="50"/>
       <c r="L123" s="50"/>
       <c r="M123" s="129">
-        <f t="shared" si="96"/>
+        <f t="shared" si="103"/>
         <v>0</v>
       </c>
       <c r="N123" s="39">
@@ -10759,11 +10883,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P123" s="73">
-        <f t="shared" si="97"/>
+        <f t="shared" si="104"/>
         <v>0</v>
       </c>
       <c r="Q123" s="40">
-        <f t="shared" si="98"/>
+        <f t="shared" si="105"/>
         <v>0</v>
       </c>
       <c r="R123" s="51" t="e">
@@ -10779,30 +10903,30 @@
         <v>0</v>
       </c>
       <c r="U123" s="53" t="e">
-        <f t="shared" si="99"/>
+        <f t="shared" si="106"/>
         <v>#VALUE!</v>
       </c>
       <c r="V123" s="54" t="e">
-        <f t="shared" si="100"/>
+        <f t="shared" si="107"/>
         <v>#VALUE!</v>
       </c>
       <c r="W123" s="55">
-        <f t="shared" si="101"/>
+        <f t="shared" si="108"/>
         <v>0</v>
       </c>
       <c r="X123" s="55">
-        <f t="shared" si="102"/>
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
       <c r="Y123" s="56" t="e">
-        <f t="shared" si="103"/>
+        <f t="shared" si="110"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="124" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A124" s="78"/>
       <c r="B124" s="47">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C124" s="128"/>
       <c r="D124" s="50"/>
@@ -10815,7 +10939,7 @@
       <c r="K124" s="50"/>
       <c r="L124" s="50"/>
       <c r="M124" s="129">
-        <f t="shared" si="96"/>
+        <f t="shared" si="103"/>
         <v>0</v>
       </c>
       <c r="N124" s="39">
@@ -10827,11 +10951,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P124" s="73">
-        <f t="shared" si="97"/>
+        <f t="shared" si="104"/>
         <v>0</v>
       </c>
       <c r="Q124" s="40">
-        <f t="shared" si="98"/>
+        <f t="shared" si="105"/>
         <v>0</v>
       </c>
       <c r="R124" s="51" t="e">
@@ -10847,23 +10971,23 @@
         <v>0</v>
       </c>
       <c r="U124" s="53" t="e">
-        <f t="shared" si="99"/>
+        <f t="shared" si="106"/>
         <v>#VALUE!</v>
       </c>
       <c r="V124" s="54" t="e">
-        <f t="shared" si="100"/>
+        <f t="shared" si="107"/>
         <v>#VALUE!</v>
       </c>
       <c r="W124" s="55">
-        <f t="shared" si="101"/>
+        <f t="shared" si="108"/>
         <v>0</v>
       </c>
       <c r="X124" s="55">
-        <f t="shared" si="102"/>
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
       <c r="Y124" s="56" t="e">
-        <f t="shared" si="103"/>
+        <f t="shared" si="110"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -10881,7 +11005,7 @@
       <c r="K125" s="50"/>
       <c r="L125" s="50"/>
       <c r="M125" s="129">
-        <f t="shared" si="96"/>
+        <f t="shared" si="103"/>
         <v>0</v>
       </c>
       <c r="N125" s="39">
@@ -10893,11 +11017,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P125" s="73">
-        <f t="shared" si="97"/>
+        <f t="shared" si="104"/>
         <v>0</v>
       </c>
       <c r="Q125" s="40">
-        <f t="shared" si="98"/>
+        <f t="shared" si="105"/>
         <v>0</v>
       </c>
       <c r="R125" s="51" t="e">
@@ -10913,23 +11037,23 @@
         <v>0</v>
       </c>
       <c r="U125" s="53" t="e">
-        <f t="shared" si="99"/>
+        <f t="shared" si="106"/>
         <v>#VALUE!</v>
       </c>
       <c r="V125" s="54" t="e">
-        <f t="shared" si="100"/>
+        <f t="shared" si="107"/>
         <v>#VALUE!</v>
       </c>
       <c r="W125" s="55">
-        <f t="shared" si="101"/>
+        <f t="shared" si="108"/>
         <v>0</v>
       </c>
       <c r="X125" s="55">
-        <f t="shared" si="102"/>
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
       <c r="Y125" s="56" t="e">
-        <f t="shared" si="103"/>
+        <f t="shared" si="110"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -10947,7 +11071,7 @@
       <c r="K126" s="50"/>
       <c r="L126" s="50"/>
       <c r="M126" s="129">
-        <f t="shared" si="96"/>
+        <f t="shared" si="103"/>
         <v>0</v>
       </c>
       <c r="N126" s="39">
@@ -10959,11 +11083,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P126" s="73">
-        <f t="shared" si="97"/>
+        <f t="shared" si="104"/>
         <v>0</v>
       </c>
       <c r="Q126" s="40">
-        <f t="shared" si="98"/>
+        <f t="shared" si="105"/>
         <v>0</v>
       </c>
       <c r="R126" s="51" t="e">
@@ -10979,23 +11103,23 @@
         <v>0</v>
       </c>
       <c r="U126" s="53" t="e">
-        <f t="shared" si="99"/>
+        <f t="shared" si="106"/>
         <v>#VALUE!</v>
       </c>
       <c r="V126" s="54" t="e">
-        <f t="shared" si="100"/>
+        <f t="shared" si="107"/>
         <v>#VALUE!</v>
       </c>
       <c r="W126" s="55">
-        <f t="shared" si="101"/>
+        <f t="shared" si="108"/>
         <v>0</v>
       </c>
       <c r="X126" s="55">
-        <f t="shared" si="102"/>
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
       <c r="Y126" s="56" t="e">
-        <f t="shared" si="103"/>
+        <f t="shared" si="110"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -11013,7 +11137,7 @@
       <c r="K127" s="50"/>
       <c r="L127" s="50"/>
       <c r="M127" s="129">
-        <f t="shared" si="96"/>
+        <f t="shared" si="103"/>
         <v>0</v>
       </c>
       <c r="N127" s="39">
@@ -11025,11 +11149,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P127" s="73">
-        <f t="shared" si="97"/>
+        <f t="shared" si="104"/>
         <v>0</v>
       </c>
       <c r="Q127" s="40">
-        <f t="shared" si="98"/>
+        <f t="shared" si="105"/>
         <v>0</v>
       </c>
       <c r="R127" s="51" t="e">
@@ -11045,23 +11169,23 @@
         <v>0</v>
       </c>
       <c r="U127" s="53" t="e">
-        <f t="shared" si="99"/>
+        <f t="shared" si="106"/>
         <v>#VALUE!</v>
       </c>
       <c r="V127" s="54" t="e">
-        <f t="shared" si="100"/>
+        <f t="shared" si="107"/>
         <v>#VALUE!</v>
       </c>
       <c r="W127" s="55">
-        <f t="shared" si="101"/>
+        <f t="shared" si="108"/>
         <v>0</v>
       </c>
       <c r="X127" s="55">
-        <f t="shared" si="102"/>
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
       <c r="Y127" s="56" t="e">
-        <f t="shared" si="103"/>
+        <f t="shared" si="110"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -11079,7 +11203,7 @@
       <c r="K128" s="50"/>
       <c r="L128" s="50"/>
       <c r="M128" s="129">
-        <f t="shared" si="96"/>
+        <f t="shared" si="103"/>
         <v>0</v>
       </c>
       <c r="N128" s="39">
@@ -11091,11 +11215,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P128" s="73">
-        <f t="shared" si="97"/>
+        <f t="shared" si="104"/>
         <v>0</v>
       </c>
       <c r="Q128" s="40">
-        <f t="shared" si="98"/>
+        <f t="shared" si="105"/>
         <v>0</v>
       </c>
       <c r="R128" s="51" t="e">
@@ -11111,23 +11235,23 @@
         <v>0</v>
       </c>
       <c r="U128" s="53" t="e">
-        <f t="shared" si="99"/>
+        <f t="shared" si="106"/>
         <v>#VALUE!</v>
       </c>
       <c r="V128" s="54" t="e">
-        <f t="shared" si="100"/>
+        <f t="shared" si="107"/>
         <v>#VALUE!</v>
       </c>
       <c r="W128" s="55">
-        <f t="shared" si="101"/>
+        <f t="shared" si="108"/>
         <v>0</v>
       </c>
       <c r="X128" s="55">
-        <f t="shared" si="102"/>
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
       <c r="Y128" s="56" t="e">
-        <f t="shared" si="103"/>
+        <f t="shared" si="110"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -11145,7 +11269,7 @@
       <c r="K129" s="50"/>
       <c r="L129" s="50"/>
       <c r="M129" s="129">
-        <f t="shared" si="96"/>
+        <f t="shared" si="103"/>
         <v>0</v>
       </c>
       <c r="N129" s="39">
@@ -11157,11 +11281,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P129" s="73">
-        <f t="shared" si="97"/>
+        <f t="shared" si="104"/>
         <v>0</v>
       </c>
       <c r="Q129" s="40">
-        <f t="shared" si="98"/>
+        <f t="shared" si="105"/>
         <v>0</v>
       </c>
       <c r="R129" s="51" t="e">
@@ -11177,23 +11301,23 @@
         <v>0</v>
       </c>
       <c r="U129" s="53" t="e">
-        <f t="shared" si="99"/>
+        <f t="shared" si="106"/>
         <v>#VALUE!</v>
       </c>
       <c r="V129" s="54" t="e">
-        <f t="shared" si="100"/>
+        <f t="shared" si="107"/>
         <v>#VALUE!</v>
       </c>
       <c r="W129" s="55">
-        <f t="shared" si="101"/>
+        <f t="shared" si="108"/>
         <v>0</v>
       </c>
       <c r="X129" s="55">
-        <f t="shared" si="102"/>
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
       <c r="Y129" s="56" t="e">
-        <f t="shared" si="103"/>
+        <f t="shared" si="110"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -11211,7 +11335,7 @@
       <c r="K130" s="50"/>
       <c r="L130" s="50"/>
       <c r="M130" s="129">
-        <f t="shared" si="96"/>
+        <f t="shared" si="103"/>
         <v>0</v>
       </c>
       <c r="N130" s="39">
@@ -11223,11 +11347,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P130" s="73">
-        <f t="shared" si="97"/>
+        <f t="shared" si="104"/>
         <v>0</v>
       </c>
       <c r="Q130" s="40">
-        <f t="shared" si="98"/>
+        <f t="shared" si="105"/>
         <v>0</v>
       </c>
       <c r="R130" s="51" t="e">
@@ -11243,23 +11367,23 @@
         <v>0</v>
       </c>
       <c r="U130" s="53" t="e">
-        <f t="shared" si="99"/>
+        <f t="shared" si="106"/>
         <v>#VALUE!</v>
       </c>
       <c r="V130" s="54" t="e">
-        <f t="shared" si="100"/>
+        <f t="shared" si="107"/>
         <v>#VALUE!</v>
       </c>
       <c r="W130" s="55">
-        <f t="shared" si="101"/>
+        <f t="shared" si="108"/>
         <v>0</v>
       </c>
       <c r="X130" s="55">
-        <f t="shared" si="102"/>
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
       <c r="Y130" s="56" t="e">
-        <f t="shared" si="103"/>
+        <f t="shared" si="110"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -11277,7 +11401,7 @@
       <c r="K131" s="50"/>
       <c r="L131" s="50"/>
       <c r="M131" s="129">
-        <f t="shared" si="96"/>
+        <f t="shared" si="103"/>
         <v>0</v>
       </c>
       <c r="N131" s="39">
@@ -11289,11 +11413,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P131" s="73">
-        <f t="shared" si="97"/>
+        <f t="shared" si="104"/>
         <v>0</v>
       </c>
       <c r="Q131" s="40">
-        <f t="shared" si="98"/>
+        <f t="shared" si="105"/>
         <v>0</v>
       </c>
       <c r="R131" s="51" t="e">
@@ -11309,23 +11433,23 @@
         <v>0</v>
       </c>
       <c r="U131" s="53" t="e">
-        <f t="shared" si="99"/>
+        <f t="shared" si="106"/>
         <v>#VALUE!</v>
       </c>
       <c r="V131" s="54" t="e">
-        <f t="shared" si="100"/>
+        <f t="shared" si="107"/>
         <v>#VALUE!</v>
       </c>
       <c r="W131" s="55">
-        <f t="shared" si="101"/>
+        <f t="shared" si="108"/>
         <v>0</v>
       </c>
       <c r="X131" s="55">
-        <f t="shared" si="102"/>
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
       <c r="Y131" s="56" t="e">
-        <f t="shared" si="103"/>
+        <f t="shared" si="110"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -11343,7 +11467,7 @@
       <c r="K132" s="50"/>
       <c r="L132" s="50"/>
       <c r="M132" s="129">
-        <f t="shared" si="96"/>
+        <f t="shared" si="103"/>
         <v>0</v>
       </c>
       <c r="N132" s="39">
@@ -11355,11 +11479,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P132" s="73">
-        <f t="shared" si="97"/>
+        <f t="shared" si="104"/>
         <v>0</v>
       </c>
       <c r="Q132" s="40">
-        <f t="shared" si="98"/>
+        <f t="shared" si="105"/>
         <v>0</v>
       </c>
       <c r="R132" s="51" t="e">
@@ -11375,23 +11499,23 @@
         <v>0</v>
       </c>
       <c r="U132" s="53" t="e">
-        <f t="shared" si="99"/>
+        <f t="shared" si="106"/>
         <v>#VALUE!</v>
       </c>
       <c r="V132" s="54" t="e">
-        <f t="shared" si="100"/>
+        <f t="shared" si="107"/>
         <v>#VALUE!</v>
       </c>
       <c r="W132" s="55">
-        <f t="shared" si="101"/>
+        <f t="shared" si="108"/>
         <v>0</v>
       </c>
       <c r="X132" s="55">
-        <f t="shared" si="102"/>
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
       <c r="Y132" s="56" t="e">
-        <f t="shared" si="103"/>
+        <f t="shared" si="110"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -11402,44 +11526,44 @@
       </c>
       <c r="C133" s="158"/>
       <c r="D133" s="84">
-        <f t="shared" ref="D133:L133" si="104">SUM(D6:D61)</f>
-        <v>6083</v>
+        <f t="shared" ref="D133:L133" si="111">SUM(D6:D61)</f>
+        <v>6203</v>
       </c>
       <c r="E133" s="84">
-        <f t="shared" si="104"/>
+        <f t="shared" si="111"/>
         <v>0</v>
       </c>
       <c r="F133" s="84">
-        <f t="shared" si="104"/>
+        <f t="shared" si="111"/>
         <v>0</v>
       </c>
       <c r="G133" s="84">
-        <f t="shared" si="104"/>
-        <v>4462</v>
+        <f t="shared" si="111"/>
+        <v>4745</v>
       </c>
       <c r="H133" s="84">
-        <f t="shared" si="104"/>
-        <v>4607</v>
+        <f t="shared" si="111"/>
+        <v>4971</v>
       </c>
       <c r="I133" s="84">
-        <f t="shared" si="104"/>
-        <v>6799</v>
+        <f t="shared" si="111"/>
+        <v>7117</v>
       </c>
       <c r="J133" s="84">
-        <f t="shared" si="104"/>
-        <v>9181</v>
+        <f t="shared" si="111"/>
+        <v>9329</v>
       </c>
       <c r="K133" s="84">
-        <f t="shared" si="104"/>
-        <v>8417</v>
+        <f t="shared" si="111"/>
+        <v>8770</v>
       </c>
       <c r="L133" s="84">
-        <f t="shared" si="104"/>
-        <v>10999</v>
+        <f t="shared" si="111"/>
+        <v>11292</v>
       </c>
       <c r="M133" s="48">
-        <f t="shared" ref="M133:M136" si="105">SUM(D133:L133)/40</f>
-        <v>1263.7</v>
+        <f t="shared" ref="M133:M136" si="112">SUM(D133:L133)/40</f>
+        <v>1310.675</v>
       </c>
       <c r="N133" s="39">
         <f t="shared" si="18"/>
@@ -11450,12 +11574,12 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P133" s="73">
-        <f t="shared" ref="P133:P137" si="106">SUM(G133:I133)/20</f>
-        <v>793.4</v>
+        <f t="shared" ref="P133:P137" si="113">SUM(G133:I133)/20</f>
+        <v>841.65</v>
       </c>
       <c r="Q133" s="40">
-        <f t="shared" ref="Q133:Q137" si="107">SUM(J133:L133)/20</f>
-        <v>1429.85</v>
+        <f t="shared" ref="Q133:Q137" si="114">SUM(J133:L133)/20</f>
+        <v>1469.55</v>
       </c>
       <c r="R133" s="51" t="e">
         <f t="shared" si="4"/>
@@ -11474,15 +11598,15 @@
         <v>#VALUE!</v>
       </c>
       <c r="V133" s="54" t="e">
-        <f t="shared" ref="V133:V137" si="108">SUM(D133:F133)*$V$3</f>
+        <f t="shared" ref="V133:V137" si="115">SUM(D133:F133)*$V$3</f>
         <v>#VALUE!</v>
       </c>
       <c r="W133" s="55">
-        <f t="shared" ref="W133:W137" si="109">SUM(G133:I133)*$W$3</f>
+        <f t="shared" ref="W133:W137" si="116">SUM(G133:I133)*$W$3</f>
         <v>0</v>
       </c>
       <c r="X133" s="55">
-        <f t="shared" ref="X133:X137" si="110">SUM(J133:L133)*$X$3</f>
+        <f t="shared" ref="X133:X137" si="117">SUM(J133:L133)*$X$3</f>
         <v>0</v>
       </c>
       <c r="Y133" s="56" t="e">
@@ -11542,7 +11666,7 @@
       <c r="K135" s="75"/>
       <c r="L135" s="76"/>
       <c r="M135" s="48">
-        <f t="shared" si="105"/>
+        <f t="shared" si="112"/>
         <v>0</v>
       </c>
       <c r="N135" s="39">
@@ -11554,11 +11678,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P135" s="73">
-        <f t="shared" si="106"/>
+        <f t="shared" si="113"/>
         <v>0</v>
       </c>
       <c r="Q135" s="40">
-        <f t="shared" si="107"/>
+        <f t="shared" si="114"/>
         <v>0</v>
       </c>
       <c r="R135" s="51" t="e">
@@ -11578,15 +11702,15 @@
         <v>#VALUE!</v>
       </c>
       <c r="V135" s="54" t="e">
-        <f t="shared" si="108"/>
+        <f t="shared" si="115"/>
         <v>#VALUE!</v>
       </c>
       <c r="W135" s="55">
-        <f t="shared" si="109"/>
+        <f t="shared" si="116"/>
         <v>0</v>
       </c>
       <c r="X135" s="55">
-        <f t="shared" si="110"/>
+        <f t="shared" si="117"/>
         <v>0</v>
       </c>
       <c r="Y135" s="56" t="e">
@@ -11611,7 +11735,7 @@
       <c r="K136" s="75"/>
       <c r="L136" s="76"/>
       <c r="M136" s="48">
-        <f t="shared" si="105"/>
+        <f t="shared" si="112"/>
         <v>0</v>
       </c>
       <c r="N136" s="39">
@@ -11623,11 +11747,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P136" s="73">
-        <f t="shared" si="106"/>
+        <f t="shared" si="113"/>
         <v>0</v>
       </c>
       <c r="Q136" s="40">
-        <f t="shared" si="107"/>
+        <f t="shared" si="114"/>
         <v>0</v>
       </c>
       <c r="R136" s="51" t="e">
@@ -11647,15 +11771,15 @@
         <v>#VALUE!</v>
       </c>
       <c r="V136" s="54" t="e">
-        <f t="shared" si="108"/>
+        <f t="shared" si="115"/>
         <v>#VALUE!</v>
       </c>
       <c r="W136" s="55">
-        <f t="shared" si="109"/>
+        <f t="shared" si="116"/>
         <v>0</v>
       </c>
       <c r="X136" s="55">
-        <f t="shared" si="110"/>
+        <f t="shared" si="117"/>
         <v>0</v>
       </c>
       <c r="Y136" s="56" t="e">
@@ -11673,35 +11797,35 @@
         <v>0</v>
       </c>
       <c r="E137" s="83">
-        <f t="shared" ref="E137:L137" si="111">SUM(E135:E136)</f>
+        <f t="shared" ref="E137:L137" si="118">SUM(E135:E136)</f>
         <v>0</v>
       </c>
       <c r="F137" s="83">
-        <f t="shared" si="111"/>
+        <f t="shared" si="118"/>
         <v>0</v>
       </c>
       <c r="G137" s="83">
-        <f t="shared" si="111"/>
+        <f t="shared" si="118"/>
         <v>0</v>
       </c>
       <c r="H137" s="83">
-        <f t="shared" si="111"/>
+        <f t="shared" si="118"/>
         <v>0</v>
       </c>
       <c r="I137" s="83">
-        <f t="shared" si="111"/>
+        <f t="shared" si="118"/>
         <v>0</v>
       </c>
       <c r="J137" s="83">
-        <f t="shared" si="111"/>
+        <f t="shared" si="118"/>
         <v>0</v>
       </c>
       <c r="K137" s="83">
-        <f t="shared" si="111"/>
+        <f t="shared" si="118"/>
         <v>0</v>
       </c>
       <c r="L137" s="83">
-        <f t="shared" si="111"/>
+        <f t="shared" si="118"/>
         <v>0</v>
       </c>
       <c r="M137" s="112">
@@ -11717,11 +11841,11 @@
         <v>62.470500000000001</v>
       </c>
       <c r="P137" s="73">
-        <f t="shared" si="106"/>
+        <f t="shared" si="113"/>
         <v>0</v>
       </c>
       <c r="Q137" s="40">
-        <f t="shared" si="107"/>
+        <f t="shared" si="114"/>
         <v>0</v>
       </c>
       <c r="R137" s="51" t="e">
@@ -11741,15 +11865,15 @@
         <v>#VALUE!</v>
       </c>
       <c r="V137" s="54" t="e">
-        <f t="shared" si="108"/>
+        <f t="shared" si="115"/>
         <v>#VALUE!</v>
       </c>
       <c r="W137" s="55">
-        <f t="shared" si="109"/>
+        <f t="shared" si="116"/>
         <v>0</v>
       </c>
       <c r="X137" s="55">
-        <f t="shared" si="110"/>
+        <f t="shared" si="117"/>
         <v>0</v>
       </c>
       <c r="Y137" s="56" t="e">
@@ -11764,90 +11888,90 @@
       <c r="C138" s="160"/>
       <c r="D138" s="85">
         <f>SUM(D133,D137)</f>
-        <v>6083</v>
+        <v>6203</v>
       </c>
       <c r="E138" s="85">
-        <f t="shared" ref="E138:L138" si="112">SUM(E133,E137)</f>
+        <f t="shared" ref="E138:L138" si="119">SUM(E133,E137)</f>
         <v>0</v>
       </c>
       <c r="F138" s="85">
-        <f t="shared" si="112"/>
+        <f t="shared" si="119"/>
         <v>0</v>
       </c>
       <c r="G138" s="85">
-        <f t="shared" si="112"/>
-        <v>4462</v>
+        <f t="shared" si="119"/>
+        <v>4745</v>
       </c>
       <c r="H138" s="85">
-        <f t="shared" si="112"/>
-        <v>4607</v>
+        <f t="shared" si="119"/>
+        <v>4971</v>
       </c>
       <c r="I138" s="85">
-        <f t="shared" si="112"/>
-        <v>6799</v>
+        <f t="shared" si="119"/>
+        <v>7117</v>
       </c>
       <c r="J138" s="85">
-        <f t="shared" si="112"/>
-        <v>9181</v>
+        <f t="shared" si="119"/>
+        <v>9329</v>
       </c>
       <c r="K138" s="85">
-        <f t="shared" si="112"/>
-        <v>8417</v>
+        <f t="shared" si="119"/>
+        <v>8770</v>
       </c>
       <c r="L138" s="85">
-        <f t="shared" si="112"/>
-        <v>10999</v>
+        <f t="shared" si="119"/>
+        <v>11292</v>
       </c>
       <c r="M138" s="60">
         <f t="shared" si="0"/>
-        <v>1263.7</v>
+        <v>1310.675</v>
       </c>
       <c r="N138" s="63">
         <f>SUM(N5:N137)</f>
         <v>0</v>
       </c>
       <c r="O138" s="61">
-        <f t="shared" ref="O138:Y138" si="113">SUM(O5:O137)</f>
-        <v>8183.6355000000185</v>
+        <f t="shared" ref="O138:Y138" si="120">SUM(O5:O137)</f>
+        <v>8246.106000000018</v>
       </c>
       <c r="P138" s="62">
-        <f t="shared" si="113"/>
-        <v>1592.8</v>
+        <f t="shared" si="120"/>
+        <v>1689.3</v>
       </c>
       <c r="Q138" s="64">
-        <f t="shared" si="113"/>
-        <v>2863.7</v>
+        <f t="shared" si="120"/>
+        <v>2943.1</v>
       </c>
       <c r="R138" s="65" t="e">
-        <f t="shared" si="113"/>
+        <f t="shared" si="120"/>
         <v>#VALUE!</v>
       </c>
       <c r="S138" s="66">
-        <f t="shared" si="113"/>
+        <f t="shared" si="120"/>
         <v>0</v>
       </c>
       <c r="T138" s="66">
-        <f t="shared" si="113"/>
+        <f t="shared" si="120"/>
         <v>0</v>
       </c>
       <c r="U138" s="67" t="e">
-        <f t="shared" si="113"/>
+        <f t="shared" si="120"/>
         <v>#VALUE!</v>
       </c>
       <c r="V138" s="68" t="e">
-        <f t="shared" si="113"/>
+        <f t="shared" si="120"/>
         <v>#VALUE!</v>
       </c>
       <c r="W138" s="69">
-        <f t="shared" si="113"/>
+        <f t="shared" si="120"/>
         <v>0</v>
       </c>
       <c r="X138" s="69">
-        <f t="shared" si="113"/>
+        <f t="shared" si="120"/>
         <v>0</v>
       </c>
       <c r="Y138" s="70" t="e">
-        <f t="shared" si="113"/>
+        <f t="shared" si="120"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -11963,24 +12087,24 @@
         <v>49</v>
       </c>
       <c r="D5" s="88">
-        <v>392</v>
+        <v>472</v>
       </c>
       <c r="E5" s="79">
-        <v>724</v>
+        <v>771</v>
       </c>
       <c r="F5" s="79">
         <v>600</v>
       </c>
       <c r="G5" s="102">
         <f>SUM(D5:F5)</f>
-        <v>1716</v>
+        <v>1843</v>
       </c>
       <c r="H5" s="95">
         <v>10000</v>
       </c>
       <c r="I5" s="96">
         <f>G5-H5</f>
-        <v>-8284</v>
+        <v>-8157</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>1</v>
@@ -11988,10 +12112,12 @@
       <c r="L5" s="7">
         <v>70</v>
       </c>
-      <c r="M5" s="5"/>
+      <c r="M5" s="5">
+        <v>7924</v>
+      </c>
       <c r="N5" s="6">
         <f t="shared" ref="N5:N11" si="0">M5/40</f>
-        <v>0</v>
+        <v>198.1</v>
       </c>
       <c r="O5" s="81"/>
     </row>
@@ -12001,11 +12127,11 @@
       </c>
       <c r="D6" s="104">
         <f>D5*40</f>
-        <v>15680</v>
+        <v>18880</v>
       </c>
       <c r="E6" s="104">
         <f t="shared" ref="E6:F6" si="1">E5*40</f>
-        <v>28960</v>
+        <v>30840</v>
       </c>
       <c r="F6" s="104">
         <f t="shared" si="1"/>
@@ -12013,7 +12139,7 @@
       </c>
       <c r="G6" s="105">
         <f>SUM(D6:F6)</f>
-        <v>68640</v>
+        <v>73720</v>
       </c>
       <c r="H6" s="97">
         <f>H5*40</f>
@@ -12021,7 +12147,7 @@
       </c>
       <c r="I6" s="98">
         <f>G6-H6</f>
-        <v>-331360</v>
+        <v>-326280</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>2</v>
@@ -12029,10 +12155,12 @@
       <c r="L6" s="7">
         <v>70</v>
       </c>
-      <c r="M6" s="5"/>
+      <c r="M6" s="5">
+        <v>4534</v>
+      </c>
       <c r="N6" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>113.35</v>
       </c>
       <c r="O6" s="81"/>
       <c r="S6" s="124"/>
@@ -12061,10 +12189,12 @@
       <c r="L7" s="7">
         <v>70</v>
       </c>
-      <c r="M7" s="5"/>
+      <c r="M7" s="5">
+        <v>7446</v>
+      </c>
       <c r="N7" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>186.15</v>
       </c>
       <c r="O7" s="81"/>
       <c r="S7" s="136" t="s">
@@ -12102,10 +12232,12 @@
       <c r="L8" s="7">
         <v>120</v>
       </c>
-      <c r="M8" s="5"/>
+      <c r="M8" s="5">
+        <v>263</v>
+      </c>
       <c r="N8" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>6.5750000000000002</v>
       </c>
       <c r="O8" s="81"/>
       <c r="S8" s="79">
@@ -12138,11 +12270,11 @@
       </c>
       <c r="D9" s="106">
         <f>D8-D5</f>
-        <v>-392</v>
+        <v>-472</v>
       </c>
       <c r="E9" s="106">
         <f>E8-E5</f>
-        <v>-724</v>
+        <v>-771</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>5</v>
@@ -12150,10 +12282,12 @@
       <c r="L9" s="7">
         <v>120</v>
       </c>
-      <c r="M9" s="5"/>
+      <c r="M9" s="5">
+        <v>4655</v>
+      </c>
       <c r="N9" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>116.375</v>
       </c>
       <c r="O9" s="81"/>
       <c r="S9" s="79">
@@ -12189,10 +12323,12 @@
       <c r="L10" s="7">
         <v>120</v>
       </c>
-      <c r="M10" s="5"/>
+      <c r="M10" s="5">
+        <v>17</v>
+      </c>
       <c r="N10" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="O10" s="81"/>
       <c r="S10" s="79">
@@ -12232,10 +12368,12 @@
       <c r="L11" s="7">
         <v>60</v>
       </c>
-      <c r="M11" s="5"/>
+      <c r="M11" s="5">
+        <v>23361</v>
+      </c>
       <c r="N11" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>584.02499999999998</v>
       </c>
       <c r="O11" s="81"/>
       <c r="S11" s="79">
@@ -12270,7 +12408,7 @@
       </c>
       <c r="G12" s="91">
         <f>D12+G5</f>
-        <v>5916</v>
+        <v>6043</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>11</v>
@@ -12278,11 +12416,11 @@
       <c r="L12" s="2"/>
       <c r="M12" s="8">
         <f>SUM(M5:M11)</f>
-        <v>0</v>
+        <v>48200</v>
       </c>
       <c r="N12" s="9">
         <f>SUM(N5:N11)</f>
-        <v>0</v>
+        <v>1205</v>
       </c>
       <c r="O12" s="9">
         <f>SUM(O5:O11)</f>
@@ -12321,7 +12459,7 @@
       </c>
       <c r="G13" s="91">
         <f>G12*40</f>
-        <v>236640</v>
+        <v>241720</v>
       </c>
       <c r="S13" s="172" t="s">
         <v>85</v>
@@ -12380,7 +12518,7 @@
       <c r="N17" s="121"/>
       <c r="O17" s="122">
         <f>N17-M5</f>
-        <v>0</v>
+        <v>-7924</v>
       </c>
     </row>
     <row r="18" spans="4:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
@@ -12394,7 +12532,7 @@
       <c r="N18" s="5"/>
       <c r="O18" s="122">
         <f>N18-M6</f>
-        <v>0</v>
+        <v>-4534</v>
       </c>
     </row>
     <row r="19" spans="4:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
@@ -12411,7 +12549,7 @@
       <c r="N19" s="5"/>
       <c r="O19" s="122">
         <f t="shared" ref="O19:O23" si="4">N19-M7</f>
-        <v>0</v>
+        <v>-7446</v>
       </c>
     </row>
     <row r="20" spans="4:15" ht="24" thickBot="1" x14ac:dyDescent="0.6">
@@ -12432,7 +12570,7 @@
       <c r="N20" s="5"/>
       <c r="O20" s="122">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-263</v>
       </c>
     </row>
     <row r="21" spans="4:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
@@ -12461,7 +12599,7 @@
       <c r="N21" s="5"/>
       <c r="O21" s="122">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-4655</v>
       </c>
     </row>
     <row r="22" spans="4:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
@@ -12487,7 +12625,7 @@
       <c r="N22" s="5"/>
       <c r="O22" s="122">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-17</v>
       </c>
     </row>
     <row r="23" spans="4:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
@@ -12513,7 +12651,7 @@
       <c r="N23" s="5"/>
       <c r="O23" s="122">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-23361</v>
       </c>
     </row>
     <row r="24" spans="4:15" ht="24" thickBot="1" x14ac:dyDescent="0.6">
@@ -12543,7 +12681,7 @@
       </c>
       <c r="O24" s="117">
         <f>SUM(O17:O23)</f>
-        <v>0</v>
+        <v>-48200</v>
       </c>
     </row>
     <row r="25" spans="4:15" ht="24" thickBot="1" x14ac:dyDescent="0.6">
@@ -12573,7 +12711,7 @@
       </c>
       <c r="O25" s="117">
         <f>O24/40</f>
-        <v>0</v>
+        <v>-1205</v>
       </c>
     </row>
     <row r="26" spans="4:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">

--- a/Aug_2026/daily Reports/LMT Orders.xlsx
+++ b/Aug_2026/daily Reports/LMT Orders.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26F9212D-A787-43EB-93A4-8837CB21D008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D460CD9-C054-4D43-87CB-0C232DD75B82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="126">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -386,6 +386,21 @@
   <si>
     <t xml:space="preserve">4 Season </t>
   </si>
+  <si>
+    <t xml:space="preserve">Raja Saab Wapda Town </t>
+  </si>
+  <si>
+    <t>Jalal sons  Main Market</t>
+  </si>
+  <si>
+    <t>Crown Market Singh pura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mb/SB Traders  Shadbagh </t>
+  </si>
+  <si>
+    <t>Sweera GT Road</t>
+  </si>
 </sst>
 </file>
 
@@ -1273,7 +1288,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="189">
+  <cellXfs count="181">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1748,20 +1763,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2300,7 +2301,7 @@
     <row r="1" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B1" s="147">
         <f ca="1">TODAY()</f>
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="C1" s="147"/>
       <c r="D1" s="147"/>
@@ -4498,36 +4499,36 @@
       </c>
     </row>
     <row r="29" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A29" s="181">
+      <c r="A29" s="78">
         <v>46246</v>
       </c>
-      <c r="B29" s="182">
+      <c r="B29" s="47">
         <v>25</v>
       </c>
-      <c r="C29" s="183" t="s">
+      <c r="C29" s="57" t="s">
         <v>53</v>
       </c>
-      <c r="D29" s="184">
+      <c r="D29" s="74">
         <v>40</v>
       </c>
-      <c r="E29" s="185"/>
-      <c r="F29" s="186"/>
-      <c r="G29" s="187">
+      <c r="E29" s="75"/>
+      <c r="F29" s="76"/>
+      <c r="G29" s="50">
         <v>40</v>
       </c>
-      <c r="H29" s="185">
+      <c r="H29" s="75">
         <v>40</v>
       </c>
-      <c r="I29" s="188">
+      <c r="I29" s="49">
         <v>40</v>
       </c>
-      <c r="J29" s="187">
+      <c r="J29" s="50">
         <v>20</v>
       </c>
-      <c r="K29" s="185">
+      <c r="K29" s="75">
         <v>20</v>
       </c>
-      <c r="L29" s="186">
+      <c r="L29" s="76">
         <v>20</v>
       </c>
       <c r="M29" s="48">
@@ -4584,34 +4585,34 @@
       </c>
     </row>
     <row r="30" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A30" s="181">
+      <c r="A30" s="78">
         <v>46246</v>
       </c>
-      <c r="B30" s="182">
+      <c r="B30" s="47">
         <v>26</v>
       </c>
-      <c r="C30" s="183" t="s">
+      <c r="C30" s="57" t="s">
         <v>111</v>
       </c>
-      <c r="D30" s="184"/>
-      <c r="E30" s="185"/>
-      <c r="F30" s="186"/>
-      <c r="G30" s="187">
+      <c r="D30" s="74"/>
+      <c r="E30" s="75"/>
+      <c r="F30" s="76"/>
+      <c r="G30" s="50">
         <v>200</v>
       </c>
-      <c r="H30" s="185">
+      <c r="H30" s="75">
         <v>200</v>
       </c>
-      <c r="I30" s="188">
+      <c r="I30" s="49">
         <v>200</v>
       </c>
-      <c r="J30" s="187">
+      <c r="J30" s="50">
         <v>200</v>
       </c>
-      <c r="K30" s="185">
+      <c r="K30" s="75">
         <v>200</v>
       </c>
-      <c r="L30" s="186">
+      <c r="L30" s="76">
         <v>200</v>
       </c>
       <c r="M30" s="48">
@@ -4668,34 +4669,34 @@
       </c>
     </row>
     <row r="31" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A31" s="181">
+      <c r="A31" s="78">
         <v>46246</v>
       </c>
-      <c r="B31" s="182">
+      <c r="B31" s="47">
         <v>27</v>
       </c>
-      <c r="C31" s="183" t="s">
+      <c r="C31" s="57" t="s">
         <v>112</v>
       </c>
-      <c r="D31" s="184"/>
-      <c r="E31" s="185"/>
-      <c r="F31" s="186"/>
-      <c r="G31" s="187">
+      <c r="D31" s="74"/>
+      <c r="E31" s="75"/>
+      <c r="F31" s="76"/>
+      <c r="G31" s="50">
         <v>40</v>
       </c>
-      <c r="H31" s="185">
+      <c r="H31" s="75">
         <v>40</v>
       </c>
-      <c r="I31" s="188">
+      <c r="I31" s="49">
         <v>40</v>
       </c>
-      <c r="J31" s="187">
+      <c r="J31" s="50">
         <v>40</v>
       </c>
-      <c r="K31" s="185">
+      <c r="K31" s="75">
         <v>40</v>
       </c>
-      <c r="L31" s="186">
+      <c r="L31" s="76">
         <v>40</v>
       </c>
       <c r="M31" s="48">
@@ -4752,30 +4753,30 @@
       </c>
     </row>
     <row r="32" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A32" s="181">
+      <c r="A32" s="78">
         <v>46246</v>
       </c>
       <c r="B32" s="47">
         <v>28</v>
       </c>
-      <c r="C32" s="183" t="s">
+      <c r="C32" s="57" t="s">
         <v>91</v>
       </c>
-      <c r="D32" s="184"/>
-      <c r="E32" s="185"/>
-      <c r="F32" s="186"/>
-      <c r="G32" s="187">
+      <c r="D32" s="74"/>
+      <c r="E32" s="75"/>
+      <c r="F32" s="76"/>
+      <c r="G32" s="50">
         <v>200</v>
       </c>
-      <c r="H32" s="185"/>
-      <c r="I32" s="188">
+      <c r="H32" s="75"/>
+      <c r="I32" s="49">
         <v>160</v>
       </c>
-      <c r="J32" s="187">
+      <c r="J32" s="50">
         <v>120</v>
       </c>
-      <c r="K32" s="185"/>
-      <c r="L32" s="186">
+      <c r="K32" s="75"/>
+      <c r="L32" s="76">
         <v>160</v>
       </c>
       <c r="M32" s="48">
@@ -4832,34 +4833,34 @@
       </c>
     </row>
     <row r="33" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A33" s="181">
+      <c r="A33" s="78">
         <v>46246</v>
       </c>
       <c r="B33" s="47">
         <v>29</v>
       </c>
-      <c r="C33" s="183" t="s">
+      <c r="C33" s="57" t="s">
         <v>103</v>
       </c>
-      <c r="D33" s="184"/>
-      <c r="E33" s="185"/>
-      <c r="F33" s="186"/>
-      <c r="G33" s="187">
+      <c r="D33" s="74"/>
+      <c r="E33" s="75"/>
+      <c r="F33" s="76"/>
+      <c r="G33" s="50">
         <v>120</v>
       </c>
-      <c r="H33" s="185">
+      <c r="H33" s="75">
         <v>80</v>
       </c>
-      <c r="I33" s="188">
+      <c r="I33" s="49">
         <v>40</v>
       </c>
-      <c r="J33" s="187">
+      <c r="J33" s="50">
         <v>140</v>
       </c>
-      <c r="K33" s="185">
+      <c r="K33" s="75">
         <v>120</v>
       </c>
-      <c r="L33" s="186">
+      <c r="L33" s="76">
         <v>180</v>
       </c>
       <c r="M33" s="48">
@@ -4916,36 +4917,36 @@
       </c>
     </row>
     <row r="34" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A34" s="181">
+      <c r="A34" s="78">
         <v>46246</v>
       </c>
       <c r="B34" s="47">
         <v>30</v>
       </c>
-      <c r="C34" s="183" t="s">
+      <c r="C34" s="57" t="s">
         <v>33</v>
       </c>
-      <c r="D34" s="184">
+      <c r="D34" s="74">
         <v>4000</v>
       </c>
-      <c r="E34" s="185"/>
-      <c r="F34" s="186"/>
-      <c r="G34" s="187">
+      <c r="E34" s="75"/>
+      <c r="F34" s="76"/>
+      <c r="G34" s="50">
         <v>1600</v>
       </c>
-      <c r="H34" s="185">
+      <c r="H34" s="75">
         <v>1600</v>
       </c>
-      <c r="I34" s="188">
+      <c r="I34" s="49">
         <v>800</v>
       </c>
-      <c r="J34" s="187">
+      <c r="J34" s="50">
         <v>4000</v>
       </c>
-      <c r="K34" s="185">
+      <c r="K34" s="75">
         <v>3200</v>
       </c>
-      <c r="L34" s="186">
+      <c r="L34" s="76">
         <v>2800</v>
       </c>
       <c r="M34" s="48">
@@ -5002,28 +5003,28 @@
       </c>
     </row>
     <row r="35" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A35" s="181">
+      <c r="A35" s="78">
         <v>46246</v>
       </c>
       <c r="B35" s="47">
         <v>31</v>
       </c>
-      <c r="C35" s="183" t="s">
+      <c r="C35" s="57" t="s">
         <v>116</v>
       </c>
-      <c r="D35" s="184"/>
-      <c r="E35" s="185"/>
-      <c r="F35" s="186"/>
-      <c r="G35" s="187"/>
-      <c r="H35" s="185"/>
-      <c r="I35" s="188"/>
-      <c r="J35" s="187">
+      <c r="D35" s="74"/>
+      <c r="E35" s="75"/>
+      <c r="F35" s="76"/>
+      <c r="G35" s="50"/>
+      <c r="H35" s="75"/>
+      <c r="I35" s="49"/>
+      <c r="J35" s="50">
         <v>880</v>
       </c>
-      <c r="K35" s="185">
+      <c r="K35" s="75">
         <v>640</v>
       </c>
-      <c r="L35" s="186">
+      <c r="L35" s="76">
         <v>880</v>
       </c>
       <c r="M35" s="48">
@@ -5080,30 +5081,30 @@
       </c>
     </row>
     <row r="36" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A36" s="181">
+      <c r="A36" s="78">
         <v>46247</v>
       </c>
       <c r="B36" s="47">
         <v>32</v>
       </c>
-      <c r="C36" s="183" t="s">
+      <c r="C36" s="57" t="s">
         <v>113</v>
       </c>
-      <c r="D36" s="184"/>
-      <c r="E36" s="185"/>
-      <c r="F36" s="186"/>
-      <c r="G36" s="187"/>
-      <c r="H36" s="185"/>
-      <c r="I36" s="188">
+      <c r="D36" s="74"/>
+      <c r="E36" s="75"/>
+      <c r="F36" s="76"/>
+      <c r="G36" s="50"/>
+      <c r="H36" s="75"/>
+      <c r="I36" s="49">
         <v>200</v>
       </c>
-      <c r="J36" s="187">
+      <c r="J36" s="50">
         <v>40</v>
       </c>
-      <c r="K36" s="185">
+      <c r="K36" s="75">
         <v>40</v>
       </c>
-      <c r="L36" s="186">
+      <c r="L36" s="76">
         <v>120</v>
       </c>
       <c r="M36" s="48">
@@ -5333,7 +5334,7 @@
       <c r="A39" s="140">
         <v>46249</v>
       </c>
-      <c r="B39" s="182">
+      <c r="B39" s="47">
         <v>35</v>
       </c>
       <c r="C39" s="142" t="s">
@@ -5419,7 +5420,7 @@
       <c r="A40" s="140">
         <v>46249</v>
       </c>
-      <c r="B40" s="182">
+      <c r="B40" s="47">
         <v>36</v>
       </c>
       <c r="C40" s="142" t="s">
@@ -5505,7 +5506,7 @@
       <c r="A41" s="140">
         <v>46249</v>
       </c>
-      <c r="B41" s="182">
+      <c r="B41" s="47">
         <v>37</v>
       </c>
       <c r="C41" s="142" t="s">
@@ -5668,23 +5669,33 @@
       </c>
     </row>
     <row r="43" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A43" s="78"/>
-      <c r="B43" s="47">
+      <c r="A43" s="140">
+        <v>46252</v>
+      </c>
+      <c r="B43" s="141">
         <v>39</v>
       </c>
-      <c r="C43" s="57"/>
-      <c r="D43" s="74"/>
-      <c r="E43" s="75"/>
-      <c r="F43" s="76"/>
-      <c r="G43" s="50"/>
-      <c r="H43" s="75"/>
-      <c r="I43" s="49"/>
-      <c r="J43" s="50"/>
-      <c r="K43" s="75"/>
-      <c r="L43" s="76"/>
+      <c r="C43" s="142" t="s">
+        <v>123</v>
+      </c>
+      <c r="D43" s="143"/>
+      <c r="E43" s="144"/>
+      <c r="F43" s="145"/>
+      <c r="G43" s="146"/>
+      <c r="H43" s="144"/>
+      <c r="I43" s="56">
+        <v>80</v>
+      </c>
+      <c r="J43" s="146"/>
+      <c r="K43" s="144">
+        <v>39</v>
+      </c>
+      <c r="L43" s="145">
+        <v>80</v>
+      </c>
       <c r="M43" s="48">
         <f t="shared" si="68"/>
-        <v>0</v>
+        <v>4.9749999999999996</v>
       </c>
       <c r="N43" s="39">
         <f t="shared" si="18"/>
@@ -5696,11 +5707,11 @@
       </c>
       <c r="P43" s="73">
         <f t="shared" si="69"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q43" s="40">
         <f t="shared" si="70"/>
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="R43" s="51" t="e">
         <f t="shared" si="4"/>
@@ -5736,23 +5747,37 @@
       </c>
     </row>
     <row r="44" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A44" s="78"/>
-      <c r="B44" s="47">
+      <c r="A44" s="140">
+        <v>46252</v>
+      </c>
+      <c r="B44" s="141">
         <v>40</v>
       </c>
-      <c r="C44" s="57"/>
-      <c r="D44" s="74"/>
-      <c r="E44" s="75"/>
-      <c r="F44" s="76"/>
-      <c r="G44" s="50"/>
-      <c r="H44" s="75"/>
-      <c r="I44" s="49"/>
-      <c r="J44" s="50"/>
-      <c r="K44" s="75"/>
-      <c r="L44" s="76"/>
+      <c r="C44" s="142" t="s">
+        <v>122</v>
+      </c>
+      <c r="D44" s="143"/>
+      <c r="E44" s="144"/>
+      <c r="F44" s="145"/>
+      <c r="G44" s="146"/>
+      <c r="H44" s="144">
+        <v>48</v>
+      </c>
+      <c r="I44" s="56">
+        <v>80</v>
+      </c>
+      <c r="J44" s="146">
+        <v>80</v>
+      </c>
+      <c r="K44" s="144">
+        <v>80</v>
+      </c>
+      <c r="L44" s="145">
+        <v>120</v>
+      </c>
       <c r="M44" s="48">
         <f t="shared" si="68"/>
-        <v>0</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="N44" s="39">
         <f t="shared" si="18"/>
@@ -5764,11 +5789,11 @@
       </c>
       <c r="P44" s="73">
         <f t="shared" si="69"/>
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="Q44" s="40">
         <f t="shared" si="70"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="R44" s="51" t="e">
         <f t="shared" si="4"/>
@@ -5804,23 +5829,35 @@
       </c>
     </row>
     <row r="45" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A45" s="78"/>
-      <c r="B45" s="47">
+      <c r="A45" s="140">
+        <v>46252</v>
+      </c>
+      <c r="B45" s="141">
         <v>41</v>
       </c>
-      <c r="C45" s="57"/>
-      <c r="D45" s="74"/>
-      <c r="E45" s="75"/>
-      <c r="F45" s="76"/>
-      <c r="G45" s="50"/>
-      <c r="H45" s="75"/>
-      <c r="I45" s="49"/>
-      <c r="J45" s="50"/>
-      <c r="K45" s="75"/>
-      <c r="L45" s="76"/>
+      <c r="C45" s="142" t="s">
+        <v>121</v>
+      </c>
+      <c r="D45" s="143"/>
+      <c r="E45" s="144"/>
+      <c r="F45" s="145"/>
+      <c r="G45" s="146"/>
+      <c r="H45" s="144"/>
+      <c r="I45" s="56">
+        <v>200</v>
+      </c>
+      <c r="J45" s="146">
+        <v>120</v>
+      </c>
+      <c r="K45" s="144">
+        <v>200</v>
+      </c>
+      <c r="L45" s="145">
+        <v>80</v>
+      </c>
       <c r="M45" s="48">
         <f t="shared" si="68"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="N45" s="39">
         <f t="shared" si="18"/>
@@ -5832,11 +5869,11 @@
       </c>
       <c r="P45" s="73">
         <f t="shared" si="69"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q45" s="40">
         <f t="shared" si="70"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="R45" s="51" t="e">
         <f t="shared" si="4"/>
@@ -5872,23 +5909,39 @@
       </c>
     </row>
     <row r="46" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A46" s="78"/>
-      <c r="B46" s="47">
+      <c r="A46" s="140">
+        <v>46252</v>
+      </c>
+      <c r="B46" s="141">
         <v>42</v>
       </c>
-      <c r="C46" s="57"/>
-      <c r="D46" s="74"/>
-      <c r="E46" s="75"/>
-      <c r="F46" s="76"/>
-      <c r="G46" s="50"/>
-      <c r="H46" s="75"/>
-      <c r="I46" s="49"/>
-      <c r="J46" s="50"/>
-      <c r="K46" s="75"/>
-      <c r="L46" s="76"/>
+      <c r="C46" s="142" t="s">
+        <v>124</v>
+      </c>
+      <c r="D46" s="143"/>
+      <c r="E46" s="144"/>
+      <c r="F46" s="145"/>
+      <c r="G46" s="146">
+        <v>80</v>
+      </c>
+      <c r="H46" s="144">
+        <v>40</v>
+      </c>
+      <c r="I46" s="56">
+        <v>120</v>
+      </c>
+      <c r="J46" s="146">
+        <v>40</v>
+      </c>
+      <c r="K46" s="144">
+        <v>80</v>
+      </c>
+      <c r="L46" s="145">
+        <v>120</v>
+      </c>
       <c r="M46" s="48">
         <f t="shared" si="68"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N46" s="39">
         <f t="shared" si="18"/>
@@ -5900,11 +5953,11 @@
       </c>
       <c r="P46" s="73">
         <f t="shared" si="69"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q46" s="40">
         <f t="shared" si="70"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="R46" s="51" t="e">
         <f t="shared" si="4"/>
@@ -5940,23 +5993,39 @@
       </c>
     </row>
     <row r="47" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A47" s="78"/>
-      <c r="B47" s="47">
+      <c r="A47" s="140">
+        <v>46252</v>
+      </c>
+      <c r="B47" s="141">
         <v>43</v>
       </c>
-      <c r="C47" s="57"/>
-      <c r="D47" s="74"/>
-      <c r="E47" s="75"/>
-      <c r="F47" s="76"/>
-      <c r="G47" s="50"/>
-      <c r="H47" s="75"/>
-      <c r="I47" s="49"/>
-      <c r="J47" s="50"/>
-      <c r="K47" s="75"/>
-      <c r="L47" s="76"/>
+      <c r="C47" s="142" t="s">
+        <v>125</v>
+      </c>
+      <c r="D47" s="143"/>
+      <c r="E47" s="144"/>
+      <c r="F47" s="145"/>
+      <c r="G47" s="146">
+        <v>200</v>
+      </c>
+      <c r="H47" s="144">
+        <v>200</v>
+      </c>
+      <c r="I47" s="56">
+        <v>200</v>
+      </c>
+      <c r="J47" s="146">
+        <v>200</v>
+      </c>
+      <c r="K47" s="144">
+        <v>200</v>
+      </c>
+      <c r="L47" s="145">
+        <v>200</v>
+      </c>
       <c r="M47" s="48">
         <f t="shared" si="68"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="N47" s="39">
         <f t="shared" si="18"/>
@@ -5968,11 +6037,11 @@
       </c>
       <c r="P47" s="73">
         <f t="shared" si="69"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="Q47" s="40">
         <f t="shared" si="70"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="R47" s="51"/>
       <c r="S47" s="52"/>
@@ -6041,7 +6110,7 @@
     </row>
     <row r="49" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A49" s="78"/>
-      <c r="B49" s="182">
+      <c r="B49" s="47">
         <v>45</v>
       </c>
       <c r="C49" s="57"/>
@@ -6091,7 +6160,7 @@
     </row>
     <row r="50" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A50" s="78"/>
-      <c r="B50" s="182">
+      <c r="B50" s="47">
         <v>46</v>
       </c>
       <c r="C50" s="57"/>
@@ -6141,7 +6210,7 @@
     </row>
     <row r="51" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A51" s="78"/>
-      <c r="B51" s="182">
+      <c r="B51" s="47">
         <v>47</v>
       </c>
       <c r="C51" s="57"/>
@@ -6541,7 +6610,7 @@
     </row>
     <row r="59" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A59" s="78"/>
-      <c r="B59" s="182">
+      <c r="B59" s="47">
         <v>55</v>
       </c>
       <c r="C59" s="57"/>
@@ -6591,7 +6660,7 @@
     </row>
     <row r="60" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A60" s="78"/>
-      <c r="B60" s="182">
+      <c r="B60" s="47">
         <v>56</v>
       </c>
       <c r="C60" s="57"/>
@@ -6641,7 +6710,7 @@
     </row>
     <row r="61" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A61" s="78"/>
-      <c r="B61" s="182">
+      <c r="B61" s="47">
         <v>57</v>
       </c>
       <c r="C61" s="57"/>
@@ -7185,7 +7254,7 @@
     </row>
     <row r="69" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A69" s="78"/>
-      <c r="B69" s="182">
+      <c r="B69" s="47">
         <v>65</v>
       </c>
       <c r="C69" s="128"/>
@@ -7253,7 +7322,7 @@
     </row>
     <row r="70" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A70" s="78"/>
-      <c r="B70" s="182">
+      <c r="B70" s="47">
         <v>66</v>
       </c>
       <c r="C70" s="128"/>
@@ -7321,7 +7390,7 @@
     </row>
     <row r="71" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A71" s="78"/>
-      <c r="B71" s="182">
+      <c r="B71" s="47">
         <v>67</v>
       </c>
       <c r="C71" s="128"/>
@@ -7865,7 +7934,7 @@
     </row>
     <row r="79" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A79" s="78"/>
-      <c r="B79" s="182">
+      <c r="B79" s="47">
         <v>75</v>
       </c>
       <c r="C79" s="139"/>
@@ -7933,7 +8002,7 @@
     </row>
     <row r="80" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A80" s="78"/>
-      <c r="B80" s="182">
+      <c r="B80" s="47">
         <v>76</v>
       </c>
       <c r="C80" s="128"/>
@@ -8001,7 +8070,7 @@
     </row>
     <row r="81" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A81" s="78"/>
-      <c r="B81" s="182">
+      <c r="B81" s="47">
         <v>77</v>
       </c>
       <c r="C81" s="128"/>
@@ -8545,7 +8614,7 @@
     </row>
     <row r="89" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A89" s="78"/>
-      <c r="B89" s="182">
+      <c r="B89" s="47">
         <v>85</v>
       </c>
       <c r="C89" s="128"/>
@@ -8613,7 +8682,7 @@
     </row>
     <row r="90" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A90" s="78"/>
-      <c r="B90" s="182">
+      <c r="B90" s="47">
         <v>86</v>
       </c>
       <c r="C90" s="128"/>
@@ -8681,7 +8750,7 @@
     </row>
     <row r="91" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A91" s="78"/>
-      <c r="B91" s="182">
+      <c r="B91" s="47">
         <v>87</v>
       </c>
       <c r="C91" s="128"/>
@@ -9225,7 +9294,7 @@
     </row>
     <row r="99" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A99" s="78"/>
-      <c r="B99" s="182">
+      <c r="B99" s="47">
         <v>95</v>
       </c>
       <c r="C99" s="128"/>
@@ -9293,7 +9362,7 @@
     </row>
     <row r="100" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A100" s="78"/>
-      <c r="B100" s="182">
+      <c r="B100" s="47">
         <v>96</v>
       </c>
       <c r="C100" s="128"/>
@@ -9361,7 +9430,7 @@
     </row>
     <row r="101" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A101" s="78"/>
-      <c r="B101" s="182">
+      <c r="B101" s="47">
         <v>97</v>
       </c>
       <c r="C101" s="128"/>
@@ -9905,7 +9974,7 @@
     </row>
     <row r="109" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A109" s="78"/>
-      <c r="B109" s="182">
+      <c r="B109" s="47">
         <v>105</v>
       </c>
       <c r="C109" s="128"/>
@@ -9973,7 +10042,7 @@
     </row>
     <row r="110" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A110" s="78"/>
-      <c r="B110" s="182">
+      <c r="B110" s="47">
         <v>106</v>
       </c>
       <c r="C110" s="128"/>
@@ -10041,7 +10110,7 @@
     </row>
     <row r="111" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A111" s="78"/>
-      <c r="B111" s="182">
+      <c r="B111" s="47">
         <v>107</v>
       </c>
       <c r="C111" s="128"/>
@@ -10585,7 +10654,7 @@
     </row>
     <row r="119" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A119" s="78"/>
-      <c r="B119" s="182">
+      <c r="B119" s="47">
         <v>115</v>
       </c>
       <c r="C119" s="128"/>
@@ -10653,7 +10722,7 @@
     </row>
     <row r="120" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A120" s="78"/>
-      <c r="B120" s="182">
+      <c r="B120" s="47">
         <v>116</v>
       </c>
       <c r="C120" s="128"/>
@@ -10721,7 +10790,7 @@
     </row>
     <row r="121" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A121" s="78"/>
-      <c r="B121" s="182">
+      <c r="B121" s="47">
         <v>117</v>
       </c>
       <c r="C121" s="128"/>
@@ -11539,31 +11608,31 @@
       </c>
       <c r="G133" s="84">
         <f t="shared" si="111"/>
-        <v>4745</v>
+        <v>5025</v>
       </c>
       <c r="H133" s="84">
         <f t="shared" si="111"/>
-        <v>4971</v>
+        <v>5259</v>
       </c>
       <c r="I133" s="84">
         <f t="shared" si="111"/>
-        <v>7117</v>
+        <v>7797</v>
       </c>
       <c r="J133" s="84">
         <f t="shared" si="111"/>
-        <v>9329</v>
+        <v>9769</v>
       </c>
       <c r="K133" s="84">
         <f t="shared" si="111"/>
-        <v>8770</v>
+        <v>9369</v>
       </c>
       <c r="L133" s="84">
         <f t="shared" si="111"/>
-        <v>11292</v>
+        <v>11892</v>
       </c>
       <c r="M133" s="48">
         <f t="shared" ref="M133:M136" si="112">SUM(D133:L133)/40</f>
-        <v>1310.675</v>
+        <v>1382.85</v>
       </c>
       <c r="N133" s="39">
         <f t="shared" si="18"/>
@@ -11575,11 +11644,11 @@
       </c>
       <c r="P133" s="73">
         <f t="shared" ref="P133:P137" si="113">SUM(G133:I133)/20</f>
-        <v>841.65</v>
+        <v>904.05</v>
       </c>
       <c r="Q133" s="40">
         <f t="shared" ref="Q133:Q137" si="114">SUM(J133:L133)/20</f>
-        <v>1469.55</v>
+        <v>1551.5</v>
       </c>
       <c r="R133" s="51" t="e">
         <f t="shared" si="4"/>
@@ -11900,31 +11969,31 @@
       </c>
       <c r="G138" s="85">
         <f t="shared" si="119"/>
-        <v>4745</v>
+        <v>5025</v>
       </c>
       <c r="H138" s="85">
         <f t="shared" si="119"/>
-        <v>4971</v>
+        <v>5259</v>
       </c>
       <c r="I138" s="85">
         <f t="shared" si="119"/>
-        <v>7117</v>
+        <v>7797</v>
       </c>
       <c r="J138" s="85">
         <f t="shared" si="119"/>
-        <v>9329</v>
+        <v>9769</v>
       </c>
       <c r="K138" s="85">
         <f t="shared" si="119"/>
-        <v>8770</v>
+        <v>9369</v>
       </c>
       <c r="L138" s="85">
         <f t="shared" si="119"/>
-        <v>11292</v>
+        <v>11892</v>
       </c>
       <c r="M138" s="60">
         <f t="shared" si="0"/>
-        <v>1310.675</v>
+        <v>1382.85</v>
       </c>
       <c r="N138" s="63">
         <f>SUM(N5:N137)</f>
@@ -11936,11 +12005,11 @@
       </c>
       <c r="P138" s="62">
         <f t="shared" si="120"/>
-        <v>1689.3</v>
+        <v>1814.1</v>
       </c>
       <c r="Q138" s="64">
         <f t="shared" si="120"/>
-        <v>2943.1</v>
+        <v>3107</v>
       </c>
       <c r="R138" s="65" t="e">
         <f t="shared" si="120"/>
@@ -12087,24 +12156,24 @@
         <v>49</v>
       </c>
       <c r="D5" s="88">
-        <v>472</v>
+        <v>505</v>
       </c>
       <c r="E5" s="79">
-        <v>771</v>
+        <v>844</v>
       </c>
       <c r="F5" s="79">
         <v>600</v>
       </c>
       <c r="G5" s="102">
         <f>SUM(D5:F5)</f>
-        <v>1843</v>
+        <v>1949</v>
       </c>
       <c r="H5" s="95">
         <v>10000</v>
       </c>
       <c r="I5" s="96">
         <f>G5-H5</f>
-        <v>-8157</v>
+        <v>-8051</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>1</v>
@@ -12127,11 +12196,11 @@
       </c>
       <c r="D6" s="104">
         <f>D5*40</f>
-        <v>18880</v>
+        <v>20200</v>
       </c>
       <c r="E6" s="104">
         <f t="shared" ref="E6:F6" si="1">E5*40</f>
-        <v>30840</v>
+        <v>33760</v>
       </c>
       <c r="F6" s="104">
         <f t="shared" si="1"/>
@@ -12139,7 +12208,7 @@
       </c>
       <c r="G6" s="105">
         <f>SUM(D6:F6)</f>
-        <v>73720</v>
+        <v>77960</v>
       </c>
       <c r="H6" s="97">
         <f>H5*40</f>
@@ -12147,7 +12216,7 @@
       </c>
       <c r="I6" s="98">
         <f>G6-H6</f>
-        <v>-326280</v>
+        <v>-322040</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>2</v>
@@ -12270,11 +12339,11 @@
       </c>
       <c r="D9" s="106">
         <f>D8-D5</f>
-        <v>-472</v>
+        <v>-505</v>
       </c>
       <c r="E9" s="106">
         <f>E8-E5</f>
-        <v>-771</v>
+        <v>-844</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>5</v>
@@ -12408,7 +12477,7 @@
       </c>
       <c r="G12" s="91">
         <f>D12+G5</f>
-        <v>6043</v>
+        <v>6149</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>11</v>
@@ -12459,7 +12528,7 @@
       </c>
       <c r="G13" s="91">
         <f>G12*40</f>
-        <v>241720</v>
+        <v>245960</v>
       </c>
       <c r="S13" s="172" t="s">
         <v>85</v>

--- a/Aug_2026/daily Reports/LMT Orders.xlsx
+++ b/Aug_2026/daily Reports/LMT Orders.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D460CD9-C054-4D43-87CB-0C232DD75B82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DCC901A-DE6F-412C-AA99-A3FF26DEF446}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="127">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -401,6 +401,9 @@
   <si>
     <t>Sweera GT Road</t>
   </si>
+  <si>
+    <t xml:space="preserve">Zubaida Traders </t>
+  </si>
 </sst>
 </file>
 
@@ -1662,6 +1665,45 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1696,45 +1738,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2299,14 +2302,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="147">
+      <c r="B1" s="160">
         <f ca="1">TODAY()</f>
-        <v>46253</v>
-      </c>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="147"/>
+        <v>46254</v>
+      </c>
+      <c r="C1" s="160"/>
+      <c r="D1" s="160"/>
+      <c r="E1" s="160"/>
+      <c r="F1" s="160"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
       <c r="I1" s="10"/>
@@ -2328,10 +2331,10 @@
       <c r="Y1" s="10"/>
     </row>
     <row r="2" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="169" t="s">
+      <c r="A2" s="157" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="148" t="s">
+      <c r="B2" s="161" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2364,13 +2367,13 @@
       <c r="L2" s="15">
         <v>120</v>
       </c>
-      <c r="M2" s="161"/>
-      <c r="N2" s="162"/>
-      <c r="O2" s="163"/>
-      <c r="P2" s="164" t="s">
+      <c r="M2" s="149"/>
+      <c r="N2" s="150"/>
+      <c r="O2" s="151"/>
+      <c r="P2" s="152" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="165"/>
+      <c r="Q2" s="153"/>
       <c r="R2" s="18">
         <v>0.05</v>
       </c>
@@ -2389,8 +2392,8 @@
       <c r="Y2" s="20"/>
     </row>
     <row r="3" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="169"/>
-      <c r="B3" s="149"/>
+      <c r="A3" s="157"/>
+      <c r="B3" s="162"/>
       <c r="C3" s="23" t="s">
         <v>15</v>
       </c>
@@ -2421,29 +2424,29 @@
       <c r="L3" s="29">
         <v>72.64</v>
       </c>
-      <c r="M3" s="166" t="s">
+      <c r="M3" s="154" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="167"/>
-      <c r="O3" s="168"/>
+      <c r="N3" s="155"/>
+      <c r="O3" s="156"/>
       <c r="P3" s="71"/>
       <c r="Q3" s="72"/>
-      <c r="R3" s="151" t="s">
+      <c r="R3" s="164" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="152"/>
-      <c r="T3" s="152"/>
-      <c r="U3" s="153"/>
-      <c r="V3" s="154" t="s">
+      <c r="S3" s="165"/>
+      <c r="T3" s="165"/>
+      <c r="U3" s="166"/>
+      <c r="V3" s="167" t="s">
         <v>17</v>
       </c>
-      <c r="W3" s="155"/>
-      <c r="X3" s="155"/>
-      <c r="Y3" s="156"/>
+      <c r="W3" s="168"/>
+      <c r="X3" s="168"/>
+      <c r="Y3" s="169"/>
     </row>
     <row r="4" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="169"/>
-      <c r="B4" s="150"/>
+      <c r="A4" s="157"/>
+      <c r="B4" s="163"/>
       <c r="C4" s="30" t="s">
         <v>18</v>
       </c>
@@ -6059,23 +6062,39 @@
       <c r="Y47" s="56"/>
     </row>
     <row r="48" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A48" s="78"/>
+      <c r="A48" s="140">
+        <v>46253</v>
+      </c>
       <c r="B48" s="47">
         <v>44</v>
       </c>
-      <c r="C48" s="57"/>
+      <c r="C48" s="57" t="s">
+        <v>115</v>
+      </c>
       <c r="D48" s="74"/>
       <c r="E48" s="75"/>
       <c r="F48" s="76"/>
-      <c r="G48" s="50"/>
-      <c r="H48" s="75"/>
-      <c r="I48" s="49"/>
-      <c r="J48" s="50"/>
-      <c r="K48" s="75"/>
-      <c r="L48" s="76"/>
+      <c r="G48" s="50">
+        <v>599</v>
+      </c>
+      <c r="H48" s="75">
+        <v>600</v>
+      </c>
+      <c r="I48" s="49">
+        <v>600</v>
+      </c>
+      <c r="J48" s="50">
+        <v>599</v>
+      </c>
+      <c r="K48" s="75">
+        <v>592</v>
+      </c>
+      <c r="L48" s="76">
+        <v>596</v>
+      </c>
       <c r="M48" s="48">
         <f t="shared" ref="M48:M60" si="83">SUM(D48:L48)/40</f>
-        <v>0</v>
+        <v>89.65</v>
       </c>
       <c r="N48" s="39">
         <f t="shared" si="18"/>
@@ -6087,11 +6106,11 @@
       </c>
       <c r="P48" s="73">
         <f t="shared" ref="P48:P60" si="84">SUM(G48:I48)/20</f>
-        <v>0</v>
+        <v>89.95</v>
       </c>
       <c r="Q48" s="40">
         <f t="shared" ref="Q48:Q60" si="85">SUM(J48:L48)/20</f>
-        <v>0</v>
+        <v>89.35</v>
       </c>
       <c r="R48" s="51"/>
       <c r="S48" s="52"/>
@@ -6109,23 +6128,39 @@
       <c r="Y48" s="56"/>
     </row>
     <row r="49" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A49" s="78"/>
+      <c r="A49" s="140">
+        <v>46253</v>
+      </c>
       <c r="B49" s="47">
         <v>45</v>
       </c>
-      <c r="C49" s="57"/>
+      <c r="C49" s="57" t="s">
+        <v>126</v>
+      </c>
       <c r="D49" s="74"/>
       <c r="E49" s="75"/>
       <c r="F49" s="76"/>
-      <c r="G49" s="50"/>
-      <c r="H49" s="75"/>
-      <c r="I49" s="49"/>
-      <c r="J49" s="50"/>
-      <c r="K49" s="75"/>
-      <c r="L49" s="76"/>
+      <c r="G49" s="50">
+        <v>400</v>
+      </c>
+      <c r="H49" s="75">
+        <v>400</v>
+      </c>
+      <c r="I49" s="49">
+        <v>1200</v>
+      </c>
+      <c r="J49" s="50">
+        <v>400</v>
+      </c>
+      <c r="K49" s="75">
+        <v>600</v>
+      </c>
+      <c r="L49" s="76">
+        <v>2000</v>
+      </c>
       <c r="M49" s="48">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="N49" s="39">
         <f t="shared" si="18"/>
@@ -6137,11 +6172,11 @@
       </c>
       <c r="P49" s="73">
         <f t="shared" si="84"/>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q49" s="40">
         <f t="shared" si="85"/>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="R49" s="51"/>
       <c r="S49" s="52"/>
@@ -6159,23 +6194,39 @@
       <c r="Y49" s="56"/>
     </row>
     <row r="50" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A50" s="78"/>
+      <c r="A50" s="140">
+        <v>46254</v>
+      </c>
       <c r="B50" s="47">
         <v>46</v>
       </c>
-      <c r="C50" s="57"/>
+      <c r="C50" s="57" t="s">
+        <v>64</v>
+      </c>
       <c r="D50" s="74"/>
       <c r="E50" s="75"/>
       <c r="F50" s="76"/>
-      <c r="G50" s="50"/>
-      <c r="H50" s="75"/>
-      <c r="I50" s="49"/>
-      <c r="J50" s="50"/>
-      <c r="K50" s="75"/>
-      <c r="L50" s="76"/>
+      <c r="G50" s="50">
+        <v>120</v>
+      </c>
+      <c r="H50" s="75">
+        <v>40</v>
+      </c>
+      <c r="I50" s="49">
+        <v>520</v>
+      </c>
+      <c r="J50" s="50">
+        <v>279</v>
+      </c>
+      <c r="K50" s="75">
+        <v>120</v>
+      </c>
+      <c r="L50" s="76">
+        <v>240</v>
+      </c>
       <c r="M50" s="48">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>32.975000000000001</v>
       </c>
       <c r="N50" s="39">
         <f t="shared" si="18"/>
@@ -6187,11 +6238,11 @@
       </c>
       <c r="P50" s="73">
         <f t="shared" si="84"/>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="Q50" s="40">
         <f t="shared" si="85"/>
-        <v>0</v>
+        <v>31.95</v>
       </c>
       <c r="R50" s="51"/>
       <c r="S50" s="52"/>
@@ -6209,23 +6260,39 @@
       <c r="Y50" s="56"/>
     </row>
     <row r="51" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A51" s="78"/>
+      <c r="A51" s="140">
+        <v>46254</v>
+      </c>
       <c r="B51" s="47">
         <v>47</v>
       </c>
-      <c r="C51" s="57"/>
+      <c r="C51" s="57" t="s">
+        <v>97</v>
+      </c>
       <c r="D51" s="74"/>
       <c r="E51" s="75"/>
       <c r="F51" s="76"/>
-      <c r="G51" s="50"/>
-      <c r="H51" s="75"/>
-      <c r="I51" s="49"/>
-      <c r="J51" s="50"/>
-      <c r="K51" s="75"/>
-      <c r="L51" s="76"/>
+      <c r="G51" s="50">
+        <v>40</v>
+      </c>
+      <c r="H51" s="75">
+        <v>80</v>
+      </c>
+      <c r="I51" s="49">
+        <v>80</v>
+      </c>
+      <c r="J51" s="50">
+        <v>40</v>
+      </c>
+      <c r="K51" s="75">
+        <v>40</v>
+      </c>
+      <c r="L51" s="76">
+        <v>80</v>
+      </c>
       <c r="M51" s="48">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N51" s="39">
         <f t="shared" si="18"/>
@@ -6237,11 +6304,11 @@
       </c>
       <c r="P51" s="73">
         <f t="shared" si="84"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q51" s="40">
         <f t="shared" si="85"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R51" s="51"/>
       <c r="S51" s="52"/>
@@ -6259,23 +6326,31 @@
       <c r="Y51" s="56"/>
     </row>
     <row r="52" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A52" s="78"/>
+      <c r="A52" s="140">
+        <v>46254</v>
+      </c>
       <c r="B52" s="47">
         <v>48</v>
       </c>
-      <c r="C52" s="57"/>
+      <c r="C52" s="57" t="s">
+        <v>92</v>
+      </c>
       <c r="D52" s="74"/>
       <c r="E52" s="75"/>
       <c r="F52" s="76"/>
       <c r="G52" s="50"/>
       <c r="H52" s="75"/>
-      <c r="I52" s="49"/>
+      <c r="I52" s="49">
+        <v>240</v>
+      </c>
       <c r="J52" s="50"/>
       <c r="K52" s="75"/>
-      <c r="L52" s="76"/>
+      <c r="L52" s="76">
+        <v>360</v>
+      </c>
       <c r="M52" s="48">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="N52" s="39">
         <f t="shared" si="18"/>
@@ -6287,11 +6362,11 @@
       </c>
       <c r="P52" s="73">
         <f t="shared" si="84"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q52" s="40">
         <f t="shared" si="85"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="R52" s="51"/>
       <c r="S52" s="52"/>
@@ -11590,10 +11665,10 @@
     </row>
     <row r="133" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A133" s="78"/>
-      <c r="B133" s="157" t="s">
+      <c r="B133" s="170" t="s">
         <v>11</v>
       </c>
-      <c r="C133" s="158"/>
+      <c r="C133" s="171"/>
       <c r="D133" s="84">
         <f t="shared" ref="D133:L133" si="111">SUM(D6:D61)</f>
         <v>6203</v>
@@ -11608,31 +11683,31 @@
       </c>
       <c r="G133" s="84">
         <f t="shared" si="111"/>
-        <v>5025</v>
+        <v>6184</v>
       </c>
       <c r="H133" s="84">
         <f t="shared" si="111"/>
-        <v>5259</v>
+        <v>6379</v>
       </c>
       <c r="I133" s="84">
         <f t="shared" si="111"/>
-        <v>7797</v>
+        <v>10437</v>
       </c>
       <c r="J133" s="84">
         <f t="shared" si="111"/>
-        <v>9769</v>
+        <v>11087</v>
       </c>
       <c r="K133" s="84">
         <f t="shared" si="111"/>
-        <v>9369</v>
+        <v>10721</v>
       </c>
       <c r="L133" s="84">
         <f t="shared" si="111"/>
-        <v>11892</v>
+        <v>15168</v>
       </c>
       <c r="M133" s="48">
         <f t="shared" ref="M133:M136" si="112">SUM(D133:L133)/40</f>
-        <v>1382.85</v>
+        <v>1654.4749999999999</v>
       </c>
       <c r="N133" s="39">
         <f t="shared" si="18"/>
@@ -11644,11 +11719,11 @@
       </c>
       <c r="P133" s="73">
         <f t="shared" ref="P133:P137" si="113">SUM(G133:I133)/20</f>
-        <v>904.05</v>
+        <v>1150</v>
       </c>
       <c r="Q133" s="40">
         <f t="shared" ref="Q133:Q137" si="114">SUM(J133:L133)/20</f>
-        <v>1551.5</v>
+        <v>1848.8</v>
       </c>
       <c r="R133" s="51" t="e">
         <f t="shared" si="4"/>
@@ -11857,10 +11932,10 @@
       </c>
     </row>
     <row r="137" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B137" s="170" t="s">
+      <c r="B137" s="158" t="s">
         <v>70</v>
       </c>
-      <c r="C137" s="171"/>
+      <c r="C137" s="159"/>
       <c r="D137" s="83">
         <f>SUM(D135:D136)</f>
         <v>0</v>
@@ -11951,10 +12026,10 @@
       </c>
     </row>
     <row r="138" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B138" s="159" t="s">
+      <c r="B138" s="147" t="s">
         <v>11</v>
       </c>
-      <c r="C138" s="160"/>
+      <c r="C138" s="148"/>
       <c r="D138" s="85">
         <f>SUM(D133,D137)</f>
         <v>6203</v>
@@ -11969,31 +12044,31 @@
       </c>
       <c r="G138" s="85">
         <f t="shared" si="119"/>
-        <v>5025</v>
+        <v>6184</v>
       </c>
       <c r="H138" s="85">
         <f t="shared" si="119"/>
-        <v>5259</v>
+        <v>6379</v>
       </c>
       <c r="I138" s="85">
         <f t="shared" si="119"/>
-        <v>7797</v>
+        <v>10437</v>
       </c>
       <c r="J138" s="85">
         <f t="shared" si="119"/>
-        <v>9769</v>
+        <v>11087</v>
       </c>
       <c r="K138" s="85">
         <f t="shared" si="119"/>
-        <v>9369</v>
+        <v>10721</v>
       </c>
       <c r="L138" s="85">
         <f t="shared" si="119"/>
-        <v>11892</v>
+        <v>15168</v>
       </c>
       <c r="M138" s="60">
         <f t="shared" si="0"/>
-        <v>1382.85</v>
+        <v>1654.4749999999999</v>
       </c>
       <c r="N138" s="63">
         <f>SUM(N5:N137)</f>
@@ -12005,11 +12080,11 @@
       </c>
       <c r="P138" s="62">
         <f t="shared" si="120"/>
-        <v>1814.1</v>
+        <v>2306</v>
       </c>
       <c r="Q138" s="64">
         <f t="shared" si="120"/>
-        <v>3107</v>
+        <v>3701.6</v>
       </c>
       <c r="R138" s="65" t="e">
         <f t="shared" si="120"/>
@@ -12046,17 +12121,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="R3:U3"/>
+    <mergeCell ref="V3:Y3"/>
+    <mergeCell ref="B133:C133"/>
     <mergeCell ref="B138:C138"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="P2:Q2"/>
     <mergeCell ref="M3:O3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B137:C137"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="R3:U3"/>
-    <mergeCell ref="V3:Y3"/>
-    <mergeCell ref="B133:C133"/>
   </mergeCells>
   <conditionalFormatting sqref="C46:C60">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
@@ -12156,24 +12231,24 @@
         <v>49</v>
       </c>
       <c r="D5" s="88">
-        <v>505</v>
+        <v>572</v>
       </c>
       <c r="E5" s="79">
-        <v>844</v>
+        <v>1116</v>
       </c>
       <c r="F5" s="79">
         <v>600</v>
       </c>
       <c r="G5" s="102">
         <f>SUM(D5:F5)</f>
-        <v>1949</v>
+        <v>2288</v>
       </c>
       <c r="H5" s="95">
         <v>10000</v>
       </c>
       <c r="I5" s="96">
         <f>G5-H5</f>
-        <v>-8051</v>
+        <v>-7712</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>1</v>
@@ -12196,11 +12271,11 @@
       </c>
       <c r="D6" s="104">
         <f>D5*40</f>
-        <v>20200</v>
+        <v>22880</v>
       </c>
       <c r="E6" s="104">
         <f t="shared" ref="E6:F6" si="1">E5*40</f>
-        <v>33760</v>
+        <v>44640</v>
       </c>
       <c r="F6" s="104">
         <f t="shared" si="1"/>
@@ -12208,7 +12283,7 @@
       </c>
       <c r="G6" s="105">
         <f>SUM(D6:F6)</f>
-        <v>77960</v>
+        <v>91520</v>
       </c>
       <c r="H6" s="97">
         <f>H5*40</f>
@@ -12216,7 +12291,7 @@
       </c>
       <c r="I6" s="98">
         <f>G6-H6</f>
-        <v>-322040</v>
+        <v>-308480</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>2</v>
@@ -12339,11 +12414,11 @@
       </c>
       <c r="D9" s="106">
         <f>D8-D5</f>
-        <v>-505</v>
+        <v>-572</v>
       </c>
       <c r="E9" s="106">
         <f>E8-E5</f>
-        <v>-844</v>
+        <v>-1116</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>5</v>
@@ -12477,7 +12552,7 @@
       </c>
       <c r="G12" s="91">
         <f>D12+G5</f>
-        <v>6149</v>
+        <v>6488</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>11</v>
@@ -12528,7 +12603,7 @@
       </c>
       <c r="G13" s="91">
         <f>G12*40</f>
-        <v>245960</v>
+        <v>259520</v>
       </c>
       <c r="S13" s="172" t="s">
         <v>85</v>

--- a/Aug_2026/daily Reports/LMT Orders.xlsx
+++ b/Aug_2026/daily Reports/LMT Orders.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DCC901A-DE6F-412C-AA99-A3FF26DEF446}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4386B453-304A-410E-AE89-494B0FABBB1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="128">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -404,6 +404,9 @@
   <si>
     <t xml:space="preserve">Zubaida Traders </t>
   </si>
+  <si>
+    <t>Vip</t>
+  </si>
 </sst>
 </file>
 
@@ -2304,7 +2307,7 @@
     <row r="1" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B1" s="160">
         <f ca="1">TODAY()</f>
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C1" s="160"/>
       <c r="D1" s="160"/>
@@ -5334,36 +5337,36 @@
       </c>
     </row>
     <row r="39" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A39" s="140">
+      <c r="A39" s="78">
         <v>46249</v>
       </c>
       <c r="B39" s="47">
         <v>35</v>
       </c>
-      <c r="C39" s="142" t="s">
+      <c r="C39" s="57" t="s">
         <v>118</v>
       </c>
-      <c r="D39" s="143">
+      <c r="D39" s="74">
         <v>40</v>
       </c>
-      <c r="E39" s="144"/>
-      <c r="F39" s="145"/>
-      <c r="G39" s="146">
+      <c r="E39" s="75"/>
+      <c r="F39" s="76"/>
+      <c r="G39" s="50">
         <v>20</v>
       </c>
-      <c r="H39" s="144">
+      <c r="H39" s="75">
         <v>20</v>
       </c>
-      <c r="I39" s="56">
+      <c r="I39" s="49">
         <v>40</v>
       </c>
-      <c r="J39" s="146">
+      <c r="J39" s="50">
         <v>40</v>
       </c>
-      <c r="K39" s="144">
+      <c r="K39" s="75">
         <v>20</v>
       </c>
-      <c r="L39" s="145">
+      <c r="L39" s="76">
         <v>20</v>
       </c>
       <c r="M39" s="48">
@@ -5420,36 +5423,36 @@
       </c>
     </row>
     <row r="40" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A40" s="140">
+      <c r="A40" s="78">
         <v>46249</v>
       </c>
       <c r="B40" s="47">
         <v>36</v>
       </c>
-      <c r="C40" s="142" t="s">
+      <c r="C40" s="57" t="s">
         <v>119</v>
       </c>
-      <c r="D40" s="143">
+      <c r="D40" s="74">
         <v>80</v>
       </c>
-      <c r="E40" s="144"/>
-      <c r="F40" s="145"/>
-      <c r="G40" s="146">
+      <c r="E40" s="75"/>
+      <c r="F40" s="76"/>
+      <c r="G40" s="50">
         <v>103</v>
       </c>
-      <c r="H40" s="144">
+      <c r="H40" s="75">
         <v>104</v>
       </c>
-      <c r="I40" s="56">
+      <c r="I40" s="49">
         <v>38</v>
       </c>
-      <c r="J40" s="146">
+      <c r="J40" s="50">
         <v>68</v>
       </c>
-      <c r="K40" s="144">
+      <c r="K40" s="75">
         <v>93</v>
       </c>
-      <c r="L40" s="145">
+      <c r="L40" s="76">
         <v>33</v>
       </c>
       <c r="M40" s="48">
@@ -5506,32 +5509,32 @@
       </c>
     </row>
     <row r="41" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A41" s="140">
+      <c r="A41" s="78">
         <v>46249</v>
       </c>
       <c r="B41" s="47">
         <v>37</v>
       </c>
-      <c r="C41" s="142" t="s">
+      <c r="C41" s="57" t="s">
         <v>120</v>
       </c>
-      <c r="D41" s="143"/>
-      <c r="E41" s="144"/>
-      <c r="F41" s="145"/>
-      <c r="G41" s="146">
+      <c r="D41" s="74"/>
+      <c r="E41" s="75"/>
+      <c r="F41" s="76"/>
+      <c r="G41" s="50">
         <v>120</v>
       </c>
-      <c r="H41" s="144">
+      <c r="H41" s="75">
         <v>200</v>
       </c>
-      <c r="I41" s="56">
+      <c r="I41" s="49">
         <v>200</v>
       </c>
-      <c r="J41" s="146"/>
-      <c r="K41" s="144">
+      <c r="J41" s="50"/>
+      <c r="K41" s="75">
         <v>200</v>
       </c>
-      <c r="L41" s="145">
+      <c r="L41" s="76">
         <v>200</v>
       </c>
       <c r="M41" s="48">
@@ -5672,28 +5675,28 @@
       </c>
     </row>
     <row r="43" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A43" s="140">
+      <c r="A43" s="78">
         <v>46252</v>
       </c>
-      <c r="B43" s="141">
+      <c r="B43" s="47">
         <v>39</v>
       </c>
-      <c r="C43" s="142" t="s">
+      <c r="C43" s="57" t="s">
         <v>123</v>
       </c>
-      <c r="D43" s="143"/>
-      <c r="E43" s="144"/>
-      <c r="F43" s="145"/>
-      <c r="G43" s="146"/>
-      <c r="H43" s="144"/>
-      <c r="I43" s="56">
+      <c r="D43" s="74"/>
+      <c r="E43" s="75"/>
+      <c r="F43" s="76"/>
+      <c r="G43" s="50"/>
+      <c r="H43" s="75"/>
+      <c r="I43" s="49">
         <v>80</v>
       </c>
-      <c r="J43" s="146"/>
-      <c r="K43" s="144">
+      <c r="J43" s="50"/>
+      <c r="K43" s="75">
         <v>39</v>
       </c>
-      <c r="L43" s="145">
+      <c r="L43" s="76">
         <v>80</v>
       </c>
       <c r="M43" s="48">
@@ -5750,32 +5753,32 @@
       </c>
     </row>
     <row r="44" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A44" s="140">
+      <c r="A44" s="78">
         <v>46252</v>
       </c>
-      <c r="B44" s="141">
+      <c r="B44" s="47">
         <v>40</v>
       </c>
-      <c r="C44" s="142" t="s">
+      <c r="C44" s="57" t="s">
         <v>122</v>
       </c>
-      <c r="D44" s="143"/>
-      <c r="E44" s="144"/>
-      <c r="F44" s="145"/>
-      <c r="G44" s="146"/>
-      <c r="H44" s="144">
+      <c r="D44" s="74"/>
+      <c r="E44" s="75"/>
+      <c r="F44" s="76"/>
+      <c r="G44" s="50"/>
+      <c r="H44" s="75">
         <v>48</v>
       </c>
-      <c r="I44" s="56">
+      <c r="I44" s="49">
         <v>80</v>
       </c>
-      <c r="J44" s="146">
+      <c r="J44" s="50">
         <v>80</v>
       </c>
-      <c r="K44" s="144">
+      <c r="K44" s="75">
         <v>80</v>
       </c>
-      <c r="L44" s="145">
+      <c r="L44" s="76">
         <v>120</v>
       </c>
       <c r="M44" s="48">
@@ -5832,30 +5835,30 @@
       </c>
     </row>
     <row r="45" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A45" s="140">
+      <c r="A45" s="78">
         <v>46252</v>
       </c>
-      <c r="B45" s="141">
+      <c r="B45" s="47">
         <v>41</v>
       </c>
-      <c r="C45" s="142" t="s">
+      <c r="C45" s="57" t="s">
         <v>121</v>
       </c>
-      <c r="D45" s="143"/>
-      <c r="E45" s="144"/>
-      <c r="F45" s="145"/>
-      <c r="G45" s="146"/>
-      <c r="H45" s="144"/>
-      <c r="I45" s="56">
+      <c r="D45" s="74"/>
+      <c r="E45" s="75"/>
+      <c r="F45" s="76"/>
+      <c r="G45" s="50"/>
+      <c r="H45" s="75"/>
+      <c r="I45" s="49">
         <v>200</v>
       </c>
-      <c r="J45" s="146">
+      <c r="J45" s="50">
         <v>120</v>
       </c>
-      <c r="K45" s="144">
+      <c r="K45" s="75">
         <v>200</v>
       </c>
-      <c r="L45" s="145">
+      <c r="L45" s="76">
         <v>80</v>
       </c>
       <c r="M45" s="48">
@@ -5912,34 +5915,34 @@
       </c>
     </row>
     <row r="46" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A46" s="140">
+      <c r="A46" s="78">
         <v>46252</v>
       </c>
-      <c r="B46" s="141">
+      <c r="B46" s="47">
         <v>42</v>
       </c>
-      <c r="C46" s="142" t="s">
+      <c r="C46" s="57" t="s">
         <v>124</v>
       </c>
-      <c r="D46" s="143"/>
-      <c r="E46" s="144"/>
-      <c r="F46" s="145"/>
-      <c r="G46" s="146">
+      <c r="D46" s="74"/>
+      <c r="E46" s="75"/>
+      <c r="F46" s="76"/>
+      <c r="G46" s="50">
         <v>80</v>
       </c>
-      <c r="H46" s="144">
+      <c r="H46" s="75">
         <v>40</v>
       </c>
-      <c r="I46" s="56">
+      <c r="I46" s="49">
         <v>120</v>
       </c>
-      <c r="J46" s="146">
+      <c r="J46" s="50">
         <v>40</v>
       </c>
-      <c r="K46" s="144">
+      <c r="K46" s="75">
         <v>80</v>
       </c>
-      <c r="L46" s="145">
+      <c r="L46" s="76">
         <v>120</v>
       </c>
       <c r="M46" s="48">
@@ -5996,34 +5999,34 @@
       </c>
     </row>
     <row r="47" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A47" s="140">
+      <c r="A47" s="78">
         <v>46252</v>
       </c>
-      <c r="B47" s="141">
+      <c r="B47" s="47">
         <v>43</v>
       </c>
-      <c r="C47" s="142" t="s">
+      <c r="C47" s="57" t="s">
         <v>125</v>
       </c>
-      <c r="D47" s="143"/>
-      <c r="E47" s="144"/>
-      <c r="F47" s="145"/>
-      <c r="G47" s="146">
+      <c r="D47" s="74"/>
+      <c r="E47" s="75"/>
+      <c r="F47" s="76"/>
+      <c r="G47" s="50">
         <v>200</v>
       </c>
-      <c r="H47" s="144">
+      <c r="H47" s="75">
         <v>200</v>
       </c>
-      <c r="I47" s="56">
+      <c r="I47" s="49">
         <v>200</v>
       </c>
-      <c r="J47" s="146">
+      <c r="J47" s="50">
         <v>200</v>
       </c>
-      <c r="K47" s="144">
+      <c r="K47" s="75">
         <v>200</v>
       </c>
-      <c r="L47" s="145">
+      <c r="L47" s="76">
         <v>200</v>
       </c>
       <c r="M47" s="48">
@@ -6062,7 +6065,7 @@
       <c r="Y47" s="56"/>
     </row>
     <row r="48" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A48" s="140">
+      <c r="A48" s="78">
         <v>46253</v>
       </c>
       <c r="B48" s="47">
@@ -6128,7 +6131,7 @@
       <c r="Y48" s="56"/>
     </row>
     <row r="49" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A49" s="140">
+      <c r="A49" s="78">
         <v>46253</v>
       </c>
       <c r="B49" s="47">
@@ -6200,28 +6203,28 @@
       <c r="B50" s="47">
         <v>46</v>
       </c>
-      <c r="C50" s="57" t="s">
+      <c r="C50" s="142" t="s">
         <v>64</v>
       </c>
-      <c r="D50" s="74"/>
-      <c r="E50" s="75"/>
-      <c r="F50" s="76"/>
-      <c r="G50" s="50">
+      <c r="D50" s="143"/>
+      <c r="E50" s="144"/>
+      <c r="F50" s="145"/>
+      <c r="G50" s="146">
         <v>120</v>
       </c>
-      <c r="H50" s="75">
+      <c r="H50" s="144">
         <v>40</v>
       </c>
-      <c r="I50" s="49">
+      <c r="I50" s="56">
         <v>520</v>
       </c>
-      <c r="J50" s="50">
+      <c r="J50" s="146">
         <v>279</v>
       </c>
-      <c r="K50" s="75">
+      <c r="K50" s="144">
         <v>120</v>
       </c>
-      <c r="L50" s="76">
+      <c r="L50" s="145">
         <v>240</v>
       </c>
       <c r="M50" s="48">
@@ -6266,28 +6269,28 @@
       <c r="B51" s="47">
         <v>47</v>
       </c>
-      <c r="C51" s="57" t="s">
+      <c r="C51" s="142" t="s">
         <v>97</v>
       </c>
-      <c r="D51" s="74"/>
-      <c r="E51" s="75"/>
-      <c r="F51" s="76"/>
-      <c r="G51" s="50">
+      <c r="D51" s="143"/>
+      <c r="E51" s="144"/>
+      <c r="F51" s="145"/>
+      <c r="G51" s="146">
         <v>40</v>
       </c>
-      <c r="H51" s="75">
+      <c r="H51" s="144">
         <v>80</v>
       </c>
-      <c r="I51" s="49">
+      <c r="I51" s="56">
         <v>80</v>
       </c>
-      <c r="J51" s="50">
+      <c r="J51" s="146">
         <v>40</v>
       </c>
-      <c r="K51" s="75">
+      <c r="K51" s="144">
         <v>40</v>
       </c>
-      <c r="L51" s="76">
+      <c r="L51" s="145">
         <v>80</v>
       </c>
       <c r="M51" s="48">
@@ -6332,20 +6335,20 @@
       <c r="B52" s="47">
         <v>48</v>
       </c>
-      <c r="C52" s="57" t="s">
+      <c r="C52" s="142" t="s">
         <v>92</v>
       </c>
-      <c r="D52" s="74"/>
-      <c r="E52" s="75"/>
-      <c r="F52" s="76"/>
-      <c r="G52" s="50"/>
-      <c r="H52" s="75"/>
-      <c r="I52" s="49">
+      <c r="D52" s="143"/>
+      <c r="E52" s="144"/>
+      <c r="F52" s="145"/>
+      <c r="G52" s="146"/>
+      <c r="H52" s="144"/>
+      <c r="I52" s="56">
         <v>240</v>
       </c>
-      <c r="J52" s="50"/>
-      <c r="K52" s="75"/>
-      <c r="L52" s="76">
+      <c r="J52" s="146"/>
+      <c r="K52" s="144"/>
+      <c r="L52" s="145">
         <v>360</v>
       </c>
       <c r="M52" s="48">
@@ -6384,23 +6387,35 @@
       <c r="Y52" s="56"/>
     </row>
     <row r="53" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A53" s="78"/>
+      <c r="A53" s="140">
+        <v>46254</v>
+      </c>
       <c r="B53" s="47">
         <v>49</v>
       </c>
-      <c r="C53" s="57"/>
-      <c r="D53" s="74"/>
-      <c r="E53" s="75"/>
-      <c r="F53" s="76"/>
-      <c r="G53" s="50"/>
-      <c r="H53" s="75"/>
-      <c r="I53" s="49"/>
-      <c r="J53" s="50"/>
-      <c r="K53" s="75"/>
-      <c r="L53" s="76"/>
+      <c r="C53" s="142" t="s">
+        <v>96</v>
+      </c>
+      <c r="D53" s="143"/>
+      <c r="E53" s="144"/>
+      <c r="F53" s="145"/>
+      <c r="G53" s="146">
+        <v>200</v>
+      </c>
+      <c r="H53" s="144"/>
+      <c r="I53" s="56">
+        <v>194</v>
+      </c>
+      <c r="J53" s="146">
+        <v>200</v>
+      </c>
+      <c r="K53" s="144"/>
+      <c r="L53" s="145">
+        <v>180</v>
+      </c>
       <c r="M53" s="48">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>19.350000000000001</v>
       </c>
       <c r="N53" s="39">
         <f t="shared" si="18"/>
@@ -6412,11 +6427,11 @@
       </c>
       <c r="P53" s="73">
         <f t="shared" si="84"/>
-        <v>0</v>
+        <v>19.7</v>
       </c>
       <c r="Q53" s="40">
         <f t="shared" si="85"/>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="R53" s="51"/>
       <c r="S53" s="52"/>
@@ -6434,23 +6449,33 @@
       <c r="Y53" s="56"/>
     </row>
     <row r="54" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A54" s="78"/>
+      <c r="A54" s="140">
+        <v>46254</v>
+      </c>
       <c r="B54" s="47">
         <v>50</v>
       </c>
-      <c r="C54" s="57"/>
-      <c r="D54" s="74"/>
-      <c r="E54" s="75"/>
-      <c r="F54" s="76"/>
-      <c r="G54" s="50"/>
-      <c r="H54" s="75"/>
-      <c r="I54" s="49"/>
-      <c r="J54" s="50"/>
-      <c r="K54" s="75"/>
-      <c r="L54" s="76"/>
+      <c r="C54" s="142" t="s">
+        <v>127</v>
+      </c>
+      <c r="D54" s="143"/>
+      <c r="E54" s="144"/>
+      <c r="F54" s="145"/>
+      <c r="G54" s="146"/>
+      <c r="H54" s="144"/>
+      <c r="I54" s="56"/>
+      <c r="J54" s="146">
+        <v>400</v>
+      </c>
+      <c r="K54" s="144">
+        <v>400</v>
+      </c>
+      <c r="L54" s="145">
+        <v>400</v>
+      </c>
       <c r="M54" s="48">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="N54" s="39">
         <f t="shared" si="18"/>
@@ -6466,7 +6491,7 @@
       </c>
       <c r="Q54" s="40">
         <f t="shared" si="85"/>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="R54" s="51"/>
       <c r="S54" s="52"/>
@@ -11683,7 +11708,7 @@
       </c>
       <c r="G133" s="84">
         <f t="shared" si="111"/>
-        <v>6184</v>
+        <v>6384</v>
       </c>
       <c r="H133" s="84">
         <f t="shared" si="111"/>
@@ -11691,23 +11716,23 @@
       </c>
       <c r="I133" s="84">
         <f t="shared" si="111"/>
-        <v>10437</v>
+        <v>10631</v>
       </c>
       <c r="J133" s="84">
         <f t="shared" si="111"/>
-        <v>11087</v>
+        <v>11687</v>
       </c>
       <c r="K133" s="84">
         <f t="shared" si="111"/>
-        <v>10721</v>
+        <v>11121</v>
       </c>
       <c r="L133" s="84">
         <f t="shared" si="111"/>
-        <v>15168</v>
+        <v>15748</v>
       </c>
       <c r="M133" s="48">
         <f t="shared" ref="M133:M136" si="112">SUM(D133:L133)/40</f>
-        <v>1654.4749999999999</v>
+        <v>1703.825</v>
       </c>
       <c r="N133" s="39">
         <f t="shared" si="18"/>
@@ -11719,11 +11744,11 @@
       </c>
       <c r="P133" s="73">
         <f t="shared" ref="P133:P137" si="113">SUM(G133:I133)/20</f>
-        <v>1150</v>
+        <v>1169.7</v>
       </c>
       <c r="Q133" s="40">
         <f t="shared" ref="Q133:Q137" si="114">SUM(J133:L133)/20</f>
-        <v>1848.8</v>
+        <v>1927.8</v>
       </c>
       <c r="R133" s="51" t="e">
         <f t="shared" si="4"/>
@@ -12044,7 +12069,7 @@
       </c>
       <c r="G138" s="85">
         <f t="shared" si="119"/>
-        <v>6184</v>
+        <v>6384</v>
       </c>
       <c r="H138" s="85">
         <f t="shared" si="119"/>
@@ -12052,23 +12077,23 @@
       </c>
       <c r="I138" s="85">
         <f t="shared" si="119"/>
-        <v>10437</v>
+        <v>10631</v>
       </c>
       <c r="J138" s="85">
         <f t="shared" si="119"/>
-        <v>11087</v>
+        <v>11687</v>
       </c>
       <c r="K138" s="85">
         <f t="shared" si="119"/>
-        <v>10721</v>
+        <v>11121</v>
       </c>
       <c r="L138" s="85">
         <f t="shared" si="119"/>
-        <v>15168</v>
+        <v>15748</v>
       </c>
       <c r="M138" s="60">
         <f t="shared" si="0"/>
-        <v>1654.4749999999999</v>
+        <v>1703.825</v>
       </c>
       <c r="N138" s="63">
         <f>SUM(N5:N137)</f>
@@ -12080,11 +12105,11 @@
       </c>
       <c r="P138" s="62">
         <f t="shared" si="120"/>
-        <v>2306</v>
+        <v>2345.4</v>
       </c>
       <c r="Q138" s="64">
         <f t="shared" si="120"/>
-        <v>3701.6</v>
+        <v>3859.6</v>
       </c>
       <c r="R138" s="65" t="e">
         <f t="shared" si="120"/>

--- a/Aug_2026/daily Reports/LMT Orders.xlsx
+++ b/Aug_2026/daily Reports/LMT Orders.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4386B453-304A-410E-AE89-494B0FABBB1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6F54B50-85AB-489C-9664-F1B1A78581CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1668,6 +1668,42 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1705,42 +1741,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2305,14 +2305,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="160">
+      <c r="B1" s="147">
         <f ca="1">TODAY()</f>
         <v>46255</v>
       </c>
-      <c r="C1" s="160"/>
-      <c r="D1" s="160"/>
-      <c r="E1" s="160"/>
-      <c r="F1" s="160"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
       <c r="I1" s="10"/>
@@ -2334,10 +2334,10 @@
       <c r="Y1" s="10"/>
     </row>
     <row r="2" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="157" t="s">
+      <c r="A2" s="169" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="161" t="s">
+      <c r="B2" s="148" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2370,13 +2370,13 @@
       <c r="L2" s="15">
         <v>120</v>
       </c>
-      <c r="M2" s="149"/>
-      <c r="N2" s="150"/>
-      <c r="O2" s="151"/>
-      <c r="P2" s="152" t="s">
+      <c r="M2" s="161"/>
+      <c r="N2" s="162"/>
+      <c r="O2" s="163"/>
+      <c r="P2" s="164" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="153"/>
+      <c r="Q2" s="165"/>
       <c r="R2" s="18">
         <v>0.05</v>
       </c>
@@ -2395,8 +2395,8 @@
       <c r="Y2" s="20"/>
     </row>
     <row r="3" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="157"/>
-      <c r="B3" s="162"/>
+      <c r="A3" s="169"/>
+      <c r="B3" s="149"/>
       <c r="C3" s="23" t="s">
         <v>15</v>
       </c>
@@ -2427,29 +2427,29 @@
       <c r="L3" s="29">
         <v>72.64</v>
       </c>
-      <c r="M3" s="154" t="s">
+      <c r="M3" s="166" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="155"/>
-      <c r="O3" s="156"/>
+      <c r="N3" s="167"/>
+      <c r="O3" s="168"/>
       <c r="P3" s="71"/>
       <c r="Q3" s="72"/>
-      <c r="R3" s="164" t="s">
+      <c r="R3" s="151" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="165"/>
-      <c r="T3" s="165"/>
-      <c r="U3" s="166"/>
-      <c r="V3" s="167" t="s">
+      <c r="S3" s="152"/>
+      <c r="T3" s="152"/>
+      <c r="U3" s="153"/>
+      <c r="V3" s="154" t="s">
         <v>17</v>
       </c>
-      <c r="W3" s="168"/>
-      <c r="X3" s="168"/>
-      <c r="Y3" s="169"/>
+      <c r="W3" s="155"/>
+      <c r="X3" s="155"/>
+      <c r="Y3" s="156"/>
     </row>
     <row r="4" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="157"/>
-      <c r="B4" s="163"/>
+      <c r="A4" s="169"/>
+      <c r="B4" s="150"/>
       <c r="C4" s="30" t="s">
         <v>18</v>
       </c>
@@ -11690,10 +11690,10 @@
     </row>
     <row r="133" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A133" s="78"/>
-      <c r="B133" s="170" t="s">
+      <c r="B133" s="157" t="s">
         <v>11</v>
       </c>
-      <c r="C133" s="171"/>
+      <c r="C133" s="158"/>
       <c r="D133" s="84">
         <f t="shared" ref="D133:L133" si="111">SUM(D6:D61)</f>
         <v>6203</v>
@@ -11957,10 +11957,10 @@
       </c>
     </row>
     <row r="137" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B137" s="158" t="s">
+      <c r="B137" s="170" t="s">
         <v>70</v>
       </c>
-      <c r="C137" s="159"/>
+      <c r="C137" s="171"/>
       <c r="D137" s="83">
         <f>SUM(D135:D136)</f>
         <v>0</v>
@@ -12051,10 +12051,10 @@
       </c>
     </row>
     <row r="138" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B138" s="147" t="s">
+      <c r="B138" s="159" t="s">
         <v>11</v>
       </c>
-      <c r="C138" s="148"/>
+      <c r="C138" s="160"/>
       <c r="D138" s="85">
         <f>SUM(D133,D137)</f>
         <v>6203</v>
@@ -12146,17 +12146,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="R3:U3"/>
-    <mergeCell ref="V3:Y3"/>
-    <mergeCell ref="B133:C133"/>
     <mergeCell ref="B138:C138"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="P2:Q2"/>
     <mergeCell ref="M3:O3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B137:C137"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="R3:U3"/>
+    <mergeCell ref="V3:Y3"/>
+    <mergeCell ref="B133:C133"/>
   </mergeCells>
   <conditionalFormatting sqref="C46:C60">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
@@ -12256,24 +12256,24 @@
         <v>49</v>
       </c>
       <c r="D5" s="88">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="E5" s="79">
-        <v>1116</v>
+        <v>1165</v>
       </c>
       <c r="F5" s="79">
         <v>600</v>
       </c>
       <c r="G5" s="102">
         <f>SUM(D5:F5)</f>
-        <v>2288</v>
+        <v>2342</v>
       </c>
       <c r="H5" s="95">
         <v>10000</v>
       </c>
       <c r="I5" s="96">
         <f>G5-H5</f>
-        <v>-7712</v>
+        <v>-7658</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>1</v>
@@ -12296,11 +12296,11 @@
       </c>
       <c r="D6" s="104">
         <f>D5*40</f>
-        <v>22880</v>
+        <v>23080</v>
       </c>
       <c r="E6" s="104">
         <f t="shared" ref="E6:F6" si="1">E5*40</f>
-        <v>44640</v>
+        <v>46600</v>
       </c>
       <c r="F6" s="104">
         <f t="shared" si="1"/>
@@ -12308,7 +12308,7 @@
       </c>
       <c r="G6" s="105">
         <f>SUM(D6:F6)</f>
-        <v>91520</v>
+        <v>93680</v>
       </c>
       <c r="H6" s="97">
         <f>H5*40</f>
@@ -12316,7 +12316,7 @@
       </c>
       <c r="I6" s="98">
         <f>G6-H6</f>
-        <v>-308480</v>
+        <v>-306320</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>2</v>
@@ -12408,7 +12408,9 @@
         <f t="shared" si="0"/>
         <v>6.5750000000000002</v>
       </c>
-      <c r="O8" s="81"/>
+      <c r="O8" s="81">
+        <v>50</v>
+      </c>
       <c r="S8" s="79">
         <v>120</v>
       </c>
@@ -12439,11 +12441,11 @@
       </c>
       <c r="D9" s="106">
         <f>D8-D5</f>
-        <v>-572</v>
+        <v>-577</v>
       </c>
       <c r="E9" s="106">
         <f>E8-E5</f>
-        <v>-1116</v>
+        <v>-1165</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>5</v>
@@ -12458,7 +12460,9 @@
         <f t="shared" si="0"/>
         <v>116.375</v>
       </c>
-      <c r="O9" s="81"/>
+      <c r="O9" s="81">
+        <v>23</v>
+      </c>
       <c r="S9" s="79">
         <v>120</v>
       </c>
@@ -12544,7 +12548,12 @@
         <f t="shared" si="0"/>
         <v>584.02499999999998</v>
       </c>
-      <c r="O11" s="81"/>
+      <c r="O11" s="81">
+        <v>125</v>
+      </c>
+      <c r="P11">
+        <v>4</v>
+      </c>
       <c r="S11" s="79">
         <v>70</v>
       </c>
@@ -12577,7 +12586,7 @@
       </c>
       <c r="G12" s="91">
         <f>D12+G5</f>
-        <v>6488</v>
+        <v>6542</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>11</v>
@@ -12593,7 +12602,7 @@
       </c>
       <c r="O12" s="9">
         <f>SUM(O5:O11)</f>
-        <v>0</v>
+        <v>198</v>
       </c>
       <c r="S12" s="79">
         <v>70</v>
@@ -12628,7 +12637,7 @@
       </c>
       <c r="G13" s="91">
         <f>G12*40</f>
-        <v>259520</v>
+        <v>261680</v>
       </c>
       <c r="S13" s="172" t="s">
         <v>85</v>

--- a/Aug_2026/daily Reports/LMT Orders.xlsx
+++ b/Aug_2026/daily Reports/LMT Orders.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6F54B50-85AB-489C-9664-F1B1A78581CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD820C4D-44C5-4DA4-8609-6B1DBAC86601}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="137">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -406,6 +406,33 @@
   </si>
   <si>
     <t>Vip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Al Rehmat </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jala Sons Behria </t>
+  </si>
+  <si>
+    <t>Clinic</t>
+  </si>
+  <si>
+    <t>Jalal Sons Izmir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prime </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RI Mart </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rainbow C NC </t>
+  </si>
+  <si>
+    <t>Jalal Sons Behria Orchard</t>
+  </si>
+  <si>
+    <t>Rainbow CNC DHA</t>
   </si>
 </sst>
 </file>
@@ -1668,6 +1695,45 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1702,45 +1768,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2305,14 +2332,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="147">
+      <c r="B1" s="160">
         <f ca="1">TODAY()</f>
-        <v>46255</v>
-      </c>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="147"/>
+        <v>46258</v>
+      </c>
+      <c r="C1" s="160"/>
+      <c r="D1" s="160"/>
+      <c r="E1" s="160"/>
+      <c r="F1" s="160"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
       <c r="I1" s="10"/>
@@ -2334,10 +2361,10 @@
       <c r="Y1" s="10"/>
     </row>
     <row r="2" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="169" t="s">
+      <c r="A2" s="157" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="148" t="s">
+      <c r="B2" s="161" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2370,13 +2397,13 @@
       <c r="L2" s="15">
         <v>120</v>
       </c>
-      <c r="M2" s="161"/>
-      <c r="N2" s="162"/>
-      <c r="O2" s="163"/>
-      <c r="P2" s="164" t="s">
+      <c r="M2" s="149"/>
+      <c r="N2" s="150"/>
+      <c r="O2" s="151"/>
+      <c r="P2" s="152" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="165"/>
+      <c r="Q2" s="153"/>
       <c r="R2" s="18">
         <v>0.05</v>
       </c>
@@ -2395,8 +2422,8 @@
       <c r="Y2" s="20"/>
     </row>
     <row r="3" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="169"/>
-      <c r="B3" s="149"/>
+      <c r="A3" s="157"/>
+      <c r="B3" s="162"/>
       <c r="C3" s="23" t="s">
         <v>15</v>
       </c>
@@ -2427,29 +2454,29 @@
       <c r="L3" s="29">
         <v>72.64</v>
       </c>
-      <c r="M3" s="166" t="s">
+      <c r="M3" s="154" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="167"/>
-      <c r="O3" s="168"/>
+      <c r="N3" s="155"/>
+      <c r="O3" s="156"/>
       <c r="P3" s="71"/>
       <c r="Q3" s="72"/>
-      <c r="R3" s="151" t="s">
+      <c r="R3" s="164" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="152"/>
-      <c r="T3" s="152"/>
-      <c r="U3" s="153"/>
-      <c r="V3" s="154" t="s">
+      <c r="S3" s="165"/>
+      <c r="T3" s="165"/>
+      <c r="U3" s="166"/>
+      <c r="V3" s="167" t="s">
         <v>17</v>
       </c>
-      <c r="W3" s="155"/>
-      <c r="X3" s="155"/>
-      <c r="Y3" s="156"/>
+      <c r="W3" s="168"/>
+      <c r="X3" s="168"/>
+      <c r="Y3" s="169"/>
     </row>
     <row r="4" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="169"/>
-      <c r="B4" s="150"/>
+      <c r="A4" s="157"/>
+      <c r="B4" s="163"/>
       <c r="C4" s="30" t="s">
         <v>18</v>
       </c>
@@ -6509,23 +6536,35 @@
       <c r="Y54" s="56"/>
     </row>
     <row r="55" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A55" s="78"/>
+      <c r="A55" s="140">
+        <v>46255</v>
+      </c>
       <c r="B55" s="47">
         <v>51</v>
       </c>
-      <c r="C55" s="57"/>
+      <c r="C55" s="57" t="s">
+        <v>128</v>
+      </c>
       <c r="D55" s="74"/>
       <c r="E55" s="75"/>
       <c r="F55" s="76"/>
       <c r="G55" s="50"/>
       <c r="H55" s="75"/>
-      <c r="I55" s="49"/>
-      <c r="J55" s="50"/>
-      <c r="K55" s="75"/>
-      <c r="L55" s="76"/>
+      <c r="I55" s="49">
+        <v>42</v>
+      </c>
+      <c r="J55" s="50">
+        <v>80</v>
+      </c>
+      <c r="K55" s="75">
+        <v>80</v>
+      </c>
+      <c r="L55" s="76">
+        <v>80</v>
+      </c>
       <c r="M55" s="48">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>7.05</v>
       </c>
       <c r="N55" s="39">
         <f t="shared" si="18"/>
@@ -6537,11 +6576,11 @@
       </c>
       <c r="P55" s="73">
         <f t="shared" si="84"/>
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q55" s="40">
         <f t="shared" si="85"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="R55" s="51"/>
       <c r="S55" s="52"/>
@@ -6559,23 +6598,39 @@
       <c r="Y55" s="56"/>
     </row>
     <row r="56" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A56" s="78"/>
+      <c r="A56" s="140">
+        <v>46255</v>
+      </c>
       <c r="B56" s="47">
         <v>52</v>
       </c>
-      <c r="C56" s="57"/>
+      <c r="C56" s="57" t="s">
+        <v>130</v>
+      </c>
       <c r="D56" s="74"/>
       <c r="E56" s="75"/>
       <c r="F56" s="76"/>
-      <c r="G56" s="50"/>
-      <c r="H56" s="75"/>
-      <c r="I56" s="49"/>
-      <c r="J56" s="50"/>
-      <c r="K56" s="75"/>
-      <c r="L56" s="76"/>
+      <c r="G56" s="50">
+        <v>160</v>
+      </c>
+      <c r="H56" s="75">
+        <v>200</v>
+      </c>
+      <c r="I56" s="49">
+        <v>80</v>
+      </c>
+      <c r="J56" s="50">
+        <v>400</v>
+      </c>
+      <c r="K56" s="75">
+        <v>280</v>
+      </c>
+      <c r="L56" s="76">
+        <v>640</v>
+      </c>
       <c r="M56" s="48">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="N56" s="39">
         <f t="shared" si="18"/>
@@ -6587,11 +6642,11 @@
       </c>
       <c r="P56" s="73">
         <f t="shared" si="84"/>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q56" s="40">
         <f t="shared" si="85"/>
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="R56" s="51"/>
       <c r="S56" s="52"/>
@@ -6609,23 +6664,39 @@
       <c r="Y56" s="56"/>
     </row>
     <row r="57" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A57" s="78"/>
+      <c r="A57" s="140">
+        <v>46255</v>
+      </c>
       <c r="B57" s="47">
         <v>53</v>
       </c>
-      <c r="C57" s="57"/>
+      <c r="C57" s="57" t="s">
+        <v>129</v>
+      </c>
       <c r="D57" s="74"/>
       <c r="E57" s="75"/>
       <c r="F57" s="76"/>
-      <c r="G57" s="50"/>
-      <c r="H57" s="75"/>
-      <c r="I57" s="49"/>
-      <c r="J57" s="50"/>
-      <c r="K57" s="75"/>
-      <c r="L57" s="76"/>
+      <c r="G57" s="50">
+        <v>40</v>
+      </c>
+      <c r="H57" s="75">
+        <v>40</v>
+      </c>
+      <c r="I57" s="49">
+        <v>40</v>
+      </c>
+      <c r="J57" s="50">
+        <v>80</v>
+      </c>
+      <c r="K57" s="75">
+        <v>80</v>
+      </c>
+      <c r="L57" s="76">
+        <v>80</v>
+      </c>
       <c r="M57" s="48">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N57" s="39">
         <f t="shared" si="18"/>
@@ -6637,11 +6708,11 @@
       </c>
       <c r="P57" s="73">
         <f t="shared" si="84"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q57" s="40">
         <f t="shared" si="85"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="R57" s="51"/>
       <c r="S57" s="52"/>
@@ -6659,23 +6730,33 @@
       <c r="Y57" s="56"/>
     </row>
     <row r="58" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A58" s="78"/>
+      <c r="A58" s="140">
+        <v>46255</v>
+      </c>
       <c r="B58" s="47">
         <v>54</v>
       </c>
-      <c r="C58" s="57"/>
+      <c r="C58" s="57" t="s">
+        <v>131</v>
+      </c>
       <c r="D58" s="75"/>
       <c r="E58" s="75"/>
       <c r="F58" s="75"/>
       <c r="G58" s="75"/>
       <c r="H58" s="75"/>
-      <c r="I58" s="127"/>
+      <c r="I58" s="127">
+        <v>80</v>
+      </c>
       <c r="J58" s="75"/>
-      <c r="K58" s="75"/>
-      <c r="L58" s="75"/>
+      <c r="K58" s="75">
+        <v>40</v>
+      </c>
+      <c r="L58" s="75">
+        <v>40</v>
+      </c>
       <c r="M58" s="129">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N58" s="39">
         <f t="shared" si="18"/>
@@ -6687,11 +6768,11 @@
       </c>
       <c r="P58" s="73">
         <f t="shared" si="84"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q58" s="40">
         <f t="shared" si="85"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R58" s="51"/>
       <c r="S58" s="52"/>
@@ -6709,12 +6790,18 @@
       <c r="Y58" s="56"/>
     </row>
     <row r="59" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A59" s="78"/>
+      <c r="A59" s="140">
+        <v>46255</v>
+      </c>
       <c r="B59" s="47">
         <v>55</v>
       </c>
-      <c r="C59" s="57"/>
-      <c r="D59" s="75"/>
+      <c r="C59" s="57" t="s">
+        <v>132</v>
+      </c>
+      <c r="D59" s="75">
+        <v>80</v>
+      </c>
       <c r="E59" s="75"/>
       <c r="F59" s="75"/>
       <c r="G59" s="75"/>
@@ -6725,7 +6812,7 @@
       <c r="L59" s="75"/>
       <c r="M59" s="129">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N59" s="39">
         <f t="shared" si="18"/>
@@ -6759,23 +6846,41 @@
       <c r="Y59" s="56"/>
     </row>
     <row r="60" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A60" s="78"/>
+      <c r="A60" s="140">
+        <v>46255</v>
+      </c>
       <c r="B60" s="47">
         <v>56</v>
       </c>
-      <c r="C60" s="57"/>
-      <c r="D60" s="75"/>
+      <c r="C60" s="57" t="s">
+        <v>133</v>
+      </c>
+      <c r="D60" s="75">
+        <v>80</v>
+      </c>
       <c r="E60" s="75"/>
       <c r="F60" s="75"/>
-      <c r="G60" s="75"/>
-      <c r="H60" s="75"/>
-      <c r="I60" s="127"/>
-      <c r="J60" s="75"/>
-      <c r="K60" s="75"/>
-      <c r="L60" s="75"/>
+      <c r="G60" s="75">
+        <v>160</v>
+      </c>
+      <c r="H60" s="75">
+        <v>80</v>
+      </c>
+      <c r="I60" s="127">
+        <v>160</v>
+      </c>
+      <c r="J60" s="75">
+        <v>160</v>
+      </c>
+      <c r="K60" s="75">
+        <v>80</v>
+      </c>
+      <c r="L60" s="75">
+        <v>160</v>
+      </c>
       <c r="M60" s="129">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N60" s="39">
         <f t="shared" si="18"/>
@@ -6787,11 +6892,11 @@
       </c>
       <c r="P60" s="73">
         <f t="shared" si="84"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Q60" s="40">
         <f t="shared" si="85"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="R60" s="51"/>
       <c r="S60" s="52"/>
@@ -6809,23 +6914,37 @@
       <c r="Y60" s="56"/>
     </row>
     <row r="61" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A61" s="78"/>
+      <c r="A61" s="140">
+        <v>46256</v>
+      </c>
       <c r="B61" s="47">
         <v>57</v>
       </c>
-      <c r="C61" s="57"/>
+      <c r="C61" s="57" t="s">
+        <v>134</v>
+      </c>
       <c r="D61" s="75"/>
       <c r="E61" s="75"/>
       <c r="F61" s="75"/>
-      <c r="G61" s="75"/>
-      <c r="H61" s="75"/>
+      <c r="G61" s="75">
+        <v>40</v>
+      </c>
+      <c r="H61" s="75">
+        <v>200</v>
+      </c>
       <c r="I61" s="127"/>
-      <c r="J61" s="75"/>
-      <c r="K61" s="75"/>
-      <c r="L61" s="75"/>
+      <c r="J61" s="75">
+        <v>120</v>
+      </c>
+      <c r="K61" s="75">
+        <v>40</v>
+      </c>
+      <c r="L61" s="75">
+        <v>160</v>
+      </c>
       <c r="M61" s="129">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N61" s="39">
         <f t="shared" si="18"/>
@@ -6837,11 +6956,11 @@
       </c>
       <c r="P61" s="73">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q61" s="40">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="R61" s="51" t="e">
         <f t="shared" si="4"/>
@@ -6877,23 +6996,39 @@
       </c>
     </row>
     <row r="62" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A62" s="78"/>
+      <c r="A62" s="140">
+        <v>46256</v>
+      </c>
       <c r="B62" s="47">
         <v>58</v>
       </c>
-      <c r="C62" s="128"/>
+      <c r="C62" s="128" t="s">
+        <v>135</v>
+      </c>
       <c r="D62" s="75"/>
       <c r="E62" s="75"/>
       <c r="F62" s="75"/>
-      <c r="G62" s="75"/>
-      <c r="H62" s="75"/>
-      <c r="I62" s="127"/>
-      <c r="J62" s="75"/>
-      <c r="K62" s="75"/>
-      <c r="L62" s="75"/>
+      <c r="G62" s="75">
+        <v>40</v>
+      </c>
+      <c r="H62" s="75">
+        <v>40</v>
+      </c>
+      <c r="I62" s="127">
+        <v>120</v>
+      </c>
+      <c r="J62" s="75">
+        <v>80</v>
+      </c>
+      <c r="K62" s="75">
+        <v>80</v>
+      </c>
+      <c r="L62" s="75">
+        <v>80</v>
+      </c>
       <c r="M62" s="129">
         <f t="shared" ref="M62:M84" si="88">SUM(D62:L62)/40</f>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="N62" s="39">
         <f t="shared" si="18"/>
@@ -6905,11 +7040,11 @@
       </c>
       <c r="P62" s="73">
         <f t="shared" ref="P62:P79" si="89">SUM(G62:I62)/20</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q62" s="40">
         <f t="shared" ref="Q62:Q79" si="90">SUM(J62:L62)/20</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="R62" s="51" t="e">
         <f t="shared" si="4"/>
@@ -6945,23 +7080,37 @@
       </c>
     </row>
     <row r="63" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A63" s="78"/>
+      <c r="A63" s="140">
+        <v>46256</v>
+      </c>
       <c r="B63" s="47">
         <v>59</v>
       </c>
-      <c r="C63" s="128"/>
+      <c r="C63" s="128" t="s">
+        <v>136</v>
+      </c>
       <c r="D63" s="75"/>
       <c r="E63" s="75"/>
       <c r="F63" s="75"/>
-      <c r="G63" s="75"/>
-      <c r="H63" s="75"/>
+      <c r="G63" s="75">
+        <v>80</v>
+      </c>
+      <c r="H63" s="75">
+        <v>40</v>
+      </c>
       <c r="I63" s="127"/>
-      <c r="J63" s="75"/>
-      <c r="K63" s="75"/>
-      <c r="L63" s="75"/>
+      <c r="J63" s="75">
+        <v>80</v>
+      </c>
+      <c r="K63" s="75">
+        <v>120</v>
+      </c>
+      <c r="L63" s="75">
+        <v>240</v>
+      </c>
       <c r="M63" s="129">
         <f t="shared" si="88"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N63" s="39">
         <f t="shared" si="18"/>
@@ -6973,11 +7122,11 @@
       </c>
       <c r="P63" s="73">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q63" s="40">
         <f t="shared" si="90"/>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="R63" s="51" t="e">
         <f t="shared" si="4"/>
@@ -11690,13 +11839,13 @@
     </row>
     <row r="133" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A133" s="78"/>
-      <c r="B133" s="157" t="s">
+      <c r="B133" s="170" t="s">
         <v>11</v>
       </c>
-      <c r="C133" s="158"/>
+      <c r="C133" s="171"/>
       <c r="D133" s="84">
         <f t="shared" ref="D133:L133" si="111">SUM(D6:D61)</f>
-        <v>6203</v>
+        <v>6363</v>
       </c>
       <c r="E133" s="84">
         <f t="shared" si="111"/>
@@ -11708,31 +11857,31 @@
       </c>
       <c r="G133" s="84">
         <f t="shared" si="111"/>
-        <v>6384</v>
+        <v>6784</v>
       </c>
       <c r="H133" s="84">
         <f t="shared" si="111"/>
-        <v>6379</v>
+        <v>6899</v>
       </c>
       <c r="I133" s="84">
         <f t="shared" si="111"/>
-        <v>10631</v>
+        <v>11033</v>
       </c>
       <c r="J133" s="84">
         <f t="shared" si="111"/>
-        <v>11687</v>
+        <v>12527</v>
       </c>
       <c r="K133" s="84">
         <f t="shared" si="111"/>
-        <v>11121</v>
+        <v>11721</v>
       </c>
       <c r="L133" s="84">
         <f t="shared" si="111"/>
-        <v>15748</v>
+        <v>16908</v>
       </c>
       <c r="M133" s="48">
         <f t="shared" ref="M133:M136" si="112">SUM(D133:L133)/40</f>
-        <v>1703.825</v>
+        <v>1805.875</v>
       </c>
       <c r="N133" s="39">
         <f t="shared" si="18"/>
@@ -11744,11 +11893,11 @@
       </c>
       <c r="P133" s="73">
         <f t="shared" ref="P133:P137" si="113">SUM(G133:I133)/20</f>
-        <v>1169.7</v>
+        <v>1235.8</v>
       </c>
       <c r="Q133" s="40">
         <f t="shared" ref="Q133:Q137" si="114">SUM(J133:L133)/20</f>
-        <v>1927.8</v>
+        <v>2057.8000000000002</v>
       </c>
       <c r="R133" s="51" t="e">
         <f t="shared" si="4"/>
@@ -11957,10 +12106,10 @@
       </c>
     </row>
     <row r="137" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B137" s="170" t="s">
+      <c r="B137" s="158" t="s">
         <v>70</v>
       </c>
-      <c r="C137" s="171"/>
+      <c r="C137" s="159"/>
       <c r="D137" s="83">
         <f>SUM(D135:D136)</f>
         <v>0</v>
@@ -12051,13 +12200,13 @@
       </c>
     </row>
     <row r="138" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B138" s="159" t="s">
+      <c r="B138" s="147" t="s">
         <v>11</v>
       </c>
-      <c r="C138" s="160"/>
+      <c r="C138" s="148"/>
       <c r="D138" s="85">
         <f>SUM(D133,D137)</f>
-        <v>6203</v>
+        <v>6363</v>
       </c>
       <c r="E138" s="85">
         <f t="shared" ref="E138:L138" si="119">SUM(E133,E137)</f>
@@ -12069,31 +12218,31 @@
       </c>
       <c r="G138" s="85">
         <f t="shared" si="119"/>
-        <v>6384</v>
+        <v>6784</v>
       </c>
       <c r="H138" s="85">
         <f t="shared" si="119"/>
-        <v>6379</v>
+        <v>6899</v>
       </c>
       <c r="I138" s="85">
         <f t="shared" si="119"/>
-        <v>10631</v>
+        <v>11033</v>
       </c>
       <c r="J138" s="85">
         <f t="shared" si="119"/>
-        <v>11687</v>
+        <v>12527</v>
       </c>
       <c r="K138" s="85">
         <f t="shared" si="119"/>
-        <v>11121</v>
+        <v>11721</v>
       </c>
       <c r="L138" s="85">
         <f t="shared" si="119"/>
-        <v>15748</v>
+        <v>16908</v>
       </c>
       <c r="M138" s="60">
         <f t="shared" si="0"/>
-        <v>1703.825</v>
+        <v>1805.875</v>
       </c>
       <c r="N138" s="63">
         <f>SUM(N5:N137)</f>
@@ -12105,11 +12254,11 @@
       </c>
       <c r="P138" s="62">
         <f t="shared" si="120"/>
-        <v>2345.4</v>
+        <v>2493.6</v>
       </c>
       <c r="Q138" s="64">
         <f t="shared" si="120"/>
-        <v>3859.6</v>
+        <v>4153.6000000000004</v>
       </c>
       <c r="R138" s="65" t="e">
         <f t="shared" si="120"/>
@@ -12146,17 +12295,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="R3:U3"/>
+    <mergeCell ref="V3:Y3"/>
+    <mergeCell ref="B133:C133"/>
     <mergeCell ref="B138:C138"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="P2:Q2"/>
     <mergeCell ref="M3:O3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B137:C137"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="R3:U3"/>
-    <mergeCell ref="V3:Y3"/>
-    <mergeCell ref="B133:C133"/>
   </mergeCells>
   <conditionalFormatting sqref="C46:C60">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
@@ -12256,24 +12405,24 @@
         <v>49</v>
       </c>
       <c r="D5" s="88">
-        <v>577</v>
+        <v>658</v>
       </c>
       <c r="E5" s="79">
-        <v>1165</v>
+        <v>1293</v>
       </c>
       <c r="F5" s="79">
         <v>600</v>
       </c>
       <c r="G5" s="102">
         <f>SUM(D5:F5)</f>
-        <v>2342</v>
+        <v>2551</v>
       </c>
       <c r="H5" s="95">
         <v>10000</v>
       </c>
       <c r="I5" s="96">
         <f>G5-H5</f>
-        <v>-7658</v>
+        <v>-7449</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>1</v>
@@ -12296,11 +12445,11 @@
       </c>
       <c r="D6" s="104">
         <f>D5*40</f>
-        <v>23080</v>
+        <v>26320</v>
       </c>
       <c r="E6" s="104">
         <f t="shared" ref="E6:F6" si="1">E5*40</f>
-        <v>46600</v>
+        <v>51720</v>
       </c>
       <c r="F6" s="104">
         <f t="shared" si="1"/>
@@ -12308,7 +12457,7 @@
       </c>
       <c r="G6" s="105">
         <f>SUM(D6:F6)</f>
-        <v>93680</v>
+        <v>102040</v>
       </c>
       <c r="H6" s="97">
         <f>H5*40</f>
@@ -12316,7 +12465,7 @@
       </c>
       <c r="I6" s="98">
         <f>G6-H6</f>
-        <v>-306320</v>
+        <v>-297960</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>2</v>
@@ -12441,11 +12590,11 @@
       </c>
       <c r="D9" s="106">
         <f>D8-D5</f>
-        <v>-577</v>
+        <v>-658</v>
       </c>
       <c r="E9" s="106">
         <f>E8-E5</f>
-        <v>-1165</v>
+        <v>-1293</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>5</v>
@@ -12586,7 +12735,7 @@
       </c>
       <c r="G12" s="91">
         <f>D12+G5</f>
-        <v>6542</v>
+        <v>6751</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>11</v>
@@ -12637,7 +12786,7 @@
       </c>
       <c r="G13" s="91">
         <f>G12*40</f>
-        <v>261680</v>
+        <v>270040</v>
       </c>
       <c r="S13" s="172" t="s">
         <v>85</v>

--- a/Aug_2026/daily Reports/LMT Orders.xlsx
+++ b/Aug_2026/daily Reports/LMT Orders.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD820C4D-44C5-4DA4-8609-6B1DBAC86601}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AC59D48-595D-4CB3-BBB7-571158EB960A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="139">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -433,6 +433,12 @@
   </si>
   <si>
     <t>Rainbow CNC DHA</t>
+  </si>
+  <si>
+    <t>LGS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RI Mart Jore Pull </t>
   </si>
 </sst>
 </file>
@@ -1321,7 +1327,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="181">
+  <cellXfs count="186">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1695,6 +1701,17 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2332,14 +2349,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="160">
+      <c r="B1" s="165">
         <f ca="1">TODAY()</f>
-        <v>46258</v>
-      </c>
-      <c r="C1" s="160"/>
-      <c r="D1" s="160"/>
-      <c r="E1" s="160"/>
-      <c r="F1" s="160"/>
+        <v>46259</v>
+      </c>
+      <c r="C1" s="165"/>
+      <c r="D1" s="165"/>
+      <c r="E1" s="165"/>
+      <c r="F1" s="165"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
       <c r="I1" s="10"/>
@@ -2361,10 +2378,10 @@
       <c r="Y1" s="10"/>
     </row>
     <row r="2" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="157" t="s">
+      <c r="A2" s="162" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="161" t="s">
+      <c r="B2" s="166" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2397,13 +2414,13 @@
       <c r="L2" s="15">
         <v>120</v>
       </c>
-      <c r="M2" s="149"/>
-      <c r="N2" s="150"/>
-      <c r="O2" s="151"/>
-      <c r="P2" s="152" t="s">
+      <c r="M2" s="154"/>
+      <c r="N2" s="155"/>
+      <c r="O2" s="156"/>
+      <c r="P2" s="157" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="153"/>
+      <c r="Q2" s="158"/>
       <c r="R2" s="18">
         <v>0.05</v>
       </c>
@@ -2422,8 +2439,8 @@
       <c r="Y2" s="20"/>
     </row>
     <row r="3" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="157"/>
-      <c r="B3" s="162"/>
+      <c r="A3" s="162"/>
+      <c r="B3" s="167"/>
       <c r="C3" s="23" t="s">
         <v>15</v>
       </c>
@@ -2454,29 +2471,29 @@
       <c r="L3" s="29">
         <v>72.64</v>
       </c>
-      <c r="M3" s="154" t="s">
+      <c r="M3" s="159" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="155"/>
-      <c r="O3" s="156"/>
+      <c r="N3" s="160"/>
+      <c r="O3" s="161"/>
       <c r="P3" s="71"/>
       <c r="Q3" s="72"/>
-      <c r="R3" s="164" t="s">
+      <c r="R3" s="169" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="165"/>
-      <c r="T3" s="165"/>
-      <c r="U3" s="166"/>
-      <c r="V3" s="167" t="s">
+      <c r="S3" s="170"/>
+      <c r="T3" s="170"/>
+      <c r="U3" s="171"/>
+      <c r="V3" s="172" t="s">
         <v>17</v>
       </c>
-      <c r="W3" s="168"/>
-      <c r="X3" s="168"/>
-      <c r="Y3" s="169"/>
+      <c r="W3" s="173"/>
+      <c r="X3" s="173"/>
+      <c r="Y3" s="174"/>
     </row>
     <row r="4" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="157"/>
-      <c r="B4" s="163"/>
+      <c r="A4" s="162"/>
+      <c r="B4" s="168"/>
       <c r="C4" s="30" t="s">
         <v>18</v>
       </c>
@@ -6224,34 +6241,34 @@
       <c r="Y49" s="56"/>
     </row>
     <row r="50" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A50" s="140">
+      <c r="A50" s="78">
         <v>46254</v>
       </c>
       <c r="B50" s="47">
         <v>46</v>
       </c>
-      <c r="C50" s="142" t="s">
+      <c r="C50" s="57" t="s">
         <v>64</v>
       </c>
-      <c r="D50" s="143"/>
-      <c r="E50" s="144"/>
-      <c r="F50" s="145"/>
-      <c r="G50" s="146">
+      <c r="D50" s="74"/>
+      <c r="E50" s="75"/>
+      <c r="F50" s="76"/>
+      <c r="G50" s="50">
         <v>120</v>
       </c>
-      <c r="H50" s="144">
+      <c r="H50" s="75">
         <v>40</v>
       </c>
-      <c r="I50" s="56">
+      <c r="I50" s="49">
         <v>520</v>
       </c>
-      <c r="J50" s="146">
+      <c r="J50" s="50">
         <v>279</v>
       </c>
-      <c r="K50" s="144">
+      <c r="K50" s="75">
         <v>120</v>
       </c>
-      <c r="L50" s="145">
+      <c r="L50" s="76">
         <v>240</v>
       </c>
       <c r="M50" s="48">
@@ -6290,34 +6307,34 @@
       <c r="Y50" s="56"/>
     </row>
     <row r="51" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A51" s="140">
+      <c r="A51" s="78">
         <v>46254</v>
       </c>
       <c r="B51" s="47">
         <v>47</v>
       </c>
-      <c r="C51" s="142" t="s">
+      <c r="C51" s="57" t="s">
         <v>97</v>
       </c>
-      <c r="D51" s="143"/>
-      <c r="E51" s="144"/>
-      <c r="F51" s="145"/>
-      <c r="G51" s="146">
+      <c r="D51" s="74"/>
+      <c r="E51" s="75"/>
+      <c r="F51" s="76"/>
+      <c r="G51" s="50">
         <v>40</v>
       </c>
-      <c r="H51" s="144">
+      <c r="H51" s="75">
         <v>80</v>
       </c>
-      <c r="I51" s="56">
+      <c r="I51" s="49">
         <v>80</v>
       </c>
-      <c r="J51" s="146">
+      <c r="J51" s="50">
         <v>40</v>
       </c>
-      <c r="K51" s="144">
+      <c r="K51" s="75">
         <v>40</v>
       </c>
-      <c r="L51" s="145">
+      <c r="L51" s="76">
         <v>80</v>
       </c>
       <c r="M51" s="48">
@@ -6356,26 +6373,26 @@
       <c r="Y51" s="56"/>
     </row>
     <row r="52" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A52" s="140">
+      <c r="A52" s="78">
         <v>46254</v>
       </c>
       <c r="B52" s="47">
         <v>48</v>
       </c>
-      <c r="C52" s="142" t="s">
+      <c r="C52" s="57" t="s">
         <v>92</v>
       </c>
-      <c r="D52" s="143"/>
-      <c r="E52" s="144"/>
-      <c r="F52" s="145"/>
-      <c r="G52" s="146"/>
-      <c r="H52" s="144"/>
-      <c r="I52" s="56">
+      <c r="D52" s="74"/>
+      <c r="E52" s="75"/>
+      <c r="F52" s="76"/>
+      <c r="G52" s="50"/>
+      <c r="H52" s="75"/>
+      <c r="I52" s="49">
         <v>240</v>
       </c>
-      <c r="J52" s="146"/>
-      <c r="K52" s="144"/>
-      <c r="L52" s="145">
+      <c r="J52" s="50"/>
+      <c r="K52" s="75"/>
+      <c r="L52" s="76">
         <v>360</v>
       </c>
       <c r="M52" s="48">
@@ -6414,30 +6431,30 @@
       <c r="Y52" s="56"/>
     </row>
     <row r="53" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A53" s="140">
+      <c r="A53" s="78">
         <v>46254</v>
       </c>
       <c r="B53" s="47">
         <v>49</v>
       </c>
-      <c r="C53" s="142" t="s">
+      <c r="C53" s="57" t="s">
         <v>96</v>
       </c>
-      <c r="D53" s="143"/>
-      <c r="E53" s="144"/>
-      <c r="F53" s="145"/>
-      <c r="G53" s="146">
+      <c r="D53" s="74"/>
+      <c r="E53" s="75"/>
+      <c r="F53" s="76"/>
+      <c r="G53" s="50">
         <v>200</v>
       </c>
-      <c r="H53" s="144"/>
-      <c r="I53" s="56">
+      <c r="H53" s="75"/>
+      <c r="I53" s="49">
         <v>194</v>
       </c>
-      <c r="J53" s="146">
+      <c r="J53" s="50">
         <v>200</v>
       </c>
-      <c r="K53" s="144"/>
-      <c r="L53" s="145">
+      <c r="K53" s="75"/>
+      <c r="L53" s="76">
         <v>180</v>
       </c>
       <c r="M53" s="48">
@@ -6476,28 +6493,28 @@
       <c r="Y53" s="56"/>
     </row>
     <row r="54" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A54" s="140">
+      <c r="A54" s="78">
         <v>46254</v>
       </c>
       <c r="B54" s="47">
         <v>50</v>
       </c>
-      <c r="C54" s="142" t="s">
+      <c r="C54" s="57" t="s">
         <v>127</v>
       </c>
-      <c r="D54" s="143"/>
-      <c r="E54" s="144"/>
-      <c r="F54" s="145"/>
-      <c r="G54" s="146"/>
-      <c r="H54" s="144"/>
-      <c r="I54" s="56"/>
-      <c r="J54" s="146">
+      <c r="D54" s="74"/>
+      <c r="E54" s="75"/>
+      <c r="F54" s="76"/>
+      <c r="G54" s="50"/>
+      <c r="H54" s="75"/>
+      <c r="I54" s="49"/>
+      <c r="J54" s="50">
         <v>400</v>
       </c>
-      <c r="K54" s="144">
+      <c r="K54" s="75">
         <v>400</v>
       </c>
-      <c r="L54" s="145">
+      <c r="L54" s="76">
         <v>400</v>
       </c>
       <c r="M54" s="48">
@@ -6536,7 +6553,7 @@
       <c r="Y54" s="56"/>
     </row>
     <row r="55" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A55" s="140">
+      <c r="A55" s="78">
         <v>46255</v>
       </c>
       <c r="B55" s="47">
@@ -6598,7 +6615,7 @@
       <c r="Y55" s="56"/>
     </row>
     <row r="56" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A56" s="140">
+      <c r="A56" s="78">
         <v>46255</v>
       </c>
       <c r="B56" s="47">
@@ -6664,7 +6681,7 @@
       <c r="Y56" s="56"/>
     </row>
     <row r="57" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A57" s="140">
+      <c r="A57" s="78">
         <v>46255</v>
       </c>
       <c r="B57" s="47">
@@ -6730,7 +6747,7 @@
       <c r="Y57" s="56"/>
     </row>
     <row r="58" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A58" s="140">
+      <c r="A58" s="78">
         <v>46255</v>
       </c>
       <c r="B58" s="47">
@@ -6790,7 +6807,7 @@
       <c r="Y58" s="56"/>
     </row>
     <row r="59" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A59" s="140">
+      <c r="A59" s="78">
         <v>46255</v>
       </c>
       <c r="B59" s="47">
@@ -6846,7 +6863,7 @@
       <c r="Y59" s="56"/>
     </row>
     <row r="60" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A60" s="140">
+      <c r="A60" s="78">
         <v>46255</v>
       </c>
       <c r="B60" s="47">
@@ -6914,7 +6931,7 @@
       <c r="Y60" s="56"/>
     </row>
     <row r="61" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A61" s="140">
+      <c r="A61" s="78">
         <v>46256</v>
       </c>
       <c r="B61" s="47">
@@ -6996,7 +7013,7 @@
       </c>
     </row>
     <row r="62" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A62" s="140">
+      <c r="A62" s="78">
         <v>46256</v>
       </c>
       <c r="B62" s="47">
@@ -7080,7 +7097,7 @@
       </c>
     </row>
     <row r="63" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A63" s="140">
+      <c r="A63" s="78">
         <v>46256</v>
       </c>
       <c r="B63" s="47">
@@ -7162,23 +7179,39 @@
       </c>
     </row>
     <row r="64" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A64" s="78"/>
-      <c r="B64" s="47">
+      <c r="A64" s="147">
+        <v>46258</v>
+      </c>
+      <c r="B64" s="148">
         <v>60</v>
       </c>
-      <c r="C64" s="128"/>
-      <c r="D64" s="75"/>
-      <c r="E64" s="75"/>
-      <c r="F64" s="75"/>
-      <c r="G64" s="75"/>
-      <c r="H64" s="75"/>
-      <c r="I64" s="127"/>
-      <c r="J64" s="75"/>
-      <c r="K64" s="75"/>
-      <c r="L64" s="75"/>
+      <c r="C64" s="149" t="s">
+        <v>64</v>
+      </c>
+      <c r="D64" s="150"/>
+      <c r="E64" s="150"/>
+      <c r="F64" s="150"/>
+      <c r="G64" s="150">
+        <v>80</v>
+      </c>
+      <c r="H64" s="150">
+        <v>80</v>
+      </c>
+      <c r="I64" s="151">
+        <v>240</v>
+      </c>
+      <c r="J64" s="150">
+        <v>80</v>
+      </c>
+      <c r="K64" s="150">
+        <v>80</v>
+      </c>
+      <c r="L64" s="150">
+        <v>100</v>
+      </c>
       <c r="M64" s="129">
         <f t="shared" si="88"/>
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="N64" s="39">
         <f t="shared" si="18"/>
@@ -7190,11 +7223,11 @@
       </c>
       <c r="P64" s="73">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Q64" s="40">
         <f t="shared" si="90"/>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="R64" s="51" t="e">
         <f t="shared" si="4"/>
@@ -7230,23 +7263,33 @@
       </c>
     </row>
     <row r="65" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A65" s="78"/>
-      <c r="B65" s="47">
+      <c r="A65" s="147">
+        <v>46258</v>
+      </c>
+      <c r="B65" s="148">
         <v>61</v>
       </c>
-      <c r="C65" s="128"/>
-      <c r="D65" s="75"/>
-      <c r="E65" s="75"/>
-      <c r="F65" s="75"/>
-      <c r="G65" s="75"/>
-      <c r="H65" s="75"/>
-      <c r="I65" s="127"/>
-      <c r="J65" s="75"/>
-      <c r="K65" s="75"/>
-      <c r="L65" s="75"/>
+      <c r="C65" s="149" t="s">
+        <v>137</v>
+      </c>
+      <c r="D65" s="150"/>
+      <c r="E65" s="150"/>
+      <c r="F65" s="150"/>
+      <c r="G65" s="150"/>
+      <c r="H65" s="150"/>
+      <c r="I65" s="151"/>
+      <c r="J65" s="150">
+        <v>40</v>
+      </c>
+      <c r="K65" s="150">
+        <v>40</v>
+      </c>
+      <c r="L65" s="150">
+        <v>40</v>
+      </c>
       <c r="M65" s="129">
         <f t="shared" si="88"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N65" s="39">
         <f t="shared" si="18"/>
@@ -7262,7 +7305,7 @@
       </c>
       <c r="Q65" s="40">
         <f t="shared" si="90"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R65" s="51" t="e">
         <f t="shared" si="4"/>
@@ -7298,23 +7341,35 @@
       </c>
     </row>
     <row r="66" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A66" s="78"/>
-      <c r="B66" s="47">
+      <c r="A66" s="147">
+        <v>46258</v>
+      </c>
+      <c r="B66" s="148">
         <v>62</v>
       </c>
-      <c r="C66" s="128"/>
-      <c r="D66" s="75"/>
-      <c r="E66" s="75"/>
-      <c r="F66" s="75"/>
-      <c r="G66" s="75"/>
-      <c r="H66" s="75"/>
-      <c r="I66" s="127"/>
-      <c r="J66" s="75"/>
-      <c r="K66" s="75"/>
-      <c r="L66" s="75"/>
+      <c r="C66" s="149" t="s">
+        <v>109</v>
+      </c>
+      <c r="D66" s="150"/>
+      <c r="E66" s="150"/>
+      <c r="F66" s="150"/>
+      <c r="G66" s="150">
+        <v>39</v>
+      </c>
+      <c r="H66" s="150">
+        <v>40</v>
+      </c>
+      <c r="I66" s="151"/>
+      <c r="J66" s="150"/>
+      <c r="K66" s="150">
+        <v>40</v>
+      </c>
+      <c r="L66" s="150">
+        <v>40</v>
+      </c>
       <c r="M66" s="129">
         <f t="shared" si="88"/>
-        <v>0</v>
+        <v>3.9750000000000001</v>
       </c>
       <c r="N66" s="39">
         <f t="shared" si="18"/>
@@ -7326,11 +7381,11 @@
       </c>
       <c r="P66" s="73">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="Q66" s="40">
         <f t="shared" si="90"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R66" s="51" t="e">
         <f t="shared" si="4"/>
@@ -7366,23 +7421,33 @@
       </c>
     </row>
     <row r="67" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A67" s="78"/>
-      <c r="B67" s="47">
+      <c r="A67" s="147">
+        <v>46258</v>
+      </c>
+      <c r="B67" s="148">
         <v>63</v>
       </c>
-      <c r="C67" s="128"/>
-      <c r="D67" s="75"/>
-      <c r="E67" s="75"/>
-      <c r="F67" s="75"/>
-      <c r="G67" s="75"/>
-      <c r="H67" s="75"/>
-      <c r="I67" s="127"/>
-      <c r="J67" s="75"/>
-      <c r="K67" s="75"/>
-      <c r="L67" s="75"/>
+      <c r="C67" s="149" t="s">
+        <v>107</v>
+      </c>
+      <c r="D67" s="150"/>
+      <c r="E67" s="150"/>
+      <c r="F67" s="150"/>
+      <c r="G67" s="150"/>
+      <c r="H67" s="150"/>
+      <c r="I67" s="151"/>
+      <c r="J67" s="150">
+        <v>80</v>
+      </c>
+      <c r="K67" s="150">
+        <v>40</v>
+      </c>
+      <c r="L67" s="150">
+        <v>40</v>
+      </c>
       <c r="M67" s="129">
         <f t="shared" si="88"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N67" s="39">
         <f t="shared" si="18"/>
@@ -7398,7 +7463,7 @@
       </c>
       <c r="Q67" s="40">
         <f t="shared" si="90"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R67" s="51" t="e">
         <f t="shared" si="4"/>
@@ -7434,23 +7499,41 @@
       </c>
     </row>
     <row r="68" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A68" s="78"/>
-      <c r="B68" s="47">
+      <c r="A68" s="147">
+        <v>46258</v>
+      </c>
+      <c r="B68" s="148">
         <v>64</v>
       </c>
-      <c r="C68" s="128"/>
-      <c r="D68" s="75"/>
-      <c r="E68" s="75"/>
-      <c r="F68" s="75"/>
-      <c r="G68" s="75"/>
-      <c r="H68" s="75"/>
-      <c r="I68" s="127"/>
-      <c r="J68" s="75"/>
-      <c r="K68" s="75"/>
-      <c r="L68" s="75"/>
+      <c r="C68" s="149" t="s">
+        <v>138</v>
+      </c>
+      <c r="D68" s="150">
+        <v>40</v>
+      </c>
+      <c r="E68" s="150"/>
+      <c r="F68" s="150"/>
+      <c r="G68" s="150">
+        <v>80</v>
+      </c>
+      <c r="H68" s="150">
+        <v>80</v>
+      </c>
+      <c r="I68" s="151">
+        <v>80</v>
+      </c>
+      <c r="J68" s="150">
+        <v>80</v>
+      </c>
+      <c r="K68" s="150">
+        <v>80</v>
+      </c>
+      <c r="L68" s="150">
+        <v>80</v>
+      </c>
       <c r="M68" s="129">
         <f t="shared" si="88"/>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="N68" s="39">
         <f t="shared" si="18"/>
@@ -7462,11 +7545,11 @@
       </c>
       <c r="P68" s="73">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q68" s="40">
         <f t="shared" si="90"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="R68" s="51" t="e">
         <f t="shared" si="4"/>
@@ -11839,10 +11922,10 @@
     </row>
     <row r="133" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A133" s="78"/>
-      <c r="B133" s="170" t="s">
+      <c r="B133" s="175" t="s">
         <v>11</v>
       </c>
-      <c r="C133" s="171"/>
+      <c r="C133" s="176"/>
       <c r="D133" s="84">
         <f t="shared" ref="D133:L133" si="111">SUM(D6:D61)</f>
         <v>6363</v>
@@ -12106,10 +12189,10 @@
       </c>
     </row>
     <row r="137" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B137" s="158" t="s">
+      <c r="B137" s="163" t="s">
         <v>70</v>
       </c>
-      <c r="C137" s="159"/>
+      <c r="C137" s="164"/>
       <c r="D137" s="83">
         <f>SUM(D135:D136)</f>
         <v>0</v>
@@ -12200,10 +12283,10 @@
       </c>
     </row>
     <row r="138" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B138" s="147" t="s">
+      <c r="B138" s="152" t="s">
         <v>11</v>
       </c>
-      <c r="C138" s="148"/>
+      <c r="C138" s="153"/>
       <c r="D138" s="85">
         <f>SUM(D133,D137)</f>
         <v>6363</v>
@@ -12254,11 +12337,11 @@
       </c>
       <c r="P138" s="62">
         <f t="shared" si="120"/>
-        <v>2493.6</v>
+        <v>2529.5500000000002</v>
       </c>
       <c r="Q138" s="64">
         <f t="shared" si="120"/>
-        <v>4153.6000000000004</v>
+        <v>4196.6000000000004</v>
       </c>
       <c r="R138" s="65" t="e">
         <f t="shared" si="120"/>
@@ -12341,25 +12424,25 @@
   <sheetData>
     <row r="2" spans="3:26" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="3:26" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C3" s="174" t="s">
+      <c r="C3" s="179" t="s">
         <v>117</v>
       </c>
-      <c r="D3" s="175"/>
-      <c r="E3" s="175"/>
-      <c r="F3" s="175"/>
-      <c r="G3" s="176"/>
-      <c r="H3" s="178" t="s">
+      <c r="D3" s="180"/>
+      <c r="E3" s="180"/>
+      <c r="F3" s="180"/>
+      <c r="G3" s="181"/>
+      <c r="H3" s="183" t="s">
         <v>62</v>
       </c>
-      <c r="I3" s="179"/>
-      <c r="K3" s="180" t="s">
+      <c r="I3" s="184"/>
+      <c r="K3" s="185" t="s">
         <v>66</v>
       </c>
-      <c r="L3" s="180"/>
-      <c r="M3" s="180"/>
-      <c r="N3" s="180"/>
-      <c r="O3" s="180"/>
-      <c r="P3" s="180"/>
+      <c r="L3" s="185"/>
+      <c r="M3" s="185"/>
+      <c r="N3" s="185"/>
+      <c r="O3" s="185"/>
+      <c r="P3" s="185"/>
     </row>
     <row r="4" spans="3:26" ht="29.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C4" s="99"/>
@@ -12405,24 +12488,24 @@
         <v>49</v>
       </c>
       <c r="D5" s="88">
-        <v>658</v>
+        <v>705</v>
       </c>
       <c r="E5" s="79">
-        <v>1293</v>
+        <v>1333</v>
       </c>
       <c r="F5" s="79">
         <v>600</v>
       </c>
       <c r="G5" s="102">
         <f>SUM(D5:F5)</f>
-        <v>2551</v>
+        <v>2638</v>
       </c>
       <c r="H5" s="95">
         <v>10000</v>
       </c>
       <c r="I5" s="96">
         <f>G5-H5</f>
-        <v>-7449</v>
+        <v>-7362</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>1</v>
@@ -12445,11 +12528,11 @@
       </c>
       <c r="D6" s="104">
         <f>D5*40</f>
-        <v>26320</v>
+        <v>28200</v>
       </c>
       <c r="E6" s="104">
         <f t="shared" ref="E6:F6" si="1">E5*40</f>
-        <v>51720</v>
+        <v>53320</v>
       </c>
       <c r="F6" s="104">
         <f t="shared" si="1"/>
@@ -12457,7 +12540,7 @@
       </c>
       <c r="G6" s="105">
         <f>SUM(D6:F6)</f>
-        <v>102040</v>
+        <v>105520</v>
       </c>
       <c r="H6" s="97">
         <f>H5*40</f>
@@ -12465,7 +12548,7 @@
       </c>
       <c r="I6" s="98">
         <f>G6-H6</f>
-        <v>-297960</v>
+        <v>-294480</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>2</v>
@@ -12590,11 +12673,11 @@
       </c>
       <c r="D9" s="106">
         <f>D8-D5</f>
-        <v>-658</v>
+        <v>-705</v>
       </c>
       <c r="E9" s="106">
         <f>E8-E5</f>
-        <v>-1293</v>
+        <v>-1333</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>5</v>
@@ -12676,14 +12759,14 @@
       </c>
     </row>
     <row r="11" spans="3:26" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C11" s="177" t="s">
+      <c r="C11" s="182" t="s">
         <v>59</v>
       </c>
-      <c r="D11" s="177"/>
-      <c r="F11" s="177" t="s">
+      <c r="D11" s="182"/>
+      <c r="F11" s="182" t="s">
         <v>68</v>
       </c>
-      <c r="G11" s="177"/>
+      <c r="G11" s="182"/>
       <c r="K11" s="1" t="s">
         <v>7</v>
       </c>
@@ -12735,7 +12818,7 @@
       </c>
       <c r="G12" s="91">
         <f>D12+G5</f>
-        <v>6751</v>
+        <v>6838</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>11</v>
@@ -12786,12 +12869,12 @@
       </c>
       <c r="G13" s="91">
         <f>G12*40</f>
-        <v>270040</v>
-      </c>
-      <c r="S13" s="172" t="s">
+        <v>273520</v>
+      </c>
+      <c r="S13" s="177" t="s">
         <v>85</v>
       </c>
-      <c r="T13" s="172"/>
+      <c r="T13" s="177"/>
       <c r="U13" s="135">
         <f>SUM(U8:U12)</f>
         <v>100</v>
@@ -12880,13 +12963,13 @@
       </c>
     </row>
     <row r="20" spans="4:15" ht="24" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="D20" s="173" t="s">
+      <c r="D20" s="178" t="s">
         <v>66</v>
       </c>
-      <c r="E20" s="173"/>
-      <c r="F20" s="173"/>
-      <c r="G20" s="173"/>
-      <c r="H20" s="173"/>
+      <c r="E20" s="178"/>
+      <c r="F20" s="178"/>
+      <c r="G20" s="178"/>
+      <c r="H20" s="178"/>
       <c r="K20" s="1" t="s">
         <v>4</v>
       </c>

--- a/Aug_2026/daily Reports/LMT Orders.xlsx
+++ b/Aug_2026/daily Reports/LMT Orders.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AC59D48-595D-4CB3-BBB7-571158EB960A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9811DE72-3340-43AB-86B1-AD4772998ED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="142">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -439,6 +439,15 @@
   </si>
   <si>
     <t xml:space="preserve">RI Mart Jore Pull </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Risen Manawan </t>
+  </si>
+  <si>
+    <t>Rainbow Sheikhupura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pak Madina </t>
   </si>
 </sst>
 </file>
@@ -1712,6 +1721,42 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1749,42 +1794,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2349,14 +2358,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="165">
+      <c r="B1" s="152">
         <f ca="1">TODAY()</f>
-        <v>46259</v>
-      </c>
-      <c r="C1" s="165"/>
-      <c r="D1" s="165"/>
-      <c r="E1" s="165"/>
-      <c r="F1" s="165"/>
+        <v>46261</v>
+      </c>
+      <c r="C1" s="152"/>
+      <c r="D1" s="152"/>
+      <c r="E1" s="152"/>
+      <c r="F1" s="152"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
       <c r="I1" s="10"/>
@@ -2378,10 +2387,10 @@
       <c r="Y1" s="10"/>
     </row>
     <row r="2" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="162" t="s">
+      <c r="A2" s="174" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="166" t="s">
+      <c r="B2" s="153" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2414,13 +2423,13 @@
       <c r="L2" s="15">
         <v>120</v>
       </c>
-      <c r="M2" s="154"/>
-      <c r="N2" s="155"/>
-      <c r="O2" s="156"/>
-      <c r="P2" s="157" t="s">
+      <c r="M2" s="166"/>
+      <c r="N2" s="167"/>
+      <c r="O2" s="168"/>
+      <c r="P2" s="169" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="158"/>
+      <c r="Q2" s="170"/>
       <c r="R2" s="18">
         <v>0.05</v>
       </c>
@@ -2439,8 +2448,8 @@
       <c r="Y2" s="20"/>
     </row>
     <row r="3" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="162"/>
-      <c r="B3" s="167"/>
+      <c r="A3" s="174"/>
+      <c r="B3" s="154"/>
       <c r="C3" s="23" t="s">
         <v>15</v>
       </c>
@@ -2471,29 +2480,29 @@
       <c r="L3" s="29">
         <v>72.64</v>
       </c>
-      <c r="M3" s="159" t="s">
+      <c r="M3" s="171" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="160"/>
-      <c r="O3" s="161"/>
+      <c r="N3" s="172"/>
+      <c r="O3" s="173"/>
       <c r="P3" s="71"/>
       <c r="Q3" s="72"/>
-      <c r="R3" s="169" t="s">
+      <c r="R3" s="156" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="170"/>
-      <c r="T3" s="170"/>
-      <c r="U3" s="171"/>
-      <c r="V3" s="172" t="s">
+      <c r="S3" s="157"/>
+      <c r="T3" s="157"/>
+      <c r="U3" s="158"/>
+      <c r="V3" s="159" t="s">
         <v>17</v>
       </c>
-      <c r="W3" s="173"/>
-      <c r="X3" s="173"/>
-      <c r="Y3" s="174"/>
+      <c r="W3" s="160"/>
+      <c r="X3" s="160"/>
+      <c r="Y3" s="161"/>
     </row>
     <row r="4" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="162"/>
-      <c r="B4" s="168"/>
+      <c r="A4" s="174"/>
+      <c r="B4" s="155"/>
       <c r="C4" s="30" t="s">
         <v>18</v>
       </c>
@@ -7585,23 +7594,31 @@
       </c>
     </row>
     <row r="69" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A69" s="78"/>
+      <c r="A69" s="78">
+        <v>46259</v>
+      </c>
       <c r="B69" s="47">
         <v>65</v>
       </c>
-      <c r="C69" s="128"/>
+      <c r="C69" s="128" t="s">
+        <v>139</v>
+      </c>
       <c r="D69" s="75"/>
       <c r="E69" s="75"/>
       <c r="F69" s="75"/>
       <c r="G69" s="75"/>
       <c r="H69" s="75"/>
-      <c r="I69" s="127"/>
+      <c r="I69" s="127">
+        <v>80</v>
+      </c>
       <c r="J69" s="75"/>
       <c r="K69" s="75"/>
-      <c r="L69" s="75"/>
+      <c r="L69" s="75">
+        <v>80</v>
+      </c>
       <c r="M69" s="129">
         <f t="shared" si="88"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N69" s="39">
         <f t="shared" si="18"/>
@@ -7613,11 +7630,11 @@
       </c>
       <c r="P69" s="73">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q69" s="40">
         <f t="shared" si="90"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R69" s="51" t="e">
         <f t="shared" si="4"/>
@@ -7653,23 +7670,33 @@
       </c>
     </row>
     <row r="70" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A70" s="78"/>
+      <c r="A70" s="78">
+        <v>46259</v>
+      </c>
       <c r="B70" s="47">
         <v>66</v>
       </c>
-      <c r="C70" s="128"/>
+      <c r="C70" s="128" t="s">
+        <v>100</v>
+      </c>
       <c r="D70" s="75"/>
       <c r="E70" s="75"/>
       <c r="F70" s="75"/>
-      <c r="G70" s="75"/>
-      <c r="H70" s="75"/>
+      <c r="G70" s="75">
+        <v>40</v>
+      </c>
+      <c r="H70" s="75">
+        <v>40</v>
+      </c>
       <c r="I70" s="127"/>
       <c r="J70" s="75"/>
       <c r="K70" s="75"/>
-      <c r="L70" s="75"/>
+      <c r="L70" s="75">
+        <v>80</v>
+      </c>
       <c r="M70" s="129">
         <f t="shared" si="88"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N70" s="39">
         <f t="shared" si="18"/>
@@ -7681,11 +7708,11 @@
       </c>
       <c r="P70" s="73">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q70" s="40">
         <f t="shared" si="90"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R70" s="51" t="e">
         <f t="shared" si="4"/>
@@ -7721,11 +7748,15 @@
       </c>
     </row>
     <row r="71" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A71" s="78"/>
+      <c r="A71" s="78">
+        <v>46259</v>
+      </c>
       <c r="B71" s="47">
         <v>67</v>
       </c>
-      <c r="C71" s="128"/>
+      <c r="C71" s="128" t="s">
+        <v>98</v>
+      </c>
       <c r="D71" s="75"/>
       <c r="E71" s="75"/>
       <c r="F71" s="75"/>
@@ -7733,11 +7764,15 @@
       <c r="H71" s="75"/>
       <c r="I71" s="127"/>
       <c r="J71" s="75"/>
-      <c r="K71" s="75"/>
-      <c r="L71" s="75"/>
+      <c r="K71" s="75">
+        <v>80</v>
+      </c>
+      <c r="L71" s="75">
+        <v>160</v>
+      </c>
       <c r="M71" s="129">
         <f t="shared" si="88"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N71" s="39">
         <f t="shared" si="18"/>
@@ -7753,7 +7788,7 @@
       </c>
       <c r="Q71" s="40">
         <f t="shared" si="90"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="R71" s="51" t="e">
         <f t="shared" si="4"/>
@@ -7789,23 +7824,31 @@
       </c>
     </row>
     <row r="72" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A72" s="78"/>
+      <c r="A72" s="78">
+        <v>46259</v>
+      </c>
       <c r="B72" s="47">
         <v>68</v>
       </c>
-      <c r="C72" s="128"/>
+      <c r="C72" s="128" t="s">
+        <v>140</v>
+      </c>
       <c r="D72" s="75"/>
       <c r="E72" s="75"/>
       <c r="F72" s="75"/>
       <c r="G72" s="75"/>
       <c r="H72" s="75"/>
       <c r="I72" s="127"/>
-      <c r="J72" s="75"/>
+      <c r="J72" s="75">
+        <v>160</v>
+      </c>
       <c r="K72" s="75"/>
-      <c r="L72" s="75"/>
+      <c r="L72" s="75">
+        <v>40</v>
+      </c>
       <c r="M72" s="129">
         <f t="shared" si="88"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N72" s="39">
         <f t="shared" si="18"/>
@@ -7821,7 +7864,7 @@
       </c>
       <c r="Q72" s="40">
         <f t="shared" si="90"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R72" s="51" t="e">
         <f t="shared" si="4"/>
@@ -7857,23 +7900,35 @@
       </c>
     </row>
     <row r="73" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A73" s="78"/>
+      <c r="A73" s="78">
+        <v>46259</v>
+      </c>
       <c r="B73" s="47">
         <v>69</v>
       </c>
-      <c r="C73" s="128"/>
-      <c r="D73" s="75"/>
+      <c r="C73" s="128" t="s">
+        <v>141</v>
+      </c>
+      <c r="D73" s="75">
+        <v>160</v>
+      </c>
       <c r="E73" s="75"/>
       <c r="F73" s="75"/>
-      <c r="G73" s="75"/>
+      <c r="G73" s="75">
+        <v>160</v>
+      </c>
       <c r="H73" s="75"/>
       <c r="I73" s="127"/>
       <c r="J73" s="75"/>
-      <c r="K73" s="75"/>
-      <c r="L73" s="75"/>
+      <c r="K73" s="75">
+        <v>40</v>
+      </c>
+      <c r="L73" s="75">
+        <v>160</v>
+      </c>
       <c r="M73" s="129">
         <f t="shared" si="88"/>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="N73" s="39">
         <f t="shared" si="18"/>
@@ -7885,11 +7940,11 @@
       </c>
       <c r="P73" s="73">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q73" s="40">
         <f t="shared" si="90"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R73" s="51" t="e">
         <f t="shared" si="4"/>
@@ -7925,23 +7980,39 @@
       </c>
     </row>
     <row r="74" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A74" s="78"/>
+      <c r="A74" s="78">
+        <v>46259</v>
+      </c>
       <c r="B74" s="47">
         <v>70</v>
       </c>
-      <c r="C74" s="128"/>
+      <c r="C74" s="128" t="s">
+        <v>64</v>
+      </c>
       <c r="D74" s="75"/>
       <c r="E74" s="75"/>
       <c r="F74" s="75"/>
-      <c r="G74" s="75"/>
-      <c r="H74" s="75"/>
-      <c r="I74" s="127"/>
-      <c r="J74" s="75"/>
-      <c r="K74" s="75"/>
-      <c r="L74" s="75"/>
+      <c r="G74" s="75">
+        <v>0</v>
+      </c>
+      <c r="H74" s="75">
+        <v>80</v>
+      </c>
+      <c r="I74" s="127">
+        <v>160</v>
+      </c>
+      <c r="J74" s="75">
+        <v>20</v>
+      </c>
+      <c r="K74" s="75">
+        <v>20</v>
+      </c>
+      <c r="L74" s="75">
+        <v>20</v>
+      </c>
       <c r="M74" s="129">
         <f t="shared" si="88"/>
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="N74" s="39">
         <f t="shared" si="18"/>
@@ -7953,11 +8024,11 @@
       </c>
       <c r="P74" s="73">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q74" s="40">
         <f t="shared" si="90"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R74" s="51" t="e">
         <f t="shared" si="4"/>
@@ -11922,10 +11993,10 @@
     </row>
     <row r="133" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A133" s="78"/>
-      <c r="B133" s="175" t="s">
+      <c r="B133" s="162" t="s">
         <v>11</v>
       </c>
-      <c r="C133" s="176"/>
+      <c r="C133" s="163"/>
       <c r="D133" s="84">
         <f t="shared" ref="D133:L133" si="111">SUM(D6:D61)</f>
         <v>6363</v>
@@ -12189,10 +12260,10 @@
       </c>
     </row>
     <row r="137" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B137" s="163" t="s">
+      <c r="B137" s="175" t="s">
         <v>70</v>
       </c>
-      <c r="C137" s="164"/>
+      <c r="C137" s="176"/>
       <c r="D137" s="83">
         <f>SUM(D135:D136)</f>
         <v>0</v>
@@ -12283,10 +12354,10 @@
       </c>
     </row>
     <row r="138" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B138" s="152" t="s">
+      <c r="B138" s="164" t="s">
         <v>11</v>
       </c>
-      <c r="C138" s="153"/>
+      <c r="C138" s="165"/>
       <c r="D138" s="85">
         <f>SUM(D133,D137)</f>
         <v>6363</v>
@@ -12337,11 +12408,11 @@
       </c>
       <c r="P138" s="62">
         <f t="shared" si="120"/>
-        <v>2529.5500000000002</v>
+        <v>2557.5500000000002</v>
       </c>
       <c r="Q138" s="64">
         <f t="shared" si="120"/>
-        <v>4196.6000000000004</v>
+        <v>4239.6000000000004</v>
       </c>
       <c r="R138" s="65" t="e">
         <f t="shared" si="120"/>
@@ -12378,17 +12449,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="R3:U3"/>
-    <mergeCell ref="V3:Y3"/>
-    <mergeCell ref="B133:C133"/>
     <mergeCell ref="B138:C138"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="P2:Q2"/>
     <mergeCell ref="M3:O3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B137:C137"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="R3:U3"/>
+    <mergeCell ref="V3:Y3"/>
+    <mergeCell ref="B133:C133"/>
   </mergeCells>
   <conditionalFormatting sqref="C46:C60">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
@@ -12488,24 +12559,24 @@
         <v>49</v>
       </c>
       <c r="D5" s="88">
-        <v>705</v>
+        <v>738</v>
       </c>
       <c r="E5" s="79">
-        <v>1333</v>
+        <v>1373</v>
       </c>
       <c r="F5" s="79">
         <v>600</v>
       </c>
       <c r="G5" s="102">
         <f>SUM(D5:F5)</f>
-        <v>2638</v>
+        <v>2711</v>
       </c>
       <c r="H5" s="95">
         <v>10000</v>
       </c>
       <c r="I5" s="96">
         <f>G5-H5</f>
-        <v>-7362</v>
+        <v>-7289</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>1</v>
@@ -12528,11 +12599,11 @@
       </c>
       <c r="D6" s="104">
         <f>D5*40</f>
-        <v>28200</v>
+        <v>29520</v>
       </c>
       <c r="E6" s="104">
         <f t="shared" ref="E6:F6" si="1">E5*40</f>
-        <v>53320</v>
+        <v>54920</v>
       </c>
       <c r="F6" s="104">
         <f t="shared" si="1"/>
@@ -12540,7 +12611,7 @@
       </c>
       <c r="G6" s="105">
         <f>SUM(D6:F6)</f>
-        <v>105520</v>
+        <v>108440</v>
       </c>
       <c r="H6" s="97">
         <f>H5*40</f>
@@ -12548,7 +12619,7 @@
       </c>
       <c r="I6" s="98">
         <f>G6-H6</f>
-        <v>-294480</v>
+        <v>-291560</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>2</v>
@@ -12673,11 +12744,11 @@
       </c>
       <c r="D9" s="106">
         <f>D8-D5</f>
-        <v>-705</v>
+        <v>-738</v>
       </c>
       <c r="E9" s="106">
         <f>E8-E5</f>
-        <v>-1333</v>
+        <v>-1373</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>5</v>
@@ -12818,7 +12889,7 @@
       </c>
       <c r="G12" s="91">
         <f>D12+G5</f>
-        <v>6838</v>
+        <v>6911</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>11</v>
@@ -12869,7 +12940,7 @@
       </c>
       <c r="G13" s="91">
         <f>G12*40</f>
-        <v>273520</v>
+        <v>276440</v>
       </c>
       <c r="S13" s="177" t="s">
         <v>85</v>

--- a/Aug_2026/daily Reports/LMT Orders.xlsx
+++ b/Aug_2026/daily Reports/LMT Orders.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9811DE72-3340-43AB-86B1-AD4772998ED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BF312AE-BB23-43F4-8E06-31E2AAA9A090}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="147">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -448,6 +448,21 @@
   </si>
   <si>
     <t xml:space="preserve">Pak Madina </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Askari Punjab Society </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Risen Shadbagh </t>
+  </si>
+  <si>
+    <t>Risen Sabzazaar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Risen Thoker </t>
+  </si>
+  <si>
+    <t>Risen Askari 11</t>
   </si>
 </sst>
 </file>
@@ -1336,7 +1351,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="186">
+  <cellXfs count="193">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1695,9 +1710,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="16" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1721,6 +1733,63 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="16" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1755,45 +1824,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2358,14 +2388,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="152">
+      <c r="B1" s="172">
         <f ca="1">TODAY()</f>
-        <v>46261</v>
-      </c>
-      <c r="C1" s="152"/>
-      <c r="D1" s="152"/>
-      <c r="E1" s="152"/>
-      <c r="F1" s="152"/>
+        <v>46262</v>
+      </c>
+      <c r="C1" s="172"/>
+      <c r="D1" s="172"/>
+      <c r="E1" s="172"/>
+      <c r="F1" s="172"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
       <c r="I1" s="10"/>
@@ -2387,10 +2417,10 @@
       <c r="Y1" s="10"/>
     </row>
     <row r="2" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="174" t="s">
+      <c r="A2" s="169" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="153" t="s">
+      <c r="B2" s="173" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2423,13 +2453,13 @@
       <c r="L2" s="15">
         <v>120</v>
       </c>
-      <c r="M2" s="166"/>
-      <c r="N2" s="167"/>
-      <c r="O2" s="168"/>
-      <c r="P2" s="169" t="s">
+      <c r="M2" s="161"/>
+      <c r="N2" s="162"/>
+      <c r="O2" s="163"/>
+      <c r="P2" s="164" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="170"/>
+      <c r="Q2" s="165"/>
       <c r="R2" s="18">
         <v>0.05</v>
       </c>
@@ -2448,8 +2478,8 @@
       <c r="Y2" s="20"/>
     </row>
     <row r="3" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="174"/>
-      <c r="B3" s="154"/>
+      <c r="A3" s="169"/>
+      <c r="B3" s="174"/>
       <c r="C3" s="23" t="s">
         <v>15</v>
       </c>
@@ -2480,29 +2510,29 @@
       <c r="L3" s="29">
         <v>72.64</v>
       </c>
-      <c r="M3" s="171" t="s">
+      <c r="M3" s="166" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="172"/>
-      <c r="O3" s="173"/>
+      <c r="N3" s="167"/>
+      <c r="O3" s="168"/>
       <c r="P3" s="71"/>
       <c r="Q3" s="72"/>
-      <c r="R3" s="156" t="s">
+      <c r="R3" s="176" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="157"/>
-      <c r="T3" s="157"/>
-      <c r="U3" s="158"/>
-      <c r="V3" s="159" t="s">
+      <c r="S3" s="177"/>
+      <c r="T3" s="177"/>
+      <c r="U3" s="178"/>
+      <c r="V3" s="179" t="s">
         <v>17</v>
       </c>
-      <c r="W3" s="160"/>
-      <c r="X3" s="160"/>
-      <c r="Y3" s="161"/>
+      <c r="W3" s="180"/>
+      <c r="X3" s="180"/>
+      <c r="Y3" s="181"/>
     </row>
     <row r="4" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="174"/>
-      <c r="B4" s="155"/>
+      <c r="A4" s="169"/>
+      <c r="B4" s="175"/>
       <c r="C4" s="30" t="s">
         <v>18</v>
       </c>
@@ -3476,36 +3506,36 @@
       </c>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A16" s="140">
+      <c r="A16" s="139">
         <v>46241</v>
       </c>
-      <c r="B16" s="141">
+      <c r="B16" s="140">
         <v>12</v>
       </c>
-      <c r="C16" s="142" t="s">
+      <c r="C16" s="141" t="s">
         <v>102</v>
       </c>
-      <c r="D16" s="143">
+      <c r="D16" s="142">
         <v>120</v>
       </c>
-      <c r="E16" s="144"/>
-      <c r="F16" s="145"/>
-      <c r="G16" s="146">
+      <c r="E16" s="143"/>
+      <c r="F16" s="144"/>
+      <c r="G16" s="145">
         <v>120</v>
       </c>
-      <c r="H16" s="144">
+      <c r="H16" s="143">
         <v>120</v>
       </c>
       <c r="I16" s="56">
         <v>120</v>
       </c>
-      <c r="J16" s="146">
+      <c r="J16" s="145">
         <v>120</v>
       </c>
-      <c r="K16" s="144">
+      <c r="K16" s="143">
         <v>120</v>
       </c>
-      <c r="L16" s="145">
+      <c r="L16" s="144">
         <v>120</v>
       </c>
       <c r="M16" s="48">
@@ -3562,34 +3592,34 @@
       </c>
     </row>
     <row r="17" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A17" s="140">
+      <c r="A17" s="139">
         <v>46242</v>
       </c>
-      <c r="B17" s="141">
+      <c r="B17" s="140">
         <v>13</v>
       </c>
-      <c r="C17" s="142" t="s">
+      <c r="C17" s="141" t="s">
         <v>97</v>
       </c>
-      <c r="D17" s="143"/>
-      <c r="E17" s="144"/>
-      <c r="F17" s="145"/>
-      <c r="G17" s="146">
+      <c r="D17" s="142"/>
+      <c r="E17" s="143"/>
+      <c r="F17" s="144"/>
+      <c r="G17" s="145">
         <v>24</v>
       </c>
-      <c r="H17" s="144">
+      <c r="H17" s="143">
         <v>4</v>
       </c>
       <c r="I17" s="56">
         <v>39</v>
       </c>
-      <c r="J17" s="146">
+      <c r="J17" s="145">
         <v>38</v>
       </c>
-      <c r="K17" s="144">
+      <c r="K17" s="143">
         <v>77</v>
       </c>
-      <c r="L17" s="145">
+      <c r="L17" s="144">
         <v>80</v>
       </c>
       <c r="M17" s="48">
@@ -3646,34 +3676,34 @@
       </c>
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A18" s="140">
+      <c r="A18" s="139">
         <v>46242</v>
       </c>
-      <c r="B18" s="141">
+      <c r="B18" s="140">
         <v>14</v>
       </c>
-      <c r="C18" s="142" t="s">
+      <c r="C18" s="141" t="s">
         <v>98</v>
       </c>
-      <c r="D18" s="143"/>
-      <c r="E18" s="144"/>
-      <c r="F18" s="145"/>
-      <c r="G18" s="146">
+      <c r="D18" s="142"/>
+      <c r="E18" s="143"/>
+      <c r="F18" s="144"/>
+      <c r="G18" s="145">
         <v>80</v>
       </c>
-      <c r="H18" s="144">
+      <c r="H18" s="143">
         <v>120</v>
       </c>
       <c r="I18" s="56">
         <v>200</v>
       </c>
-      <c r="J18" s="146">
+      <c r="J18" s="145">
         <v>160</v>
       </c>
-      <c r="K18" s="144">
+      <c r="K18" s="143">
         <v>39</v>
       </c>
-      <c r="L18" s="145">
+      <c r="L18" s="144">
         <v>280</v>
       </c>
       <c r="M18" s="48">
@@ -3730,34 +3760,34 @@
       </c>
     </row>
     <row r="19" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A19" s="140">
+      <c r="A19" s="139">
         <v>46242</v>
       </c>
-      <c r="B19" s="141">
+      <c r="B19" s="140">
         <v>15</v>
       </c>
-      <c r="C19" s="142" t="s">
+      <c r="C19" s="141" t="s">
         <v>99</v>
       </c>
-      <c r="D19" s="143"/>
-      <c r="E19" s="144"/>
-      <c r="F19" s="145"/>
-      <c r="G19" s="146">
+      <c r="D19" s="142"/>
+      <c r="E19" s="143"/>
+      <c r="F19" s="144"/>
+      <c r="G19" s="145">
         <v>40</v>
       </c>
-      <c r="H19" s="144">
+      <c r="H19" s="143">
         <v>40</v>
       </c>
       <c r="I19" s="56">
         <v>120</v>
       </c>
-      <c r="J19" s="146">
+      <c r="J19" s="145">
         <v>120</v>
       </c>
-      <c r="K19" s="144">
+      <c r="K19" s="143">
         <v>80</v>
       </c>
-      <c r="L19" s="145">
+      <c r="L19" s="144">
         <v>120</v>
       </c>
       <c r="M19" s="48">
@@ -3814,32 +3844,32 @@
       </c>
     </row>
     <row r="20" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A20" s="140">
+      <c r="A20" s="139">
         <v>46242</v>
       </c>
-      <c r="B20" s="141">
+      <c r="B20" s="140">
         <v>16</v>
       </c>
-      <c r="C20" s="142" t="s">
+      <c r="C20" s="141" t="s">
         <v>100</v>
       </c>
-      <c r="D20" s="143"/>
-      <c r="E20" s="144"/>
-      <c r="F20" s="145"/>
-      <c r="G20" s="146"/>
-      <c r="H20" s="144">
+      <c r="D20" s="142"/>
+      <c r="E20" s="143"/>
+      <c r="F20" s="144"/>
+      <c r="G20" s="145"/>
+      <c r="H20" s="143">
         <v>120</v>
       </c>
       <c r="I20" s="56">
         <v>120</v>
       </c>
-      <c r="J20" s="146">
+      <c r="J20" s="145">
         <v>120</v>
       </c>
-      <c r="K20" s="144">
+      <c r="K20" s="143">
         <v>120</v>
       </c>
-      <c r="L20" s="145">
+      <c r="L20" s="144">
         <v>120</v>
       </c>
       <c r="M20" s="48">
@@ -3896,34 +3926,34 @@
       </c>
     </row>
     <row r="21" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A21" s="140">
+      <c r="A21" s="139">
         <v>46242</v>
       </c>
-      <c r="B21" s="141">
+      <c r="B21" s="140">
         <v>17</v>
       </c>
-      <c r="C21" s="142" t="s">
+      <c r="C21" s="141" t="s">
         <v>101</v>
       </c>
-      <c r="D21" s="143"/>
-      <c r="E21" s="144"/>
-      <c r="F21" s="145"/>
-      <c r="G21" s="146">
+      <c r="D21" s="142"/>
+      <c r="E21" s="143"/>
+      <c r="F21" s="144"/>
+      <c r="G21" s="145">
         <v>600</v>
       </c>
-      <c r="H21" s="144">
+      <c r="H21" s="143">
         <v>600</v>
       </c>
       <c r="I21" s="56">
         <v>2800</v>
       </c>
-      <c r="J21" s="146">
+      <c r="J21" s="145">
         <v>600</v>
       </c>
-      <c r="K21" s="144">
+      <c r="K21" s="143">
         <v>1000</v>
       </c>
-      <c r="L21" s="145">
+      <c r="L21" s="144">
         <v>2000</v>
       </c>
       <c r="M21" s="48">
@@ -7188,34 +7218,34 @@
       </c>
     </row>
     <row r="64" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A64" s="147">
+      <c r="A64" s="146">
         <v>46258</v>
       </c>
-      <c r="B64" s="148">
+      <c r="B64" s="147">
         <v>60</v>
       </c>
-      <c r="C64" s="149" t="s">
+      <c r="C64" s="148" t="s">
         <v>64</v>
       </c>
-      <c r="D64" s="150"/>
-      <c r="E64" s="150"/>
-      <c r="F64" s="150"/>
-      <c r="G64" s="150">
+      <c r="D64" s="149"/>
+      <c r="E64" s="149"/>
+      <c r="F64" s="149"/>
+      <c r="G64" s="149">
         <v>80</v>
       </c>
-      <c r="H64" s="150">
+      <c r="H64" s="149">
         <v>80</v>
       </c>
-      <c r="I64" s="151">
+      <c r="I64" s="150">
         <v>240</v>
       </c>
-      <c r="J64" s="150">
+      <c r="J64" s="149">
         <v>80</v>
       </c>
-      <c r="K64" s="150">
+      <c r="K64" s="149">
         <v>80</v>
       </c>
-      <c r="L64" s="150">
+      <c r="L64" s="149">
         <v>100</v>
       </c>
       <c r="M64" s="129">
@@ -7272,28 +7302,28 @@
       </c>
     </row>
     <row r="65" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A65" s="147">
+      <c r="A65" s="146">
         <v>46258</v>
       </c>
-      <c r="B65" s="148">
+      <c r="B65" s="147">
         <v>61</v>
       </c>
-      <c r="C65" s="149" t="s">
+      <c r="C65" s="148" t="s">
         <v>137</v>
       </c>
-      <c r="D65" s="150"/>
-      <c r="E65" s="150"/>
-      <c r="F65" s="150"/>
-      <c r="G65" s="150"/>
-      <c r="H65" s="150"/>
-      <c r="I65" s="151"/>
-      <c r="J65" s="150">
+      <c r="D65" s="149"/>
+      <c r="E65" s="149"/>
+      <c r="F65" s="149"/>
+      <c r="G65" s="149"/>
+      <c r="H65" s="149"/>
+      <c r="I65" s="150"/>
+      <c r="J65" s="149">
         <v>40</v>
       </c>
-      <c r="K65" s="150">
+      <c r="K65" s="149">
         <v>40</v>
       </c>
-      <c r="L65" s="150">
+      <c r="L65" s="149">
         <v>40</v>
       </c>
       <c r="M65" s="129">
@@ -7350,30 +7380,30 @@
       </c>
     </row>
     <row r="66" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A66" s="147">
+      <c r="A66" s="146">
         <v>46258</v>
       </c>
-      <c r="B66" s="148">
+      <c r="B66" s="147">
         <v>62</v>
       </c>
-      <c r="C66" s="149" t="s">
+      <c r="C66" s="148" t="s">
         <v>109</v>
       </c>
-      <c r="D66" s="150"/>
-      <c r="E66" s="150"/>
-      <c r="F66" s="150"/>
-      <c r="G66" s="150">
+      <c r="D66" s="149"/>
+      <c r="E66" s="149"/>
+      <c r="F66" s="149"/>
+      <c r="G66" s="149">
         <v>39</v>
       </c>
-      <c r="H66" s="150">
+      <c r="H66" s="149">
         <v>40</v>
       </c>
-      <c r="I66" s="151"/>
-      <c r="J66" s="150"/>
-      <c r="K66" s="150">
+      <c r="I66" s="150"/>
+      <c r="J66" s="149"/>
+      <c r="K66" s="149">
         <v>40</v>
       </c>
-      <c r="L66" s="150">
+      <c r="L66" s="149">
         <v>40</v>
       </c>
       <c r="M66" s="129">
@@ -7430,28 +7460,28 @@
       </c>
     </row>
     <row r="67" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A67" s="147">
+      <c r="A67" s="146">
         <v>46258</v>
       </c>
-      <c r="B67" s="148">
+      <c r="B67" s="147">
         <v>63</v>
       </c>
-      <c r="C67" s="149" t="s">
+      <c r="C67" s="148" t="s">
         <v>107</v>
       </c>
-      <c r="D67" s="150"/>
-      <c r="E67" s="150"/>
-      <c r="F67" s="150"/>
-      <c r="G67" s="150"/>
-      <c r="H67" s="150"/>
-      <c r="I67" s="151"/>
-      <c r="J67" s="150">
+      <c r="D67" s="149"/>
+      <c r="E67" s="149"/>
+      <c r="F67" s="149"/>
+      <c r="G67" s="149"/>
+      <c r="H67" s="149"/>
+      <c r="I67" s="150"/>
+      <c r="J67" s="149">
         <v>80</v>
       </c>
-      <c r="K67" s="150">
+      <c r="K67" s="149">
         <v>40</v>
       </c>
-      <c r="L67" s="150">
+      <c r="L67" s="149">
         <v>40</v>
       </c>
       <c r="M67" s="129">
@@ -7508,36 +7538,36 @@
       </c>
     </row>
     <row r="68" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A68" s="147">
+      <c r="A68" s="146">
         <v>46258</v>
       </c>
-      <c r="B68" s="148">
+      <c r="B68" s="147">
         <v>64</v>
       </c>
-      <c r="C68" s="149" t="s">
+      <c r="C68" s="148" t="s">
         <v>138</v>
       </c>
-      <c r="D68" s="150">
+      <c r="D68" s="149">
         <v>40</v>
       </c>
-      <c r="E68" s="150"/>
-      <c r="F68" s="150"/>
-      <c r="G68" s="150">
+      <c r="E68" s="149"/>
+      <c r="F68" s="149"/>
+      <c r="G68" s="149">
         <v>80</v>
       </c>
-      <c r="H68" s="150">
+      <c r="H68" s="149">
         <v>80</v>
       </c>
-      <c r="I68" s="151">
+      <c r="I68" s="150">
         <v>80</v>
       </c>
-      <c r="J68" s="150">
+      <c r="J68" s="149">
         <v>80</v>
       </c>
-      <c r="K68" s="150">
+      <c r="K68" s="149">
         <v>80</v>
       </c>
-      <c r="L68" s="150">
+      <c r="L68" s="149">
         <v>80</v>
       </c>
       <c r="M68" s="129">
@@ -7999,7 +8029,7 @@
         <v>80</v>
       </c>
       <c r="I74" s="127">
-        <v>160</v>
+        <v>360</v>
       </c>
       <c r="J74" s="75">
         <v>20</v>
@@ -8008,11 +8038,11 @@
         <v>20</v>
       </c>
       <c r="L74" s="75">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="M74" s="129">
         <f t="shared" si="88"/>
-        <v>7.5</v>
+        <v>13</v>
       </c>
       <c r="N74" s="39">
         <f t="shared" si="18"/>
@@ -8024,11 +8054,11 @@
       </c>
       <c r="P74" s="73">
         <f t="shared" si="89"/>
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="Q74" s="40">
         <f t="shared" si="90"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R74" s="51" t="e">
         <f t="shared" si="4"/>
@@ -8064,23 +8094,41 @@
       </c>
     </row>
     <row r="75" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A75" s="78"/>
-      <c r="B75" s="47">
+      <c r="A75" s="151">
+        <v>46261</v>
+      </c>
+      <c r="B75" s="152">
         <v>71</v>
       </c>
-      <c r="C75" s="139"/>
-      <c r="D75" s="75"/>
-      <c r="E75" s="75"/>
-      <c r="F75" s="50"/>
-      <c r="G75" s="75"/>
-      <c r="H75" s="75"/>
-      <c r="I75" s="127"/>
-      <c r="J75" s="75"/>
-      <c r="K75" s="75"/>
-      <c r="L75" s="75"/>
+      <c r="C75" s="153" t="s">
+        <v>142</v>
+      </c>
+      <c r="D75" s="154">
+        <v>80</v>
+      </c>
+      <c r="E75" s="154"/>
+      <c r="F75" s="155"/>
+      <c r="G75" s="154">
+        <v>120</v>
+      </c>
+      <c r="H75" s="154">
+        <v>80</v>
+      </c>
+      <c r="I75" s="156">
+        <v>120</v>
+      </c>
+      <c r="J75" s="154">
+        <v>120</v>
+      </c>
+      <c r="K75" s="154">
+        <v>80</v>
+      </c>
+      <c r="L75" s="154">
+        <v>120</v>
+      </c>
       <c r="M75" s="129">
         <f t="shared" si="88"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="N75" s="39">
         <f t="shared" si="18"/>
@@ -8092,11 +8140,11 @@
       </c>
       <c r="P75" s="73">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q75" s="40">
         <f t="shared" si="90"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="R75" s="51" t="e">
         <f t="shared" si="4"/>
@@ -8132,23 +8180,35 @@
       </c>
     </row>
     <row r="76" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A76" s="78"/>
-      <c r="B76" s="47">
+      <c r="A76" s="151">
+        <v>46261</v>
+      </c>
+      <c r="B76" s="152">
         <v>72</v>
       </c>
-      <c r="C76" s="139"/>
-      <c r="D76" s="75"/>
-      <c r="E76" s="50"/>
-      <c r="F76" s="50"/>
-      <c r="G76" s="75"/>
-      <c r="H76" s="75"/>
-      <c r="I76" s="127"/>
-      <c r="J76" s="75"/>
-      <c r="K76" s="75"/>
-      <c r="L76" s="75"/>
+      <c r="C76" s="153" t="s">
+        <v>92</v>
+      </c>
+      <c r="D76" s="154">
+        <v>200</v>
+      </c>
+      <c r="E76" s="155"/>
+      <c r="F76" s="155"/>
+      <c r="G76" s="154"/>
+      <c r="H76" s="154"/>
+      <c r="I76" s="156">
+        <v>199</v>
+      </c>
+      <c r="J76" s="154"/>
+      <c r="K76" s="154">
+        <v>199</v>
+      </c>
+      <c r="L76" s="154">
+        <v>200</v>
+      </c>
       <c r="M76" s="129">
         <f t="shared" si="88"/>
-        <v>0</v>
+        <v>19.95</v>
       </c>
       <c r="N76" s="39">
         <f t="shared" si="18"/>
@@ -8160,11 +8220,11 @@
       </c>
       <c r="P76" s="73">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>9.9499999999999993</v>
       </c>
       <c r="Q76" s="40">
         <f t="shared" si="90"/>
-        <v>0</v>
+        <v>19.95</v>
       </c>
       <c r="R76" s="51" t="e">
         <f t="shared" si="4"/>
@@ -8200,23 +8260,37 @@
       </c>
     </row>
     <row r="77" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A77" s="78"/>
-      <c r="B77" s="47">
+      <c r="A77" s="151">
+        <v>46261</v>
+      </c>
+      <c r="B77" s="152">
         <v>73</v>
       </c>
-      <c r="C77" s="139"/>
-      <c r="D77" s="75"/>
-      <c r="E77" s="50"/>
-      <c r="F77" s="50"/>
-      <c r="G77" s="75"/>
-      <c r="H77" s="75"/>
-      <c r="I77" s="127"/>
-      <c r="J77" s="75"/>
-      <c r="K77" s="75"/>
-      <c r="L77" s="75"/>
+      <c r="C77" s="153" t="s">
+        <v>143</v>
+      </c>
+      <c r="D77" s="154"/>
+      <c r="E77" s="155"/>
+      <c r="F77" s="155"/>
+      <c r="G77" s="154">
+        <v>80</v>
+      </c>
+      <c r="H77" s="154">
+        <v>80</v>
+      </c>
+      <c r="I77" s="156"/>
+      <c r="J77" s="154">
+        <v>120</v>
+      </c>
+      <c r="K77" s="154">
+        <v>120</v>
+      </c>
+      <c r="L77" s="154">
+        <v>120</v>
+      </c>
       <c r="M77" s="129">
         <f t="shared" si="88"/>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="N77" s="39">
         <f t="shared" si="18"/>
@@ -8228,11 +8302,11 @@
       </c>
       <c r="P77" s="73">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q77" s="40">
         <f t="shared" si="90"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="R77" s="51" t="e">
         <f t="shared" si="4"/>
@@ -8268,23 +8342,39 @@
       </c>
     </row>
     <row r="78" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A78" s="78"/>
-      <c r="B78" s="47">
+      <c r="A78" s="151">
+        <v>46261</v>
+      </c>
+      <c r="B78" s="152">
         <v>74</v>
       </c>
-      <c r="C78" s="139"/>
-      <c r="D78" s="75"/>
-      <c r="E78" s="50"/>
-      <c r="F78" s="50"/>
-      <c r="G78" s="50"/>
-      <c r="H78" s="50"/>
-      <c r="I78" s="129"/>
-      <c r="J78" s="50"/>
-      <c r="K78" s="50"/>
-      <c r="L78" s="50"/>
+      <c r="C78" s="153" t="s">
+        <v>144</v>
+      </c>
+      <c r="D78" s="154"/>
+      <c r="E78" s="155"/>
+      <c r="F78" s="155"/>
+      <c r="G78" s="155">
+        <v>40</v>
+      </c>
+      <c r="H78" s="155">
+        <v>80</v>
+      </c>
+      <c r="I78" s="157">
+        <v>80</v>
+      </c>
+      <c r="J78" s="155">
+        <v>80</v>
+      </c>
+      <c r="K78" s="155">
+        <v>80</v>
+      </c>
+      <c r="L78" s="155">
+        <v>80</v>
+      </c>
       <c r="M78" s="129">
         <f t="shared" si="88"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="N78" s="39">
         <f t="shared" si="18"/>
@@ -8296,11 +8386,11 @@
       </c>
       <c r="P78" s="73">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q78" s="40">
         <f t="shared" si="90"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="R78" s="51" t="e">
         <f t="shared" si="4"/>
@@ -8336,23 +8426,37 @@
       </c>
     </row>
     <row r="79" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A79" s="78"/>
-      <c r="B79" s="47">
+      <c r="A79" s="151">
+        <v>46261</v>
+      </c>
+      <c r="B79" s="152">
         <v>75</v>
       </c>
-      <c r="C79" s="139"/>
-      <c r="D79" s="75"/>
-      <c r="E79" s="50"/>
-      <c r="F79" s="50"/>
-      <c r="G79" s="50"/>
-      <c r="H79" s="50"/>
-      <c r="I79" s="129"/>
-      <c r="J79" s="50"/>
-      <c r="K79" s="50"/>
-      <c r="L79" s="50"/>
+      <c r="C79" s="153" t="s">
+        <v>145</v>
+      </c>
+      <c r="D79" s="154"/>
+      <c r="E79" s="155"/>
+      <c r="F79" s="155"/>
+      <c r="G79" s="155">
+        <v>40</v>
+      </c>
+      <c r="H79" s="155"/>
+      <c r="I79" s="157">
+        <v>40</v>
+      </c>
+      <c r="J79" s="155">
+        <v>40</v>
+      </c>
+      <c r="K79" s="155">
+        <v>39</v>
+      </c>
+      <c r="L79" s="155">
+        <v>80</v>
+      </c>
       <c r="M79" s="129">
         <f t="shared" si="88"/>
-        <v>0</v>
+        <v>5.9749999999999996</v>
       </c>
       <c r="N79" s="39">
         <f t="shared" si="18"/>
@@ -8364,11 +8468,11 @@
       </c>
       <c r="P79" s="73">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q79" s="40">
         <f t="shared" si="90"/>
-        <v>0</v>
+        <v>7.95</v>
       </c>
       <c r="R79" s="51" t="e">
         <f t="shared" si="4"/>
@@ -8404,23 +8508,39 @@
       </c>
     </row>
     <row r="80" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A80" s="78"/>
-      <c r="B80" s="47">
+      <c r="A80" s="151">
+        <v>46261</v>
+      </c>
+      <c r="B80" s="152">
         <v>76</v>
       </c>
-      <c r="C80" s="128"/>
-      <c r="D80" s="50"/>
-      <c r="E80" s="50"/>
-      <c r="F80" s="50"/>
-      <c r="G80" s="50"/>
-      <c r="H80" s="50"/>
-      <c r="I80" s="129"/>
-      <c r="J80" s="50"/>
-      <c r="K80" s="50"/>
-      <c r="L80" s="50"/>
+      <c r="C80" s="158" t="s">
+        <v>146</v>
+      </c>
+      <c r="D80" s="155"/>
+      <c r="E80" s="155"/>
+      <c r="F80" s="155"/>
+      <c r="G80" s="155">
+        <v>40</v>
+      </c>
+      <c r="H80" s="155">
+        <v>40</v>
+      </c>
+      <c r="I80" s="157">
+        <v>40</v>
+      </c>
+      <c r="J80" s="155">
+        <v>40</v>
+      </c>
+      <c r="K80" s="155">
+        <v>39</v>
+      </c>
+      <c r="L80" s="155">
+        <v>80</v>
+      </c>
       <c r="M80" s="129">
         <f t="shared" si="88"/>
-        <v>0</v>
+        <v>6.9749999999999996</v>
       </c>
       <c r="N80" s="39">
         <f t="shared" si="18"/>
@@ -8432,11 +8552,11 @@
       </c>
       <c r="P80" s="73">
         <f t="shared" ref="P80:P84" si="96">SUM(G80:I80)/20</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q80" s="40">
         <f t="shared" ref="Q80:Q84" si="97">SUM(J80:L80)/20</f>
-        <v>0</v>
+        <v>7.95</v>
       </c>
       <c r="R80" s="51" t="e">
         <f t="shared" si="4"/>
@@ -8472,23 +8592,39 @@
       </c>
     </row>
     <row r="81" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A81" s="78"/>
-      <c r="B81" s="47">
+      <c r="A81" s="151">
+        <v>46261</v>
+      </c>
+      <c r="B81" s="152">
         <v>77</v>
       </c>
-      <c r="C81" s="128"/>
-      <c r="D81" s="50"/>
-      <c r="E81" s="50"/>
-      <c r="F81" s="50"/>
-      <c r="G81" s="50"/>
-      <c r="H81" s="50"/>
-      <c r="I81" s="129"/>
-      <c r="J81" s="50"/>
-      <c r="K81" s="50"/>
-      <c r="L81" s="50"/>
+      <c r="C81" s="158" t="s">
+        <v>126</v>
+      </c>
+      <c r="D81" s="155"/>
+      <c r="E81" s="155"/>
+      <c r="F81" s="155"/>
+      <c r="G81" s="155">
+        <v>400</v>
+      </c>
+      <c r="H81" s="155">
+        <v>800</v>
+      </c>
+      <c r="I81" s="157">
+        <v>800</v>
+      </c>
+      <c r="J81" s="155">
+        <v>800</v>
+      </c>
+      <c r="K81" s="155">
+        <v>800</v>
+      </c>
+      <c r="L81" s="155">
+        <v>2000</v>
+      </c>
       <c r="M81" s="129">
         <f t="shared" si="88"/>
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="N81" s="39">
         <f t="shared" si="18"/>
@@ -8500,11 +8636,11 @@
       </c>
       <c r="P81" s="73">
         <f t="shared" si="96"/>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q81" s="40">
         <f t="shared" si="97"/>
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="R81" s="51" t="e">
         <f t="shared" si="4"/>
@@ -11993,10 +12129,10 @@
     </row>
     <row r="133" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A133" s="78"/>
-      <c r="B133" s="162" t="s">
+      <c r="B133" s="182" t="s">
         <v>11</v>
       </c>
-      <c r="C133" s="163"/>
+      <c r="C133" s="183"/>
       <c r="D133" s="84">
         <f t="shared" ref="D133:L133" si="111">SUM(D6:D61)</f>
         <v>6363</v>
@@ -12260,10 +12396,10 @@
       </c>
     </row>
     <row r="137" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B137" s="175" t="s">
+      <c r="B137" s="170" t="s">
         <v>70</v>
       </c>
-      <c r="C137" s="176"/>
+      <c r="C137" s="171"/>
       <c r="D137" s="83">
         <f>SUM(D135:D136)</f>
         <v>0</v>
@@ -12354,10 +12490,10 @@
       </c>
     </row>
     <row r="138" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B138" s="164" t="s">
+      <c r="B138" s="159" t="s">
         <v>11</v>
       </c>
-      <c r="C138" s="165"/>
+      <c r="C138" s="160"/>
       <c r="D138" s="85">
         <f>SUM(D133,D137)</f>
         <v>6363</v>
@@ -12408,11 +12544,11 @@
       </c>
       <c r="P138" s="62">
         <f t="shared" si="120"/>
-        <v>2557.5500000000002</v>
+        <v>2721.5</v>
       </c>
       <c r="Q138" s="64">
         <f t="shared" si="120"/>
-        <v>4239.6000000000004</v>
+        <v>4502.45</v>
       </c>
       <c r="R138" s="65" t="e">
         <f t="shared" si="120"/>
@@ -12449,17 +12585,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="R3:U3"/>
+    <mergeCell ref="V3:Y3"/>
+    <mergeCell ref="B133:C133"/>
     <mergeCell ref="B138:C138"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="P2:Q2"/>
     <mergeCell ref="M3:O3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B137:C137"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="R3:U3"/>
-    <mergeCell ref="V3:Y3"/>
-    <mergeCell ref="B133:C133"/>
   </mergeCells>
   <conditionalFormatting sqref="C46:C60">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
@@ -12495,25 +12631,25 @@
   <sheetData>
     <row r="2" spans="3:26" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="3:26" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C3" s="179" t="s">
+      <c r="C3" s="186" t="s">
         <v>117</v>
       </c>
-      <c r="D3" s="180"/>
-      <c r="E3" s="180"/>
-      <c r="F3" s="180"/>
-      <c r="G3" s="181"/>
-      <c r="H3" s="183" t="s">
+      <c r="D3" s="187"/>
+      <c r="E3" s="187"/>
+      <c r="F3" s="187"/>
+      <c r="G3" s="188"/>
+      <c r="H3" s="190" t="s">
         <v>62</v>
       </c>
-      <c r="I3" s="184"/>
-      <c r="K3" s="185" t="s">
+      <c r="I3" s="191"/>
+      <c r="K3" s="192" t="s">
         <v>66</v>
       </c>
-      <c r="L3" s="185"/>
-      <c r="M3" s="185"/>
-      <c r="N3" s="185"/>
-      <c r="O3" s="185"/>
-      <c r="P3" s="185"/>
+      <c r="L3" s="192"/>
+      <c r="M3" s="192"/>
+      <c r="N3" s="192"/>
+      <c r="O3" s="192"/>
+      <c r="P3" s="192"/>
     </row>
     <row r="4" spans="3:26" ht="29.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C4" s="99"/>
@@ -12559,24 +12695,24 @@
         <v>49</v>
       </c>
       <c r="D5" s="88">
-        <v>738</v>
+        <v>769</v>
       </c>
       <c r="E5" s="79">
-        <v>1373</v>
+        <v>1594</v>
       </c>
       <c r="F5" s="79">
         <v>600</v>
       </c>
       <c r="G5" s="102">
         <f>SUM(D5:F5)</f>
-        <v>2711</v>
+        <v>2963</v>
       </c>
       <c r="H5" s="95">
         <v>10000</v>
       </c>
       <c r="I5" s="96">
         <f>G5-H5</f>
-        <v>-7289</v>
+        <v>-7037</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>1</v>
@@ -12599,11 +12735,11 @@
       </c>
       <c r="D6" s="104">
         <f>D5*40</f>
-        <v>29520</v>
+        <v>30760</v>
       </c>
       <c r="E6" s="104">
         <f t="shared" ref="E6:F6" si="1">E5*40</f>
-        <v>54920</v>
+        <v>63760</v>
       </c>
       <c r="F6" s="104">
         <f t="shared" si="1"/>
@@ -12611,7 +12747,7 @@
       </c>
       <c r="G6" s="105">
         <f>SUM(D6:F6)</f>
-        <v>108440</v>
+        <v>118520</v>
       </c>
       <c r="H6" s="97">
         <f>H5*40</f>
@@ -12619,7 +12755,7 @@
       </c>
       <c r="I6" s="98">
         <f>G6-H6</f>
-        <v>-291560</v>
+        <v>-281480</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>2</v>
@@ -12744,11 +12880,11 @@
       </c>
       <c r="D9" s="106">
         <f>D8-D5</f>
-        <v>-738</v>
+        <v>-769</v>
       </c>
       <c r="E9" s="106">
         <f>E8-E5</f>
-        <v>-1373</v>
+        <v>-1594</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>5</v>
@@ -12830,14 +12966,14 @@
       </c>
     </row>
     <row r="11" spans="3:26" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C11" s="182" t="s">
+      <c r="C11" s="189" t="s">
         <v>59</v>
       </c>
-      <c r="D11" s="182"/>
-      <c r="F11" s="182" t="s">
+      <c r="D11" s="189"/>
+      <c r="F11" s="189" t="s">
         <v>68</v>
       </c>
-      <c r="G11" s="182"/>
+      <c r="G11" s="189"/>
       <c r="K11" s="1" t="s">
         <v>7</v>
       </c>
@@ -12889,7 +13025,7 @@
       </c>
       <c r="G12" s="91">
         <f>D12+G5</f>
-        <v>6911</v>
+        <v>7163</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>11</v>
@@ -12940,12 +13076,12 @@
       </c>
       <c r="G13" s="91">
         <f>G12*40</f>
-        <v>276440</v>
-      </c>
-      <c r="S13" s="177" t="s">
+        <v>286520</v>
+      </c>
+      <c r="S13" s="184" t="s">
         <v>85</v>
       </c>
-      <c r="T13" s="177"/>
+      <c r="T13" s="184"/>
       <c r="U13" s="135">
         <f>SUM(U8:U12)</f>
         <v>100</v>
@@ -13034,13 +13170,13 @@
       </c>
     </row>
     <row r="20" spans="4:15" ht="24" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="D20" s="178" t="s">
+      <c r="D20" s="185" t="s">
         <v>66</v>
       </c>
-      <c r="E20" s="178"/>
-      <c r="F20" s="178"/>
-      <c r="G20" s="178"/>
-      <c r="H20" s="178"/>
+      <c r="E20" s="185"/>
+      <c r="F20" s="185"/>
+      <c r="G20" s="185"/>
+      <c r="H20" s="185"/>
       <c r="K20" s="1" t="s">
         <v>4</v>
       </c>

--- a/Aug_2026/daily Reports/LMT Orders.xlsx
+++ b/Aug_2026/daily Reports/LMT Orders.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BF312AE-BB23-43F4-8E06-31E2AAA9A090}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A00CADE-39AE-4292-93FF-E7D3B0AFE0C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="149">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -463,6 +463,12 @@
   </si>
   <si>
     <t>Risen Askari 11</t>
+  </si>
+  <si>
+    <t>Gourmet Food</t>
+  </si>
+  <si>
+    <t>Clinix Werehouse</t>
   </si>
 </sst>
 </file>
@@ -2390,7 +2396,7 @@
     <row r="1" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B1" s="172">
         <f ca="1">TODAY()</f>
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="C1" s="172"/>
       <c r="D1" s="172"/>
@@ -8676,23 +8682,39 @@
       </c>
     </row>
     <row r="82" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A82" s="78"/>
+      <c r="A82" s="139">
+        <v>46262</v>
+      </c>
       <c r="B82" s="47">
         <v>78</v>
       </c>
-      <c r="C82" s="128"/>
+      <c r="C82" s="128" t="s">
+        <v>147</v>
+      </c>
       <c r="D82" s="50"/>
       <c r="E82" s="50"/>
       <c r="F82" s="50"/>
-      <c r="G82" s="50"/>
-      <c r="H82" s="50"/>
-      <c r="I82" s="129"/>
-      <c r="J82" s="50"/>
-      <c r="K82" s="50"/>
-      <c r="L82" s="50"/>
+      <c r="G82" s="50">
+        <v>40</v>
+      </c>
+      <c r="H82" s="50">
+        <v>80</v>
+      </c>
+      <c r="I82" s="129">
+        <v>480</v>
+      </c>
+      <c r="J82" s="50">
+        <v>80</v>
+      </c>
+      <c r="K82" s="50">
+        <v>60</v>
+      </c>
+      <c r="L82" s="50">
+        <v>80</v>
+      </c>
       <c r="M82" s="129">
         <f t="shared" si="88"/>
-        <v>0</v>
+        <v>20.5</v>
       </c>
       <c r="N82" s="39">
         <f t="shared" si="18"/>
@@ -8704,11 +8726,11 @@
       </c>
       <c r="P82" s="73">
         <f t="shared" si="96"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="Q82" s="40">
         <f t="shared" si="97"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="R82" s="51" t="e">
         <f t="shared" si="4"/>
@@ -8744,23 +8766,39 @@
       </c>
     </row>
     <row r="83" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A83" s="78"/>
+      <c r="A83" s="139">
+        <v>46262</v>
+      </c>
       <c r="B83" s="47">
         <v>79</v>
       </c>
-      <c r="C83" s="128"/>
+      <c r="C83" s="128" t="s">
+        <v>148</v>
+      </c>
       <c r="D83" s="50"/>
       <c r="E83" s="50"/>
       <c r="F83" s="50"/>
-      <c r="G83" s="50"/>
-      <c r="H83" s="50"/>
-      <c r="I83" s="129"/>
-      <c r="J83" s="50"/>
-      <c r="K83" s="50"/>
-      <c r="L83" s="50"/>
+      <c r="G83" s="50">
+        <v>80</v>
+      </c>
+      <c r="H83" s="50">
+        <v>80</v>
+      </c>
+      <c r="I83" s="129">
+        <v>120</v>
+      </c>
+      <c r="J83" s="50">
+        <v>160</v>
+      </c>
+      <c r="K83" s="50">
+        <v>40</v>
+      </c>
+      <c r="L83" s="50">
+        <v>240</v>
+      </c>
       <c r="M83" s="129">
         <f t="shared" si="88"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="N83" s="39">
         <f t="shared" si="18"/>
@@ -8772,11 +8810,11 @@
       </c>
       <c r="P83" s="73">
         <f t="shared" si="96"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q83" s="40">
         <f t="shared" si="97"/>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="R83" s="51" t="e">
         <f t="shared" si="4"/>
@@ -12544,11 +12582,11 @@
       </c>
       <c r="P138" s="62">
         <f t="shared" si="120"/>
-        <v>2721.5</v>
+        <v>2765.5</v>
       </c>
       <c r="Q138" s="64">
         <f t="shared" si="120"/>
-        <v>4502.45</v>
+        <v>4535.45</v>
       </c>
       <c r="R138" s="65" t="e">
         <f t="shared" si="120"/>
@@ -12695,24 +12733,24 @@
         <v>49</v>
       </c>
       <c r="D5" s="88">
-        <v>769</v>
+        <v>800</v>
       </c>
       <c r="E5" s="79">
-        <v>1594</v>
+        <v>1633</v>
       </c>
       <c r="F5" s="79">
         <v>600</v>
       </c>
       <c r="G5" s="102">
         <f>SUM(D5:F5)</f>
-        <v>2963</v>
+        <v>3033</v>
       </c>
       <c r="H5" s="95">
         <v>10000</v>
       </c>
       <c r="I5" s="96">
         <f>G5-H5</f>
-        <v>-7037</v>
+        <v>-6967</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>1</v>
@@ -12735,11 +12773,11 @@
       </c>
       <c r="D6" s="104">
         <f>D5*40</f>
-        <v>30760</v>
+        <v>32000</v>
       </c>
       <c r="E6" s="104">
         <f t="shared" ref="E6:F6" si="1">E5*40</f>
-        <v>63760</v>
+        <v>65320</v>
       </c>
       <c r="F6" s="104">
         <f t="shared" si="1"/>
@@ -12747,7 +12785,7 @@
       </c>
       <c r="G6" s="105">
         <f>SUM(D6:F6)</f>
-        <v>118520</v>
+        <v>121320</v>
       </c>
       <c r="H6" s="97">
         <f>H5*40</f>
@@ -12755,7 +12793,7 @@
       </c>
       <c r="I6" s="98">
         <f>G6-H6</f>
-        <v>-281480</v>
+        <v>-278680</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>2</v>
@@ -12880,11 +12918,11 @@
       </c>
       <c r="D9" s="106">
         <f>D8-D5</f>
-        <v>-769</v>
+        <v>-800</v>
       </c>
       <c r="E9" s="106">
         <f>E8-E5</f>
-        <v>-1594</v>
+        <v>-1633</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>5</v>
@@ -13025,7 +13063,7 @@
       </c>
       <c r="G12" s="91">
         <f>D12+G5</f>
-        <v>7163</v>
+        <v>7233</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>11</v>
@@ -13076,7 +13114,7 @@
       </c>
       <c r="G13" s="91">
         <f>G12*40</f>
-        <v>286520</v>
+        <v>289320</v>
       </c>
       <c r="S13" s="184" t="s">
         <v>85</v>

--- a/Aug_2026/daily Reports/LMT Orders.xlsx
+++ b/Aug_2026/daily Reports/LMT Orders.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2116F1E2-9EA4-4A19-95DB-21A11FF47479}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D18CF405-BAF1-4A28-9561-569268310099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="176">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -475,6 +475,81 @@
   </si>
   <si>
     <t xml:space="preserve">Cario Mart </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Risen Fateh Gher </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gourmet Food Johar Town </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gourmet Food 12G Johar Town </t>
+  </si>
+  <si>
+    <t>Gourmet Food Naseer Abad</t>
+  </si>
+  <si>
+    <t>Gourmet Food Multan Road Fwara Chowk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gourmet Food Faisal Town </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gourmet Food 18G Iqbal Town </t>
+  </si>
+  <si>
+    <t>Gourmet Food Samnabad Lhr</t>
+  </si>
+  <si>
+    <t>Gourmet Food Ghalib Market</t>
+  </si>
+  <si>
+    <t>Gourmet Food Islam Pura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gourmet Food Jinnah Hospital </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gourmet Food Shama Cenima </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gourmet Food Muslim Town Ayubia </t>
+  </si>
+  <si>
+    <t>Gourmet Food Walton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gourmet Food C Block Model Town </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gourmet Food Liyaqat Chowk </t>
+  </si>
+  <si>
+    <t>Gourmet Food Krishan Nagar</t>
+  </si>
+  <si>
+    <t>Gourmet Food Poonch Road</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gourmet Food Nadeem Shaheed </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gourmet Food Gulshan Ravi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gourmet Food Link Road Model Town </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gourmet Food Jauray Pull </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gourmet Food Bhatta Chowk </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gourmet Food EME Society </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gourmet Food  DHA XX- Block </t>
   </si>
 </sst>
 </file>
@@ -1363,7 +1438,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="195">
+  <cellXfs count="197">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1769,6 +1844,49 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1803,45 +1921,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2406,14 +2485,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="161">
+      <c r="B1" s="176">
         <f ca="1">TODAY()</f>
-        <v>46266</v>
-      </c>
-      <c r="C1" s="161"/>
-      <c r="D1" s="161"/>
-      <c r="E1" s="161"/>
-      <c r="F1" s="161"/>
+        <v>46268</v>
+      </c>
+      <c r="C1" s="176"/>
+      <c r="D1" s="176"/>
+      <c r="E1" s="176"/>
+      <c r="F1" s="176"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
       <c r="I1" s="10"/>
@@ -2435,10 +2514,10 @@
       <c r="Y1" s="10"/>
     </row>
     <row r="2" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="183" t="s">
+      <c r="A2" s="173" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="162" t="s">
+      <c r="B2" s="177" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2471,13 +2550,13 @@
       <c r="L2" s="15">
         <v>120</v>
       </c>
-      <c r="M2" s="175"/>
-      <c r="N2" s="176"/>
-      <c r="O2" s="177"/>
-      <c r="P2" s="178" t="s">
+      <c r="M2" s="165"/>
+      <c r="N2" s="166"/>
+      <c r="O2" s="167"/>
+      <c r="P2" s="168" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="179"/>
+      <c r="Q2" s="169"/>
       <c r="R2" s="18">
         <v>0.05</v>
       </c>
@@ -2496,8 +2575,8 @@
       <c r="Y2" s="20"/>
     </row>
     <row r="3" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="183"/>
-      <c r="B3" s="163"/>
+      <c r="A3" s="173"/>
+      <c r="B3" s="178"/>
       <c r="C3" s="23" t="s">
         <v>15</v>
       </c>
@@ -2528,29 +2607,29 @@
       <c r="L3" s="29">
         <v>72.64</v>
       </c>
-      <c r="M3" s="180" t="s">
+      <c r="M3" s="170" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="181"/>
-      <c r="O3" s="182"/>
+      <c r="N3" s="171"/>
+      <c r="O3" s="172"/>
       <c r="P3" s="71"/>
       <c r="Q3" s="72"/>
-      <c r="R3" s="165" t="s">
+      <c r="R3" s="180" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="166"/>
-      <c r="T3" s="166"/>
-      <c r="U3" s="167"/>
-      <c r="V3" s="168" t="s">
+      <c r="S3" s="181"/>
+      <c r="T3" s="181"/>
+      <c r="U3" s="182"/>
+      <c r="V3" s="183" t="s">
         <v>17</v>
       </c>
-      <c r="W3" s="169"/>
-      <c r="X3" s="169"/>
-      <c r="Y3" s="170"/>
+      <c r="W3" s="184"/>
+      <c r="X3" s="184"/>
+      <c r="Y3" s="185"/>
     </row>
     <row r="4" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="183"/>
-      <c r="B4" s="164"/>
+      <c r="A4" s="173"/>
+      <c r="B4" s="179"/>
       <c r="C4" s="30" t="s">
         <v>18</v>
       </c>
@@ -9118,23 +9197,35 @@
       </c>
     </row>
     <row r="87" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A87" s="78"/>
-      <c r="B87" s="47">
+      <c r="A87" s="146">
+        <v>46265</v>
+      </c>
+      <c r="B87" s="147">
         <v>83</v>
       </c>
-      <c r="C87" s="128"/>
-      <c r="D87" s="50"/>
-      <c r="E87" s="50"/>
-      <c r="F87" s="50"/>
-      <c r="G87" s="50"/>
-      <c r="H87" s="50"/>
-      <c r="I87" s="129"/>
-      <c r="J87" s="50"/>
-      <c r="K87" s="50"/>
-      <c r="L87" s="50"/>
+      <c r="C87" s="148" t="s">
+        <v>151</v>
+      </c>
+      <c r="D87" s="161"/>
+      <c r="E87" s="161"/>
+      <c r="F87" s="161"/>
+      <c r="G87" s="161"/>
+      <c r="H87" s="161">
+        <v>119</v>
+      </c>
+      <c r="I87" s="162">
+        <v>200</v>
+      </c>
+      <c r="J87" s="161"/>
+      <c r="K87" s="161">
+        <v>79</v>
+      </c>
+      <c r="L87" s="161">
+        <v>118</v>
+      </c>
       <c r="M87" s="129">
         <f t="shared" si="103"/>
-        <v>0</v>
+        <v>12.9</v>
       </c>
       <c r="N87" s="39">
         <f t="shared" si="18"/>
@@ -9146,11 +9237,11 @@
       </c>
       <c r="P87" s="73">
         <f t="shared" si="104"/>
-        <v>0</v>
+        <v>15.95</v>
       </c>
       <c r="Q87" s="40">
         <f t="shared" si="105"/>
-        <v>0</v>
+        <v>9.85</v>
       </c>
       <c r="R87" s="51" t="e">
         <f t="shared" si="4"/>
@@ -9186,23 +9277,29 @@
       </c>
     </row>
     <row r="88" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A88" s="78"/>
-      <c r="B88" s="47">
+      <c r="A88" s="146">
+        <v>46265</v>
+      </c>
+      <c r="B88" s="147">
         <v>84</v>
       </c>
-      <c r="C88" s="128"/>
-      <c r="D88" s="50"/>
-      <c r="E88" s="50"/>
-      <c r="F88" s="50"/>
-      <c r="G88" s="50"/>
-      <c r="H88" s="50"/>
-      <c r="I88" s="129"/>
-      <c r="J88" s="50"/>
-      <c r="K88" s="50"/>
-      <c r="L88" s="50"/>
+      <c r="C88" s="148" t="s">
+        <v>90</v>
+      </c>
+      <c r="D88" s="161"/>
+      <c r="E88" s="161"/>
+      <c r="F88" s="161"/>
+      <c r="G88" s="161"/>
+      <c r="H88" s="161"/>
+      <c r="I88" s="162"/>
+      <c r="J88" s="161"/>
+      <c r="K88" s="161"/>
+      <c r="L88" s="161">
+        <v>200</v>
+      </c>
       <c r="M88" s="129">
         <f t="shared" si="103"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N88" s="39">
         <f t="shared" si="18"/>
@@ -9218,7 +9315,7 @@
       </c>
       <c r="Q88" s="40">
         <f t="shared" si="105"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R88" s="51" t="e">
         <f t="shared" si="4"/>
@@ -9258,19 +9355,29 @@
       <c r="B89" s="47">
         <v>85</v>
       </c>
-      <c r="C89" s="128"/>
+      <c r="C89" s="128" t="s">
+        <v>152</v>
+      </c>
       <c r="D89" s="50"/>
       <c r="E89" s="50"/>
       <c r="F89" s="50"/>
-      <c r="G89" s="50"/>
-      <c r="H89" s="50"/>
+      <c r="G89" s="50">
+        <v>40</v>
+      </c>
+      <c r="H89" s="50">
+        <v>40</v>
+      </c>
       <c r="I89" s="129"/>
-      <c r="J89" s="50"/>
-      <c r="K89" s="50"/>
+      <c r="J89" s="50">
+        <v>20</v>
+      </c>
+      <c r="K89" s="50">
+        <v>40</v>
+      </c>
       <c r="L89" s="50"/>
       <c r="M89" s="129">
         <f t="shared" si="103"/>
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N89" s="39">
         <f t="shared" si="18"/>
@@ -9282,11 +9389,11 @@
       </c>
       <c r="P89" s="73">
         <f t="shared" si="104"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q89" s="40">
         <f t="shared" si="105"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R89" s="51" t="e">
         <f t="shared" si="4"/>
@@ -9326,7 +9433,9 @@
       <c r="B90" s="47">
         <v>86</v>
       </c>
-      <c r="C90" s="128"/>
+      <c r="C90" s="128" t="s">
+        <v>153</v>
+      </c>
       <c r="D90" s="50"/>
       <c r="E90" s="50"/>
       <c r="F90" s="50"/>
@@ -9335,10 +9444,12 @@
       <c r="I90" s="129"/>
       <c r="J90" s="50"/>
       <c r="K90" s="50"/>
-      <c r="L90" s="50"/>
+      <c r="L90" s="50">
+        <v>40</v>
+      </c>
       <c r="M90" s="129">
         <f t="shared" si="103"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N90" s="39">
         <f t="shared" si="18"/>
@@ -9354,7 +9465,7 @@
       </c>
       <c r="Q90" s="40">
         <f t="shared" si="105"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R90" s="51" t="e">
         <f t="shared" si="4"/>
@@ -9394,19 +9505,33 @@
       <c r="B91" s="47">
         <v>87</v>
       </c>
-      <c r="C91" s="128"/>
+      <c r="C91" s="128" t="s">
+        <v>154</v>
+      </c>
       <c r="D91" s="50"/>
       <c r="E91" s="50"/>
       <c r="F91" s="50"/>
-      <c r="G91" s="50"/>
-      <c r="H91" s="50"/>
-      <c r="I91" s="129"/>
-      <c r="J91" s="50"/>
-      <c r="K91" s="50"/>
-      <c r="L91" s="50"/>
+      <c r="G91" s="50">
+        <v>200</v>
+      </c>
+      <c r="H91" s="50">
+        <v>200</v>
+      </c>
+      <c r="I91" s="129">
+        <v>200</v>
+      </c>
+      <c r="J91" s="50">
+        <v>200</v>
+      </c>
+      <c r="K91" s="50">
+        <v>200</v>
+      </c>
+      <c r="L91" s="50">
+        <v>200</v>
+      </c>
       <c r="M91" s="129">
         <f t="shared" si="103"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="N91" s="39">
         <f t="shared" si="18"/>
@@ -9418,11 +9543,11 @@
       </c>
       <c r="P91" s="73">
         <f t="shared" si="104"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="Q91" s="40">
         <f t="shared" si="105"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="R91" s="51" t="e">
         <f t="shared" si="4"/>
@@ -9462,7 +9587,9 @@
       <c r="B92" s="47">
         <v>88</v>
       </c>
-      <c r="C92" s="128"/>
+      <c r="C92" s="128" t="s">
+        <v>155</v>
+      </c>
       <c r="D92" s="50"/>
       <c r="E92" s="50"/>
       <c r="F92" s="50"/>
@@ -9471,10 +9598,12 @@
       <c r="I92" s="129"/>
       <c r="J92" s="50"/>
       <c r="K92" s="50"/>
-      <c r="L92" s="50"/>
+      <c r="L92" s="50">
+        <v>40</v>
+      </c>
       <c r="M92" s="129">
         <f t="shared" si="103"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N92" s="39">
         <f t="shared" si="18"/>
@@ -9490,7 +9619,7 @@
       </c>
       <c r="Q92" s="40">
         <f t="shared" si="105"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R92" s="51" t="e">
         <f t="shared" si="4"/>
@@ -9530,19 +9659,23 @@
       <c r="B93" s="47">
         <v>89</v>
       </c>
-      <c r="C93" s="128"/>
+      <c r="C93" s="128" t="s">
+        <v>156</v>
+      </c>
       <c r="D93" s="50"/>
       <c r="E93" s="50"/>
       <c r="F93" s="50"/>
       <c r="G93" s="50"/>
       <c r="H93" s="50"/>
-      <c r="I93" s="129"/>
+      <c r="I93" s="129">
+        <v>30</v>
+      </c>
       <c r="J93" s="50"/>
       <c r="K93" s="50"/>
       <c r="L93" s="50"/>
       <c r="M93" s="129">
         <f t="shared" si="103"/>
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="N93" s="39">
         <f t="shared" si="18"/>
@@ -9554,7 +9687,7 @@
       </c>
       <c r="P93" s="73">
         <f t="shared" si="104"/>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q93" s="40">
         <f t="shared" si="105"/>
@@ -9598,19 +9731,23 @@
       <c r="B94" s="47">
         <v>90</v>
       </c>
-      <c r="C94" s="128"/>
+      <c r="C94" s="128" t="s">
+        <v>157</v>
+      </c>
       <c r="D94" s="50"/>
       <c r="E94" s="50"/>
       <c r="F94" s="50"/>
       <c r="G94" s="50"/>
       <c r="H94" s="50"/>
-      <c r="I94" s="129"/>
+      <c r="I94" s="129">
+        <v>40</v>
+      </c>
       <c r="J94" s="50"/>
       <c r="K94" s="50"/>
       <c r="L94" s="50"/>
       <c r="M94" s="129">
         <f t="shared" si="103"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N94" s="39">
         <f t="shared" si="18"/>
@@ -9622,7 +9759,7 @@
       </c>
       <c r="P94" s="73">
         <f t="shared" si="104"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q94" s="40">
         <f t="shared" si="105"/>
@@ -9666,19 +9803,23 @@
       <c r="B95" s="47">
         <v>91</v>
       </c>
-      <c r="C95" s="128"/>
+      <c r="C95" s="128" t="s">
+        <v>158</v>
+      </c>
       <c r="D95" s="50"/>
       <c r="E95" s="50"/>
       <c r="F95" s="50"/>
       <c r="G95" s="50"/>
       <c r="H95" s="50"/>
-      <c r="I95" s="129"/>
+      <c r="I95" s="129">
+        <v>40</v>
+      </c>
       <c r="J95" s="50"/>
       <c r="K95" s="50"/>
       <c r="L95" s="50"/>
       <c r="M95" s="129">
         <f t="shared" si="103"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N95" s="39">
         <f t="shared" si="18"/>
@@ -9690,7 +9831,7 @@
       </c>
       <c r="P95" s="73">
         <f t="shared" si="104"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q95" s="40">
         <f t="shared" si="105"/>
@@ -9734,7 +9875,9 @@
       <c r="B96" s="47">
         <v>92</v>
       </c>
-      <c r="C96" s="128"/>
+      <c r="C96" s="128" t="s">
+        <v>159</v>
+      </c>
       <c r="D96" s="50"/>
       <c r="E96" s="50"/>
       <c r="F96" s="50"/>
@@ -9743,10 +9886,12 @@
       <c r="I96" s="129"/>
       <c r="J96" s="50"/>
       <c r="K96" s="50"/>
-      <c r="L96" s="50"/>
+      <c r="L96" s="50">
+        <v>20</v>
+      </c>
       <c r="M96" s="129">
         <f t="shared" si="103"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N96" s="39">
         <f t="shared" si="18"/>
@@ -9762,7 +9907,7 @@
       </c>
       <c r="Q96" s="40">
         <f t="shared" si="105"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R96" s="51" t="e">
         <f t="shared" si="4"/>
@@ -9802,19 +9947,25 @@
       <c r="B97" s="47">
         <v>93</v>
       </c>
-      <c r="C97" s="128"/>
+      <c r="C97" s="128" t="s">
+        <v>160</v>
+      </c>
       <c r="D97" s="50"/>
       <c r="E97" s="50"/>
       <c r="F97" s="50"/>
       <c r="G97" s="50"/>
-      <c r="H97" s="50"/>
-      <c r="I97" s="129"/>
+      <c r="H97" s="50">
+        <v>30</v>
+      </c>
+      <c r="I97" s="129">
+        <v>40</v>
+      </c>
       <c r="J97" s="50"/>
       <c r="K97" s="50"/>
       <c r="L97" s="50"/>
       <c r="M97" s="129">
         <f t="shared" si="103"/>
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="N97" s="39">
         <f t="shared" si="18"/>
@@ -9826,7 +9977,7 @@
       </c>
       <c r="P97" s="73">
         <f t="shared" si="104"/>
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q97" s="40">
         <f t="shared" si="105"/>
@@ -9870,19 +10021,23 @@
       <c r="B98" s="47">
         <v>94</v>
       </c>
-      <c r="C98" s="128"/>
+      <c r="C98" s="128" t="s">
+        <v>161</v>
+      </c>
       <c r="D98" s="50"/>
       <c r="E98" s="50"/>
       <c r="F98" s="50"/>
       <c r="G98" s="50"/>
-      <c r="H98" s="50"/>
+      <c r="H98" s="50">
+        <v>30</v>
+      </c>
       <c r="I98" s="129"/>
       <c r="J98" s="50"/>
       <c r="K98" s="50"/>
       <c r="L98" s="50"/>
       <c r="M98" s="129">
         <f t="shared" si="103"/>
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="N98" s="39">
         <f t="shared" si="18"/>
@@ -9894,7 +10049,7 @@
       </c>
       <c r="P98" s="73">
         <f t="shared" si="104"/>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q98" s="40">
         <f t="shared" si="105"/>
@@ -9938,19 +10093,23 @@
       <c r="B99" s="47">
         <v>95</v>
       </c>
-      <c r="C99" s="128"/>
+      <c r="C99" s="128" t="s">
+        <v>162</v>
+      </c>
       <c r="D99" s="50"/>
       <c r="E99" s="50"/>
       <c r="F99" s="50"/>
       <c r="G99" s="50"/>
       <c r="H99" s="50"/>
       <c r="I99" s="129"/>
-      <c r="J99" s="50"/>
+      <c r="J99" s="50">
+        <v>40</v>
+      </c>
       <c r="K99" s="50"/>
       <c r="L99" s="50"/>
       <c r="M99" s="129">
         <f t="shared" si="103"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N99" s="39">
         <f t="shared" si="18"/>
@@ -9966,7 +10125,7 @@
       </c>
       <c r="Q99" s="40">
         <f t="shared" si="105"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R99" s="51" t="e">
         <f t="shared" si="4"/>
@@ -10006,11 +10165,15 @@
       <c r="B100" s="47">
         <v>96</v>
       </c>
-      <c r="C100" s="128"/>
+      <c r="C100" s="128" t="s">
+        <v>163</v>
+      </c>
       <c r="D100" s="50"/>
       <c r="E100" s="50"/>
       <c r="F100" s="50"/>
-      <c r="G100" s="50"/>
+      <c r="G100" s="50">
+        <v>30</v>
+      </c>
       <c r="H100" s="50"/>
       <c r="I100" s="129"/>
       <c r="J100" s="50"/>
@@ -10018,7 +10181,7 @@
       <c r="L100" s="50"/>
       <c r="M100" s="129">
         <f t="shared" si="103"/>
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="N100" s="39">
         <f t="shared" si="18"/>
@@ -10030,7 +10193,7 @@
       </c>
       <c r="P100" s="73">
         <f t="shared" si="104"/>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q100" s="40">
         <f t="shared" si="105"/>
@@ -10074,7 +10237,9 @@
       <c r="B101" s="47">
         <v>97</v>
       </c>
-      <c r="C101" s="128"/>
+      <c r="C101" s="128" t="s">
+        <v>164</v>
+      </c>
       <c r="D101" s="50"/>
       <c r="E101" s="50"/>
       <c r="F101" s="50"/>
@@ -10082,11 +10247,13 @@
       <c r="H101" s="50"/>
       <c r="I101" s="129"/>
       <c r="J101" s="50"/>
-      <c r="K101" s="50"/>
+      <c r="K101" s="50">
+        <v>20</v>
+      </c>
       <c r="L101" s="50"/>
       <c r="M101" s="129">
         <f t="shared" si="103"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N101" s="39">
         <f t="shared" si="18"/>
@@ -10102,7 +10269,7 @@
       </c>
       <c r="Q101" s="40">
         <f t="shared" si="105"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R101" s="51" t="e">
         <f t="shared" si="4"/>
@@ -10142,7 +10309,9 @@
       <c r="B102" s="47">
         <v>98</v>
       </c>
-      <c r="C102" s="128"/>
+      <c r="C102" s="128" t="s">
+        <v>165</v>
+      </c>
       <c r="D102" s="50"/>
       <c r="E102" s="50"/>
       <c r="F102" s="50"/>
@@ -10150,11 +10319,13 @@
       <c r="H102" s="50"/>
       <c r="I102" s="129"/>
       <c r="J102" s="50"/>
-      <c r="K102" s="50"/>
+      <c r="K102" s="50">
+        <v>20</v>
+      </c>
       <c r="L102" s="50"/>
       <c r="M102" s="129">
         <f t="shared" si="103"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N102" s="39">
         <f t="shared" si="18"/>
@@ -10170,7 +10341,7 @@
       </c>
       <c r="Q102" s="40">
         <f t="shared" si="105"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R102" s="51" t="e">
         <f t="shared" si="4"/>
@@ -10210,19 +10381,23 @@
       <c r="B103" s="47">
         <v>99</v>
       </c>
-      <c r="C103" s="128"/>
+      <c r="C103" s="128" t="s">
+        <v>166</v>
+      </c>
       <c r="D103" s="50"/>
       <c r="E103" s="50"/>
       <c r="F103" s="50"/>
       <c r="G103" s="50"/>
       <c r="H103" s="50"/>
-      <c r="I103" s="129"/>
+      <c r="I103" s="129">
+        <v>40</v>
+      </c>
       <c r="J103" s="50"/>
       <c r="K103" s="50"/>
       <c r="L103" s="50"/>
       <c r="M103" s="129">
         <f t="shared" si="103"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N103" s="39">
         <f t="shared" si="18"/>
@@ -10234,7 +10409,7 @@
       </c>
       <c r="P103" s="73">
         <f t="shared" si="104"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q103" s="40">
         <f t="shared" si="105"/>
@@ -10278,19 +10453,25 @@
       <c r="B104" s="47">
         <v>100</v>
       </c>
-      <c r="C104" s="128"/>
+      <c r="C104" s="128" t="s">
+        <v>167</v>
+      </c>
       <c r="D104" s="50"/>
       <c r="E104" s="50"/>
       <c r="F104" s="50"/>
       <c r="G104" s="50"/>
-      <c r="H104" s="50"/>
+      <c r="H104" s="50">
+        <v>30</v>
+      </c>
       <c r="I104" s="129"/>
       <c r="J104" s="50"/>
       <c r="K104" s="50"/>
-      <c r="L104" s="50"/>
+      <c r="L104" s="50">
+        <v>20</v>
+      </c>
       <c r="M104" s="129">
         <f t="shared" si="103"/>
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="N104" s="39">
         <f t="shared" si="18"/>
@@ -10302,11 +10483,11 @@
       </c>
       <c r="P104" s="73">
         <f t="shared" si="104"/>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q104" s="40">
         <f t="shared" si="105"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R104" s="51" t="e">
         <f t="shared" si="4"/>
@@ -10346,19 +10527,23 @@
       <c r="B105" s="47">
         <v>101</v>
       </c>
-      <c r="C105" s="128"/>
+      <c r="C105" s="128" t="s">
+        <v>168</v>
+      </c>
       <c r="D105" s="50"/>
       <c r="E105" s="50"/>
       <c r="F105" s="50"/>
       <c r="G105" s="50"/>
       <c r="H105" s="50"/>
       <c r="I105" s="129"/>
-      <c r="J105" s="50"/>
+      <c r="J105" s="50">
+        <v>20</v>
+      </c>
       <c r="K105" s="50"/>
       <c r="L105" s="50"/>
       <c r="M105" s="129">
         <f t="shared" si="103"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N105" s="39">
         <f t="shared" si="18"/>
@@ -10374,7 +10559,7 @@
       </c>
       <c r="Q105" s="40">
         <f t="shared" si="105"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R105" s="51" t="e">
         <f t="shared" si="4"/>
@@ -10414,19 +10599,25 @@
       <c r="B106" s="47">
         <v>102</v>
       </c>
-      <c r="C106" s="128"/>
+      <c r="C106" s="128" t="s">
+        <v>169</v>
+      </c>
       <c r="D106" s="50"/>
       <c r="E106" s="50"/>
       <c r="F106" s="50"/>
       <c r="G106" s="50"/>
       <c r="H106" s="50"/>
       <c r="I106" s="129"/>
-      <c r="J106" s="50"/>
+      <c r="J106" s="50">
+        <v>40</v>
+      </c>
       <c r="K106" s="50"/>
-      <c r="L106" s="50"/>
+      <c r="L106" s="50">
+        <v>40</v>
+      </c>
       <c r="M106" s="129">
         <f t="shared" si="103"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N106" s="39">
         <f t="shared" si="18"/>
@@ -10442,7 +10633,7 @@
       </c>
       <c r="Q106" s="40">
         <f t="shared" si="105"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R106" s="51" t="e">
         <f t="shared" si="4"/>
@@ -10482,7 +10673,9 @@
       <c r="B107" s="47">
         <v>103</v>
       </c>
-      <c r="C107" s="128"/>
+      <c r="C107" s="128" t="s">
+        <v>170</v>
+      </c>
       <c r="D107" s="50"/>
       <c r="E107" s="50"/>
       <c r="F107" s="50"/>
@@ -10491,10 +10684,12 @@
       <c r="I107" s="129"/>
       <c r="J107" s="50"/>
       <c r="K107" s="50"/>
-      <c r="L107" s="50"/>
+      <c r="L107" s="50">
+        <v>20</v>
+      </c>
       <c r="M107" s="129">
         <f t="shared" si="103"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N107" s="39">
         <f t="shared" si="18"/>
@@ -10510,7 +10705,7 @@
       </c>
       <c r="Q107" s="40">
         <f t="shared" si="105"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R107" s="51" t="e">
         <f t="shared" si="4"/>
@@ -10550,19 +10745,27 @@
       <c r="B108" s="47">
         <v>104</v>
       </c>
-      <c r="C108" s="128"/>
+      <c r="C108" s="128" t="s">
+        <v>171</v>
+      </c>
       <c r="D108" s="50"/>
       <c r="E108" s="50"/>
       <c r="F108" s="50"/>
-      <c r="G108" s="50"/>
+      <c r="G108" s="50">
+        <v>40</v>
+      </c>
       <c r="H108" s="50"/>
-      <c r="I108" s="129"/>
+      <c r="I108" s="129">
+        <v>40</v>
+      </c>
       <c r="J108" s="50"/>
-      <c r="K108" s="50"/>
+      <c r="K108" s="50">
+        <v>20</v>
+      </c>
       <c r="L108" s="50"/>
       <c r="M108" s="129">
         <f t="shared" si="103"/>
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="N108" s="39">
         <f t="shared" si="18"/>
@@ -10574,11 +10777,11 @@
       </c>
       <c r="P108" s="73">
         <f t="shared" si="104"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q108" s="40">
         <f t="shared" si="105"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R108" s="51" t="e">
         <f t="shared" si="4"/>
@@ -10618,19 +10821,23 @@
       <c r="B109" s="47">
         <v>105</v>
       </c>
-      <c r="C109" s="128"/>
+      <c r="C109" s="128" t="s">
+        <v>172</v>
+      </c>
       <c r="D109" s="50"/>
       <c r="E109" s="50"/>
       <c r="F109" s="50"/>
       <c r="G109" s="50"/>
       <c r="H109" s="50"/>
-      <c r="I109" s="129"/>
+      <c r="I109" s="129">
+        <v>40</v>
+      </c>
       <c r="J109" s="50"/>
       <c r="K109" s="50"/>
       <c r="L109" s="50"/>
       <c r="M109" s="129">
         <f t="shared" si="103"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N109" s="39">
         <f t="shared" si="18"/>
@@ -10642,7 +10849,7 @@
       </c>
       <c r="P109" s="73">
         <f t="shared" si="104"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q109" s="40">
         <f t="shared" si="105"/>
@@ -10686,19 +10893,23 @@
       <c r="B110" s="47">
         <v>106</v>
       </c>
-      <c r="C110" s="128"/>
+      <c r="C110" s="128" t="s">
+        <v>173</v>
+      </c>
       <c r="D110" s="50"/>
       <c r="E110" s="50"/>
       <c r="F110" s="50"/>
       <c r="G110" s="50"/>
       <c r="H110" s="50"/>
-      <c r="I110" s="129"/>
+      <c r="I110" s="129">
+        <v>40</v>
+      </c>
       <c r="J110" s="50"/>
       <c r="K110" s="50"/>
       <c r="L110" s="50"/>
       <c r="M110" s="129">
         <f t="shared" si="103"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N110" s="39">
         <f t="shared" si="18"/>
@@ -10710,7 +10921,7 @@
       </c>
       <c r="P110" s="73">
         <f t="shared" si="104"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q110" s="40">
         <f t="shared" si="105"/>
@@ -10754,19 +10965,25 @@
       <c r="B111" s="47">
         <v>107</v>
       </c>
-      <c r="C111" s="128"/>
+      <c r="C111" s="128" t="s">
+        <v>174</v>
+      </c>
       <c r="D111" s="50"/>
       <c r="E111" s="50"/>
       <c r="F111" s="50"/>
-      <c r="G111" s="50"/>
-      <c r="H111" s="50"/>
+      <c r="G111" s="50">
+        <v>30</v>
+      </c>
+      <c r="H111" s="50">
+        <v>40</v>
+      </c>
       <c r="I111" s="129"/>
       <c r="J111" s="50"/>
       <c r="K111" s="50"/>
       <c r="L111" s="50"/>
       <c r="M111" s="129">
         <f t="shared" si="103"/>
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="N111" s="39">
         <f t="shared" si="18"/>
@@ -10778,7 +10995,7 @@
       </c>
       <c r="P111" s="73">
         <f t="shared" si="104"/>
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q111" s="40">
         <f t="shared" si="105"/>
@@ -10822,11 +11039,15 @@
       <c r="B112" s="47">
         <v>108</v>
       </c>
-      <c r="C112" s="128"/>
+      <c r="C112" s="128" t="s">
+        <v>175</v>
+      </c>
       <c r="D112" s="50"/>
       <c r="E112" s="50"/>
       <c r="F112" s="50"/>
-      <c r="G112" s="50"/>
+      <c r="G112" s="50">
+        <v>40</v>
+      </c>
       <c r="H112" s="50"/>
       <c r="I112" s="129"/>
       <c r="J112" s="50"/>
@@ -10834,7 +11055,7 @@
       <c r="L112" s="50"/>
       <c r="M112" s="129">
         <f t="shared" si="103"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N112" s="39">
         <f t="shared" si="18"/>
@@ -10846,7 +11067,7 @@
       </c>
       <c r="P112" s="73">
         <f t="shared" si="104"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q112" s="40">
         <f t="shared" si="105"/>
@@ -12231,10 +12452,10 @@
     </row>
     <row r="133" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A133" s="78"/>
-      <c r="B133" s="171" t="s">
+      <c r="B133" s="186" t="s">
         <v>11</v>
       </c>
-      <c r="C133" s="172"/>
+      <c r="C133" s="187"/>
       <c r="D133" s="84">
         <f t="shared" ref="D133:L133" si="111">SUM(D6:D61)</f>
         <v>6363</v>
@@ -12498,10 +12719,10 @@
       </c>
     </row>
     <row r="137" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B137" s="184" t="s">
+      <c r="B137" s="174" t="s">
         <v>70</v>
       </c>
-      <c r="C137" s="185"/>
+      <c r="C137" s="175"/>
       <c r="D137" s="83">
         <f>SUM(D135:D136)</f>
         <v>0</v>
@@ -12592,10 +12813,10 @@
       </c>
     </row>
     <row r="138" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B138" s="173" t="s">
+      <c r="B138" s="163" t="s">
         <v>11</v>
       </c>
-      <c r="C138" s="174"/>
+      <c r="C138" s="164"/>
       <c r="D138" s="85">
         <f>SUM(D133,D137)</f>
         <v>6363</v>
@@ -12646,11 +12867,11 @@
       </c>
       <c r="P138" s="62">
         <f t="shared" si="120"/>
-        <v>2997.5</v>
+        <v>3076.45</v>
       </c>
       <c r="Q138" s="64">
         <f t="shared" si="120"/>
-        <v>5275.45</v>
+        <v>5345.2999999999993</v>
       </c>
       <c r="R138" s="65" t="e">
         <f t="shared" si="120"/>
@@ -12687,17 +12908,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="R3:U3"/>
+    <mergeCell ref="V3:Y3"/>
+    <mergeCell ref="B133:C133"/>
     <mergeCell ref="B138:C138"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="P2:Q2"/>
     <mergeCell ref="M3:O3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B137:C137"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="R3:U3"/>
-    <mergeCell ref="V3:Y3"/>
-    <mergeCell ref="B133:C133"/>
   </mergeCells>
   <conditionalFormatting sqref="C46:C60">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
@@ -12733,25 +12954,25 @@
   <sheetData>
     <row r="2" spans="3:26" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="3:26" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C3" s="188" t="s">
+      <c r="C3" s="190" t="s">
         <v>117</v>
       </c>
-      <c r="D3" s="189"/>
-      <c r="E3" s="189"/>
-      <c r="F3" s="189"/>
-      <c r="G3" s="190"/>
-      <c r="H3" s="192" t="s">
+      <c r="D3" s="191"/>
+      <c r="E3" s="191"/>
+      <c r="F3" s="191"/>
+      <c r="G3" s="192"/>
+      <c r="H3" s="194" t="s">
         <v>62</v>
       </c>
-      <c r="I3" s="193"/>
-      <c r="K3" s="194" t="s">
+      <c r="I3" s="195"/>
+      <c r="K3" s="196" t="s">
         <v>66</v>
       </c>
-      <c r="L3" s="194"/>
-      <c r="M3" s="194"/>
-      <c r="N3" s="194"/>
-      <c r="O3" s="194"/>
-      <c r="P3" s="194"/>
+      <c r="L3" s="196"/>
+      <c r="M3" s="196"/>
+      <c r="N3" s="196"/>
+      <c r="O3" s="196"/>
+      <c r="P3" s="196"/>
     </row>
     <row r="4" spans="3:26" ht="29.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C4" s="99"/>
@@ -12797,24 +13018,24 @@
         <v>49</v>
       </c>
       <c r="D5" s="88">
-        <v>860</v>
+        <v>1089.5</v>
       </c>
       <c r="E5" s="79">
-        <v>1659</v>
+        <v>1726</v>
       </c>
       <c r="F5" s="79">
         <v>1100</v>
       </c>
       <c r="G5" s="102">
         <f>SUM(D5:F5)</f>
-        <v>3619</v>
+        <v>3915.5</v>
       </c>
       <c r="H5" s="95">
         <v>10000</v>
       </c>
       <c r="I5" s="96">
         <f>G5-H5</f>
-        <v>-6381</v>
+        <v>-6084.5</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>1</v>
@@ -12837,11 +13058,11 @@
       </c>
       <c r="D6" s="104">
         <f>D5*40</f>
-        <v>34400</v>
+        <v>43580</v>
       </c>
       <c r="E6" s="104">
         <f t="shared" ref="E6:F6" si="1">E5*40</f>
-        <v>66360</v>
+        <v>69040</v>
       </c>
       <c r="F6" s="104">
         <f t="shared" si="1"/>
@@ -12849,7 +13070,7 @@
       </c>
       <c r="G6" s="105">
         <f>SUM(D6:F6)</f>
-        <v>144760</v>
+        <v>156620</v>
       </c>
       <c r="H6" s="97">
         <f>H5*40</f>
@@ -12857,7 +13078,7 @@
       </c>
       <c r="I6" s="98">
         <f>G6-H6</f>
-        <v>-255240</v>
+        <v>-243380</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>2</v>
@@ -12982,11 +13203,11 @@
       </c>
       <c r="D9" s="106">
         <f>D8-D5</f>
-        <v>-860</v>
+        <v>-1089.5</v>
       </c>
       <c r="E9" s="106">
         <f>E8-E5</f>
-        <v>-1659</v>
+        <v>-1726</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>5</v>
@@ -13068,14 +13289,14 @@
       </c>
     </row>
     <row r="11" spans="3:26" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C11" s="191" t="s">
+      <c r="C11" s="193" t="s">
         <v>59</v>
       </c>
-      <c r="D11" s="191"/>
-      <c r="F11" s="191" t="s">
+      <c r="D11" s="193"/>
+      <c r="F11" s="193" t="s">
         <v>68</v>
       </c>
-      <c r="G11" s="191"/>
+      <c r="G11" s="193"/>
       <c r="K11" s="1" t="s">
         <v>7</v>
       </c>
@@ -13127,7 +13348,7 @@
       </c>
       <c r="G12" s="91">
         <f>D12+G5</f>
-        <v>7819</v>
+        <v>8115.5</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>11</v>
@@ -13178,12 +13399,12 @@
       </c>
       <c r="G13" s="91">
         <f>G12*40</f>
-        <v>312760</v>
-      </c>
-      <c r="S13" s="186" t="s">
+        <v>324620</v>
+      </c>
+      <c r="S13" s="188" t="s">
         <v>85</v>
       </c>
-      <c r="T13" s="186"/>
+      <c r="T13" s="188"/>
       <c r="U13" s="135">
         <f>SUM(U8:U12)</f>
         <v>100</v>
@@ -13272,13 +13493,13 @@
       </c>
     </row>
     <row r="20" spans="4:15" ht="24" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="D20" s="187" t="s">
+      <c r="D20" s="189" t="s">
         <v>66</v>
       </c>
-      <c r="E20" s="187"/>
-      <c r="F20" s="187"/>
-      <c r="G20" s="187"/>
-      <c r="H20" s="187"/>
+      <c r="E20" s="189"/>
+      <c r="F20" s="189"/>
+      <c r="G20" s="189"/>
+      <c r="H20" s="189"/>
       <c r="K20" s="1" t="s">
         <v>4</v>
       </c>
